--- a/xlsx/MWV.xlsx
+++ b/xlsx/MWV.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Program Files\Kingsoft\WPS Office\12.1.0.28488\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Parker\WebstormProjects\konzert-public-data\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$474</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,22 +41,22 @@
     <t>MWV</t>
   </si>
   <si>
-    <t>OPUS</t>
-  </si>
-  <si>
-    <t>DATE</t>
-  </si>
-  <si>
-    <t>TITLE</t>
+    <t>Opus</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Title</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>WORKPARTS</t>
-  </si>
-  <si>
-    <t>NOTE</t>
+    <t>Workparts</t>
+  </si>
+  <si>
+    <t>Note</t>
   </si>
   <si>
     <t>MWV Q 11</t>
@@ -5893,7 +5893,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5919,16 +5919,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6487,25 +6478,25 @@
   </cols>
   <sheetData>
     <row r="1" s="2" customFormat="1" customHeight="1" spans="1:7">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -8022,10 +8013,10 @@
       <c r="C89" s="3">
         <v>1833</v>
       </c>
-      <c r="D89" s="11" t="s">
+      <c r="D89" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="E89" s="12"/>
+      <c r="E89" s="9"/>
       <c r="F89" s="6" t="s">
         <v>126</v>
       </c>
@@ -10255,7 +10246,7 @@
       <c r="C219" s="3">
         <v>1844</v>
       </c>
-      <c r="D219" s="13" t="s">
+      <c r="D219" s="10" t="s">
         <v>824</v>
       </c>
     </row>
@@ -12369,16 +12360,16 @@
       <c r="B346" s="3" t="s">
         <v>1260</v>
       </c>
-      <c r="C346" s="14">
+      <c r="C346" s="11">
         <v>1841</v>
       </c>
-      <c r="D346" s="15" t="s">
+      <c r="D346" s="12" t="s">
         <v>1261</v>
       </c>
-      <c r="F346" s="16" t="s">
+      <c r="F346" s="13" t="s">
         <v>1262</v>
       </c>
-      <c r="G346" s="17" t="s">
+      <c r="G346" s="14" t="s">
         <v>1263</v>
       </c>
     </row>
@@ -12389,10 +12380,10 @@
       <c r="B347" s="3" t="s">
         <v>1265</v>
       </c>
-      <c r="C347" s="14">
+      <c r="C347" s="11">
         <v>1845</v>
       </c>
-      <c r="D347" s="15" t="s">
+      <c r="D347" s="12" t="s">
         <v>1266</v>
       </c>
       <c r="F347" s="6" t="s">
@@ -12406,10 +12397,10 @@
       <c r="B348" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="C348" s="14">
+      <c r="C348" s="11">
         <v>1824</v>
       </c>
-      <c r="D348" s="15" t="s">
+      <c r="D348" s="12" t="s">
         <v>1269</v>
       </c>
       <c r="F348" s="5" t="s">
@@ -13392,7 +13383,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G28" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G474" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/xlsx/MWV.xlsx
+++ b/xlsx/MWV.xlsx
@@ -5053,6 +5053,30 @@
     <t>Strings</t>
   </si>
   <si>
+    <t>N 2</t>
+  </si>
+  <si>
+    <t>N 3</t>
+  </si>
+  <si>
+    <t>N 4</t>
+  </si>
+  <si>
+    <t>N 5</t>
+  </si>
+  <si>
+    <t>N 6</t>
+  </si>
+  <si>
+    <t>N 7</t>
+  </si>
+  <si>
+    <t>N 8</t>
+  </si>
+  <si>
+    <t>N 9</t>
+  </si>
+  <si>
     <t>N 10</t>
   </si>
   <si>
@@ -5062,30 +5086,6 @@
     <t>N 12</t>
   </si>
   <si>
-    <t>N 2</t>
-  </si>
-  <si>
-    <t>N 3</t>
-  </si>
-  <si>
-    <t>N 4</t>
-  </si>
-  <si>
-    <t>N 5</t>
-  </si>
-  <si>
-    <t>N 6</t>
-  </si>
-  <si>
-    <t>N 7</t>
-  </si>
-  <si>
-    <t>N 8</t>
-  </si>
-  <si>
-    <t>N 9</t>
-  </si>
-  <si>
     <t>Q 20</t>
   </si>
   <si>
@@ -5215,6 +5215,54 @@
     <t>Blanche et Vermeille</t>
   </si>
   <si>
+    <t>M 2</t>
+  </si>
+  <si>
+    <t>Musik zu einem Lustspiel</t>
+  </si>
+  <si>
+    <t>M 3</t>
+  </si>
+  <si>
+    <t>L’homme automate</t>
+  </si>
+  <si>
+    <t>M 4</t>
+  </si>
+  <si>
+    <t>Musik zu einer Freischütz-Parodie</t>
+  </si>
+  <si>
+    <t>M 5</t>
+  </si>
+  <si>
+    <t>Musik zu einer Mozart-Parodie</t>
+  </si>
+  <si>
+    <t>M 6</t>
+  </si>
+  <si>
+    <t>Was wir bringen</t>
+  </si>
+  <si>
+    <t>M 7</t>
+  </si>
+  <si>
+    <t>Der standhafte Prinz</t>
+  </si>
+  <si>
+    <t>M 8</t>
+  </si>
+  <si>
+    <t>Andreas Hofer</t>
+  </si>
+  <si>
+    <t>M 9</t>
+  </si>
+  <si>
+    <t>Kurfürst Johann Wilhelm im Theater</t>
+  </si>
+  <si>
     <t>M 10</t>
   </si>
   <si>
@@ -5233,54 +5281,6 @@
     <t>König Oedipus</t>
   </si>
   <si>
-    <t>M 2</t>
-  </si>
-  <si>
-    <t>Musik zu einem Lustspiel</t>
-  </si>
-  <si>
-    <t>M 3</t>
-  </si>
-  <si>
-    <t>L’homme automate</t>
-  </si>
-  <si>
-    <t>M 4</t>
-  </si>
-  <si>
-    <t>Musik zu einer Freischütz-Parodie</t>
-  </si>
-  <si>
-    <t>M 5</t>
-  </si>
-  <si>
-    <t>Musik zu einer Mozart-Parodie</t>
-  </si>
-  <si>
-    <t>M 6</t>
-  </si>
-  <si>
-    <t>Was wir bringen</t>
-  </si>
-  <si>
-    <t>M 7</t>
-  </si>
-  <si>
-    <t>Der standhafte Prinz</t>
-  </si>
-  <si>
-    <t>M 8</t>
-  </si>
-  <si>
-    <t>Andreas Hofer</t>
-  </si>
-  <si>
-    <t>M 9</t>
-  </si>
-  <si>
-    <t>Kurfürst Johann Wilhelm im Theater</t>
-  </si>
-  <si>
     <t>N 17</t>
   </si>
   <si>
@@ -5293,25 +5293,40 @@
     <t>Recitativo. Largo</t>
   </si>
   <si>
+    <t>O 2</t>
+  </si>
+  <si>
+    <t>O 3</t>
+  </si>
+  <si>
+    <t>O 4</t>
+  </si>
+  <si>
+    <t>Violin, Piano, Strings</t>
+  </si>
+  <si>
+    <t>O 5</t>
+  </si>
+  <si>
+    <t>O 6</t>
+  </si>
+  <si>
     <t>O 13</t>
   </si>
   <si>
-    <t>O 2</t>
-  </si>
-  <si>
-    <t>O 3</t>
-  </si>
-  <si>
-    <t>O 4</t>
-  </si>
-  <si>
-    <t>Violin, Piano, Strings</t>
-  </si>
-  <si>
-    <t>O 5</t>
-  </si>
-  <si>
-    <t>O 6</t>
+    <t>P 6</t>
+  </si>
+  <si>
+    <t>Kindersinfonie</t>
+  </si>
+  <si>
+    <t>P 8</t>
+  </si>
+  <si>
+    <t>P 9</t>
+  </si>
+  <si>
+    <t>Militärstück</t>
   </si>
   <si>
     <t>P 10</t>
@@ -5336,21 +5351,6 @@
   </si>
   <si>
     <t>P 19</t>
-  </si>
-  <si>
-    <t>P 6</t>
-  </si>
-  <si>
-    <t>Kindersinfonie</t>
-  </si>
-  <si>
-    <t>P 8</t>
-  </si>
-  <si>
-    <t>P 9</t>
-  </si>
-  <si>
-    <t>Militärstück</t>
   </si>
   <si>
     <t>U 65</t>
@@ -6202,7 +6202,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6265,9 +6265,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6875,7 +6872,7 @@
       </c>
     </row>
     <row r="2" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A2" s="21">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
       <c r="B2" s="13" t="s">
@@ -6900,7 +6897,7 @@
       <c r="I2" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="21" t="s">
         <v>16</v>
       </c>
       <c r="K2" s="17" t="s">
@@ -6911,7 +6908,7 @@
       </c>
     </row>
     <row r="3" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A3" s="21">
+      <c r="A3" s="12">
         <v>2</v>
       </c>
       <c r="B3" s="13" t="s">
@@ -6936,7 +6933,7 @@
       <c r="I3" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="22" t="s">
+      <c r="J3" s="21" t="s">
         <v>22</v>
       </c>
       <c r="K3" s="17" t="s">
@@ -6947,7 +6944,7 @@
       </c>
     </row>
     <row r="4" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A4" s="21">
+      <c r="A4" s="12">
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
@@ -6972,7 +6969,7 @@
       <c r="I4" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="J4" s="21" t="s">
         <v>28</v>
       </c>
       <c r="K4" s="17" t="s">
@@ -6983,7 +6980,7 @@
       </c>
     </row>
     <row r="5" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A5" s="21">
+      <c r="A5" s="12">
         <v>4</v>
       </c>
       <c r="B5" s="13" t="s">
@@ -7008,7 +7005,7 @@
       <c r="I5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J5" s="22" t="s">
+      <c r="J5" s="21" t="s">
         <v>33</v>
       </c>
       <c r="K5" s="17" t="s">
@@ -7017,7 +7014,7 @@
       <c r="L5" s="17"/>
     </row>
     <row r="6" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A6" s="21">
+      <c r="A6" s="12">
         <v>5</v>
       </c>
       <c r="B6" s="13" t="s">
@@ -7053,7 +7050,7 @@
       <c r="L6" s="17"/>
     </row>
     <row r="7" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A7" s="21">
+      <c r="A7" s="12">
         <v>6</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -7078,7 +7075,7 @@
       <c r="I7" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="22" t="s">
+      <c r="J7" s="21" t="s">
         <v>46</v>
       </c>
       <c r="K7" s="17" t="s">
@@ -7089,7 +7086,7 @@
       </c>
     </row>
     <row r="8" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A8" s="21">
+      <c r="A8" s="12">
         <v>7</v>
       </c>
       <c r="B8" s="13"/>
@@ -7115,7 +7112,7 @@
       <c r="L8" s="17"/>
     </row>
     <row r="9" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A9" s="21">
+      <c r="A9" s="12">
         <v>7.1</v>
       </c>
       <c r="B9" s="13" t="s">
@@ -7151,7 +7148,7 @@
       <c r="L9" s="17"/>
     </row>
     <row r="10" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A10" s="21">
+      <c r="A10" s="12">
         <v>7.2</v>
       </c>
       <c r="B10" s="13" t="s">
@@ -7187,7 +7184,7 @@
       <c r="L10" s="17"/>
     </row>
     <row r="11" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A11" s="21">
+      <c r="A11" s="12">
         <v>7.3</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -7223,7 +7220,7 @@
       <c r="L11" s="17"/>
     </row>
     <row r="12" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A12" s="21">
+      <c r="A12" s="12">
         <v>7.4</v>
       </c>
       <c r="B12" s="13" t="s">
@@ -7259,7 +7256,7 @@
       <c r="L12" s="17"/>
     </row>
     <row r="13" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A13" s="21">
+      <c r="A13" s="12">
         <v>7.5</v>
       </c>
       <c r="B13" s="13" t="s">
@@ -7295,7 +7292,7 @@
       <c r="L13" s="17"/>
     </row>
     <row r="14" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A14" s="21">
+      <c r="A14" s="12">
         <v>7.6</v>
       </c>
       <c r="B14" s="13" t="s">
@@ -7331,7 +7328,7 @@
       <c r="L14" s="17"/>
     </row>
     <row r="15" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A15" s="21">
+      <c r="A15" s="12">
         <v>7.7</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -7367,7 +7364,7 @@
       <c r="L15" s="17"/>
     </row>
     <row r="16" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A16" s="21">
+      <c r="A16" s="12">
         <v>8</v>
       </c>
       <c r="B16" s="13"/>
@@ -7393,7 +7390,7 @@
       <c r="L16" s="17"/>
     </row>
     <row r="17" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="21">
+      <c r="A17" s="12">
         <v>8.01</v>
       </c>
       <c r="B17" s="13" t="s">
@@ -7431,7 +7428,7 @@
       </c>
     </row>
     <row r="18" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A18" s="21">
+      <c r="A18" s="12">
         <v>8.02</v>
       </c>
       <c r="B18" s="13"/>
@@ -7463,7 +7460,7 @@
       </c>
     </row>
     <row r="19" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A19" s="21">
+      <c r="A19" s="12">
         <v>8.03</v>
       </c>
       <c r="B19" s="13"/>
@@ -7495,7 +7492,7 @@
       </c>
     </row>
     <row r="20" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="21">
+      <c r="A20" s="12">
         <v>8.04</v>
       </c>
       <c r="B20" s="13" t="s">
@@ -7533,7 +7530,7 @@
       </c>
     </row>
     <row r="21" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="21">
+      <c r="A21" s="12">
         <v>8.05</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -7571,7 +7568,7 @@
       </c>
     </row>
     <row r="22" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A22" s="21">
+      <c r="A22" s="12">
         <v>8.06</v>
       </c>
       <c r="B22" s="13" t="s">
@@ -7609,7 +7606,7 @@
       </c>
     </row>
     <row r="23" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A23" s="21">
+      <c r="A23" s="12">
         <v>8.07</v>
       </c>
       <c r="B23" s="13" t="s">
@@ -7647,7 +7644,7 @@
       </c>
     </row>
     <row r="24" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A24" s="21">
+      <c r="A24" s="12">
         <v>8.08</v>
       </c>
       <c r="B24" s="13" t="s">
@@ -7685,7 +7682,7 @@
       </c>
     </row>
     <row r="25" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="21">
+      <c r="A25" s="12">
         <v>8.09</v>
       </c>
       <c r="B25" s="13" t="s">
@@ -7723,7 +7720,7 @@
       </c>
     </row>
     <row r="26" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="21">
+      <c r="A26" s="12">
         <v>8.1</v>
       </c>
       <c r="B26" s="13" t="s">
@@ -7761,7 +7758,7 @@
       </c>
     </row>
     <row r="27" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A27" s="21">
+      <c r="A27" s="12">
         <v>8.11</v>
       </c>
       <c r="B27" s="13" t="s">
@@ -7799,7 +7796,7 @@
       </c>
     </row>
     <row r="28" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A28" s="21">
+      <c r="A28" s="12">
         <v>8.12</v>
       </c>
       <c r="B28" s="13"/>
@@ -7831,7 +7828,7 @@
       </c>
     </row>
     <row r="29" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A29" s="21">
+      <c r="A29" s="12">
         <v>9</v>
       </c>
       <c r="B29" s="13"/>
@@ -7857,7 +7854,7 @@
       <c r="L29" s="17"/>
     </row>
     <row r="30" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A30" s="21">
+      <c r="A30" s="12">
         <v>9.01</v>
       </c>
       <c r="B30" s="13" t="s">
@@ -7895,7 +7892,7 @@
       </c>
     </row>
     <row r="31" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A31" s="21">
+      <c r="A31" s="12">
         <v>9.02</v>
       </c>
       <c r="B31" s="13" t="s">
@@ -7933,7 +7930,7 @@
       </c>
     </row>
     <row r="32" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A32" s="21">
+      <c r="A32" s="12">
         <v>9.03</v>
       </c>
       <c r="B32" s="13" t="s">
@@ -7971,7 +7968,7 @@
       </c>
     </row>
     <row r="33" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A33" s="21">
+      <c r="A33" s="12">
         <v>9.04</v>
       </c>
       <c r="B33" s="13" t="s">
@@ -8009,7 +8006,7 @@
       </c>
     </row>
     <row r="34" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="21">
+      <c r="A34" s="12">
         <v>9.05</v>
       </c>
       <c r="B34" s="13" t="s">
@@ -8047,7 +8044,7 @@
       </c>
     </row>
     <row r="35" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="21">
+      <c r="A35" s="12">
         <v>9.06</v>
       </c>
       <c r="B35" s="13" t="s">
@@ -8085,7 +8082,7 @@
       </c>
     </row>
     <row r="36" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A36" s="21">
+      <c r="A36" s="12">
         <v>9.07</v>
       </c>
       <c r="B36" s="13"/>
@@ -8117,7 +8114,7 @@
       </c>
     </row>
     <row r="37" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="21">
+      <c r="A37" s="12">
         <v>9.08</v>
       </c>
       <c r="B37" s="13" t="s">
@@ -8155,7 +8152,7 @@
       </c>
     </row>
     <row r="38" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A38" s="21">
+      <c r="A38" s="12">
         <v>9.09</v>
       </c>
       <c r="B38" s="13" t="s">
@@ -8193,7 +8190,7 @@
       </c>
     </row>
     <row r="39" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A39" s="21">
+      <c r="A39" s="12">
         <v>9.1</v>
       </c>
       <c r="B39" s="13"/>
@@ -8225,7 +8222,7 @@
       </c>
     </row>
     <row r="40" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A40" s="21">
+      <c r="A40" s="12">
         <v>9.11</v>
       </c>
       <c r="B40" s="13" t="s">
@@ -8263,7 +8260,7 @@
       </c>
     </row>
     <row r="41" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A41" s="21">
+      <c r="A41" s="12">
         <v>9.12</v>
       </c>
       <c r="B41" s="13"/>
@@ -8295,7 +8292,7 @@
       </c>
     </row>
     <row r="42" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A42" s="21">
+      <c r="A42" s="12">
         <v>10</v>
       </c>
       <c r="B42" s="13" t="s">
@@ -8329,7 +8326,7 @@
       </c>
     </row>
     <row r="43" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A43" s="21">
+      <c r="A43" s="12">
         <v>11</v>
       </c>
       <c r="B43" s="13" t="s">
@@ -8356,7 +8353,7 @@
       <c r="I43" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="J43" s="22" t="s">
+      <c r="J43" s="21" t="s">
         <v>199</v>
       </c>
       <c r="K43" s="17" t="s">
@@ -8365,7 +8362,7 @@
       <c r="L43" s="17"/>
     </row>
     <row r="44" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A44" s="21">
+      <c r="A44" s="12">
         <v>12</v>
       </c>
       <c r="B44" s="13" t="s">
@@ -8390,7 +8387,7 @@
       <c r="I44" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="J44" s="22" t="s">
+      <c r="J44" s="21" t="s">
         <v>204</v>
       </c>
       <c r="K44" s="17" t="s">
@@ -8401,7 +8398,7 @@
       </c>
     </row>
     <row r="45" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="21">
+      <c r="A45" s="12">
         <v>13</v>
       </c>
       <c r="B45" s="13" t="s">
@@ -8426,7 +8423,7 @@
       <c r="I45" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J45" s="22" t="s">
+      <c r="J45" s="21" t="s">
         <v>209</v>
       </c>
       <c r="K45" s="17" t="s">
@@ -8437,7 +8434,7 @@
       </c>
     </row>
     <row r="46" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="21">
+      <c r="A46" s="12">
         <v>14</v>
       </c>
       <c r="B46" s="13" t="s">
@@ -8464,7 +8461,7 @@
       <c r="I46" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="J46" s="22" t="s">
+      <c r="J46" s="21" t="s">
         <v>214</v>
       </c>
       <c r="K46" s="17" t="s">
@@ -8473,7 +8470,7 @@
       <c r="L46" s="17"/>
     </row>
     <row r="47" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="21">
+      <c r="A47" s="12">
         <v>15</v>
       </c>
       <c r="B47" s="13" t="s">
@@ -8500,7 +8497,7 @@
       <c r="I47" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="J47" s="22" t="s">
+      <c r="J47" s="21" t="s">
         <v>219</v>
       </c>
       <c r="K47" s="17" t="s">
@@ -8509,7 +8506,7 @@
       <c r="L47" s="17"/>
     </row>
     <row r="48" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="21">
+      <c r="A48" s="12">
         <v>16</v>
       </c>
       <c r="B48" s="13"/>
@@ -8533,7 +8530,7 @@
       <c r="L48" s="17"/>
     </row>
     <row r="49" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="21">
+      <c r="A49" s="12">
         <v>16.1</v>
       </c>
       <c r="B49" s="13" t="s">
@@ -8558,7 +8555,7 @@
       <c r="I49" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="J49" s="22" t="s">
+      <c r="J49" s="21" t="s">
         <v>224</v>
       </c>
       <c r="K49" s="17" t="s">
@@ -8567,7 +8564,7 @@
       <c r="L49" s="17"/>
     </row>
     <row r="50" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A50" s="21">
+      <c r="A50" s="12">
         <v>16.2</v>
       </c>
       <c r="B50" s="13" t="s">
@@ -8601,7 +8598,7 @@
       <c r="L50" s="17"/>
     </row>
     <row r="51" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A51" s="21">
+      <c r="A51" s="12">
         <v>16.3</v>
       </c>
       <c r="B51" s="13" t="s">
@@ -8628,7 +8625,7 @@
       <c r="I51" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="J51" s="22" t="s">
+      <c r="J51" s="21" t="s">
         <v>55</v>
       </c>
       <c r="K51" s="17" t="s">
@@ -8637,7 +8634,7 @@
       <c r="L51" s="17"/>
     </row>
     <row r="52" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A52" s="21">
+      <c r="A52" s="12">
         <v>17</v>
       </c>
       <c r="B52" s="13" t="s">
@@ -8662,7 +8659,7 @@
       <c r="I52" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="J52" s="22" t="s">
+      <c r="J52" s="21" t="s">
         <v>234</v>
       </c>
       <c r="K52" s="17" t="s">
@@ -8671,7 +8668,7 @@
       <c r="L52" s="17"/>
     </row>
     <row r="53" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A53" s="21">
+      <c r="A53" s="12">
         <v>18</v>
       </c>
       <c r="B53" s="13" t="s">
@@ -8696,7 +8693,7 @@
       <c r="I53" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J53" s="22" t="s">
+      <c r="J53" s="21" t="s">
         <v>240</v>
       </c>
       <c r="K53" s="17" t="s">
@@ -8707,7 +8704,7 @@
       </c>
     </row>
     <row r="54" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A54" s="21">
+      <c r="A54" s="12">
         <v>19.1</v>
       </c>
       <c r="B54" s="13"/>
@@ -8733,7 +8730,7 @@
       <c r="L54" s="17"/>
     </row>
     <row r="55" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A55" s="21">
+      <c r="A55" s="12">
         <v>19.11</v>
       </c>
       <c r="B55" s="13" t="s">
@@ -8771,7 +8768,7 @@
       </c>
     </row>
     <row r="56" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A56" s="21">
+      <c r="A56" s="12">
         <v>19.12</v>
       </c>
       <c r="B56" s="13" t="s">
@@ -8809,7 +8806,7 @@
       </c>
     </row>
     <row r="57" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A57" s="21">
+      <c r="A57" s="12">
         <v>19.13</v>
       </c>
       <c r="B57" s="13" t="s">
@@ -8847,7 +8844,7 @@
       </c>
     </row>
     <row r="58" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A58" s="21">
+      <c r="A58" s="12">
         <v>19.14</v>
       </c>
       <c r="B58" s="13" t="s">
@@ -8885,7 +8882,7 @@
       </c>
     </row>
     <row r="59" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A59" s="21">
+      <c r="A59" s="12">
         <v>19.15</v>
       </c>
       <c r="B59" s="13" t="s">
@@ -8923,7 +8920,7 @@
       </c>
     </row>
     <row r="60" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A60" s="21">
+      <c r="A60" s="12">
         <v>19.16</v>
       </c>
       <c r="B60" s="13" t="s">
@@ -8961,7 +8958,7 @@
       </c>
     </row>
     <row r="61" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A61" s="21">
+      <c r="A61" s="12">
         <v>19.2</v>
       </c>
       <c r="B61" s="13"/>
@@ -8989,7 +8986,7 @@
       </c>
     </row>
     <row r="62" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A62" s="21">
+      <c r="A62" s="12">
         <v>19.21</v>
       </c>
       <c r="B62" s="13" t="s">
@@ -9023,7 +9020,7 @@
       <c r="L62" s="17"/>
     </row>
     <row r="63" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A63" s="21">
+      <c r="A63" s="12">
         <v>19.22</v>
       </c>
       <c r="B63" s="13" t="s">
@@ -9057,7 +9054,7 @@
       <c r="L63" s="17"/>
     </row>
     <row r="64" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A64" s="21">
+      <c r="A64" s="12">
         <v>19.23</v>
       </c>
       <c r="B64" s="13" t="s">
@@ -9091,7 +9088,7 @@
       <c r="L64" s="17"/>
     </row>
     <row r="65" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A65" s="21">
+      <c r="A65" s="12">
         <v>19.24</v>
       </c>
       <c r="B65" s="13" t="s">
@@ -9125,7 +9122,7 @@
       <c r="L65" s="17"/>
     </row>
     <row r="66" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A66" s="21">
+      <c r="A66" s="12">
         <v>19.25</v>
       </c>
       <c r="B66" s="13" t="s">
@@ -9159,7 +9156,7 @@
       <c r="L66" s="17"/>
     </row>
     <row r="67" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A67" s="21">
+      <c r="A67" s="12">
         <v>19.26</v>
       </c>
       <c r="B67" s="13" t="s">
@@ -9193,7 +9190,7 @@
       <c r="L67" s="17"/>
     </row>
     <row r="68" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A68" s="21">
+      <c r="A68" s="12">
         <v>20</v>
       </c>
       <c r="B68" s="13" t="s">
@@ -9218,7 +9215,7 @@
       <c r="I68" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="J68" s="22" t="s">
+      <c r="J68" s="21" t="s">
         <v>293</v>
       </c>
       <c r="K68" s="17" t="s">
@@ -9227,7 +9224,7 @@
       <c r="L68" s="17"/>
     </row>
     <row r="69" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A69" s="21">
+      <c r="A69" s="12">
         <v>21</v>
       </c>
       <c r="B69" s="13" t="s">
@@ -9263,12 +9260,12 @@
       <c r="L69" s="17" t="s">
         <v>302</v>
       </c>
-      <c r="M69" s="23" t="s">
+      <c r="M69" s="22" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="70" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A70" s="21">
+      <c r="A70" s="12">
         <v>22</v>
       </c>
       <c r="B70" s="13" t="s">
@@ -9298,13 +9295,13 @@
       <c r="J70" s="16" t="s">
         <v>309</v>
       </c>
-      <c r="K70" s="22" t="s">
+      <c r="K70" s="21" t="s">
         <v>310</v>
       </c>
       <c r="L70" s="17"/>
     </row>
     <row r="71" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A71" s="21">
+      <c r="A71" s="12">
         <v>23</v>
       </c>
       <c r="B71" s="13"/>
@@ -9324,13 +9321,13 @@
       </c>
       <c r="I71" s="15"/>
       <c r="J71" s="16"/>
-      <c r="K71" s="22" t="s">
+      <c r="K71" s="21" t="s">
         <v>313</v>
       </c>
       <c r="L71" s="17"/>
     </row>
     <row r="72" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A72" s="21">
+      <c r="A72" s="12">
         <v>23.1</v>
       </c>
       <c r="B72" s="13" t="s">
@@ -9355,7 +9352,7 @@
         <v>50</v>
       </c>
       <c r="I72" s="15"/>
-      <c r="J72" s="22" t="s">
+      <c r="J72" s="21" t="s">
         <v>318</v>
       </c>
       <c r="K72" s="17" t="s">
@@ -9364,7 +9361,7 @@
       <c r="L72" s="17"/>
     </row>
     <row r="73" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A73" s="21">
+      <c r="A73" s="12">
         <v>23.2</v>
       </c>
       <c r="B73" s="13" t="s">
@@ -9400,7 +9397,7 @@
       <c r="L73" s="17"/>
     </row>
     <row r="74" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A74" s="21">
+      <c r="A74" s="12">
         <v>23.3</v>
       </c>
       <c r="B74" s="13" t="s">
@@ -9436,7 +9433,7 @@
       <c r="L74" s="17"/>
     </row>
     <row r="75" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A75" s="21">
+      <c r="A75" s="12">
         <v>24</v>
       </c>
       <c r="B75" s="13" t="s">
@@ -9461,7 +9458,7 @@
       <c r="I75" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="J75" s="22" t="s">
+      <c r="J75" s="21" t="s">
         <v>332</v>
       </c>
       <c r="K75" s="17" t="s">
@@ -9470,7 +9467,7 @@
       <c r="L75" s="17"/>
     </row>
     <row r="76" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A76" s="21">
+      <c r="A76" s="12">
         <v>25</v>
       </c>
       <c r="B76" s="13" t="s">
@@ -9495,10 +9492,10 @@
       <c r="I76" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="J76" s="22" t="s">
+      <c r="J76" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="K76" s="22" t="s">
+      <c r="K76" s="21" t="s">
         <v>310</v>
       </c>
       <c r="L76" s="17" t="s">
@@ -9506,7 +9503,7 @@
       </c>
     </row>
     <row r="77" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A77" s="21">
+      <c r="A77" s="12">
         <v>26</v>
       </c>
       <c r="B77" s="13" t="s">
@@ -9539,12 +9536,12 @@
       <c r="K77" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="L77" s="22" t="s">
+      <c r="L77" s="21" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="78" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A78" s="21">
+      <c r="A78" s="12">
         <v>27</v>
       </c>
       <c r="B78" s="13" t="s">
@@ -9577,12 +9574,12 @@
       <c r="K78" s="17" t="s">
         <v>349</v>
       </c>
-      <c r="L78" s="22" t="s">
+      <c r="L78" s="21" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="79" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A79" s="21">
+      <c r="A79" s="12">
         <v>28</v>
       </c>
       <c r="B79" s="13" t="s">
@@ -9609,7 +9606,7 @@
       <c r="I79" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="J79" s="22" t="s">
+      <c r="J79" s="21" t="s">
         <v>354</v>
       </c>
       <c r="K79" s="17" t="s">
@@ -9618,7 +9615,7 @@
       <c r="L79" s="17"/>
     </row>
     <row r="80" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A80" s="21">
+      <c r="A80" s="12">
         <v>29</v>
       </c>
       <c r="B80" s="13" t="s">
@@ -9646,13 +9643,13 @@
       <c r="J80" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="K80" s="22" t="s">
+      <c r="K80" s="21" t="s">
         <v>310</v>
       </c>
       <c r="L80" s="17"/>
     </row>
     <row r="81" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A81" s="21">
+      <c r="A81" s="12">
         <v>30</v>
       </c>
       <c r="B81" s="13"/>
@@ -9680,7 +9677,7 @@
       </c>
     </row>
     <row r="82" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A82" s="21">
+      <c r="A82" s="12">
         <v>30.1</v>
       </c>
       <c r="B82" s="13" t="s">
@@ -9714,7 +9711,7 @@
       <c r="L82" s="17"/>
     </row>
     <row r="83" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A83" s="21">
+      <c r="A83" s="12">
         <v>30.2</v>
       </c>
       <c r="B83" s="13" t="s">
@@ -9748,7 +9745,7 @@
       <c r="L83" s="17"/>
     </row>
     <row r="84" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A84" s="21">
+      <c r="A84" s="12">
         <v>30.3</v>
       </c>
       <c r="B84" s="13" t="s">
@@ -9782,7 +9779,7 @@
       <c r="L84" s="17"/>
     </row>
     <row r="85" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A85" s="21">
+      <c r="A85" s="12">
         <v>30.4</v>
       </c>
       <c r="B85" s="13" t="s">
@@ -9816,7 +9813,7 @@
       <c r="L85" s="17"/>
     </row>
     <row r="86" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A86" s="21">
+      <c r="A86" s="12">
         <v>30.5</v>
       </c>
       <c r="B86" s="13" t="s">
@@ -9850,7 +9847,7 @@
       <c r="L86" s="17"/>
     </row>
     <row r="87" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A87" s="21">
+      <c r="A87" s="12">
         <v>30.6</v>
       </c>
       <c r="B87" s="13" t="s">
@@ -9884,7 +9881,7 @@
       <c r="L87" s="17"/>
     </row>
     <row r="88" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A88" s="21">
+      <c r="A88" s="12">
         <v>31</v>
       </c>
       <c r="B88" s="13" t="s">
@@ -9909,16 +9906,16 @@
         <v>382</v>
       </c>
       <c r="I88" s="15"/>
-      <c r="J88" s="22" t="s">
+      <c r="J88" s="21" t="s">
         <v>383</v>
       </c>
-      <c r="K88" s="22" t="s">
+      <c r="K88" s="21" t="s">
         <v>384</v>
       </c>
       <c r="L88" s="17"/>
     </row>
     <row r="89" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A89" s="21">
+      <c r="A89" s="12">
         <v>32</v>
       </c>
       <c r="B89" s="13" t="s">
@@ -9951,12 +9948,12 @@
       <c r="K89" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="L89" s="22" t="s">
+      <c r="L89" s="21" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="90" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A90" s="21">
+      <c r="A90" s="12">
         <v>33</v>
       </c>
       <c r="B90" s="13"/>
@@ -9982,7 +9979,7 @@
       <c r="L90" s="17"/>
     </row>
     <row r="91" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A91" s="21">
+      <c r="A91" s="12">
         <v>33.1</v>
       </c>
       <c r="B91" s="13" t="s">
@@ -10016,7 +10013,7 @@
       <c r="L91" s="17"/>
     </row>
     <row r="92" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A92" s="21">
+      <c r="A92" s="12">
         <v>33.2</v>
       </c>
       <c r="B92" s="13" t="s">
@@ -10050,7 +10047,7 @@
       <c r="L92" s="17"/>
     </row>
     <row r="93" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A93" s="21">
+      <c r="A93" s="12">
         <v>33.3</v>
       </c>
       <c r="B93" s="13" t="s">
@@ -10084,7 +10081,7 @@
       <c r="L93" s="17"/>
     </row>
     <row r="94" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A94" s="21">
+      <c r="A94" s="12">
         <v>34</v>
       </c>
       <c r="B94" s="13"/>
@@ -10110,7 +10107,7 @@
       <c r="L94" s="17"/>
     </row>
     <row r="95" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A95" s="21">
+      <c r="A95" s="12">
         <v>34.1</v>
       </c>
       <c r="B95" s="13" t="s">
@@ -10148,7 +10145,7 @@
       </c>
     </row>
     <row r="96" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A96" s="21">
+      <c r="A96" s="12">
         <v>34.2</v>
       </c>
       <c r="B96" s="13" t="s">
@@ -10184,7 +10181,7 @@
       <c r="L96" s="17"/>
     </row>
     <row r="97" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A97" s="21">
+      <c r="A97" s="12">
         <v>34.3</v>
       </c>
       <c r="B97" s="13" t="s">
@@ -10220,7 +10217,7 @@
       <c r="L97" s="17"/>
     </row>
     <row r="98" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A98" s="21">
+      <c r="A98" s="12">
         <v>34.4</v>
       </c>
       <c r="B98" s="13" t="s">
@@ -10256,7 +10253,7 @@
       <c r="L98" s="17"/>
     </row>
     <row r="99" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A99" s="21">
+      <c r="A99" s="12">
         <v>34.5</v>
       </c>
       <c r="B99" s="13" t="s">
@@ -10292,7 +10289,7 @@
       <c r="L99" s="17"/>
     </row>
     <row r="100" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A100" s="21">
+      <c r="A100" s="12">
         <v>34.6</v>
       </c>
       <c r="B100" s="13" t="s">
@@ -10328,7 +10325,7 @@
       <c r="L100" s="17"/>
     </row>
     <row r="101" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A101" s="21">
+      <c r="A101" s="12">
         <v>35</v>
       </c>
       <c r="B101" s="13"/>
@@ -10352,7 +10349,7 @@
       <c r="L101" s="17"/>
     </row>
     <row r="102" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A102" s="21">
+      <c r="A102" s="12">
         <v>35.11</v>
       </c>
       <c r="B102" s="13" t="s">
@@ -10386,7 +10383,7 @@
       <c r="L102" s="17"/>
     </row>
     <row r="103" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A103" s="21">
+      <c r="A103" s="12">
         <v>35.12</v>
       </c>
       <c r="B103" s="13" t="s">
@@ -10416,7 +10413,7 @@
       <c r="L103" s="17"/>
     </row>
     <row r="104" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A104" s="21">
+      <c r="A104" s="12">
         <v>35.21</v>
       </c>
       <c r="B104" s="13" t="s">
@@ -10450,7 +10447,7 @@
       <c r="L104" s="17"/>
     </row>
     <row r="105" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A105" s="21">
+      <c r="A105" s="12">
         <v>35.22</v>
       </c>
       <c r="B105" s="13" t="s">
@@ -10480,7 +10477,7 @@
       <c r="L105" s="17"/>
     </row>
     <row r="106" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A106" s="21">
+      <c r="A106" s="12">
         <v>35.31</v>
       </c>
       <c r="B106" s="13" t="s">
@@ -10514,7 +10511,7 @@
       <c r="L106" s="17"/>
     </row>
     <row r="107" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A107" s="21">
+      <c r="A107" s="12">
         <v>35.32</v>
       </c>
       <c r="B107" s="13" t="s">
@@ -10544,7 +10541,7 @@
       <c r="L107" s="17"/>
     </row>
     <row r="108" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A108" s="21">
+      <c r="A108" s="12">
         <v>35.41</v>
       </c>
       <c r="B108" s="13" t="s">
@@ -10578,7 +10575,7 @@
       <c r="L108" s="17"/>
     </row>
     <row r="109" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A109" s="21">
+      <c r="A109" s="12">
         <v>35.42</v>
       </c>
       <c r="B109" s="13" t="s">
@@ -10608,7 +10605,7 @@
       <c r="L109" s="17"/>
     </row>
     <row r="110" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A110" s="21">
+      <c r="A110" s="12">
         <v>35.51</v>
       </c>
       <c r="B110" s="13" t="s">
@@ -10642,7 +10639,7 @@
       <c r="L110" s="17"/>
     </row>
     <row r="111" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A111" s="21">
+      <c r="A111" s="12">
         <v>35.52</v>
       </c>
       <c r="B111" s="13" t="s">
@@ -10672,7 +10669,7 @@
       <c r="L111" s="17"/>
     </row>
     <row r="112" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A112" s="21">
+      <c r="A112" s="12">
         <v>35.61</v>
       </c>
       <c r="B112" s="13" t="s">
@@ -10706,7 +10703,7 @@
       <c r="L112" s="17"/>
     </row>
     <row r="113" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A113" s="21">
+      <c r="A113" s="12">
         <v>35.62</v>
       </c>
       <c r="B113" s="13" t="s">
@@ -10736,7 +10733,7 @@
       <c r="L113" s="17"/>
     </row>
     <row r="114" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A114" s="21">
+      <c r="A114" s="12">
         <v>36</v>
       </c>
       <c r="B114" s="13" t="s">
@@ -10770,7 +10767,7 @@
       </c>
     </row>
     <row r="115" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A115" s="21">
+      <c r="A115" s="12">
         <v>37</v>
       </c>
       <c r="B115" s="13"/>
@@ -10794,7 +10791,7 @@
       <c r="L115" s="17"/>
     </row>
     <row r="116" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A116" s="21">
+      <c r="A116" s="12">
         <v>37.1</v>
       </c>
       <c r="B116" s="13" t="s">
@@ -10828,7 +10825,7 @@
       <c r="L116" s="17"/>
     </row>
     <row r="117" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A117" s="21">
+      <c r="A117" s="12">
         <v>37.11</v>
       </c>
       <c r="B117" s="13" t="s">
@@ -10854,7 +10851,7 @@
       <c r="L117" s="17"/>
     </row>
     <row r="118" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A118" s="21">
+      <c r="A118" s="12">
         <v>37.2</v>
       </c>
       <c r="B118" s="13" t="s">
@@ -10888,7 +10885,7 @@
       <c r="L118" s="17"/>
     </row>
     <row r="119" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A119" s="21">
+      <c r="A119" s="12">
         <v>37.21</v>
       </c>
       <c r="B119" s="13" t="s">
@@ -10914,7 +10911,7 @@
       <c r="L119" s="17"/>
     </row>
     <row r="120" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A120" s="21">
+      <c r="A120" s="12">
         <v>37.3</v>
       </c>
       <c r="B120" s="13" t="s">
@@ -10948,7 +10945,7 @@
       <c r="L120" s="17"/>
     </row>
     <row r="121" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A121" s="21">
+      <c r="A121" s="12">
         <v>37.31</v>
       </c>
       <c r="B121" s="13" t="s">
@@ -10974,7 +10971,7 @@
       <c r="L121" s="17"/>
     </row>
     <row r="122" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A122" s="21">
+      <c r="A122" s="12">
         <v>38</v>
       </c>
       <c r="B122" s="13"/>
@@ -11002,7 +10999,7 @@
       </c>
     </row>
     <row r="123" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A123" s="21">
+      <c r="A123" s="12">
         <v>38.1</v>
       </c>
       <c r="B123" s="13" t="s">
@@ -11036,7 +11033,7 @@
       <c r="L123" s="17"/>
     </row>
     <row r="124" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A124" s="21">
+      <c r="A124" s="12">
         <v>38.2</v>
       </c>
       <c r="B124" s="13" t="s">
@@ -11070,7 +11067,7 @@
       <c r="L124" s="17"/>
     </row>
     <row r="125" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A125" s="21">
+      <c r="A125" s="12">
         <v>38.3</v>
       </c>
       <c r="B125" s="13" t="s">
@@ -11104,7 +11101,7 @@
       <c r="L125" s="17"/>
     </row>
     <row r="126" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A126" s="21">
+      <c r="A126" s="12">
         <v>38.4</v>
       </c>
       <c r="B126" s="13" t="s">
@@ -11138,7 +11135,7 @@
       <c r="L126" s="17"/>
     </row>
     <row r="127" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A127" s="21">
+      <c r="A127" s="12">
         <v>38.5</v>
       </c>
       <c r="B127" s="13" t="s">
@@ -11172,7 +11169,7 @@
       <c r="L127" s="17"/>
     </row>
     <row r="128" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A128" s="21">
+      <c r="A128" s="12">
         <v>38.6</v>
       </c>
       <c r="B128" s="13" t="s">
@@ -11206,7 +11203,7 @@
       <c r="L128" s="17"/>
     </row>
     <row r="129" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A129" s="21">
+      <c r="A129" s="12">
         <v>39</v>
       </c>
       <c r="B129" s="13"/>
@@ -11232,7 +11229,7 @@
       <c r="L129" s="17"/>
     </row>
     <row r="130" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A130" s="21">
+      <c r="A130" s="12">
         <v>39.1</v>
       </c>
       <c r="B130" s="13" t="s">
@@ -11268,7 +11265,7 @@
       <c r="L130" s="17"/>
     </row>
     <row r="131" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A131" s="21">
+      <c r="A131" s="12">
         <v>39.2</v>
       </c>
       <c r="B131" s="13" t="s">
@@ -11293,7 +11290,7 @@
         <v>513</v>
       </c>
       <c r="I131" s="15"/>
-      <c r="J131" s="22" t="s">
+      <c r="J131" s="21" t="s">
         <v>523</v>
       </c>
       <c r="K131" s="17" t="s">
@@ -11302,7 +11299,7 @@
       <c r="L131" s="17"/>
     </row>
     <row r="132" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A132" s="21">
+      <c r="A132" s="12">
         <v>39.3</v>
       </c>
       <c r="B132" s="13" t="s">
@@ -11327,7 +11324,7 @@
         <v>513</v>
       </c>
       <c r="I132" s="15"/>
-      <c r="J132" s="22" t="s">
+      <c r="J132" s="21" t="s">
         <v>527</v>
       </c>
       <c r="K132" s="17" t="s">
@@ -11338,7 +11335,7 @@
       </c>
     </row>
     <row r="133" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A133" s="21">
+      <c r="A133" s="12">
         <v>40</v>
       </c>
       <c r="B133" s="13" t="s">
@@ -11363,10 +11360,10 @@
       <c r="I133" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="J133" s="22" t="s">
+      <c r="J133" s="21" t="s">
         <v>531</v>
       </c>
-      <c r="K133" s="22" t="s">
+      <c r="K133" s="21" t="s">
         <v>310</v>
       </c>
       <c r="L133" s="17" t="s">
@@ -11374,7 +11371,7 @@
       </c>
     </row>
     <row r="134" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A134" s="21">
+      <c r="A134" s="12">
         <v>41</v>
       </c>
       <c r="B134" s="13"/>
@@ -11400,7 +11397,7 @@
       <c r="L134" s="17"/>
     </row>
     <row r="135" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A135" s="21">
+      <c r="A135" s="12">
         <v>41.1</v>
       </c>
       <c r="B135" s="13" t="s">
@@ -11438,7 +11435,7 @@
       </c>
     </row>
     <row r="136" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A136" s="21">
+      <c r="A136" s="12">
         <v>41.2</v>
       </c>
       <c r="B136" s="13" t="s">
@@ -11476,7 +11473,7 @@
       </c>
     </row>
     <row r="137" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A137" s="21">
+      <c r="A137" s="12">
         <v>41.3</v>
       </c>
       <c r="B137" s="13" t="s">
@@ -11514,7 +11511,7 @@
       </c>
     </row>
     <row r="138" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A138" s="21">
+      <c r="A138" s="12">
         <v>41.4</v>
       </c>
       <c r="B138" s="13" t="s">
@@ -11552,7 +11549,7 @@
       </c>
     </row>
     <row r="139" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A139" s="21">
+      <c r="A139" s="12">
         <v>41.5</v>
       </c>
       <c r="B139" s="13" t="s">
@@ -11590,7 +11587,7 @@
       </c>
     </row>
     <row r="140" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A140" s="21">
+      <c r="A140" s="12">
         <v>41.6</v>
       </c>
       <c r="B140" s="13" t="s">
@@ -11628,7 +11625,7 @@
       </c>
     </row>
     <row r="141" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A141" s="21">
+      <c r="A141" s="12">
         <v>42</v>
       </c>
       <c r="B141" s="13" t="s">
@@ -11653,7 +11650,7 @@
         <v>382</v>
       </c>
       <c r="I141" s="15"/>
-      <c r="J141" s="22" t="s">
+      <c r="J141" s="21" t="s">
         <v>569</v>
       </c>
       <c r="K141" s="17" t="s">
@@ -11662,7 +11659,7 @@
       <c r="L141" s="17"/>
     </row>
     <row r="142" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A142" s="21">
+      <c r="A142" s="12">
         <v>43</v>
       </c>
       <c r="B142" s="13" t="s">
@@ -11687,16 +11684,16 @@
       <c r="I142" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="J142" s="22" t="s">
+      <c r="J142" s="21" t="s">
         <v>573</v>
       </c>
-      <c r="K142" s="22" t="s">
+      <c r="K142" s="21" t="s">
         <v>310</v>
       </c>
       <c r="L142" s="17"/>
     </row>
     <row r="143" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A143" s="21">
+      <c r="A143" s="12">
         <v>44</v>
       </c>
       <c r="B143" s="13"/>
@@ -11722,7 +11719,7 @@
       <c r="L143" s="17"/>
     </row>
     <row r="144" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A144" s="21">
+      <c r="A144" s="12">
         <v>44.1</v>
       </c>
       <c r="B144" s="13" t="s">
@@ -11747,7 +11744,7 @@
       <c r="I144" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="J144" s="22" t="s">
+      <c r="J144" s="21" t="s">
         <v>579</v>
       </c>
       <c r="K144" s="17" t="s">
@@ -11758,7 +11755,7 @@
       </c>
     </row>
     <row r="145" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A145" s="21">
+      <c r="A145" s="12">
         <v>44.2</v>
       </c>
       <c r="B145" s="13" t="s">
@@ -11783,7 +11780,7 @@
       <c r="I145" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J145" s="22" t="s">
+      <c r="J145" s="21" t="s">
         <v>583</v>
       </c>
       <c r="K145" s="17" t="s">
@@ -11794,7 +11791,7 @@
       </c>
     </row>
     <row r="146" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A146" s="21">
+      <c r="A146" s="12">
         <v>44.3</v>
       </c>
       <c r="B146" s="13" t="s">
@@ -11819,7 +11816,7 @@
       <c r="I146" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="J146" s="22" t="s">
+      <c r="J146" s="21" t="s">
         <v>587</v>
       </c>
       <c r="K146" s="17" t="s">
@@ -11830,7 +11827,7 @@
       </c>
     </row>
     <row r="147" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A147" s="21">
+      <c r="A147" s="12">
         <v>45</v>
       </c>
       <c r="B147" s="13" t="s">
@@ -11855,7 +11852,7 @@
       <c r="I147" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="J147" s="22" t="s">
+      <c r="J147" s="21" t="s">
         <v>591</v>
       </c>
       <c r="K147" s="17" t="s">
@@ -11866,7 +11863,7 @@
       </c>
     </row>
     <row r="148" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A148" s="21">
+      <c r="A148" s="12">
         <v>46</v>
       </c>
       <c r="B148" s="13" t="s">
@@ -11891,7 +11888,7 @@
         <v>382</v>
       </c>
       <c r="I148" s="15"/>
-      <c r="J148" s="22" t="s">
+      <c r="J148" s="21" t="s">
         <v>597</v>
       </c>
       <c r="K148" s="17" t="s">
@@ -11900,7 +11897,7 @@
       <c r="L148" s="17"/>
     </row>
     <row r="149" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A149" s="21">
+      <c r="A149" s="12">
         <v>47</v>
       </c>
       <c r="B149" s="13"/>
@@ -11926,7 +11923,7 @@
       <c r="L149" s="17"/>
     </row>
     <row r="150" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A150" s="21">
+      <c r="A150" s="12">
         <v>47.1</v>
       </c>
       <c r="B150" s="13" t="s">
@@ -11964,7 +11961,7 @@
       </c>
     </row>
     <row r="151" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A151" s="21">
+      <c r="A151" s="12">
         <v>47.2</v>
       </c>
       <c r="B151" s="13" t="s">
@@ -12002,7 +11999,7 @@
       </c>
     </row>
     <row r="152" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A152" s="21">
+      <c r="A152" s="12">
         <v>47.3</v>
       </c>
       <c r="B152" s="13" t="s">
@@ -12040,7 +12037,7 @@
       </c>
     </row>
     <row r="153" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A153" s="21">
+      <c r="A153" s="12">
         <v>47.4</v>
       </c>
       <c r="B153" s="13" t="s">
@@ -12078,7 +12075,7 @@
       </c>
     </row>
     <row r="154" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A154" s="21">
+      <c r="A154" s="12">
         <v>47.5</v>
       </c>
       <c r="B154" s="13" t="s">
@@ -12116,7 +12113,7 @@
       </c>
     </row>
     <row r="155" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A155" s="21">
+      <c r="A155" s="12">
         <v>47.6</v>
       </c>
       <c r="B155" s="13" t="s">
@@ -12154,7 +12151,7 @@
       </c>
     </row>
     <row r="156" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A156" s="21">
+      <c r="A156" s="12">
         <v>48</v>
       </c>
       <c r="B156" s="13"/>
@@ -12180,7 +12177,7 @@
       <c r="L156" s="17"/>
     </row>
     <row r="157" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A157" s="21">
+      <c r="A157" s="12">
         <v>48.1</v>
       </c>
       <c r="B157" s="13" t="s">
@@ -12218,7 +12215,7 @@
       </c>
     </row>
     <row r="158" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A158" s="21">
+      <c r="A158" s="12">
         <v>48.2</v>
       </c>
       <c r="B158" s="13" t="s">
@@ -12256,7 +12253,7 @@
       </c>
     </row>
     <row r="159" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A159" s="21">
+      <c r="A159" s="12">
         <v>48.3</v>
       </c>
       <c r="B159" s="13" t="s">
@@ -12294,7 +12291,7 @@
       </c>
     </row>
     <row r="160" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A160" s="21">
+      <c r="A160" s="12">
         <v>48.4</v>
       </c>
       <c r="B160" s="13" t="s">
@@ -12332,7 +12329,7 @@
       </c>
     </row>
     <row r="161" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A161" s="21">
+      <c r="A161" s="12">
         <v>48.5</v>
       </c>
       <c r="B161" s="13" t="s">
@@ -12370,7 +12367,7 @@
       </c>
     </row>
     <row r="162" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A162" s="21">
+      <c r="A162" s="12">
         <v>48.6</v>
       </c>
       <c r="B162" s="13" t="s">
@@ -12408,7 +12405,7 @@
       </c>
     </row>
     <row r="163" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A163" s="21">
+      <c r="A163" s="12">
         <v>49</v>
       </c>
       <c r="B163" s="13" t="s">
@@ -12433,7 +12430,7 @@
       <c r="I163" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="J163" s="22" t="s">
+      <c r="J163" s="21" t="s">
         <v>652</v>
       </c>
       <c r="K163" s="17" t="s">
@@ -12444,7 +12441,7 @@
       </c>
     </row>
     <row r="164" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A164" s="21">
+      <c r="A164" s="12">
         <v>50</v>
       </c>
       <c r="B164" s="13"/>
@@ -12470,7 +12467,7 @@
       <c r="L164" s="17"/>
     </row>
     <row r="165" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A165" s="21">
+      <c r="A165" s="12">
         <v>50.1</v>
       </c>
       <c r="B165" s="13" t="s">
@@ -12508,7 +12505,7 @@
       </c>
     </row>
     <row r="166" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A166" s="21">
+      <c r="A166" s="12">
         <v>50.2</v>
       </c>
       <c r="B166" s="13" t="s">
@@ -12546,7 +12543,7 @@
       </c>
     </row>
     <row r="167" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A167" s="21">
+      <c r="A167" s="12">
         <v>50.3</v>
       </c>
       <c r="B167" s="13" t="s">
@@ -12584,7 +12581,7 @@
       </c>
     </row>
     <row r="168" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A168" s="21">
+      <c r="A168" s="12">
         <v>50.4</v>
       </c>
       <c r="B168" s="13" t="s">
@@ -12622,7 +12619,7 @@
       </c>
     </row>
     <row r="169" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A169" s="21">
+      <c r="A169" s="12">
         <v>50.5</v>
       </c>
       <c r="B169" s="13" t="s">
@@ -12660,7 +12657,7 @@
       </c>
     </row>
     <row r="170" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A170" s="21">
+      <c r="A170" s="12">
         <v>50.6</v>
       </c>
       <c r="B170" s="13" t="s">
@@ -12698,7 +12695,7 @@
       </c>
     </row>
     <row r="171" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A171" s="21">
+      <c r="A171" s="12">
         <v>51</v>
       </c>
       <c r="B171" s="13" t="s">
@@ -12725,7 +12722,7 @@
       <c r="I171" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="J171" s="22" t="s">
+      <c r="J171" s="21" t="s">
         <v>684</v>
       </c>
       <c r="K171" s="17" t="s">
@@ -12734,7 +12731,7 @@
       <c r="L171" s="17"/>
     </row>
     <row r="172" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A172" s="21">
+      <c r="A172" s="12">
         <v>52</v>
       </c>
       <c r="B172" s="13" t="s">
@@ -12761,7 +12758,7 @@
       <c r="I172" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="J172" s="22" t="s">
+      <c r="J172" s="21" t="s">
         <v>689</v>
       </c>
       <c r="K172" s="17" t="s">
@@ -12770,7 +12767,7 @@
       <c r="L172" s="17"/>
     </row>
     <row r="173" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A173" s="21">
+      <c r="A173" s="12">
         <v>53</v>
       </c>
       <c r="B173" s="13"/>
@@ -12798,7 +12795,7 @@
       </c>
     </row>
     <row r="174" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A174" s="21">
+      <c r="A174" s="12">
         <v>53.1</v>
       </c>
       <c r="B174" s="13" t="s">
@@ -12832,7 +12829,7 @@
       <c r="L174" s="17"/>
     </row>
     <row r="175" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A175" s="21">
+      <c r="A175" s="12">
         <v>53.2</v>
       </c>
       <c r="B175" s="13" t="s">
@@ -12866,7 +12863,7 @@
       <c r="L175" s="17"/>
     </row>
     <row r="176" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A176" s="21">
+      <c r="A176" s="12">
         <v>53.3</v>
       </c>
       <c r="B176" s="13" t="s">
@@ -12900,7 +12897,7 @@
       <c r="L176" s="17"/>
     </row>
     <row r="177" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A177" s="21">
+      <c r="A177" s="12">
         <v>53.4</v>
       </c>
       <c r="B177" s="13" t="s">
@@ -12934,7 +12931,7 @@
       <c r="L177" s="17"/>
     </row>
     <row r="178" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A178" s="21">
+      <c r="A178" s="12">
         <v>53.5</v>
       </c>
       <c r="B178" s="13" t="s">
@@ -12968,7 +12965,7 @@
       <c r="L178" s="17"/>
     </row>
     <row r="179" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A179" s="21">
+      <c r="A179" s="12">
         <v>53.6</v>
       </c>
       <c r="B179" s="13" t="s">
@@ -13002,7 +12999,7 @@
       <c r="L179" s="17"/>
     </row>
     <row r="180" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A180" s="21">
+      <c r="A180" s="12">
         <v>54</v>
       </c>
       <c r="B180" s="13" t="s">
@@ -13032,7 +13029,7 @@
       <c r="L180" s="17"/>
     </row>
     <row r="181" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A181" s="21">
+      <c r="A181" s="12">
         <v>55</v>
       </c>
       <c r="B181" s="13" t="s">
@@ -13057,7 +13054,7 @@
         <v>715</v>
       </c>
       <c r="I181" s="15"/>
-      <c r="J181" s="22" t="s">
+      <c r="J181" s="21" t="s">
         <v>716</v>
       </c>
       <c r="K181" s="17" t="s">
@@ -13068,7 +13065,7 @@
       </c>
     </row>
     <row r="182" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A182" s="21">
+      <c r="A182" s="12">
         <v>56</v>
       </c>
       <c r="B182" s="13" t="s">
@@ -13095,7 +13092,7 @@
       <c r="I182" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="J182" s="22" t="s">
+      <c r="J182" s="21" t="s">
         <v>723</v>
       </c>
       <c r="K182" s="17" t="s">
@@ -13104,7 +13101,7 @@
       <c r="L182" s="17"/>
     </row>
     <row r="183" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A183" s="21">
+      <c r="A183" s="12">
         <v>57</v>
       </c>
       <c r="B183" s="13"/>
@@ -13130,7 +13127,7 @@
       <c r="L183" s="17"/>
     </row>
     <row r="184" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A184" s="21">
+      <c r="A184" s="12">
         <v>57.1</v>
       </c>
       <c r="B184" s="13" t="s">
@@ -13168,7 +13165,7 @@
       </c>
     </row>
     <row r="185" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A185" s="21">
+      <c r="A185" s="12">
         <v>57.2</v>
       </c>
       <c r="B185" s="13" t="s">
@@ -13206,7 +13203,7 @@
       </c>
     </row>
     <row r="186" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A186" s="21">
+      <c r="A186" s="12">
         <v>57.3</v>
       </c>
       <c r="B186" s="13" t="s">
@@ -13244,7 +13241,7 @@
       </c>
     </row>
     <row r="187" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A187" s="21">
+      <c r="A187" s="12">
         <v>57.4</v>
       </c>
       <c r="B187" s="13" t="s">
@@ -13282,7 +13279,7 @@
       </c>
     </row>
     <row r="188" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A188" s="21">
+      <c r="A188" s="12">
         <v>57.5</v>
       </c>
       <c r="B188" s="13" t="s">
@@ -13320,7 +13317,7 @@
       </c>
     </row>
     <row r="189" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A189" s="21">
+      <c r="A189" s="12">
         <v>57.6</v>
       </c>
       <c r="B189" s="13" t="s">
@@ -13358,7 +13355,7 @@
       </c>
     </row>
     <row r="190" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A190" s="21">
+      <c r="A190" s="12">
         <v>58</v>
       </c>
       <c r="B190" s="13" t="s">
@@ -13383,7 +13380,7 @@
       <c r="I190" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="J190" s="22" t="s">
+      <c r="J190" s="21" t="s">
         <v>753</v>
       </c>
       <c r="K190" s="17" t="s">
@@ -13394,7 +13391,7 @@
       </c>
     </row>
     <row r="191" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A191" s="21">
+      <c r="A191" s="12">
         <v>59</v>
       </c>
       <c r="B191" s="13"/>
@@ -13413,14 +13410,14 @@
         <v>83</v>
       </c>
       <c r="I191" s="15"/>
-      <c r="J191" s="22"/>
+      <c r="J191" s="21"/>
       <c r="K191" s="17" t="s">
         <v>536</v>
       </c>
       <c r="L191" s="17"/>
     </row>
     <row r="192" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A192" s="21">
+      <c r="A192" s="12">
         <v>59.1</v>
       </c>
       <c r="B192" s="13" t="s">
@@ -13447,7 +13444,7 @@
       <c r="I192" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J192" s="22" t="s">
+      <c r="J192" s="21" t="s">
         <v>104</v>
       </c>
       <c r="K192" s="17" t="s">
@@ -13458,7 +13455,7 @@
       </c>
     </row>
     <row r="193" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A193" s="21">
+      <c r="A193" s="12">
         <v>59.2</v>
       </c>
       <c r="B193" s="13" t="s">
@@ -13483,7 +13480,7 @@
         <v>83</v>
       </c>
       <c r="I193" s="15"/>
-      <c r="J193" s="22" t="s">
+      <c r="J193" s="21" t="s">
         <v>624</v>
       </c>
       <c r="K193" s="17"/>
@@ -13492,7 +13489,7 @@
       </c>
     </row>
     <row r="194" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A194" s="21">
+      <c r="A194" s="12">
         <v>59.3</v>
       </c>
       <c r="B194" s="13" t="s">
@@ -13517,7 +13514,7 @@
         <v>83</v>
       </c>
       <c r="I194" s="15"/>
-      <c r="J194" s="22" t="s">
+      <c r="J194" s="21" t="s">
         <v>768</v>
       </c>
       <c r="K194" s="17"/>
@@ -13526,7 +13523,7 @@
       </c>
     </row>
     <row r="195" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A195" s="21">
+      <c r="A195" s="12">
         <v>59.4</v>
       </c>
       <c r="B195" s="13" t="s">
@@ -13551,7 +13548,7 @@
         <v>83</v>
       </c>
       <c r="I195" s="15"/>
-      <c r="J195" s="22" t="s">
+      <c r="J195" s="21" t="s">
         <v>55</v>
       </c>
       <c r="K195" s="17"/>
@@ -13560,7 +13557,7 @@
       </c>
     </row>
     <row r="196" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A196" s="21">
+      <c r="A196" s="12">
         <v>59.5</v>
       </c>
       <c r="B196" s="13" t="s">
@@ -13585,7 +13582,7 @@
         <v>83</v>
       </c>
       <c r="I196" s="15"/>
-      <c r="J196" s="22" t="s">
+      <c r="J196" s="21" t="s">
         <v>644</v>
       </c>
       <c r="K196" s="17"/>
@@ -13594,7 +13591,7 @@
       </c>
     </row>
     <row r="197" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A197" s="21">
+      <c r="A197" s="12">
         <v>59.6</v>
       </c>
       <c r="B197" s="13" t="s">
@@ -13619,7 +13616,7 @@
         <v>83</v>
       </c>
       <c r="I197" s="15"/>
-      <c r="J197" s="22" t="s">
+      <c r="J197" s="21" t="s">
         <v>778</v>
       </c>
       <c r="K197" s="17"/>
@@ -13628,7 +13625,7 @@
       </c>
     </row>
     <row r="198" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A198" s="21">
+      <c r="A198" s="12">
         <v>60</v>
       </c>
       <c r="B198" s="13" t="s">
@@ -13653,7 +13650,7 @@
         <v>784</v>
       </c>
       <c r="I198" s="15"/>
-      <c r="J198" s="22" t="s">
+      <c r="J198" s="21" t="s">
         <v>785</v>
       </c>
       <c r="K198" s="17" t="s">
@@ -13664,7 +13661,7 @@
       </c>
     </row>
     <row r="199" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A199" s="21">
+      <c r="A199" s="12">
         <v>61</v>
       </c>
       <c r="B199" s="13" t="s">
@@ -13689,19 +13686,19 @@
         <v>715</v>
       </c>
       <c r="I199" s="15"/>
-      <c r="J199" s="22" t="s">
+      <c r="J199" s="21" t="s">
         <v>790</v>
       </c>
       <c r="K199" s="17"/>
       <c r="L199" s="17" t="s">
         <v>791</v>
       </c>
-      <c r="M199" s="23" t="s">
+      <c r="M199" s="22" t="s">
         <v>792</v>
       </c>
     </row>
     <row r="200" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A200" s="21">
+      <c r="A200" s="12">
         <v>62</v>
       </c>
       <c r="B200" s="13"/>
@@ -13729,7 +13726,7 @@
       </c>
     </row>
     <row r="201" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A201" s="21">
+      <c r="A201" s="12">
         <v>62.1</v>
       </c>
       <c r="B201" s="13" t="s">
@@ -13763,7 +13760,7 @@
       <c r="L201" s="17"/>
     </row>
     <row r="202" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A202" s="21">
+      <c r="A202" s="12">
         <v>62.2</v>
       </c>
       <c r="B202" s="13" t="s">
@@ -13797,7 +13794,7 @@
       <c r="L202" s="17"/>
     </row>
     <row r="203" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A203" s="21">
+      <c r="A203" s="12">
         <v>62.3</v>
       </c>
       <c r="B203" s="13" t="s">
@@ -13831,7 +13828,7 @@
       <c r="L203" s="17"/>
     </row>
     <row r="204" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A204" s="21">
+      <c r="A204" s="12">
         <v>62.4</v>
       </c>
       <c r="B204" s="13" t="s">
@@ -13865,7 +13862,7 @@
       <c r="L204" s="17"/>
     </row>
     <row r="205" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A205" s="21">
+      <c r="A205" s="12">
         <v>62.5</v>
       </c>
       <c r="B205" s="13" t="s">
@@ -13899,7 +13896,7 @@
       <c r="L205" s="17"/>
     </row>
     <row r="206" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A206" s="21">
+      <c r="A206" s="12">
         <v>62.6</v>
       </c>
       <c r="B206" s="13" t="s">
@@ -13933,7 +13930,7 @@
       <c r="L206" s="17"/>
     </row>
     <row r="207" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A207" s="21">
+      <c r="A207" s="12">
         <v>63</v>
       </c>
       <c r="B207" s="13"/>
@@ -13959,7 +13956,7 @@
       <c r="L207" s="17"/>
     </row>
     <row r="208" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A208" s="21">
+      <c r="A208" s="12">
         <v>63.1</v>
       </c>
       <c r="B208" s="13" t="s">
@@ -13997,7 +13994,7 @@
       </c>
     </row>
     <row r="209" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A209" s="21">
+      <c r="A209" s="12">
         <v>63.2</v>
       </c>
       <c r="B209" s="13" t="s">
@@ -14035,7 +14032,7 @@
       </c>
     </row>
     <row r="210" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A210" s="21">
+      <c r="A210" s="12">
         <v>63.3</v>
       </c>
       <c r="B210" s="13" t="s">
@@ -14073,7 +14070,7 @@
       </c>
     </row>
     <row r="211" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A211" s="21">
+      <c r="A211" s="12">
         <v>63.4</v>
       </c>
       <c r="B211" s="13" t="s">
@@ -14111,7 +14108,7 @@
       </c>
     </row>
     <row r="212" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A212" s="21">
+      <c r="A212" s="12">
         <v>63.5</v>
       </c>
       <c r="B212" s="13" t="s">
@@ -14149,7 +14146,7 @@
       </c>
     </row>
     <row r="213" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A213" s="21">
+      <c r="A213" s="12">
         <v>63.6</v>
       </c>
       <c r="B213" s="13" t="s">
@@ -14187,7 +14184,7 @@
       </c>
     </row>
     <row r="214" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A214" s="21">
+      <c r="A214" s="12">
         <v>64</v>
       </c>
       <c r="B214" s="13" t="s">
@@ -14205,13 +14202,14 @@
       <c r="F214" s="13">
         <v>1844</v>
       </c>
+      <c r="G214" s="11"/>
       <c r="H214" s="13" t="s">
         <v>336</v>
       </c>
       <c r="I214" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J214" s="22" t="s">
+      <c r="J214" s="21" t="s">
         <v>840</v>
       </c>
       <c r="K214" s="17" t="s">
@@ -14220,7 +14218,7 @@
       <c r="L214" s="17"/>
     </row>
     <row r="215" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A215" s="21">
+      <c r="A215" s="12">
         <v>65</v>
       </c>
       <c r="B215" s="13"/>
@@ -14246,7 +14244,7 @@
       <c r="L215" s="17"/>
     </row>
     <row r="216" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A216" s="21">
+      <c r="A216" s="12">
         <v>65.1</v>
       </c>
       <c r="B216" s="13" t="s">
@@ -14273,7 +14271,7 @@
       <c r="I216" s="15" t="s">
         <v>848</v>
       </c>
-      <c r="J216" s="22" t="s">
+      <c r="J216" s="21" t="s">
         <v>849</v>
       </c>
       <c r="K216" s="17" t="s">
@@ -14282,7 +14280,7 @@
       <c r="L216" s="17"/>
     </row>
     <row r="217" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A217" s="21">
+      <c r="A217" s="12">
         <v>65.2</v>
       </c>
       <c r="B217" s="13" t="s">
@@ -14309,7 +14307,7 @@
       <c r="I217" s="15" t="s">
         <v>853</v>
       </c>
-      <c r="J217" s="22" t="s">
+      <c r="J217" s="21" t="s">
         <v>854</v>
       </c>
       <c r="K217" s="17" t="s">
@@ -14318,7 +14316,7 @@
       <c r="L217" s="17"/>
     </row>
     <row r="218" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A218" s="21">
+      <c r="A218" s="12">
         <v>65.3</v>
       </c>
       <c r="B218" s="13" t="s">
@@ -14345,7 +14343,7 @@
       <c r="I218" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J218" s="22" t="s">
+      <c r="J218" s="21" t="s">
         <v>858</v>
       </c>
       <c r="K218" s="17" t="s">
@@ -14354,7 +14352,7 @@
       <c r="L218" s="17"/>
     </row>
     <row r="219" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A219" s="21">
+      <c r="A219" s="12">
         <v>65.4</v>
       </c>
       <c r="B219" s="13" t="s">
@@ -14381,7 +14379,7 @@
       <c r="I219" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="J219" s="22" t="s">
+      <c r="J219" s="21" t="s">
         <v>862</v>
       </c>
       <c r="K219" s="17" t="s">
@@ -14390,7 +14388,7 @@
       <c r="L219" s="17"/>
     </row>
     <row r="220" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A220" s="21">
+      <c r="A220" s="12">
         <v>65.5</v>
       </c>
       <c r="B220" s="13" t="s">
@@ -14417,7 +14415,7 @@
       <c r="I220" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="J220" s="22" t="s">
+      <c r="J220" s="21" t="s">
         <v>866</v>
       </c>
       <c r="K220" s="17" t="s">
@@ -14426,7 +14424,7 @@
       <c r="L220" s="17"/>
     </row>
     <row r="221" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A221" s="21">
+      <c r="A221" s="12">
         <v>65.6</v>
       </c>
       <c r="B221" s="13" t="s">
@@ -14453,7 +14451,7 @@
       <c r="I221" s="15" t="s">
         <v>870</v>
       </c>
-      <c r="J221" s="22" t="s">
+      <c r="J221" s="21" t="s">
         <v>871</v>
       </c>
       <c r="K221" s="17" t="s">
@@ -14462,7 +14460,7 @@
       <c r="L221" s="17"/>
     </row>
     <row r="222" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A222" s="21">
+      <c r="A222" s="12">
         <v>66</v>
       </c>
       <c r="B222" s="13" t="s">
@@ -14487,7 +14485,7 @@
       <c r="I222" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="J222" s="22" t="s">
+      <c r="J222" s="21" t="s">
         <v>874</v>
       </c>
       <c r="K222" s="17" t="s">
@@ -14498,7 +14496,7 @@
       </c>
     </row>
     <row r="223" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A223" s="21">
+      <c r="A223" s="12">
         <v>67</v>
       </c>
       <c r="B223" s="13"/>
@@ -14526,7 +14524,7 @@
       </c>
     </row>
     <row r="224" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A224" s="21">
+      <c r="A224" s="12">
         <v>67.1</v>
       </c>
       <c r="B224" s="13" t="s">
@@ -14560,7 +14558,7 @@
       <c r="L224" s="17"/>
     </row>
     <row r="225" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A225" s="21">
+      <c r="A225" s="12">
         <v>67.2</v>
       </c>
       <c r="B225" s="13" t="s">
@@ -14594,7 +14592,7 @@
       <c r="L225" s="17"/>
     </row>
     <row r="226" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A226" s="21">
+      <c r="A226" s="12">
         <v>67.3</v>
       </c>
       <c r="B226" s="13" t="s">
@@ -14628,7 +14626,7 @@
       <c r="L226" s="17"/>
     </row>
     <row r="227" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A227" s="21">
+      <c r="A227" s="12">
         <v>67.4</v>
       </c>
       <c r="B227" s="13" t="s">
@@ -14662,7 +14660,7 @@
       <c r="L227" s="17"/>
     </row>
     <row r="228" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A228" s="21">
+      <c r="A228" s="12">
         <v>67.5</v>
       </c>
       <c r="B228" s="13" t="s">
@@ -14696,7 +14694,7 @@
       <c r="L228" s="17"/>
     </row>
     <row r="229" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A229" s="21">
+      <c r="A229" s="12">
         <v>67.6</v>
       </c>
       <c r="B229" s="13" t="s">
@@ -14730,7 +14728,7 @@
       <c r="L229" s="17"/>
     </row>
     <row r="230" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A230" s="21">
+      <c r="A230" s="12">
         <v>68</v>
       </c>
       <c r="B230" s="13" t="s">
@@ -14768,7 +14766,7 @@
       </c>
     </row>
     <row r="231" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A231" s="21">
+      <c r="A231" s="12">
         <v>69</v>
       </c>
       <c r="B231" s="13"/>
@@ -14794,7 +14792,7 @@
       <c r="L231" s="17"/>
     </row>
     <row r="232" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A232" s="21">
+      <c r="A232" s="12">
         <v>69.1</v>
       </c>
       <c r="B232" s="13" t="s">
@@ -14830,7 +14828,7 @@
       <c r="L232" s="17"/>
     </row>
     <row r="233" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A233" s="21">
+      <c r="A233" s="12">
         <v>69.2</v>
       </c>
       <c r="B233" s="13" t="s">
@@ -14866,7 +14864,7 @@
       <c r="L233" s="17"/>
     </row>
     <row r="234" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A234" s="21">
+      <c r="A234" s="12">
         <v>69.3</v>
       </c>
       <c r="B234" s="13" t="s">
@@ -14893,7 +14891,7 @@
       <c r="I234" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="J234" s="22" t="s">
+      <c r="J234" s="21" t="s">
         <v>914</v>
       </c>
       <c r="K234" s="17" t="s">
@@ -14902,7 +14900,7 @@
       <c r="L234" s="17"/>
     </row>
     <row r="235" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A235" s="21">
+      <c r="A235" s="12">
         <v>70</v>
       </c>
       <c r="B235" s="13" t="s">
@@ -14934,7 +14932,7 @@
       <c r="L235" s="17"/>
     </row>
     <row r="236" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A236" s="21">
+      <c r="A236" s="12">
         <v>71</v>
       </c>
       <c r="B236" s="13"/>
@@ -14960,7 +14958,7 @@
       <c r="L236" s="17"/>
     </row>
     <row r="237" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A237" s="21">
+      <c r="A237" s="12">
         <v>71.1</v>
       </c>
       <c r="B237" s="13" t="s">
@@ -14998,7 +14996,7 @@
       </c>
     </row>
     <row r="238" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A238" s="21">
+      <c r="A238" s="12">
         <v>71.2</v>
       </c>
       <c r="B238" s="13" t="s">
@@ -15036,7 +15034,7 @@
       </c>
     </row>
     <row r="239" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A239" s="21">
+      <c r="A239" s="12">
         <v>71.3</v>
       </c>
       <c r="B239" s="13" t="s">
@@ -15074,7 +15072,7 @@
       </c>
     </row>
     <row r="240" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A240" s="21">
+      <c r="A240" s="12">
         <v>71.4</v>
       </c>
       <c r="B240" s="13" t="s">
@@ -15112,7 +15110,7 @@
       </c>
     </row>
     <row r="241" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A241" s="21">
+      <c r="A241" s="12">
         <v>71.5</v>
       </c>
       <c r="B241" s="13" t="s">
@@ -15150,7 +15148,7 @@
       </c>
     </row>
     <row r="242" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A242" s="21">
+      <c r="A242" s="12">
         <v>71.6</v>
       </c>
       <c r="B242" s="13" t="s">
@@ -15188,7 +15186,7 @@
       </c>
     </row>
     <row r="243" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A243" s="21">
+      <c r="A243" s="12">
         <v>72</v>
       </c>
       <c r="B243" s="13"/>
@@ -15214,7 +15212,7 @@
       <c r="L243" s="17"/>
     </row>
     <row r="244" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A244" s="21">
+      <c r="A244" s="12">
         <v>72.1</v>
       </c>
       <c r="B244" s="13" t="s">
@@ -15248,7 +15246,7 @@
       <c r="L244" s="17"/>
     </row>
     <row r="245" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A245" s="21">
+      <c r="A245" s="12">
         <v>72.2</v>
       </c>
       <c r="B245" s="13" t="s">
@@ -15282,7 +15280,7 @@
       <c r="L245" s="17"/>
     </row>
     <row r="246" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A246" s="21">
+      <c r="A246" s="12">
         <v>72.3</v>
       </c>
       <c r="B246" s="13" t="s">
@@ -15316,7 +15314,7 @@
       <c r="L246" s="17"/>
     </row>
     <row r="247" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A247" s="21">
+      <c r="A247" s="12">
         <v>72.4</v>
       </c>
       <c r="B247" s="13" t="s">
@@ -15350,7 +15348,7 @@
       <c r="L247" s="17"/>
     </row>
     <row r="248" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A248" s="21">
+      <c r="A248" s="12">
         <v>72.5</v>
       </c>
       <c r="B248" s="13" t="s">
@@ -15384,7 +15382,7 @@
       <c r="L248" s="17"/>
     </row>
     <row r="249" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A249" s="21">
+      <c r="A249" s="12">
         <v>72.6</v>
       </c>
       <c r="B249" s="13" t="s">
@@ -15418,7 +15416,7 @@
       <c r="L249" s="17"/>
     </row>
     <row r="250" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A250" s="21">
+      <c r="A250" s="12">
         <v>73</v>
       </c>
       <c r="B250" s="13" t="s">
@@ -15443,16 +15441,16 @@
         <v>957</v>
       </c>
       <c r="I250" s="15"/>
-      <c r="J250" s="22" t="s">
+      <c r="J250" s="21" t="s">
         <v>958</v>
       </c>
-      <c r="K250" s="22" t="s">
+      <c r="K250" s="21" t="s">
         <v>959</v>
       </c>
       <c r="L250" s="17"/>
     </row>
     <row r="251" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A251" s="21">
+      <c r="A251" s="12">
         <v>74</v>
       </c>
       <c r="B251" s="13" t="s">
@@ -15477,7 +15475,7 @@
         <v>715</v>
       </c>
       <c r="I251" s="15"/>
-      <c r="J251" s="22" t="s">
+      <c r="J251" s="21" t="s">
         <v>963</v>
       </c>
       <c r="K251" s="17"/>
@@ -15486,7 +15484,7 @@
       </c>
     </row>
     <row r="252" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A252" s="21">
+      <c r="A252" s="12">
         <v>75</v>
       </c>
       <c r="B252" s="13"/>
@@ -15512,7 +15510,7 @@
       <c r="L252" s="17"/>
     </row>
     <row r="253" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A253" s="21">
+      <c r="A253" s="12">
         <v>75.1</v>
       </c>
       <c r="B253" s="13" t="s">
@@ -15548,7 +15546,7 @@
       <c r="L253" s="17"/>
     </row>
     <row r="254" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A254" s="21">
+      <c r="A254" s="12">
         <v>75.2</v>
       </c>
       <c r="B254" s="13" t="s">
@@ -15582,7 +15580,7 @@
       <c r="L254" s="17"/>
     </row>
     <row r="255" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A255" s="21">
+      <c r="A255" s="12">
         <v>75.3</v>
       </c>
       <c r="B255" s="13" t="s">
@@ -15618,7 +15616,7 @@
       <c r="L255" s="17"/>
     </row>
     <row r="256" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A256" s="21">
+      <c r="A256" s="12">
         <v>75.4</v>
       </c>
       <c r="B256" s="13" t="s">
@@ -15654,7 +15652,7 @@
       <c r="L256" s="17"/>
     </row>
     <row r="257" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A257" s="21">
+      <c r="A257" s="12">
         <v>76</v>
       </c>
       <c r="B257" s="13"/>
@@ -15680,7 +15678,7 @@
       <c r="L257" s="17"/>
     </row>
     <row r="258" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A258" s="21">
+      <c r="A258" s="12">
         <v>76.1</v>
       </c>
       <c r="B258" s="13" t="s">
@@ -15716,7 +15714,7 @@
       <c r="L258" s="17"/>
     </row>
     <row r="259" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A259" s="21">
+      <c r="A259" s="12">
         <v>76.2</v>
       </c>
       <c r="B259" s="13" t="s">
@@ -15752,7 +15750,7 @@
       <c r="L259" s="17"/>
     </row>
     <row r="260" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A260" s="21">
+      <c r="A260" s="12">
         <v>76.3</v>
       </c>
       <c r="B260" s="13" t="s">
@@ -15788,7 +15786,7 @@
       <c r="L260" s="17"/>
     </row>
     <row r="261" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A261" s="21">
+      <c r="A261" s="12">
         <v>76.4</v>
       </c>
       <c r="B261" s="13" t="s">
@@ -15824,7 +15822,7 @@
       <c r="L261" s="17"/>
     </row>
     <row r="262" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A262" s="21">
+      <c r="A262" s="12">
         <v>77</v>
       </c>
       <c r="B262" s="13"/>
@@ -15850,7 +15848,7 @@
       <c r="L262" s="17"/>
     </row>
     <row r="263" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A263" s="21">
+      <c r="A263" s="12">
         <v>77.1</v>
       </c>
       <c r="B263" s="13" t="s">
@@ -15888,7 +15886,7 @@
       </c>
     </row>
     <row r="264" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A264" s="21">
+      <c r="A264" s="12">
         <v>77.2</v>
       </c>
       <c r="B264" s="13" t="s">
@@ -15926,7 +15924,7 @@
       </c>
     </row>
     <row r="265" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A265" s="21">
+      <c r="A265" s="12">
         <v>77.3</v>
       </c>
       <c r="B265" s="13" t="s">
@@ -15964,7 +15962,7 @@
       </c>
     </row>
     <row r="266" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A266" s="21">
+      <c r="A266" s="12">
         <v>78</v>
       </c>
       <c r="B266" s="13"/>
@@ -15990,7 +15988,7 @@
       <c r="L266" s="17"/>
     </row>
     <row r="267" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A267" s="21">
+      <c r="A267" s="12">
         <v>78.1</v>
       </c>
       <c r="B267" s="13" t="s">
@@ -16026,7 +16024,7 @@
       <c r="L267" s="17"/>
     </row>
     <row r="268" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A268" s="21">
+      <c r="A268" s="12">
         <v>78.2</v>
       </c>
       <c r="B268" s="13" t="s">
@@ -16062,7 +16060,7 @@
       <c r="L268" s="17"/>
     </row>
     <row r="269" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A269" s="21">
+      <c r="A269" s="12">
         <v>78.3</v>
       </c>
       <c r="B269" s="13" t="s">
@@ -16098,7 +16096,7 @@
       <c r="L269" s="17"/>
     </row>
     <row r="270" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A270" s="21">
+      <c r="A270" s="12">
         <v>79</v>
       </c>
       <c r="B270" s="13"/>
@@ -16124,7 +16122,7 @@
       <c r="L270" s="17"/>
     </row>
     <row r="271" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A271" s="21">
+      <c r="A271" s="12">
         <v>79.1</v>
       </c>
       <c r="B271" s="13" t="s">
@@ -16162,7 +16160,7 @@
       </c>
     </row>
     <row r="272" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A272" s="21">
+      <c r="A272" s="12">
         <v>79.2</v>
       </c>
       <c r="B272" s="13" t="s">
@@ -16200,7 +16198,7 @@
       </c>
     </row>
     <row r="273" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A273" s="21">
+      <c r="A273" s="12">
         <v>79.3</v>
       </c>
       <c r="B273" s="13" t="s">
@@ -16238,7 +16236,7 @@
       </c>
     </row>
     <row r="274" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A274" s="21">
+      <c r="A274" s="12">
         <v>79.4</v>
       </c>
       <c r="B274" s="13" t="s">
@@ -16276,7 +16274,7 @@
       </c>
     </row>
     <row r="275" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A275" s="21">
+      <c r="A275" s="12">
         <v>79.5</v>
       </c>
       <c r="B275" s="13" t="s">
@@ -16314,7 +16312,7 @@
       </c>
     </row>
     <row r="276" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A276" s="21">
+      <c r="A276" s="12">
         <v>79.6</v>
       </c>
       <c r="B276" s="13" t="s">
@@ -16352,7 +16350,7 @@
       </c>
     </row>
     <row r="277" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A277" s="21">
+      <c r="A277" s="12">
         <v>80</v>
       </c>
       <c r="B277" s="13" t="s">
@@ -16377,7 +16375,7 @@
       <c r="I277" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J277" s="22" t="s">
+      <c r="J277" s="21" t="s">
         <v>1061</v>
       </c>
       <c r="K277" s="17" t="s">
@@ -16388,7 +16386,7 @@
       </c>
     </row>
     <row r="278" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A278" s="21">
+      <c r="A278" s="12">
         <v>81</v>
       </c>
       <c r="B278" s="13"/>
@@ -16408,13 +16406,13 @@
       </c>
       <c r="I278" s="15"/>
       <c r="J278" s="16"/>
-      <c r="K278" s="22" t="s">
+      <c r="K278" s="21" t="s">
         <v>205</v>
       </c>
       <c r="L278" s="17"/>
     </row>
     <row r="279" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A279" s="21">
+      <c r="A279" s="12">
         <v>81.1</v>
       </c>
       <c r="B279" s="13" t="s">
@@ -16444,13 +16442,13 @@
       <c r="J279" s="16" t="s">
         <v>1068</v>
       </c>
-      <c r="K279" s="22" t="s">
+      <c r="K279" s="21" t="s">
         <v>205</v>
       </c>
       <c r="L279" s="17"/>
     </row>
     <row r="280" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A280" s="21">
+      <c r="A280" s="12">
         <v>81.2</v>
       </c>
       <c r="B280" s="13" t="s">
@@ -16480,13 +16478,13 @@
       <c r="J280" s="16" t="s">
         <v>884</v>
       </c>
-      <c r="K280" s="22" t="s">
+      <c r="K280" s="21" t="s">
         <v>205</v>
       </c>
       <c r="L280" s="17"/>
     </row>
     <row r="281" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A281" s="21">
+      <c r="A281" s="12">
         <v>81.3</v>
       </c>
       <c r="B281" s="13" t="s">
@@ -16516,13 +16514,13 @@
       <c r="J281" s="16" t="s">
         <v>1075</v>
       </c>
-      <c r="K281" s="22" t="s">
+      <c r="K281" s="21" t="s">
         <v>205</v>
       </c>
       <c r="L281" s="17"/>
     </row>
     <row r="282" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A282" s="21">
+      <c r="A282" s="12">
         <v>81.4</v>
       </c>
       <c r="B282" s="13" t="s">
@@ -16550,13 +16548,13 @@
       <c r="J282" s="16" t="s">
         <v>1078</v>
       </c>
-      <c r="K282" s="22" t="s">
+      <c r="K282" s="21" t="s">
         <v>205</v>
       </c>
       <c r="L282" s="17"/>
     </row>
     <row r="283" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A283" s="21">
+      <c r="A283" s="12">
         <v>82</v>
       </c>
       <c r="B283" s="13" t="s">
@@ -16581,7 +16579,7 @@
       <c r="I283" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="J283" s="22" t="s">
+      <c r="J283" s="21" t="s">
         <v>1082</v>
       </c>
       <c r="K283" s="17" t="s">
@@ -16590,7 +16588,7 @@
       <c r="L283" s="17"/>
     </row>
     <row r="284" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A284" s="21">
+      <c r="A284" s="12">
         <v>83</v>
       </c>
       <c r="B284" s="13" t="s">
@@ -16615,7 +16613,7 @@
       <c r="I284" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="J284" s="22" t="s">
+      <c r="J284" s="21" t="s">
         <v>1085</v>
       </c>
       <c r="K284" s="17" t="s">
@@ -16627,7 +16625,7 @@
       </c>
     </row>
     <row r="285" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A285" s="21">
+      <c r="A285" s="12">
         <v>83.1</v>
       </c>
       <c r="B285" s="13"/>
@@ -16646,7 +16644,7 @@
       <c r="I285" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="J285" s="22" t="s">
+      <c r="J285" s="21" t="s">
         <v>1089</v>
       </c>
       <c r="K285" s="17" t="s">
@@ -16657,7 +16655,7 @@
       </c>
     </row>
     <row r="286" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A286" s="21">
+      <c r="A286" s="12">
         <v>84</v>
       </c>
       <c r="B286" s="13"/>
@@ -16683,7 +16681,7 @@
       <c r="L286" s="17"/>
     </row>
     <row r="287" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A287" s="21">
+      <c r="A287" s="12">
         <v>84.1</v>
       </c>
       <c r="B287" s="13" t="s">
@@ -16721,7 +16719,7 @@
       </c>
     </row>
     <row r="288" s="11" customFormat="1" customHeight="1" spans="1:13">
-      <c r="A288" s="21">
+      <c r="A288" s="12">
         <v>84.2</v>
       </c>
       <c r="B288" s="13" t="s">
@@ -16759,7 +16757,7 @@
       </c>
     </row>
     <row r="289" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A289" s="21">
+      <c r="A289" s="12">
         <v>84.3</v>
       </c>
       <c r="B289" s="13" t="s">
@@ -16797,7 +16795,7 @@
       </c>
     </row>
     <row r="290" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A290" s="21">
+      <c r="A290" s="12">
         <v>85</v>
       </c>
       <c r="B290" s="13"/>
@@ -16825,7 +16823,7 @@
       </c>
     </row>
     <row r="291" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A291" s="21">
+      <c r="A291" s="12">
         <v>85.1</v>
       </c>
       <c r="B291" s="13" t="s">
@@ -16859,7 +16857,7 @@
       <c r="L291" s="17"/>
     </row>
     <row r="292" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A292" s="21">
+      <c r="A292" s="12">
         <v>85.2</v>
       </c>
       <c r="B292" s="13" t="s">
@@ -16893,7 +16891,7 @@
       <c r="L292" s="17"/>
     </row>
     <row r="293" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A293" s="21">
+      <c r="A293" s="12">
         <v>85.3</v>
       </c>
       <c r="B293" s="13" t="s">
@@ -16927,7 +16925,7 @@
       <c r="L293" s="17"/>
     </row>
     <row r="294" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A294" s="21">
+      <c r="A294" s="12">
         <v>85.4</v>
       </c>
       <c r="B294" s="13" t="s">
@@ -16961,7 +16959,7 @@
       <c r="L294" s="17"/>
     </row>
     <row r="295" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A295" s="21">
+      <c r="A295" s="12">
         <v>85.5</v>
       </c>
       <c r="B295" s="13" t="s">
@@ -16995,7 +16993,7 @@
       <c r="L295" s="17"/>
     </row>
     <row r="296" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A296" s="21">
+      <c r="A296" s="12">
         <v>85.6</v>
       </c>
       <c r="B296" s="13" t="s">
@@ -17029,7 +17027,7 @@
       <c r="L296" s="17"/>
     </row>
     <row r="297" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A297" s="21">
+      <c r="A297" s="12">
         <v>86</v>
       </c>
       <c r="B297" s="13"/>
@@ -17055,7 +17053,7 @@
       <c r="L297" s="17"/>
     </row>
     <row r="298" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A298" s="21">
+      <c r="A298" s="12">
         <v>86.1</v>
       </c>
       <c r="B298" s="13" t="s">
@@ -17091,7 +17089,7 @@
       </c>
     </row>
     <row r="299" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A299" s="21">
+      <c r="A299" s="12">
         <v>86.2</v>
       </c>
       <c r="B299" s="13" t="s">
@@ -17127,7 +17125,7 @@
       </c>
     </row>
     <row r="300" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A300" s="21">
+      <c r="A300" s="12">
         <v>86.3</v>
       </c>
       <c r="B300" s="13" t="s">
@@ -17165,7 +17163,7 @@
       </c>
     </row>
     <row r="301" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A301" s="21">
+      <c r="A301" s="12">
         <v>86.4</v>
       </c>
       <c r="B301" s="13" t="s">
@@ -17201,7 +17199,7 @@
       </c>
     </row>
     <row r="302" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A302" s="21">
+      <c r="A302" s="12">
         <v>86.5</v>
       </c>
       <c r="B302" s="13" t="s">
@@ -17237,7 +17235,7 @@
       </c>
     </row>
     <row r="303" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A303" s="21">
+      <c r="A303" s="12">
         <v>86.6</v>
       </c>
       <c r="B303" s="13" t="s">
@@ -17275,7 +17273,7 @@
       </c>
     </row>
     <row r="304" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A304" s="21">
+      <c r="A304" s="12">
         <v>87</v>
       </c>
       <c r="B304" s="13" t="s">
@@ -17300,7 +17298,7 @@
       <c r="I304" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="J304" s="22" t="s">
+      <c r="J304" s="21" t="s">
         <v>1147</v>
       </c>
       <c r="K304" s="17" t="s">
@@ -17311,7 +17309,7 @@
       </c>
     </row>
     <row r="305" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A305" s="21">
+      <c r="A305" s="12">
         <v>88</v>
       </c>
       <c r="B305" s="13"/>
@@ -17337,7 +17335,7 @@
       <c r="L305" s="17"/>
     </row>
     <row r="306" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A306" s="21">
+      <c r="A306" s="12">
         <v>88.1</v>
       </c>
       <c r="B306" s="13" t="s">
@@ -17375,7 +17373,7 @@
       </c>
     </row>
     <row r="307" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A307" s="21">
+      <c r="A307" s="12">
         <v>88.2</v>
       </c>
       <c r="B307" s="13" t="s">
@@ -17413,7 +17411,7 @@
       </c>
     </row>
     <row r="308" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A308" s="21">
+      <c r="A308" s="12">
         <v>88.3</v>
       </c>
       <c r="B308" s="13" t="s">
@@ -17451,7 +17449,7 @@
       </c>
     </row>
     <row r="309" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A309" s="21">
+      <c r="A309" s="12">
         <v>88.4</v>
       </c>
       <c r="B309" s="13" t="s">
@@ -17489,7 +17487,7 @@
       </c>
     </row>
     <row r="310" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A310" s="21">
+      <c r="A310" s="12">
         <v>88.5</v>
       </c>
       <c r="B310" s="13" t="s">
@@ -17527,7 +17525,7 @@
       </c>
     </row>
     <row r="311" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A311" s="21">
+      <c r="A311" s="12">
         <v>88.6</v>
       </c>
       <c r="B311" s="13" t="s">
@@ -17565,7 +17563,7 @@
       </c>
     </row>
     <row r="312" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A312" s="21">
+      <c r="A312" s="12">
         <v>89</v>
       </c>
       <c r="B312" s="13" t="s">
@@ -17590,7 +17588,7 @@
         <v>1174</v>
       </c>
       <c r="I312" s="15"/>
-      <c r="J312" s="22" t="s">
+      <c r="J312" s="21" t="s">
         <v>1175</v>
       </c>
       <c r="K312" s="17"/>
@@ -17599,7 +17597,7 @@
       </c>
     </row>
     <row r="313" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A313" s="21">
+      <c r="A313" s="12">
         <v>90</v>
       </c>
       <c r="B313" s="13" t="s">
@@ -17626,7 +17624,7 @@
       <c r="I313" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="J313" s="22" t="s">
+      <c r="J313" s="21" t="s">
         <v>1179</v>
       </c>
       <c r="K313" s="17" t="s">
@@ -17635,7 +17633,7 @@
       <c r="L313" s="17"/>
     </row>
     <row r="314" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A314" s="21">
+      <c r="A314" s="12">
         <v>91</v>
       </c>
       <c r="B314" s="13" t="s">
@@ -17660,7 +17658,7 @@
         <v>382</v>
       </c>
       <c r="I314" s="15"/>
-      <c r="J314" s="22" t="s">
+      <c r="J314" s="21" t="s">
         <v>1183</v>
       </c>
       <c r="K314" s="17" t="s">
@@ -17669,7 +17667,7 @@
       <c r="L314" s="17"/>
     </row>
     <row r="315" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A315" s="21">
+      <c r="A315" s="12">
         <v>92</v>
       </c>
       <c r="B315" s="13" t="s">
@@ -17703,7 +17701,7 @@
       <c r="L315" s="17"/>
     </row>
     <row r="316" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A316" s="21">
+      <c r="A316" s="12">
         <v>93</v>
       </c>
       <c r="B316" s="13" t="s">
@@ -17728,7 +17726,7 @@
         <v>715</v>
       </c>
       <c r="I316" s="15"/>
-      <c r="J316" s="22" t="s">
+      <c r="J316" s="21" t="s">
         <v>1192</v>
       </c>
       <c r="K316" s="17"/>
@@ -17737,7 +17735,7 @@
       </c>
     </row>
     <row r="317" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A317" s="21">
+      <c r="A317" s="12">
         <v>94</v>
       </c>
       <c r="B317" s="13" t="s">
@@ -17775,7 +17773,7 @@
       </c>
     </row>
     <row r="318" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A318" s="21">
+      <c r="A318" s="12">
         <v>95</v>
       </c>
       <c r="B318" s="13" t="s">
@@ -17811,7 +17809,7 @@
       <c r="L318" s="17"/>
     </row>
     <row r="319" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A319" s="21">
+      <c r="A319" s="12">
         <v>96</v>
       </c>
       <c r="B319" s="13" t="s">
@@ -17836,10 +17834,10 @@
         <v>1212</v>
       </c>
       <c r="I319" s="15"/>
-      <c r="J319" s="22" t="s">
+      <c r="J319" s="21" t="s">
         <v>1213</v>
       </c>
-      <c r="K319" s="22" t="s">
+      <c r="K319" s="21" t="s">
         <v>1214</v>
       </c>
       <c r="L319" s="17" t="s">
@@ -17847,7 +17845,7 @@
       </c>
     </row>
     <row r="320" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A320" s="21">
+      <c r="A320" s="12">
         <v>97</v>
       </c>
       <c r="B320" s="13" t="s">
@@ -17870,7 +17868,7 @@
         <v>470</v>
       </c>
       <c r="I320" s="15"/>
-      <c r="J320" s="22" t="s">
+      <c r="J320" s="21" t="s">
         <v>1219</v>
       </c>
       <c r="K320" s="17"/>
@@ -17879,7 +17877,7 @@
       </c>
     </row>
     <row r="321" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A321" s="21">
+      <c r="A321" s="12">
         <v>98</v>
       </c>
       <c r="B321" s="13" t="s">
@@ -17904,7 +17902,7 @@
         <v>191</v>
       </c>
       <c r="I321" s="15"/>
-      <c r="J321" s="22" t="s">
+      <c r="J321" s="21" t="s">
         <v>1224</v>
       </c>
       <c r="K321" s="17"/>
@@ -17913,7 +17911,7 @@
       </c>
     </row>
     <row r="322" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A322" s="21">
+      <c r="A322" s="12">
         <v>99</v>
       </c>
       <c r="B322" s="13"/>
@@ -17939,7 +17937,7 @@
       <c r="L322" s="17"/>
     </row>
     <row r="323" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A323" s="21">
+      <c r="A323" s="12">
         <v>99.1</v>
       </c>
       <c r="B323" s="13" t="s">
@@ -17977,7 +17975,7 @@
       </c>
     </row>
     <row r="324" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A324" s="21">
+      <c r="A324" s="12">
         <v>99.2</v>
       </c>
       <c r="B324" s="13" t="s">
@@ -18013,7 +18011,7 @@
       </c>
     </row>
     <row r="325" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A325" s="21">
+      <c r="A325" s="12">
         <v>99.3</v>
       </c>
       <c r="B325" s="13" t="s">
@@ -18049,7 +18047,7 @@
       </c>
     </row>
     <row r="326" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A326" s="21">
+      <c r="A326" s="12">
         <v>99.4</v>
       </c>
       <c r="B326" s="13" t="s">
@@ -18087,7 +18085,7 @@
       </c>
     </row>
     <row r="327" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A327" s="21">
+      <c r="A327" s="12">
         <v>99.5</v>
       </c>
       <c r="B327" s="13" t="s">
@@ -18121,7 +18119,7 @@
       </c>
     </row>
     <row r="328" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A328" s="21">
+      <c r="A328" s="12">
         <v>99.6</v>
       </c>
       <c r="B328" s="13" t="s">
@@ -18157,7 +18155,7 @@
       </c>
     </row>
     <row r="329" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A329" s="21">
+      <c r="A329" s="12">
         <v>100</v>
       </c>
       <c r="B329" s="13"/>
@@ -18183,7 +18181,7 @@
       <c r="L329" s="17"/>
     </row>
     <row r="330" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A330" s="21">
+      <c r="A330" s="12">
         <v>100.1</v>
       </c>
       <c r="B330" s="13" t="s">
@@ -18221,7 +18219,7 @@
       </c>
     </row>
     <row r="331" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A331" s="21">
+      <c r="A331" s="12">
         <v>100.2</v>
       </c>
       <c r="B331" s="13" t="s">
@@ -18259,7 +18257,7 @@
       </c>
     </row>
     <row r="332" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A332" s="21">
+      <c r="A332" s="12">
         <v>100.3</v>
       </c>
       <c r="B332" s="13" t="s">
@@ -18297,7 +18295,7 @@
       </c>
     </row>
     <row r="333" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A333" s="21">
+      <c r="A333" s="12">
         <v>100.4</v>
       </c>
       <c r="B333" s="13" t="s">
@@ -18335,7 +18333,7 @@
       </c>
     </row>
     <row r="334" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A334" s="21">
+      <c r="A334" s="12">
         <v>101</v>
       </c>
       <c r="B334" s="13" t="s">
@@ -18371,7 +18369,7 @@
       <c r="L334" s="17"/>
     </row>
     <row r="335" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A335" s="21">
+      <c r="A335" s="12">
         <v>102</v>
       </c>
       <c r="B335" s="13"/>
@@ -18397,7 +18395,7 @@
       <c r="L335" s="17"/>
     </row>
     <row r="336" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A336" s="21">
+      <c r="A336" s="12">
         <v>102.1</v>
       </c>
       <c r="B336" s="13" t="s">
@@ -18431,7 +18429,7 @@
       <c r="L336" s="17"/>
     </row>
     <row r="337" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A337" s="21">
+      <c r="A337" s="12">
         <v>102.2</v>
       </c>
       <c r="B337" s="13" t="s">
@@ -18465,7 +18463,7 @@
       <c r="L337" s="17"/>
     </row>
     <row r="338" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A338" s="21">
+      <c r="A338" s="12">
         <v>102.3</v>
       </c>
       <c r="B338" s="13" t="s">
@@ -18499,7 +18497,7 @@
       <c r="L338" s="17"/>
     </row>
     <row r="339" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A339" s="21">
+      <c r="A339" s="12">
         <v>102.4</v>
       </c>
       <c r="B339" s="13" t="s">
@@ -18533,7 +18531,7 @@
       <c r="L339" s="17"/>
     </row>
     <row r="340" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A340" s="21">
+      <c r="A340" s="12">
         <v>102.5</v>
       </c>
       <c r="B340" s="13" t="s">
@@ -18567,7 +18565,7 @@
       <c r="L340" s="17"/>
     </row>
     <row r="341" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A341" s="21">
+      <c r="A341" s="12">
         <v>102.6</v>
       </c>
       <c r="B341" s="13" t="s">
@@ -18601,7 +18599,7 @@
       <c r="L341" s="17"/>
     </row>
     <row r="342" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A342" s="21">
+      <c r="A342" s="12">
         <v>103</v>
       </c>
       <c r="B342" s="13" t="s">
@@ -18639,7 +18637,7 @@
       </c>
     </row>
     <row r="343" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A343" s="21">
+      <c r="A343" s="12">
         <v>104</v>
       </c>
       <c r="B343" s="13"/>
@@ -18663,7 +18661,7 @@
       <c r="L343" s="17"/>
     </row>
     <row r="344" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A344" s="21">
+      <c r="A344" s="12">
         <v>104.1</v>
       </c>
       <c r="B344" s="13"/>
@@ -18689,7 +18687,7 @@
       <c r="L344" s="17"/>
     </row>
     <row r="345" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A345" s="21">
+      <c r="A345" s="12">
         <v>104.11</v>
       </c>
       <c r="B345" s="13" t="s">
@@ -18723,7 +18721,7 @@
       <c r="L345" s="17"/>
     </row>
     <row r="346" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A346" s="21">
+      <c r="A346" s="12">
         <v>104.12</v>
       </c>
       <c r="B346" s="13" t="s">
@@ -18757,7 +18755,7 @@
       <c r="L346" s="17"/>
     </row>
     <row r="347" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A347" s="21">
+      <c r="A347" s="12">
         <v>104.2</v>
       </c>
       <c r="B347" s="13"/>
@@ -18783,7 +18781,7 @@
       <c r="L347" s="17"/>
     </row>
     <row r="348" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A348" s="21">
+      <c r="A348" s="12">
         <v>104.21</v>
       </c>
       <c r="B348" s="13" t="s">
@@ -18817,7 +18815,7 @@
       <c r="L348" s="17"/>
     </row>
     <row r="349" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A349" s="21">
+      <c r="A349" s="12">
         <v>104.22</v>
       </c>
       <c r="B349" s="13" t="s">
@@ -18851,7 +18849,7 @@
       <c r="L349" s="17"/>
     </row>
     <row r="350" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A350" s="21">
+      <c r="A350" s="12">
         <v>104.23</v>
       </c>
       <c r="B350" s="13" t="s">
@@ -18885,7 +18883,7 @@
       <c r="L350" s="17"/>
     </row>
     <row r="351" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A351" s="21">
+      <c r="A351" s="12">
         <v>104.3</v>
       </c>
       <c r="B351" s="13" t="s">
@@ -18919,7 +18917,7 @@
       <c r="L351" s="17"/>
     </row>
     <row r="352" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A352" s="21">
+      <c r="A352" s="12">
         <v>105</v>
       </c>
       <c r="B352" s="13" t="s">
@@ -18944,7 +18942,7 @@
       <c r="I352" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="J352" s="22" t="s">
+      <c r="J352" s="21" t="s">
         <v>1313</v>
       </c>
       <c r="K352" s="17" t="s">
@@ -18955,7 +18953,7 @@
       </c>
     </row>
     <row r="353" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A353" s="21">
+      <c r="A353" s="12">
         <v>106</v>
       </c>
       <c r="B353" s="13" t="s">
@@ -18980,7 +18978,7 @@
       <c r="I353" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="J353" s="22" t="s">
+      <c r="J353" s="21" t="s">
         <v>1317</v>
       </c>
       <c r="K353" s="17" t="s">
@@ -18991,7 +18989,7 @@
       </c>
     </row>
     <row r="354" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A354" s="21">
+      <c r="A354" s="12">
         <v>107</v>
       </c>
       <c r="B354" s="13" t="s">
@@ -19018,7 +19016,7 @@
       <c r="I354" s="15" t="s">
         <v>1322</v>
       </c>
-      <c r="J354" s="22" t="s">
+      <c r="J354" s="21" t="s">
         <v>1323</v>
       </c>
       <c r="K354" s="17" t="s">
@@ -19027,7 +19025,7 @@
       <c r="L354" s="17"/>
     </row>
     <row r="355" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A355" s="21">
+      <c r="A355" s="12">
         <v>108</v>
       </c>
       <c r="B355" s="13" t="s">
@@ -19045,25 +19043,25 @@
       <c r="F355" s="15">
         <v>1841</v>
       </c>
-      <c r="G355" s="24"/>
+      <c r="G355" s="23"/>
       <c r="H355" s="13" t="s">
         <v>1286</v>
       </c>
       <c r="I355" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="J355" s="22" t="s">
+      <c r="J355" s="21" t="s">
         <v>953</v>
       </c>
       <c r="K355" s="17" t="s">
         <v>1327</v>
       </c>
-      <c r="L355" s="25" t="s">
+      <c r="L355" s="24" t="s">
         <v>1328</v>
       </c>
     </row>
     <row r="356" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A356" s="21">
+      <c r="A356" s="12">
         <v>109</v>
       </c>
       <c r="B356" s="13" t="s">
@@ -19099,7 +19097,7 @@
       <c r="L356" s="17"/>
     </row>
     <row r="357" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A357" s="21">
+      <c r="A357" s="12">
         <v>110</v>
       </c>
       <c r="B357" s="13" t="s">
@@ -19117,14 +19115,14 @@
       <c r="F357" s="15">
         <v>1824</v>
       </c>
-      <c r="G357" s="24"/>
+      <c r="G357" s="23"/>
       <c r="H357" s="13" t="s">
         <v>1333</v>
       </c>
       <c r="I357" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="J357" s="22" t="s">
+      <c r="J357" s="21" t="s">
         <v>1334</v>
       </c>
       <c r="K357" s="17" t="s">
@@ -19133,7 +19131,7 @@
       <c r="L357" s="17"/>
     </row>
     <row r="358" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A358" s="21">
+      <c r="A358" s="12">
         <v>111</v>
       </c>
       <c r="B358" s="13" t="s">
@@ -19166,7 +19164,7 @@
       </c>
     </row>
     <row r="359" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A359" s="21">
+      <c r="A359" s="12">
         <v>112</v>
       </c>
       <c r="B359" s="13"/>
@@ -19192,7 +19190,7 @@
       <c r="L359" s="17"/>
     </row>
     <row r="360" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A360" s="21">
+      <c r="A360" s="12">
         <v>112.1</v>
       </c>
       <c r="B360" s="13"/>
@@ -19222,7 +19220,7 @@
       <c r="L360" s="17"/>
     </row>
     <row r="361" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A361" s="21">
+      <c r="A361" s="12">
         <v>112.2</v>
       </c>
       <c r="B361" s="13"/>
@@ -19252,7 +19250,7 @@
       </c>
     </row>
     <row r="362" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A362" s="21">
+      <c r="A362" s="12">
         <v>113</v>
       </c>
       <c r="B362" s="13" t="s">
@@ -19277,7 +19275,7 @@
       <c r="I362" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="J362" s="22" t="s">
+      <c r="J362" s="21" t="s">
         <v>1353</v>
       </c>
       <c r="K362" s="17" t="s">
@@ -19286,7 +19284,7 @@
       <c r="L362" s="17"/>
     </row>
     <row r="363" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A363" s="21">
+      <c r="A363" s="12">
         <v>114</v>
       </c>
       <c r="B363" s="13" t="s">
@@ -19311,7 +19309,7 @@
       <c r="I363" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="J363" s="22" t="s">
+      <c r="J363" s="21" t="s">
         <v>1358</v>
       </c>
       <c r="K363" s="17" t="s">
@@ -19320,7 +19318,7 @@
       <c r="L363" s="17"/>
     </row>
     <row r="364" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A364" s="21">
+      <c r="A364" s="12">
         <v>115</v>
       </c>
       <c r="B364" s="13"/>
@@ -19344,7 +19342,7 @@
       <c r="L364" s="17"/>
     </row>
     <row r="365" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A365" s="21">
+      <c r="A365" s="12">
         <v>115.1</v>
       </c>
       <c r="B365" s="13" t="s">
@@ -19378,7 +19376,7 @@
       <c r="L365" s="17"/>
     </row>
     <row r="366" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A366" s="21">
+      <c r="A366" s="12">
         <v>115.2</v>
       </c>
       <c r="B366" s="13" t="s">
@@ -19412,7 +19410,7 @@
       <c r="L366" s="17"/>
     </row>
     <row r="367" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A367" s="21">
+      <c r="A367" s="12">
         <v>116</v>
       </c>
       <c r="B367" s="13" t="s">
@@ -19448,7 +19446,7 @@
       <c r="L367" s="17"/>
     </row>
     <row r="368" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A368" s="21">
+      <c r="A368" s="12">
         <v>117</v>
       </c>
       <c r="B368" s="13" t="s">
@@ -19484,7 +19482,7 @@
       <c r="L368" s="17"/>
     </row>
     <row r="369" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A369" s="21">
+      <c r="A369" s="12">
         <v>118</v>
       </c>
       <c r="B369" s="13" t="s">
@@ -19511,7 +19509,7 @@
       <c r="I369" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="J369" s="22" t="s">
+      <c r="J369" s="21" t="s">
         <v>1377</v>
       </c>
       <c r="K369" s="17" t="s">
@@ -19520,7 +19518,7 @@
       <c r="L369" s="17"/>
     </row>
     <row r="370" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A370" s="21">
+      <c r="A370" s="12">
         <v>119</v>
       </c>
       <c r="B370" s="13" t="s">
@@ -19552,7 +19550,7 @@
       <c r="L370" s="17"/>
     </row>
     <row r="371" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A371" s="21">
+      <c r="A371" s="12">
         <v>120</v>
       </c>
       <c r="B371" s="13"/>
@@ -19578,7 +19576,7 @@
       <c r="L371" s="17"/>
     </row>
     <row r="372" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A372" s="21">
+      <c r="A372" s="12">
         <v>120.1</v>
       </c>
       <c r="B372" s="13" t="s">
@@ -19614,7 +19612,7 @@
       <c r="L372" s="17"/>
     </row>
     <row r="373" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A373" s="21">
+      <c r="A373" s="12">
         <v>120.2</v>
       </c>
       <c r="B373" s="13" t="s">
@@ -19650,7 +19648,7 @@
       <c r="L373" s="17"/>
     </row>
     <row r="374" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A374" s="21">
+      <c r="A374" s="12">
         <v>120.3</v>
       </c>
       <c r="B374" s="13" t="s">
@@ -19684,7 +19682,7 @@
       <c r="L374" s="17"/>
     </row>
     <row r="375" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A375" s="21">
+      <c r="A375" s="12">
         <v>120.4</v>
       </c>
       <c r="B375" s="13" t="s">
@@ -19718,7 +19716,7 @@
       <c r="L375" s="17"/>
     </row>
     <row r="376" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A376" s="21">
+      <c r="A376" s="12">
         <v>121</v>
       </c>
       <c r="B376" s="13" t="s">
@@ -19741,7 +19739,7 @@
       </c>
       <c r="H376" s="13"/>
       <c r="I376" s="15"/>
-      <c r="J376" s="22" t="s">
+      <c r="J376" s="21" t="s">
         <v>1399</v>
       </c>
       <c r="K376" s="17" t="s">
@@ -19752,7 +19750,7 @@
       </c>
     </row>
     <row r="377" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A377" s="21">
+      <c r="A377" s="12">
         <v>999.01</v>
       </c>
       <c r="B377" s="13" t="s">
@@ -19788,7 +19786,7 @@
       </c>
     </row>
     <row r="378" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A378" s="21">
+      <c r="A378" s="12">
         <v>999.02</v>
       </c>
       <c r="B378" s="13" t="s">
@@ -19824,7 +19822,7 @@
       </c>
     </row>
     <row r="379" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A379" s="21">
+      <c r="A379" s="12">
         <v>999.03</v>
       </c>
       <c r="B379" s="13" t="s">
@@ -19860,7 +19858,7 @@
       </c>
     </row>
     <row r="380" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A380" s="21">
+      <c r="A380" s="12">
         <v>999.04</v>
       </c>
       <c r="B380" s="13"/>
@@ -19878,7 +19876,7 @@
       <c r="L380" s="17"/>
     </row>
     <row r="381" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A381" s="21">
+      <c r="A381" s="12">
         <v>999.05</v>
       </c>
       <c r="B381" s="13" t="s">
@@ -19899,7 +19897,7 @@
       <c r="I381" s="15"/>
     </row>
     <row r="382" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A382" s="21">
+      <c r="A382" s="12">
         <v>999.06</v>
       </c>
       <c r="B382" s="13" t="s">
@@ -19923,7 +19921,7 @@
       <c r="L382" s="17"/>
     </row>
     <row r="383" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A383" s="21">
+      <c r="A383" s="12">
         <v>999.07</v>
       </c>
       <c r="B383" s="13" t="s">
@@ -19947,7 +19945,7 @@
       <c r="L383" s="17"/>
     </row>
     <row r="384" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A384" s="21">
+      <c r="A384" s="12">
         <v>999.08</v>
       </c>
       <c r="B384" s="13" t="s">
@@ -19968,7 +19966,7 @@
       <c r="I384" s="15"/>
     </row>
     <row r="385" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A385" s="21">
+      <c r="A385" s="12">
         <v>999.09</v>
       </c>
       <c r="B385" s="13" t="s">
@@ -19989,7 +19987,7 @@
       <c r="I385" s="15"/>
     </row>
     <row r="386" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A386" s="21">
+      <c r="A386" s="12">
         <v>999.1</v>
       </c>
       <c r="B386" s="13" t="s">
@@ -20013,7 +20011,7 @@
       <c r="L386" s="17"/>
     </row>
     <row r="387" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A387" s="21">
+      <c r="A387" s="12">
         <v>999.11</v>
       </c>
       <c r="B387" s="13"/>
@@ -20028,7 +20026,7 @@
       <c r="I387" s="15"/>
     </row>
     <row r="388" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A388" s="21">
+      <c r="A388" s="12">
         <v>999.12</v>
       </c>
       <c r="B388" s="13" t="s">
@@ -20049,7 +20047,7 @@
       <c r="I388" s="15"/>
     </row>
     <row r="389" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A389" s="21">
+      <c r="A389" s="12">
         <v>999.13</v>
       </c>
       <c r="B389" s="13" t="s">
@@ -20070,7 +20068,7 @@
       <c r="I389" s="15"/>
     </row>
     <row r="390" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A390" s="21">
+      <c r="A390" s="12">
         <v>999.14</v>
       </c>
       <c r="B390" s="13" t="s">
@@ -20096,7 +20094,7 @@
       </c>
     </row>
     <row r="391" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A391" s="21">
+      <c r="A391" s="12">
         <v>999.15</v>
       </c>
       <c r="B391" s="13" t="s">
@@ -20120,7 +20118,7 @@
       <c r="L391" s="17"/>
     </row>
     <row r="392" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A392" s="21">
+      <c r="A392" s="12">
         <v>999.16</v>
       </c>
       <c r="B392" s="13" t="s">
@@ -20141,7 +20139,7 @@
       <c r="I392" s="15"/>
     </row>
     <row r="393" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A393" s="21">
+      <c r="A393" s="12">
         <v>999.17</v>
       </c>
       <c r="B393" s="13"/>
@@ -20156,7 +20154,7 @@
       <c r="I393" s="15"/>
     </row>
     <row r="394" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A394" s="21">
+      <c r="A394" s="12">
         <v>999.18</v>
       </c>
       <c r="B394" s="13"/>
@@ -20171,12 +20169,12 @@
       <c r="I394" s="15"/>
     </row>
     <row r="395" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A395" s="21">
+      <c r="A395" s="12">
         <v>999.19</v>
       </c>
       <c r="B395" s="11"/>
       <c r="C395" s="13"/>
-      <c r="D395" s="26"/>
+      <c r="D395" s="25"/>
       <c r="E395" s="13" t="s">
         <v>1441</v>
       </c>
@@ -20188,7 +20186,7 @@
       <c r="I395" s="15"/>
     </row>
     <row r="396" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A396" s="21">
+      <c r="A396" s="12">
         <v>999.191</v>
       </c>
       <c r="B396" s="13" t="s">
@@ -20214,7 +20212,7 @@
       </c>
     </row>
     <row r="397" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A397" s="21">
+      <c r="A397" s="12">
         <v>999.192</v>
       </c>
       <c r="B397" s="13" t="s">
@@ -20240,7 +20238,7 @@
       </c>
     </row>
     <row r="398" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A398" s="21">
+      <c r="A398" s="12">
         <v>999.2</v>
       </c>
       <c r="B398" s="13" t="s">
@@ -20261,7 +20259,7 @@
       <c r="I398" s="15"/>
     </row>
     <row r="399" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A399" s="21">
+      <c r="A399" s="12">
         <v>999.21</v>
       </c>
       <c r="B399" s="13" t="s">
@@ -20282,7 +20280,7 @@
       <c r="I399" s="15"/>
     </row>
     <row r="400" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A400" s="21">
+      <c r="A400" s="12">
         <v>999.22</v>
       </c>
       <c r="B400" s="13" t="s">
@@ -20303,7 +20301,7 @@
       <c r="I400" s="15"/>
     </row>
     <row r="401" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A401" s="21">
+      <c r="A401" s="12">
         <v>999.23</v>
       </c>
       <c r="B401" s="13" t="s">
@@ -20324,7 +20322,7 @@
       <c r="I401" s="15"/>
     </row>
     <row r="402" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A402" s="21">
+      <c r="A402" s="12">
         <v>999.24</v>
       </c>
       <c r="B402" s="13" t="s">
@@ -20349,7 +20347,7 @@
       <c r="I402" s="15"/>
     </row>
     <row r="403" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A403" s="21">
+      <c r="A403" s="12">
         <v>999.25</v>
       </c>
       <c r="B403" s="13" t="s">
@@ -20381,7 +20379,7 @@
       </c>
     </row>
     <row r="404" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A404" s="21">
+      <c r="A404" s="12">
         <v>999.26</v>
       </c>
       <c r="B404" s="13"/>
@@ -20402,7 +20400,7 @@
       </c>
     </row>
     <row r="405" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A405" s="21">
+      <c r="A405" s="12">
         <v>999.27</v>
       </c>
       <c r="B405" s="13" t="s">
@@ -20429,7 +20427,7 @@
       </c>
     </row>
     <row r="406" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A406" s="21">
+      <c r="A406" s="12">
         <v>999.27</v>
       </c>
       <c r="B406" s="13" t="s">
@@ -20454,7 +20452,7 @@
       <c r="I406" s="15"/>
     </row>
     <row r="407" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A407" s="21">
+      <c r="A407" s="12">
         <v>999.28</v>
       </c>
       <c r="B407" s="13" t="s">
@@ -20486,7 +20484,7 @@
       <c r="L407" s="17"/>
     </row>
     <row r="408" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A408" s="21">
+      <c r="A408" s="12">
         <v>999.29</v>
       </c>
       <c r="B408" s="13" t="s">
@@ -20511,7 +20509,7 @@
       <c r="I408" s="15"/>
     </row>
     <row r="409" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A409" s="21" t="s">
+      <c r="A409" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B409" s="13" t="s">
@@ -20539,7 +20537,7 @@
       <c r="L409" s="17"/>
     </row>
     <row r="410" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A410" s="21" t="s">
+      <c r="A410" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B410" s="13" t="s">
@@ -20549,7 +20547,7 @@
         <v>195</v>
       </c>
       <c r="D410" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E410" s="13"/>
       <c r="F410" s="13"/>
@@ -20558,7 +20556,7 @@
         <v>198</v>
       </c>
       <c r="I410" s="15" t="s">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="J410" s="16"/>
       <c r="K410" s="17" t="s">
@@ -20567,7 +20565,7 @@
       <c r="L410" s="17"/>
     </row>
     <row r="411" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A411" s="21" t="s">
+      <c r="A411" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B411" s="13" t="s">
@@ -20577,7 +20575,7 @@
         <v>195</v>
       </c>
       <c r="D411" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E411" s="13"/>
       <c r="F411" s="13"/>
@@ -20586,7 +20584,7 @@
         <v>198</v>
       </c>
       <c r="I411" s="15" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
       <c r="J411" s="16"/>
       <c r="K411" s="17" t="s">
@@ -20595,7 +20593,7 @@
       <c r="L411" s="17"/>
     </row>
     <row r="412" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A412" s="21" t="s">
+      <c r="A412" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B412" s="13" t="s">
@@ -20605,7 +20603,7 @@
         <v>195</v>
       </c>
       <c r="D412" s="14">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E412" s="13"/>
       <c r="F412" s="13"/>
@@ -20614,7 +20612,7 @@
         <v>198</v>
       </c>
       <c r="I412" s="15" t="s">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="J412" s="16"/>
       <c r="K412" s="17" t="s">
@@ -20623,17 +20621,17 @@
       <c r="L412" s="17"/>
     </row>
     <row r="413" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A413" s="21" t="s">
+      <c r="A413" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B413" s="13" t="s">
-        <v>194</v>
+        <v>1485</v>
       </c>
       <c r="C413" s="13" t="s">
         <v>195</v>
       </c>
       <c r="D413" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E413" s="13"/>
       <c r="F413" s="13"/>
@@ -20642,7 +20640,7 @@
         <v>198</v>
       </c>
       <c r="I413" s="15" t="s">
-        <v>15</v>
+        <v>463</v>
       </c>
       <c r="J413" s="16"/>
       <c r="K413" s="17" t="s">
@@ -20651,17 +20649,17 @@
       <c r="L413" s="17"/>
     </row>
     <row r="414" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A414" s="21" t="s">
+      <c r="A414" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B414" s="13" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C414" s="13" t="s">
         <v>195</v>
       </c>
       <c r="D414" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E414" s="13"/>
       <c r="F414" s="13"/>
@@ -20670,7 +20668,7 @@
         <v>198</v>
       </c>
       <c r="I414" s="15" t="s">
-        <v>63</v>
+        <v>126</v>
       </c>
       <c r="J414" s="16"/>
       <c r="K414" s="17" t="s">
@@ -20679,17 +20677,17 @@
       <c r="L414" s="17"/>
     </row>
     <row r="415" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A415" s="21" t="s">
+      <c r="A415" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B415" s="13" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C415" s="13" t="s">
         <v>195</v>
       </c>
       <c r="D415" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E415" s="13"/>
       <c r="F415" s="13"/>
@@ -20698,7 +20696,7 @@
         <v>198</v>
       </c>
       <c r="I415" s="15" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="J415" s="16"/>
       <c r="K415" s="17" t="s">
@@ -20707,17 +20705,17 @@
       <c r="L415" s="17"/>
     </row>
     <row r="416" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A416" s="21" t="s">
+      <c r="A416" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B416" s="13" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="C416" s="13" t="s">
         <v>195</v>
       </c>
       <c r="D416" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E416" s="13"/>
       <c r="F416" s="13"/>
@@ -20726,7 +20724,7 @@
         <v>198</v>
       </c>
       <c r="I416" s="15" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="J416" s="16"/>
       <c r="K416" s="17" t="s">
@@ -20735,17 +20733,17 @@
       <c r="L416" s="17"/>
     </row>
     <row r="417" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A417" s="21" t="s">
+      <c r="A417" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B417" s="13" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="C417" s="13" t="s">
         <v>195</v>
       </c>
       <c r="D417" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E417" s="13"/>
       <c r="F417" s="13"/>
@@ -20754,7 +20752,7 @@
         <v>198</v>
       </c>
       <c r="I417" s="15" t="s">
-        <v>463</v>
+        <v>331</v>
       </c>
       <c r="J417" s="16"/>
       <c r="K417" s="17" t="s">
@@ -20763,17 +20761,17 @@
       <c r="L417" s="17"/>
     </row>
     <row r="418" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A418" s="21" t="s">
+      <c r="A418" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B418" s="13" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C418" s="13" t="s">
         <v>195</v>
       </c>
       <c r="D418" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E418" s="13"/>
       <c r="F418" s="13"/>
@@ -20782,7 +20780,7 @@
         <v>198</v>
       </c>
       <c r="I418" s="15" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J418" s="16"/>
       <c r="K418" s="17" t="s">
@@ -20791,17 +20789,17 @@
       <c r="L418" s="17"/>
     </row>
     <row r="419" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A419" s="21" t="s">
+      <c r="A419" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B419" s="13" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C419" s="13" t="s">
         <v>195</v>
       </c>
       <c r="D419" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E419" s="13"/>
       <c r="F419" s="13"/>
@@ -20810,7 +20808,7 @@
         <v>198</v>
       </c>
       <c r="I419" s="15" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="J419" s="16"/>
       <c r="K419" s="17" t="s">
@@ -20819,17 +20817,17 @@
       <c r="L419" s="17"/>
     </row>
     <row r="420" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A420" s="21" t="s">
+      <c r="A420" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B420" s="13" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="C420" s="13" t="s">
         <v>195</v>
       </c>
       <c r="D420" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E420" s="13"/>
       <c r="F420" s="13"/>
@@ -20838,7 +20836,7 @@
         <v>198</v>
       </c>
       <c r="I420" s="15" t="s">
-        <v>63</v>
+        <v>122</v>
       </c>
       <c r="J420" s="16"/>
       <c r="K420" s="17" t="s">
@@ -20847,17 +20845,17 @@
       <c r="L420" s="17"/>
     </row>
     <row r="421" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A421" s="21" t="s">
+      <c r="A421" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B421" s="13" t="s">
-        <v>1492</v>
+        <v>194</v>
       </c>
       <c r="C421" s="13" t="s">
         <v>195</v>
       </c>
       <c r="D421" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E421" s="13"/>
       <c r="F421" s="13"/>
@@ -20866,7 +20864,7 @@
         <v>198</v>
       </c>
       <c r="I421" s="15" t="s">
-        <v>331</v>
+        <v>15</v>
       </c>
       <c r="J421" s="16"/>
       <c r="K421" s="17" t="s">
@@ -20875,7 +20873,7 @@
       <c r="L421" s="17"/>
     </row>
     <row r="422" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A422" s="21" t="s">
+      <c r="A422" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B422" s="13" t="s">
@@ -20903,7 +20901,7 @@
       <c r="L422" s="17"/>
     </row>
     <row r="423" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A423" s="21" t="s">
+      <c r="A423" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B423" s="13"/>
@@ -20925,7 +20923,7 @@
       <c r="L423" s="17"/>
     </row>
     <row r="424" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A424" s="21" t="s">
+      <c r="A424" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B424" s="13"/>
@@ -20947,7 +20945,7 @@
       <c r="L424" s="17"/>
     </row>
     <row r="425" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A425" s="21" t="s">
+      <c r="A425" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B425" s="13"/>
@@ -20969,7 +20967,7 @@
       <c r="L425" s="17"/>
     </row>
     <row r="426" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A426" s="21" t="s">
+      <c r="A426" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B426" s="13"/>
@@ -20991,7 +20989,7 @@
       <c r="L426" s="17"/>
     </row>
     <row r="427" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A427" s="21" t="s">
+      <c r="A427" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B427" s="13"/>
@@ -21013,7 +21011,7 @@
       <c r="L427" s="17"/>
     </row>
     <row r="428" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A428" s="21" t="s">
+      <c r="A428" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B428" s="13"/>
@@ -21035,7 +21033,7 @@
       <c r="L428" s="17"/>
     </row>
     <row r="429" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A429" s="21" t="s">
+      <c r="A429" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B429" s="13"/>
@@ -21057,7 +21055,7 @@
       <c r="L429" s="17"/>
     </row>
     <row r="430" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A430" s="21" t="s">
+      <c r="A430" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B430" s="13"/>
@@ -21079,7 +21077,7 @@
       <c r="L430" s="17"/>
     </row>
     <row r="431" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A431" s="21" t="s">
+      <c r="A431" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B431" s="13"/>
@@ -21101,7 +21099,7 @@
       <c r="L431" s="17"/>
     </row>
     <row r="432" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A432" s="21" t="s">
+      <c r="A432" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B432" s="13"/>
@@ -21123,7 +21121,7 @@
       <c r="L432" s="17"/>
     </row>
     <row r="433" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A433" s="21" t="s">
+      <c r="A433" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B433" s="13"/>
@@ -21145,7 +21143,7 @@
       <c r="L433" s="17"/>
     </row>
     <row r="434" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A434" s="21" t="s">
+      <c r="A434" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B434" s="13"/>
@@ -21167,7 +21165,7 @@
       <c r="L434" s="17"/>
     </row>
     <row r="435" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A435" s="21" t="s">
+      <c r="A435" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B435" s="13"/>
@@ -21189,7 +21187,7 @@
       <c r="L435" s="17"/>
     </row>
     <row r="436" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A436" s="21" t="s">
+      <c r="A436" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B436" s="13"/>
@@ -21211,7 +21209,7 @@
       <c r="L436" s="17"/>
     </row>
     <row r="437" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A437" s="21" t="s">
+      <c r="A437" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B437" s="13"/>
@@ -21233,7 +21231,7 @@
       <c r="L437" s="17"/>
     </row>
     <row r="438" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A438" s="21" t="s">
+      <c r="A438" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B438" s="13"/>
@@ -21255,7 +21253,7 @@
       <c r="L438" s="17"/>
     </row>
     <row r="439" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A439" s="21" t="s">
+      <c r="A439" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B439" s="13"/>
@@ -21277,7 +21275,7 @@
       <c r="L439" s="17"/>
     </row>
     <row r="440" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A440" s="21" t="s">
+      <c r="A440" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B440" s="13"/>
@@ -21299,7 +21297,7 @@
       <c r="L440" s="17"/>
     </row>
     <row r="441" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A441" s="21" t="s">
+      <c r="A441" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B441" s="13"/>
@@ -21319,7 +21317,7 @@
       <c r="L441" s="17"/>
     </row>
     <row r="442" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A442" s="21" t="s">
+      <c r="A442" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B442" s="13"/>
@@ -21341,7 +21339,7 @@
       <c r="L442" s="17"/>
     </row>
     <row r="443" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A443" s="21" t="s">
+      <c r="A443" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B443" s="13"/>
@@ -21363,7 +21361,7 @@
       <c r="L443" s="17"/>
     </row>
     <row r="444" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A444" s="21" t="s">
+      <c r="A444" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B444" s="13"/>
@@ -21385,7 +21383,7 @@
       <c r="L444" s="17"/>
     </row>
     <row r="445" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A445" s="21" t="s">
+      <c r="A445" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B445" s="13"/>
@@ -21407,7 +21405,7 @@
       <c r="L445" s="17"/>
     </row>
     <row r="446" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A446" s="21" t="s">
+      <c r="A446" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B446" s="13"/>
@@ -21429,7 +21427,7 @@
       <c r="L446" s="17"/>
     </row>
     <row r="447" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A447" s="21" t="s">
+      <c r="A447" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B447" s="13"/>
@@ -21451,7 +21449,7 @@
       <c r="L447" s="17"/>
     </row>
     <row r="448" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A448" s="21" t="s">
+      <c r="A448" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B448" s="13"/>
@@ -21475,7 +21473,7 @@
       <c r="L448" s="17"/>
     </row>
     <row r="449" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A449" s="21" t="s">
+      <c r="A449" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B449" s="13"/>
@@ -21499,7 +21497,7 @@
       <c r="L449" s="17"/>
     </row>
     <row r="450" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A450" s="21" t="s">
+      <c r="A450" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B450" s="13"/>
@@ -21523,7 +21521,7 @@
       <c r="L450" s="17"/>
     </row>
     <row r="451" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A451" s="21" t="s">
+      <c r="A451" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B451" s="13"/>
@@ -21547,7 +21545,7 @@
       <c r="L451" s="17"/>
     </row>
     <row r="452" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A452" s="21" t="s">
+      <c r="A452" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B452" s="13"/>
@@ -21571,7 +21569,7 @@
       <c r="L452" s="17"/>
     </row>
     <row r="453" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A453" s="21" t="s">
+      <c r="A453" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B453" s="13"/>
@@ -21593,7 +21591,7 @@
       <c r="L453" s="17"/>
     </row>
     <row r="454" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A454" s="21" t="s">
+      <c r="A454" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B454" s="13"/>
@@ -21615,7 +21613,7 @@
       <c r="L454" s="17"/>
     </row>
     <row r="455" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A455" s="21" t="s">
+      <c r="A455" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B455" s="13"/>
@@ -21637,7 +21635,7 @@
       <c r="L455" s="17"/>
     </row>
     <row r="456" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A456" s="21" t="s">
+      <c r="A456" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B456" s="13"/>
@@ -21659,7 +21657,7 @@
       <c r="L456" s="17"/>
     </row>
     <row r="457" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A457" s="21" t="s">
+      <c r="A457" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B457" s="13"/>
@@ -21683,7 +21681,7 @@
       <c r="L457" s="17"/>
     </row>
     <row r="458" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A458" s="21" t="s">
+      <c r="A458" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B458" s="13"/>
@@ -21705,7 +21703,7 @@
       <c r="L458" s="17"/>
     </row>
     <row r="459" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A459" s="21" t="s">
+      <c r="A459" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B459" s="13"/>
@@ -21727,7 +21725,7 @@
       <c r="L459" s="17"/>
     </row>
     <row r="460" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A460" s="21" t="s">
+      <c r="A460" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B460" s="13"/>
@@ -21749,7 +21747,7 @@
       <c r="L460" s="17"/>
     </row>
     <row r="461" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A461" s="21" t="s">
+      <c r="A461" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B461" s="13"/>
@@ -21771,7 +21769,7 @@
       <c r="L461" s="17"/>
     </row>
     <row r="462" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A462" s="21" t="s">
+      <c r="A462" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B462" s="13"/>
@@ -21791,7 +21789,7 @@
       <c r="L462" s="17"/>
     </row>
     <row r="463" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A463" s="21" t="s">
+      <c r="A463" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B463" s="13"/>
@@ -21813,7 +21811,7 @@
       <c r="L463" s="17"/>
     </row>
     <row r="464" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A464" s="21" t="s">
+      <c r="A464" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B464" s="13"/>
@@ -21835,7 +21833,7 @@
       <c r="L464" s="17"/>
     </row>
     <row r="465" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A465" s="21" t="s">
+      <c r="A465" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B465" s="13"/>
@@ -21857,7 +21855,7 @@
       <c r="L465" s="17"/>
     </row>
     <row r="466" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A466" s="21" t="s">
+      <c r="A466" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B466" s="13"/>
@@ -21879,7 +21877,7 @@
       <c r="L466" s="17"/>
     </row>
     <row r="467" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A467" s="21" t="s">
+      <c r="A467" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B467" s="13"/>
@@ -21901,7 +21899,7 @@
       <c r="L467" s="17"/>
     </row>
     <row r="468" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A468" s="21" t="s">
+      <c r="A468" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B468" s="13"/>
@@ -21923,7 +21921,7 @@
       <c r="L468" s="17"/>
     </row>
     <row r="469" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A469" s="21" t="s">
+      <c r="A469" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B469" s="13"/>
@@ -21945,7 +21943,7 @@
       <c r="L469" s="17"/>
     </row>
     <row r="470" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A470" s="21" t="s">
+      <c r="A470" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B470" s="13"/>
@@ -21967,7 +21965,7 @@
       <c r="L470" s="17"/>
     </row>
     <row r="471" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A471" s="21" t="s">
+      <c r="A471" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B471" s="13"/>
@@ -21989,7 +21987,7 @@
       <c r="L471" s="17"/>
     </row>
     <row r="472" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A472" s="21" t="s">
+      <c r="A472" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B472" s="13"/>
@@ -22011,7 +22009,7 @@
       <c r="L472" s="17"/>
     </row>
     <row r="473" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A473" s="21" t="s">
+      <c r="A473" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B473" s="13"/>
@@ -22033,7 +22031,7 @@
       <c r="L473" s="17"/>
     </row>
     <row r="474" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A474" s="21" t="s">
+      <c r="A474" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B474" s="13"/>
@@ -22055,7 +22053,7 @@
       <c r="L474" s="17"/>
     </row>
     <row r="475" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A475" s="21" t="s">
+      <c r="A475" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B475" s="13"/>
@@ -22077,7 +22075,7 @@
       <c r="L475" s="17"/>
     </row>
     <row r="476" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A476" s="21" t="s">
+      <c r="A476" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B476" s="13"/>
@@ -22099,7 +22097,7 @@
       <c r="L476" s="17"/>
     </row>
     <row r="477" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A477" s="21" t="s">
+      <c r="A477" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B477" s="13"/>
@@ -22121,7 +22119,7 @@
       <c r="L477" s="17"/>
     </row>
     <row r="478" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A478" s="21" t="s">
+      <c r="A478" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B478" s="13"/>
@@ -22143,7 +22141,7 @@
       <c r="L478" s="17"/>
     </row>
     <row r="479" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A479" s="21" t="s">
+      <c r="A479" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B479" s="13"/>
@@ -22165,7 +22163,7 @@
       <c r="L479" s="17"/>
     </row>
     <row r="480" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A480" s="21" t="s">
+      <c r="A480" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B480" s="13"/>
@@ -22185,7 +22183,7 @@
       <c r="L480" s="17"/>
     </row>
     <row r="481" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A481" s="21" t="s">
+      <c r="A481" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B481" s="13"/>
@@ -22207,7 +22205,7 @@
       <c r="L481" s="17"/>
     </row>
     <row r="482" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A482" s="21" t="s">
+      <c r="A482" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B482" s="13"/>
@@ -22229,7 +22227,7 @@
       <c r="L482" s="17"/>
     </row>
     <row r="483" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A483" s="21" t="s">
+      <c r="A483" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B483" s="13"/>
@@ -22251,7 +22249,7 @@
       <c r="L483" s="17"/>
     </row>
     <row r="484" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A484" s="21" t="s">
+      <c r="A484" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B484" s="13"/>
@@ -22273,7 +22271,7 @@
       <c r="L484" s="17"/>
     </row>
     <row r="485" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A485" s="21" t="s">
+      <c r="A485" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B485" s="13"/>
@@ -22295,7 +22293,7 @@
       <c r="L485" s="17"/>
     </row>
     <row r="486" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A486" s="21" t="s">
+      <c r="A486" s="12" t="s">
         <v>1479</v>
       </c>
       <c r="B486" s="13"/>
@@ -22317,7 +22315,7 @@
       <c r="L486" s="17"/>
     </row>
     <row r="487" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A487" s="21"/>
+      <c r="A487" s="12"/>
       <c r="B487" s="13" t="s">
         <v>1522</v>
       </c>
@@ -22341,7 +22339,7 @@
       <c r="L487" s="17"/>
     </row>
     <row r="488" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A488" s="21"/>
+      <c r="A488" s="12"/>
       <c r="B488" s="13" t="s">
         <v>1524</v>
       </c>
@@ -22365,7 +22363,7 @@
       <c r="L488" s="17"/>
     </row>
     <row r="489" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A489" s="21"/>
+      <c r="A489" s="12"/>
       <c r="B489" s="13" t="s">
         <v>1527</v>
       </c>
@@ -22389,7 +22387,7 @@
       <c r="L489" s="17"/>
     </row>
     <row r="490" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A490" s="21"/>
+      <c r="A490" s="12"/>
       <c r="B490" s="13" t="s">
         <v>1530</v>
       </c>
@@ -22413,7 +22411,7 @@
       <c r="L490" s="17"/>
     </row>
     <row r="491" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A491" s="21"/>
+      <c r="A491" s="12"/>
       <c r="B491" s="13" t="s">
         <v>1532</v>
       </c>
@@ -22437,7 +22435,7 @@
       <c r="L491" s="17"/>
     </row>
     <row r="492" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A492" s="21"/>
+      <c r="A492" s="12"/>
       <c r="B492" s="13" t="s">
         <v>1534</v>
       </c>
@@ -22456,12 +22454,12 @@
         <v>715</v>
       </c>
       <c r="I492" s="15"/>
-      <c r="J492" s="22"/>
+      <c r="J492" s="21"/>
       <c r="K492" s="17"/>
       <c r="L492" s="17"/>
     </row>
     <row r="493" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A493" s="21"/>
+      <c r="A493" s="12"/>
       <c r="B493" s="13" t="s">
         <v>1536</v>
       </c>
@@ -22469,7 +22467,7 @@
         <v>712</v>
       </c>
       <c r="D493" s="14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E493" s="13"/>
       <c r="F493" s="13"/>
@@ -22480,12 +22478,12 @@
         <v>715</v>
       </c>
       <c r="I493" s="15"/>
-      <c r="J493" s="22"/>
+      <c r="J493" s="21"/>
       <c r="K493" s="17"/>
       <c r="L493" s="17"/>
     </row>
     <row r="494" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A494" s="21"/>
+      <c r="A494" s="12"/>
       <c r="B494" s="13" t="s">
         <v>1538</v>
       </c>
@@ -22493,7 +22491,7 @@
         <v>712</v>
       </c>
       <c r="D494" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E494" s="13"/>
       <c r="F494" s="13"/>
@@ -22504,12 +22502,12 @@
         <v>715</v>
       </c>
       <c r="I494" s="15"/>
-      <c r="J494" s="22"/>
+      <c r="J494" s="21"/>
       <c r="K494" s="17"/>
       <c r="L494" s="17"/>
     </row>
     <row r="495" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A495" s="21"/>
+      <c r="A495" s="12"/>
       <c r="B495" s="13" t="s">
         <v>1540</v>
       </c>
@@ -22517,7 +22515,7 @@
         <v>712</v>
       </c>
       <c r="D495" s="14">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E495" s="13"/>
       <c r="F495" s="13"/>
@@ -22528,12 +22526,12 @@
         <v>715</v>
       </c>
       <c r="I495" s="15"/>
-      <c r="J495" s="22"/>
+      <c r="J495" s="21"/>
       <c r="K495" s="17"/>
       <c r="L495" s="17"/>
     </row>
     <row r="496" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A496" s="21"/>
+      <c r="A496" s="12"/>
       <c r="B496" s="13" t="s">
         <v>1542</v>
       </c>
@@ -22541,7 +22539,7 @@
         <v>712</v>
       </c>
       <c r="D496" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E496" s="13"/>
       <c r="F496" s="13"/>
@@ -22552,12 +22550,12 @@
         <v>715</v>
       </c>
       <c r="I496" s="15"/>
-      <c r="J496" s="22"/>
+      <c r="J496" s="21"/>
       <c r="K496" s="17"/>
       <c r="L496" s="17"/>
     </row>
     <row r="497" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A497" s="21"/>
+      <c r="A497" s="12"/>
       <c r="B497" s="13" t="s">
         <v>1544</v>
       </c>
@@ -22565,7 +22563,7 @@
         <v>712</v>
       </c>
       <c r="D497" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E497" s="13"/>
       <c r="F497" s="13"/>
@@ -22576,12 +22574,12 @@
         <v>715</v>
       </c>
       <c r="I497" s="15"/>
-      <c r="J497" s="22"/>
+      <c r="J497" s="21"/>
       <c r="K497" s="17"/>
       <c r="L497" s="17"/>
     </row>
     <row r="498" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A498" s="21"/>
+      <c r="A498" s="12"/>
       <c r="B498" s="13" t="s">
         <v>1546</v>
       </c>
@@ -22589,7 +22587,7 @@
         <v>712</v>
       </c>
       <c r="D498" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E498" s="13"/>
       <c r="F498" s="13"/>
@@ -22600,12 +22598,12 @@
         <v>715</v>
       </c>
       <c r="I498" s="15"/>
-      <c r="J498" s="22"/>
+      <c r="J498" s="21"/>
       <c r="K498" s="17"/>
       <c r="L498" s="17"/>
     </row>
     <row r="499" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A499" s="21"/>
+      <c r="A499" s="12"/>
       <c r="B499" s="13" t="s">
         <v>1548</v>
       </c>
@@ -22613,7 +22611,7 @@
         <v>712</v>
       </c>
       <c r="D499" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E499" s="13"/>
       <c r="F499" s="13"/>
@@ -22624,12 +22622,12 @@
         <v>715</v>
       </c>
       <c r="I499" s="15"/>
-      <c r="J499" s="22"/>
+      <c r="J499" s="21"/>
       <c r="K499" s="17"/>
       <c r="L499" s="17"/>
     </row>
     <row r="500" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A500" s="21"/>
+      <c r="A500" s="12"/>
       <c r="B500" s="13" t="s">
         <v>1550</v>
       </c>
@@ -22637,7 +22635,7 @@
         <v>712</v>
       </c>
       <c r="D500" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E500" s="13"/>
       <c r="F500" s="13"/>
@@ -22648,12 +22646,12 @@
         <v>715</v>
       </c>
       <c r="I500" s="15"/>
-      <c r="J500" s="22"/>
+      <c r="J500" s="21"/>
       <c r="K500" s="17"/>
       <c r="L500" s="17"/>
     </row>
     <row r="501" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A501" s="21"/>
+      <c r="A501" s="12"/>
       <c r="B501" s="13" t="s">
         <v>1552</v>
       </c>
@@ -22661,7 +22659,7 @@
         <v>712</v>
       </c>
       <c r="D501" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E501" s="13"/>
       <c r="F501" s="13"/>
@@ -22672,12 +22670,12 @@
         <v>715</v>
       </c>
       <c r="I501" s="15"/>
-      <c r="J501" s="22"/>
+      <c r="J501" s="21"/>
       <c r="K501" s="17"/>
       <c r="L501" s="17"/>
     </row>
     <row r="502" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A502" s="21"/>
+      <c r="A502" s="12"/>
       <c r="B502" s="13" t="s">
         <v>1554</v>
       </c>
@@ -22685,7 +22683,7 @@
         <v>712</v>
       </c>
       <c r="D502" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E502" s="13"/>
       <c r="F502" s="13"/>
@@ -22696,12 +22694,12 @@
         <v>715</v>
       </c>
       <c r="I502" s="15"/>
-      <c r="J502" s="22"/>
+      <c r="J502" s="21"/>
       <c r="K502" s="17"/>
       <c r="L502" s="17"/>
     </row>
     <row r="503" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A503" s="21"/>
+      <c r="A503" s="12"/>
       <c r="B503" s="13" t="s">
         <v>1556</v>
       </c>
@@ -22709,7 +22707,7 @@
         <v>712</v>
       </c>
       <c r="D503" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E503" s="13"/>
       <c r="F503" s="13"/>
@@ -22720,12 +22718,12 @@
         <v>715</v>
       </c>
       <c r="I503" s="15"/>
-      <c r="J503" s="22"/>
+      <c r="J503" s="21"/>
       <c r="K503" s="17"/>
       <c r="L503" s="17"/>
     </row>
     <row r="504" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A504" s="21"/>
+      <c r="A504" s="12"/>
       <c r="B504" s="13" t="s">
         <v>1558</v>
       </c>
@@ -22744,12 +22742,12 @@
       <c r="I504" s="15" t="s">
         <v>463</v>
       </c>
-      <c r="J504" s="22"/>
+      <c r="J504" s="21"/>
       <c r="K504" s="17"/>
       <c r="L504" s="17"/>
     </row>
     <row r="505" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A505" s="21"/>
+      <c r="A505" s="12"/>
       <c r="B505" s="13" t="s">
         <v>1559</v>
       </c>
@@ -22768,12 +22766,12 @@
       <c r="I505" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="J505" s="22"/>
+      <c r="J505" s="21"/>
       <c r="K505" s="17"/>
       <c r="L505" s="17"/>
     </row>
     <row r="506" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A506" s="21"/>
+      <c r="A506" s="12"/>
       <c r="B506" s="13" t="s">
         <v>1560</v>
       </c>
@@ -22792,12 +22790,12 @@
       <c r="I506" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="J506" s="22"/>
+      <c r="J506" s="21"/>
       <c r="K506" s="17"/>
       <c r="L506" s="17"/>
     </row>
     <row r="507" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A507" s="21"/>
+      <c r="A507" s="12"/>
       <c r="B507" s="13" t="s">
         <v>1562</v>
       </c>
@@ -22805,23 +22803,25 @@
         <v>305</v>
       </c>
       <c r="D507" s="14">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E507" s="13"/>
       <c r="F507" s="13"/>
       <c r="G507" s="11"/>
-      <c r="H507" s="13"/>
+      <c r="H507" s="13" t="s">
+        <v>336</v>
+      </c>
       <c r="I507" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="J507" s="22"/>
-      <c r="K507" s="22" t="s">
-        <v>1515</v>
+        <v>103</v>
+      </c>
+      <c r="J507" s="21"/>
+      <c r="K507" s="17" t="s">
+        <v>1516</v>
       </c>
       <c r="L507" s="17"/>
     </row>
     <row r="508" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A508" s="21"/>
+      <c r="A508" s="12"/>
       <c r="B508" s="13" t="s">
         <v>1563</v>
       </c>
@@ -22829,7 +22829,7 @@
         <v>305</v>
       </c>
       <c r="D508" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E508" s="13"/>
       <c r="F508" s="13"/>
@@ -22838,16 +22838,16 @@
         <v>336</v>
       </c>
       <c r="I508" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="J508" s="22"/>
+        <v>93</v>
+      </c>
+      <c r="J508" s="21"/>
       <c r="K508" s="17" t="s">
-        <v>1516</v>
+        <v>1521</v>
       </c>
       <c r="L508" s="17"/>
     </row>
     <row r="509" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A509" s="21"/>
+      <c r="A509" s="12"/>
       <c r="B509" s="13" t="s">
         <v>1564</v>
       </c>
@@ -22855,7 +22855,7 @@
         <v>305</v>
       </c>
       <c r="D509" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E509" s="13"/>
       <c r="F509" s="13"/>
@@ -22866,22 +22866,22 @@
       <c r="I509" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="J509" s="22"/>
+      <c r="J509" s="21"/>
       <c r="K509" s="17" t="s">
-        <v>1521</v>
+        <v>1565</v>
       </c>
       <c r="L509" s="17"/>
     </row>
     <row r="510" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A510" s="21"/>
+      <c r="A510" s="12"/>
       <c r="B510" s="13" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="C510" s="13" t="s">
         <v>305</v>
       </c>
       <c r="D510" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E510" s="13"/>
       <c r="F510" s="13"/>
@@ -22890,16 +22890,16 @@
         <v>336</v>
       </c>
       <c r="I510" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="J510" s="22"/>
+        <v>45</v>
+      </c>
+      <c r="J510" s="21"/>
       <c r="K510" s="17" t="s">
-        <v>1566</v>
+        <v>1463</v>
       </c>
       <c r="L510" s="17"/>
     </row>
     <row r="511" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A511" s="21"/>
+      <c r="A511" s="12"/>
       <c r="B511" s="13" t="s">
         <v>1567</v>
       </c>
@@ -22907,7 +22907,7 @@
         <v>305</v>
       </c>
       <c r="D511" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E511" s="13"/>
       <c r="F511" s="13"/>
@@ -22916,16 +22916,16 @@
         <v>336</v>
       </c>
       <c r="I511" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="J511" s="22"/>
+        <v>411</v>
+      </c>
+      <c r="J511" s="21"/>
       <c r="K511" s="17" t="s">
         <v>1463</v>
       </c>
       <c r="L511" s="17"/>
     </row>
     <row r="512" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A512" s="21"/>
+      <c r="A512" s="12"/>
       <c r="B512" s="13" t="s">
         <v>1568</v>
       </c>
@@ -22933,25 +22933,23 @@
         <v>305</v>
       </c>
       <c r="D512" s="14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E512" s="13"/>
       <c r="F512" s="13"/>
       <c r="G512" s="11"/>
-      <c r="H512" s="13" t="s">
-        <v>336</v>
-      </c>
+      <c r="H512" s="13"/>
       <c r="I512" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="J512" s="22"/>
-      <c r="K512" s="17" t="s">
-        <v>1463</v>
+        <v>54</v>
+      </c>
+      <c r="J512" s="21"/>
+      <c r="K512" s="21" t="s">
+        <v>1515</v>
       </c>
       <c r="L512" s="17"/>
     </row>
     <row r="513" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A513" s="21"/>
+      <c r="A513" s="12"/>
       <c r="B513" s="13" t="s">
         <v>1569</v>
       </c>
@@ -22959,7 +22957,7 @@
         <v>296</v>
       </c>
       <c r="D513" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E513" s="13"/>
       <c r="F513" s="13"/>
@@ -22970,10 +22968,10 @@
       <c r="I513" s="15"/>
       <c r="J513" s="16"/>
       <c r="K513" s="17"/>
-      <c r="L513" s="22"/>
+      <c r="L513" s="21"/>
     </row>
     <row r="514" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A514" s="21"/>
+      <c r="A514" s="12"/>
       <c r="B514" s="13" t="s">
         <v>1571</v>
       </c>
@@ -22981,43 +22979,43 @@
         <v>296</v>
       </c>
       <c r="D514" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E514" s="13"/>
       <c r="F514" s="13"/>
       <c r="G514" s="11" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="H514" s="13"/>
       <c r="I514" s="15"/>
       <c r="J514" s="16"/>
       <c r="K514" s="17"/>
-      <c r="L514" s="22"/>
+      <c r="L514" s="21"/>
     </row>
     <row r="515" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A515" s="21"/>
+      <c r="A515" s="12"/>
       <c r="B515" s="13" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="C515" s="13" t="s">
         <v>296</v>
       </c>
       <c r="D515" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E515" s="13"/>
       <c r="F515" s="13"/>
       <c r="G515" s="11" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H515" s="13"/>
       <c r="I515" s="15"/>
       <c r="J515" s="16"/>
       <c r="K515" s="17"/>
-      <c r="L515" s="22"/>
+      <c r="L515" s="21"/>
     </row>
     <row r="516" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A516" s="21"/>
+      <c r="A516" s="12"/>
       <c r="B516" s="13" t="s">
         <v>1574</v>
       </c>
@@ -23025,133 +23023,133 @@
         <v>296</v>
       </c>
       <c r="D516" s="14">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E516" s="13"/>
-      <c r="F516" s="15"/>
-      <c r="G516" s="24"/>
-      <c r="H516" s="13" t="s">
-        <v>1286</v>
-      </c>
+      <c r="F516" s="13"/>
+      <c r="G516" s="11" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H516" s="13"/>
       <c r="I516" s="15"/>
-      <c r="J516" s="22"/>
+      <c r="J516" s="16"/>
       <c r="K516" s="17"/>
-      <c r="L516" s="25"/>
+      <c r="L516" s="21"/>
     </row>
     <row r="517" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A517" s="21"/>
+      <c r="A517" s="12"/>
       <c r="B517" s="13" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="C517" s="13" t="s">
         <v>296</v>
       </c>
       <c r="D517" s="14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E517" s="13"/>
-      <c r="F517" s="15"/>
-      <c r="G517" s="24"/>
-      <c r="H517" s="13" t="s">
-        <v>1286</v>
-      </c>
+      <c r="F517" s="13"/>
+      <c r="G517" s="11" t="s">
+        <v>1577</v>
+      </c>
+      <c r="H517" s="13"/>
       <c r="I517" s="15"/>
-      <c r="J517" s="22"/>
+      <c r="J517" s="16"/>
       <c r="K517" s="17"/>
-      <c r="L517" s="25"/>
+      <c r="L517" s="21"/>
     </row>
     <row r="518" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A518" s="21"/>
+      <c r="A518" s="12"/>
       <c r="B518" s="13" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C518" s="13" t="s">
         <v>296</v>
       </c>
       <c r="D518" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E518" s="13"/>
-      <c r="F518" s="15"/>
+      <c r="F518" s="13"/>
       <c r="G518" s="11" t="s">
-        <v>1572</v>
-      </c>
-      <c r="H518" s="13" t="s">
-        <v>1286</v>
-      </c>
+        <v>1577</v>
+      </c>
+      <c r="H518" s="13"/>
       <c r="I518" s="15"/>
-      <c r="J518" s="22"/>
+      <c r="J518" s="16"/>
       <c r="K518" s="17"/>
-      <c r="L518" s="25"/>
+      <c r="L518" s="21"/>
     </row>
     <row r="519" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A519" s="21"/>
+      <c r="A519" s="12"/>
       <c r="B519" s="13" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="C519" s="13" t="s">
         <v>296</v>
       </c>
       <c r="D519" s="14">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E519" s="13"/>
-      <c r="F519" s="13"/>
-      <c r="G519" s="11" t="s">
-        <v>1578</v>
-      </c>
-      <c r="H519" s="13"/>
+      <c r="F519" s="15"/>
+      <c r="G519" s="23"/>
+      <c r="H519" s="13" t="s">
+        <v>1286</v>
+      </c>
       <c r="I519" s="15"/>
-      <c r="J519" s="16"/>
+      <c r="J519" s="21"/>
       <c r="K519" s="17"/>
-      <c r="L519" s="22"/>
+      <c r="L519" s="24"/>
     </row>
     <row r="520" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A520" s="21"/>
+      <c r="A520" s="12"/>
       <c r="B520" s="13" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="C520" s="13" t="s">
         <v>296</v>
       </c>
       <c r="D520" s="14">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E520" s="13"/>
-      <c r="F520" s="13"/>
-      <c r="G520" s="11" t="s">
-        <v>1578</v>
-      </c>
-      <c r="H520" s="13"/>
+      <c r="F520" s="15"/>
+      <c r="G520" s="23"/>
+      <c r="H520" s="13" t="s">
+        <v>1286</v>
+      </c>
       <c r="I520" s="15"/>
-      <c r="J520" s="16"/>
+      <c r="J520" s="21"/>
       <c r="K520" s="17"/>
-      <c r="L520" s="22"/>
+      <c r="L520" s="24"/>
     </row>
     <row r="521" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A521" s="21"/>
+      <c r="A521" s="12"/>
       <c r="B521" s="13" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="C521" s="13" t="s">
         <v>296</v>
       </c>
       <c r="D521" s="14">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E521" s="13"/>
-      <c r="F521" s="13"/>
+      <c r="F521" s="15"/>
       <c r="G521" s="11" t="s">
-        <v>1581</v>
-      </c>
-      <c r="H521" s="13"/>
+        <v>1577</v>
+      </c>
+      <c r="H521" s="13" t="s">
+        <v>1286</v>
+      </c>
       <c r="I521" s="15"/>
-      <c r="J521" s="16"/>
+      <c r="J521" s="21"/>
       <c r="K521" s="17"/>
-      <c r="L521" s="22"/>
+      <c r="L521" s="24"/>
     </row>
     <row r="522" s="11" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A522" s="21"/>
+      <c r="A522" s="12"/>
       <c r="B522" s="13" t="s">
         <v>1582</v>
       </c>

--- a/xlsx/MWV.xlsx
+++ b/xlsx/MWV.xlsx
@@ -12,11 +12,11 @@
     <workbookView windowWidth="21942" windowHeight="9805"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MWV" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$522</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">MWV!$A$1:$M$677</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3498" uniqueCount="1632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3718" uniqueCount="1803">
   <si>
     <t>SORT</t>
   </si>
@@ -44,7 +44,7 @@
     <t>MWV</t>
   </si>
   <si>
-    <t>MWV Series</t>
+    <t>MWV Group</t>
   </si>
   <si>
     <t>MWV No.</t>
@@ -4858,12 +4858,30 @@
     <t>WoO 4</t>
   </si>
   <si>
+    <t>2 Romances pour voix avec accompagnement de piano</t>
+  </si>
+  <si>
+    <t>WoO 4/1</t>
+  </si>
+  <si>
+    <t>Keine von der Erde Schonen: Keine von der Erde Schonen</t>
+  </si>
+  <si>
+    <t>WoO 4/2</t>
+  </si>
+  <si>
+    <t>Schlafloser Augen Leuchte: Schlafloser Augen Leuchte</t>
+  </si>
+  <si>
     <t>A 11</t>
   </si>
   <si>
     <t>WoO 5</t>
   </si>
   <si>
+    <t>Verleih' uns Frieden "Da nobis pacem, Domine"</t>
+  </si>
+  <si>
     <t>U 141</t>
   </si>
   <si>
@@ -4876,18 +4894,27 @@
     <t>WoO 7</t>
   </si>
   <si>
+    <t>Der Blumenkranz: An Celia's Baum (The Garland: By Celias arbour)</t>
+  </si>
+  <si>
     <t>G 25</t>
   </si>
   <si>
     <t>WoO 8</t>
   </si>
   <si>
+    <t>Ersatz fur Unbestand: Lieblich mundet der Becher Wein</t>
+  </si>
+  <si>
     <t>D 4</t>
   </si>
   <si>
     <t>WoO 9</t>
   </si>
   <si>
+    <t>Festgesang</t>
+  </si>
+  <si>
     <t>U 136</t>
   </si>
   <si>
@@ -4897,12 +4924,36 @@
     <t>WoO 11</t>
   </si>
   <si>
+    <t>3 Volkslieder pour deux voix avec accompagnement de piano</t>
+  </si>
+  <si>
+    <t>WoO 11/1</t>
+  </si>
+  <si>
+    <t>Wie kann ich froh und lustig sein: Wie kann ich froh und lustig sein?</t>
+  </si>
+  <si>
+    <t>WoO 11/2</t>
+  </si>
+  <si>
+    <t>Abendlied: Wenn ich auf dem Lager liege</t>
+  </si>
+  <si>
+    <t>WoO 11/3</t>
+  </si>
+  <si>
+    <t>Wasserfahrt: Ich stand gelehnet an den Mast</t>
+  </si>
+  <si>
     <t>B 27</t>
   </si>
   <si>
     <t>WoO 12</t>
   </si>
   <si>
+    <t>Lord! Have mercy upon us</t>
+  </si>
+  <si>
     <t>U 157</t>
   </si>
   <si>
@@ -4915,6 +4966,9 @@
     <t>WoO 14</t>
   </si>
   <si>
+    <t>2 Lieder sacrés pour alto et chœur (SATB) avec accompagnement d'orgue</t>
+  </si>
+  <si>
     <t>also Op. 96</t>
   </si>
   <si>
@@ -4924,18 +4978,51 @@
     <t>WoO 15</t>
   </si>
   <si>
+    <t>Hor mein Bitten, Herr (Hear my prayer, o God)</t>
+  </si>
+  <si>
     <t>K 105</t>
   </si>
   <si>
     <t>WoO 16</t>
   </si>
   <si>
+    <t>Warnung vor dein Rhein: An den Rhein, an dein Rhein</t>
+  </si>
+  <si>
     <t>WoO 17</t>
   </si>
   <si>
+    <t>2 Gesange pour voix avec accompagnement de piano</t>
+  </si>
+  <si>
+    <t>WoO 17/1</t>
+  </si>
+  <si>
+    <t>Das Waldschloss: Wo noch kein Wandrer gegangen</t>
+  </si>
+  <si>
+    <t>WoO 17/2</t>
+  </si>
+  <si>
+    <t>Pegenlied: Wenn die Sonne lieblich schiene</t>
+  </si>
+  <si>
     <t>WoO 18</t>
   </si>
   <si>
+    <t>WoO 18/1</t>
+  </si>
+  <si>
+    <t>Ich hor ein Vogleinlocken: Ich hor' ein Voglein locken</t>
+  </si>
+  <si>
+    <t>WoO 18/2</t>
+  </si>
+  <si>
+    <t>Todeslied der Bojaren: Leg' in den Sarg mir</t>
+  </si>
+  <si>
     <t>WoO 19</t>
   </si>
   <si>
@@ -4963,24 +5050,36 @@
     <t>WoO 20</t>
   </si>
   <si>
+    <t>Seemans Scheidelied: Es freut sich Alles</t>
+  </si>
+  <si>
     <t>G 29</t>
   </si>
   <si>
     <t>WoO 21</t>
   </si>
   <si>
+    <t>Nachtgesang: Schlummernd an des Vaters Brust</t>
+  </si>
+  <si>
     <t>G 32</t>
   </si>
   <si>
     <t>WoO 22</t>
   </si>
   <si>
+    <t>Die Stiftungsfeier: Auf, Freunde, lasst das Jahr uns singen</t>
+  </si>
+  <si>
     <t>K 25</t>
   </si>
   <si>
     <t>WoO 23</t>
   </si>
   <si>
+    <t>Des Madchens Klage: Der Eichwald brauset</t>
+  </si>
+  <si>
     <t>B 57/1</t>
   </si>
   <si>
@@ -4990,376 +5089,790 @@
     <t>WoO 24</t>
   </si>
   <si>
+    <t>Kyrie eleison</t>
+  </si>
+  <si>
+    <t>O 9</t>
+  </si>
+  <si>
+    <t>WoO 25</t>
+  </si>
+  <si>
+    <t>Fantasie und Variationen über Webers "Preciosa" [first two variations,  finale]</t>
+  </si>
+  <si>
+    <t>2 Pianos, Orchestra</t>
+  </si>
+  <si>
+    <t>collaborative work with Ignaz Moscheles</t>
+  </si>
+  <si>
+    <t>WoO 26</t>
+  </si>
+  <si>
+    <t>Ehre sei Gott in der Höhe, Doppelchor für Sopran, Alt, Tenor und Bas</t>
+  </si>
+  <si>
+    <t>B 47</t>
+  </si>
+  <si>
+    <t>WoO 27</t>
+  </si>
+  <si>
+    <t>Heilig, Doppelchor für Sopran, Alt, Tenor und Bass</t>
+  </si>
+  <si>
+    <t>B 45</t>
+  </si>
+  <si>
+    <t>WoO 28</t>
+  </si>
+  <si>
+    <t>Psaume 100: Jauchzet dem Herrn, alle Welt</t>
+  </si>
+  <si>
+    <t>B 25</t>
+  </si>
+  <si>
+    <t>WoO 29</t>
+  </si>
+  <si>
+    <t>Te Deum für Solostimmen und Chor mit Begleitung der Orgel</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>N 1</t>
+  </si>
+  <si>
+    <t>Strings</t>
+  </si>
+  <si>
+    <t>N 2</t>
+  </si>
+  <si>
+    <t>N 3</t>
+  </si>
+  <si>
+    <t>N 4</t>
+  </si>
+  <si>
+    <t>N 5</t>
+  </si>
+  <si>
+    <t>N 6</t>
+  </si>
+  <si>
+    <t>N 7</t>
+  </si>
+  <si>
+    <t>N 8</t>
+  </si>
+  <si>
+    <t>N 9</t>
+  </si>
+  <si>
+    <t>N 10</t>
+  </si>
+  <si>
+    <t>N 11</t>
+  </si>
+  <si>
+    <t>N 12</t>
+  </si>
+  <si>
+    <t>Q 20</t>
+  </si>
+  <si>
+    <t>The Evening Bell</t>
+  </si>
+  <si>
+    <t>Harp, Piano</t>
+  </si>
+  <si>
+    <t>15 Fugues</t>
+  </si>
+  <si>
+    <t>String Quartet</t>
+  </si>
+  <si>
+    <t>2 Études</t>
+  </si>
+  <si>
+    <t>2 Petites pièces</t>
+  </si>
+  <si>
+    <t>2 Pièces</t>
+  </si>
+  <si>
+    <t>3 Fugues</t>
+  </si>
+  <si>
+    <t>4 Petites pièces</t>
+  </si>
+  <si>
+    <t>5 Petites pièces</t>
+  </si>
+  <si>
+    <t>6 Petites pièces</t>
+  </si>
+  <si>
+    <t>B major</t>
+  </si>
+  <si>
+    <t>Andante alla marcia</t>
+  </si>
+  <si>
+    <t>Chorale</t>
+  </si>
+  <si>
+    <t>Largo-Allegro</t>
+  </si>
+  <si>
+    <t>Largo-Allegro molto</t>
+  </si>
+  <si>
+    <t>Lento-Vivace</t>
+  </si>
+  <si>
+    <t>Pièce</t>
+  </si>
+  <si>
+    <t>Recitativo</t>
+  </si>
+  <si>
+    <t>Wie gross ist des Allmacht'gen Gute, chorale-prélude, 3 variations</t>
+  </si>
+  <si>
+    <t>A, Piano</t>
+  </si>
+  <si>
+    <t>Clarinet, Piano</t>
+  </si>
+  <si>
+    <t>C-sharp minor</t>
+  </si>
+  <si>
+    <t>Piano, Orchestra</t>
+  </si>
+  <si>
+    <t>Piano, Strings</t>
+  </si>
+  <si>
+    <t>Piano, Violin, Viola</t>
+  </si>
+  <si>
+    <t>Violin, Piano, Orchestra</t>
+  </si>
+  <si>
+    <t>Violin, Strings</t>
+  </si>
+  <si>
+    <t>B 57</t>
+  </si>
+  <si>
+    <t>Die Deutsche Liturgie</t>
+  </si>
+  <si>
+    <t>L 1</t>
+  </si>
+  <si>
+    <t>Soldatenliebschaft</t>
+  </si>
+  <si>
+    <t>Singspiel</t>
+  </si>
+  <si>
+    <t>L 2</t>
+  </si>
+  <si>
+    <t>Die beiden Pädagogen</t>
+  </si>
+  <si>
+    <t>Operetta</t>
+  </si>
+  <si>
+    <t>L 3</t>
+  </si>
+  <si>
+    <t>Die wandernden Komödianten</t>
+  </si>
+  <si>
+    <t>L 4</t>
+  </si>
+  <si>
+    <t>Die beiden Neffen (Der Onkel aus Boston)</t>
+  </si>
+  <si>
+    <t>M 1</t>
+  </si>
+  <si>
+    <t>Blanche et Vermeille</t>
+  </si>
+  <si>
+    <t>M 2</t>
+  </si>
+  <si>
+    <t>Musik zu einem Lustspiel</t>
+  </si>
+  <si>
+    <t>M 3</t>
+  </si>
+  <si>
+    <t>L’homme automate</t>
+  </si>
+  <si>
+    <t>M 4</t>
+  </si>
+  <si>
+    <t>Musik zu einer Freischütz-Parodie</t>
+  </si>
+  <si>
+    <t>M 5</t>
+  </si>
+  <si>
+    <t>Musik zu einer Mozart-Parodie</t>
+  </si>
+  <si>
+    <t>M 6</t>
+  </si>
+  <si>
+    <t>Was wir bringen</t>
+  </si>
+  <si>
+    <t>M 7</t>
+  </si>
+  <si>
+    <t>Der standhafte Prinz</t>
+  </si>
+  <si>
+    <t>M 8</t>
+  </si>
+  <si>
+    <t>Andreas Hofer</t>
+  </si>
+  <si>
+    <t>M 9</t>
+  </si>
+  <si>
+    <t>Kurfürst Johann Wilhelm im Theater</t>
+  </si>
+  <si>
+    <t>M 10</t>
+  </si>
+  <si>
+    <t>Alexis</t>
+  </si>
+  <si>
+    <t>M 11</t>
+  </si>
+  <si>
+    <t>Ruy Blas</t>
+  </si>
+  <si>
+    <t>M 15</t>
+  </si>
+  <si>
+    <t>König Oedipus</t>
+  </si>
+  <si>
+    <t>N 17</t>
+  </si>
+  <si>
+    <t>N 19</t>
+  </si>
+  <si>
+    <t>O 1</t>
+  </si>
+  <si>
+    <t>Recitativo. Largo</t>
+  </si>
+  <si>
+    <t>O 2</t>
+  </si>
+  <si>
+    <t>O 3</t>
+  </si>
+  <si>
+    <t>O 4</t>
+  </si>
+  <si>
+    <t>Violin, Piano, Strings</t>
+  </si>
+  <si>
+    <t>O 5</t>
+  </si>
+  <si>
+    <t>O 6</t>
+  </si>
+  <si>
+    <t>O 13</t>
+  </si>
+  <si>
+    <t>P 6</t>
+  </si>
+  <si>
+    <t>Kindersinfonie</t>
+  </si>
+  <si>
+    <t>P 8</t>
+  </si>
+  <si>
+    <t>P 9</t>
+  </si>
+  <si>
+    <t>Militärstück</t>
+  </si>
+  <si>
+    <t>P 10</t>
+  </si>
+  <si>
+    <t>Tusch</t>
+  </si>
+  <si>
+    <t>P 11</t>
+  </si>
+  <si>
+    <t>Prozessionsmarsch</t>
+  </si>
+  <si>
+    <t>P 13</t>
+  </si>
+  <si>
+    <t>P 17</t>
+  </si>
+  <si>
+    <t>P 18</t>
+  </si>
+  <si>
+    <t>P 19</t>
+  </si>
+  <si>
+    <t>U 65</t>
+  </si>
+  <si>
+    <t>2 Études  pour le piano</t>
+  </si>
+  <si>
+    <t>2 Petites pièces pour le piano</t>
+  </si>
+  <si>
+    <t>2 Petites pièces pour orgue</t>
+  </si>
+  <si>
+    <t>2 Pièces pour orgue</t>
+  </si>
+  <si>
+    <t>2 Pièces pour piano</t>
+  </si>
+  <si>
+    <t>2 Pièces sacrées pour chœurs a cappella</t>
+  </si>
+  <si>
+    <t>3 Fugues pour piano</t>
+  </si>
+  <si>
+    <t>4 Gesange pour voix avec accompagnement de piano</t>
+  </si>
+  <si>
+    <t>4 Petites pièces pour orgue</t>
+  </si>
+  <si>
+    <t>5 Petites pièces pour le piano</t>
+  </si>
+  <si>
+    <t>6 Petites pièces pour orgue</t>
+  </si>
+  <si>
+    <t>7 Chants pour la liturgie allemande</t>
+  </si>
+  <si>
+    <t>Abschied: Leb wohl mein Lieb</t>
+  </si>
+  <si>
+    <t>Ach Gott von Himmel sieh darein</t>
+  </si>
+  <si>
+    <t>Allegro, en la mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Allegro, en ré mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Allegro, en si majeur, pour orgue</t>
+  </si>
+  <si>
+    <t>Allein Gott in der Hoh' sey Ehr</t>
+  </si>
+  <si>
+    <t>Andante alla marcia, en si majeur, pour orgue</t>
+  </si>
+  <si>
+    <t>Andante sostenuto, en ré majeur, pour orgue</t>
+  </si>
+  <si>
+    <t>Andante, en fa majeur, pour piano</t>
+  </si>
+  <si>
+    <t>Andante, en la bémol majeur, pour piano</t>
+  </si>
+  <si>
+    <t>Andante, en la majeur, pour piano</t>
+  </si>
+  <si>
+    <t>Ave Maria</t>
+  </si>
+  <si>
+    <t>Ave Maris Stella</t>
+  </si>
+  <si>
+    <t>Begrussung "Cantate Humboldt", festgesang</t>
+  </si>
+  <si>
+    <t>Canon à trois parties</t>
+  </si>
+  <si>
+    <t>Canon en deux partie, en do mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Canon</t>
+  </si>
+  <si>
+    <t>Canon en deux parties</t>
+  </si>
+  <si>
+    <t>Canon en deux parties pour piano</t>
+  </si>
+  <si>
+    <t>Canon en deux parties, en si mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Canon, en fa dièse mineur</t>
+  </si>
+  <si>
+    <t>Chant sans parole, en fa dièse mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Chant sans parole, en la majeur, pour piano</t>
+  </si>
+  <si>
+    <t>Chant sans parole, en ré majeur, pour piano</t>
+  </si>
+  <si>
+    <t>Chant sans parole, en ré mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Che vuoi moi cor?</t>
+  </si>
+  <si>
+    <t>Chorale, en la bémol majeur, pour orgue</t>
+  </si>
+  <si>
+    <t>Chorale, en ré majeur, pour orgue</t>
+  </si>
+  <si>
+    <t>Christe, du Lamm Gottes</t>
+  </si>
+  <si>
+    <t>Con moto, en si bémol mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Concerto, en la bémol majeur, pour 2 pianos et orchestre</t>
+  </si>
+  <si>
+    <t>Concerto, en la mineur, pour piano et orchestre</t>
+  </si>
+  <si>
+    <t>Concerto, en mi majeur, pour 2 pianos et orchestre</t>
+  </si>
+  <si>
+    <t>Concerto, en ré mineur, pour violon et cordes</t>
+  </si>
+  <si>
+    <t>Concerto, en ré mineur, pour violon et piano avec orchestre</t>
+  </si>
+  <si>
+    <t>Das Gesetz des Herrn ist ohne Wandel</t>
+  </si>
+  <si>
+    <t>Der Abendsegen (The Evening Service)</t>
+  </si>
+  <si>
+    <t>Der Bettler: Ich danke Gott dir</t>
+  </si>
+  <si>
+    <t>Der Sanger</t>
+  </si>
+  <si>
+    <t>Der Tag: Sanft entschwanden mir</t>
+  </si>
+  <si>
+    <t>Der Verlassene: Nacht ist um mich her</t>
+  </si>
+  <si>
+    <t>Der Wasserfall: Rieselt hernieder</t>
+  </si>
+  <si>
+    <t>Der weise Giogenes</t>
+  </si>
+  <si>
+    <t>Die Himmel erzahlen</t>
+  </si>
+  <si>
+    <t>Die Nachtigall: Da ging ich hin</t>
+  </si>
+  <si>
+    <t>Double canon à quatre parties</t>
+  </si>
+  <si>
+    <t>Ehre sei dem Vater</t>
+  </si>
+  <si>
+    <t>Ein Tag sagt es dem andern</t>
+  </si>
+  <si>
+    <t>Einst ins Schlaraffenland zogen</t>
+  </si>
+  <si>
+    <t>Er hat der Sonne eine Hutte gemacht</t>
+  </si>
+  <si>
+    <t>Er kommt aus dem kinglichen Alter der Welt</t>
+  </si>
+  <si>
+    <t>Er wird offnen die Augen der Blinden</t>
+  </si>
+  <si>
+    <t>Erwartung: Bist auf ewig du gegangen</t>
+  </si>
+  <si>
+    <t>Es rauscht der Wald</t>
+  </si>
+  <si>
+    <t>Étude, en do majeur, pour piano</t>
+  </si>
+  <si>
+    <t>Étude, en fa majeur, pour piano</t>
+  </si>
+  <si>
+    <t>Fantaisie, en do mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Fantaisie, en ré mineur, pour piano à 4 mains</t>
+  </si>
+  <si>
+    <t>Fantaisie, en sol mineur, pour orgue</t>
+  </si>
+  <si>
+    <t>Fugue, en do dièse mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Fugue, en fa mineur, pour orgue</t>
+  </si>
+  <si>
+    <t>Fugue, en mi bémol majeur, pour quatuor à cordes</t>
+  </si>
+  <si>
+    <t>Fugue, en mi mineur, pour orgue</t>
+  </si>
+  <si>
+    <t>Fugue, en mi mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Fugue, en si majeur, pour orgue</t>
+  </si>
+  <si>
+    <t>Gloria</t>
+  </si>
+  <si>
+    <t>Gloria Patri (Ehre sei dem Vater)</t>
+  </si>
+  <si>
+    <t>Glory be to the Father</t>
+  </si>
+  <si>
+    <t>Gott segne Sachsenland, cantate</t>
+  </si>
+  <si>
+    <t>Gott, du bist unsre Zuversicht</t>
+  </si>
+  <si>
+    <t>Gretchen: Meine Ruh ist hin</t>
+  </si>
+  <si>
+    <t>Grosse Festmusik aun Durefest</t>
+  </si>
+  <si>
+    <t>Herr Gott, dich loben wir</t>
+  </si>
+  <si>
+    <t>Hora est</t>
+  </si>
+  <si>
+    <t>Ich will den Herrn nach seiner Gerechtigkeit preisen</t>
+  </si>
+  <si>
+    <t>Im Kahn</t>
+  </si>
+  <si>
+    <t>In feierlichen Tonen, cantate</t>
+  </si>
+  <si>
+    <t>Jagerlied: Kein bess're Lust in dieser Zeit</t>
+  </si>
+  <si>
+    <t>Jesu, meine Freude</t>
+  </si>
+  <si>
+    <t>Jesus, meine Zuversicht</t>
+  </si>
+  <si>
+    <t>Jube Domine</t>
+  </si>
+  <si>
     <t>Kyrie</t>
   </si>
   <si>
-    <t>O 9</t>
-  </si>
-  <si>
-    <t>WoO 25</t>
-  </si>
-  <si>
-    <t>Fantasie und Variationen über Webers "Preciosa" [first two variations,  finale]</t>
-  </si>
-  <si>
-    <t>2 Pianos, Orchestra</t>
-  </si>
-  <si>
-    <t>collaborative work with Ignaz Moscheles</t>
-  </si>
-  <si>
-    <t>WoO 26</t>
-  </si>
-  <si>
-    <t>Ehre sei Gott in der Höhe, Doppelchor für Sopran, Alt, Tenor und Bas</t>
-  </si>
-  <si>
-    <t>B 47</t>
-  </si>
-  <si>
-    <t>WoO 27</t>
-  </si>
-  <si>
-    <t>Heilig, Doppelchor für Sopran, Alt, Tenor und Bass</t>
-  </si>
-  <si>
-    <t>B 57/2</t>
-  </si>
-  <si>
-    <t>57/2</t>
-  </si>
-  <si>
-    <t>Heilig</t>
-  </si>
-  <si>
-    <t>B 45</t>
-  </si>
-  <si>
-    <t>WoO 28</t>
-  </si>
-  <si>
-    <t>Psaume 100: Jauchzet dem Herrn, alle Welt</t>
-  </si>
-  <si>
-    <t>B 25</t>
-  </si>
-  <si>
-    <t>WoO 29</t>
-  </si>
-  <si>
-    <t>Te Deum für Solostimmen und Chor mit Begleitung der Orgel</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>N 1</t>
-  </si>
-  <si>
-    <t>Strings</t>
-  </si>
-  <si>
-    <t>N 2</t>
-  </si>
-  <si>
-    <t>N 3</t>
-  </si>
-  <si>
-    <t>N 4</t>
-  </si>
-  <si>
-    <t>N 5</t>
-  </si>
-  <si>
-    <t>N 6</t>
-  </si>
-  <si>
-    <t>N 7</t>
-  </si>
-  <si>
-    <t>N 8</t>
-  </si>
-  <si>
-    <t>N 9</t>
-  </si>
-  <si>
-    <t>N 10</t>
-  </si>
-  <si>
-    <t>N 11</t>
-  </si>
-  <si>
-    <t>N 12</t>
-  </si>
-  <si>
-    <t>Q 20</t>
-  </si>
-  <si>
-    <t>The Evening Bell</t>
-  </si>
-  <si>
-    <t>Harp, Piano</t>
-  </si>
-  <si>
-    <t>A, Piano</t>
-  </si>
-  <si>
-    <t>Clarinet, Piano</t>
-  </si>
-  <si>
-    <t>B major</t>
-  </si>
-  <si>
-    <t>2 Petites pièces</t>
-  </si>
-  <si>
-    <t>2 Pièces</t>
-  </si>
-  <si>
-    <t>4 Petites pièces</t>
-  </si>
-  <si>
-    <t>6 Petites pièces</t>
-  </si>
-  <si>
-    <t>Andante alla marcia</t>
-  </si>
-  <si>
-    <t>Chorale</t>
-  </si>
-  <si>
-    <t>Wie gross ist des Allmacht'gen Gute, chorale-prélude, 3 variations</t>
-  </si>
-  <si>
-    <t>2 Études</t>
-  </si>
-  <si>
-    <t>C-sharp minor</t>
-  </si>
-  <si>
-    <t>5 Petites pièces</t>
-  </si>
-  <si>
-    <t>Pièce</t>
-  </si>
-  <si>
-    <t>3 Fugues</t>
-  </si>
-  <si>
-    <t>Largo-Allegro</t>
-  </si>
-  <si>
-    <t>Largo-Allegro molto</t>
-  </si>
-  <si>
-    <t>Recitativo</t>
-  </si>
-  <si>
-    <t>Lento-Vivace</t>
-  </si>
-  <si>
-    <t>Piano, Orchestra</t>
-  </si>
-  <si>
-    <t>Piano, Strings</t>
-  </si>
-  <si>
-    <t>Piano, Violin, Viola</t>
-  </si>
-  <si>
-    <t>String Quartet</t>
-  </si>
-  <si>
-    <t>15 Fugues</t>
-  </si>
-  <si>
-    <t>Violin, Piano, Orchestra</t>
-  </si>
-  <si>
-    <t>Violin, Strings</t>
-  </si>
-  <si>
-    <t>B 57</t>
-  </si>
-  <si>
-    <t>Die Deutsche Liturgie</t>
-  </si>
-  <si>
-    <t>L 1</t>
-  </si>
-  <si>
-    <t>Soldatenliebschaft</t>
-  </si>
-  <si>
-    <t>Singspiel</t>
-  </si>
-  <si>
-    <t>L 2</t>
-  </si>
-  <si>
-    <t>Die beiden Pädagogen</t>
-  </si>
-  <si>
-    <t>Operetta</t>
-  </si>
-  <si>
-    <t>L 3</t>
-  </si>
-  <si>
-    <t>Die wandernden Komödianten</t>
-  </si>
-  <si>
-    <t>L 4</t>
-  </si>
-  <si>
-    <t>Die beiden Neffen (Der Onkel aus Boston)</t>
-  </si>
-  <si>
-    <t>M 1</t>
-  </si>
-  <si>
-    <t>Blanche et Vermeille</t>
-  </si>
-  <si>
-    <t>M 2</t>
-  </si>
-  <si>
-    <t>Musik zu einem Lustspiel</t>
-  </si>
-  <si>
-    <t>M 3</t>
-  </si>
-  <si>
-    <t>L’homme automate</t>
-  </si>
-  <si>
-    <t>M 4</t>
-  </si>
-  <si>
-    <t>Musik zu einer Freischütz-Parodie</t>
-  </si>
-  <si>
-    <t>M 5</t>
-  </si>
-  <si>
-    <t>Musik zu einer Mozart-Parodie</t>
-  </si>
-  <si>
-    <t>M 6</t>
-  </si>
-  <si>
-    <t>Was wir bringen</t>
-  </si>
-  <si>
-    <t>M 7</t>
-  </si>
-  <si>
-    <t>Der standhafte Prinz</t>
-  </si>
-  <si>
-    <t>M 8</t>
-  </si>
-  <si>
-    <t>Andreas Hofer</t>
-  </si>
-  <si>
-    <t>M 9</t>
-  </si>
-  <si>
-    <t>Kurfürst Johann Wilhelm im Theater</t>
-  </si>
-  <si>
-    <t>M 10</t>
-  </si>
-  <si>
-    <t>Alexis</t>
-  </si>
-  <si>
-    <t>M 11</t>
-  </si>
-  <si>
-    <t>Ruy Blas</t>
-  </si>
-  <si>
-    <t>M 15</t>
-  </si>
-  <si>
-    <t>König Oedipus</t>
-  </si>
-  <si>
-    <t>N 17</t>
-  </si>
-  <si>
-    <t>N 19</t>
-  </si>
-  <si>
-    <t>O 1</t>
-  </si>
-  <si>
-    <t>Recitativo. Largo</t>
-  </si>
-  <si>
-    <t>O 2</t>
-  </si>
-  <si>
-    <t>O 3</t>
-  </si>
-  <si>
-    <t>O 4</t>
-  </si>
-  <si>
-    <t>Violin, Piano, Strings</t>
-  </si>
-  <si>
-    <t>O 5</t>
-  </si>
-  <si>
-    <t>O 6</t>
-  </si>
-  <si>
-    <t>O 13</t>
-  </si>
-  <si>
-    <t>P 6</t>
-  </si>
-  <si>
-    <t>Kindersinfonie</t>
-  </si>
-  <si>
-    <t>P 8</t>
-  </si>
-  <si>
-    <t>P 9</t>
-  </si>
-  <si>
-    <t>Militärstück</t>
-  </si>
-  <si>
-    <t>P 10</t>
-  </si>
-  <si>
-    <t>Tusch</t>
-  </si>
-  <si>
-    <t>P 11</t>
-  </si>
-  <si>
-    <t>Prozessionsmarsch</t>
-  </si>
-  <si>
-    <t>P 13</t>
-  </si>
-  <si>
-    <t>P 17</t>
-  </si>
-  <si>
-    <t>P 18</t>
-  </si>
-  <si>
-    <t>P 19</t>
-  </si>
-  <si>
-    <t>U 65</t>
+    <t>Largo-Allegro molto, en do mineur/majeur, pour piano</t>
+  </si>
+  <si>
+    <t>Largo-Allegro, en do mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Lass es heut am edlen Ort</t>
+  </si>
+  <si>
+    <t>Lento-Vivace, en sol mineur, pour piano à 4 mains</t>
+  </si>
+  <si>
+    <t>Lieb und Hoffnung</t>
+  </si>
+  <si>
+    <t>Lieben und Schweigen: Ich flocht ein Kranzlein schoner Lieder</t>
+  </si>
+  <si>
+    <t>Lied einer Frundin: Zarter Blumen leicht Gewinde</t>
+  </si>
+  <si>
+    <t>Lied, en fa dièse mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Lob der Trunkenheit: Trunken mussen wir alle sein</t>
+  </si>
+  <si>
+    <t>Lob des Weines: Seht, Freunde, die Glaser'</t>
+  </si>
+  <si>
+    <t>Magnificat</t>
+  </si>
+  <si>
+    <t>Mailied: Ich weiss mir'n Madchen</t>
+  </si>
+  <si>
+    <t>Musikantenprugelei: Seht doch diese Fiedlerbanden</t>
+  </si>
+  <si>
+    <t>O beata et benedicta</t>
+  </si>
+  <si>
+    <t>O konnt ich zu dir fliegen</t>
+  </si>
+  <si>
+    <t>Pièce, en mi mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Prélude, en do mineur, pour orgue</t>
+  </si>
+  <si>
+    <t>Prélude, en fa mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Presto, en do mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Presto, en fa majeur, pour violon et piano</t>
+  </si>
+  <si>
+    <t>Psaume 31: Defend me, Lord</t>
+  </si>
+  <si>
+    <t>Psaume 5: Lord hear the voice</t>
+  </si>
+  <si>
+    <t>Psaume 66</t>
+  </si>
+  <si>
+    <t>Raste Krieger, Krieg ist aus</t>
+  </si>
+  <si>
+    <t>Recitativo, en ré mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Reiterlied: Immer fort</t>
+  </si>
+  <si>
+    <t>Salve Regina</t>
+  </si>
+  <si>
+    <t>Sanft weh'n im Hauch der Abendluft</t>
+  </si>
+  <si>
+    <t>Sonate, en fa majeur, pour violon et piano</t>
+  </si>
+  <si>
+    <t>Sonate, en fa mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Sonate, en la mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Sonate, en mi bémol majeur, pour clarinette et piano</t>
+  </si>
+  <si>
+    <t>Sonate, en mi mineur, pour piano</t>
+  </si>
+  <si>
+    <t>Tag fut Tag sei Gott gepriesen</t>
+  </si>
+  <si>
+    <t>Te Deum</t>
+  </si>
+  <si>
+    <t>Trio, en do mineur, pour piano, violon et alto</t>
+  </si>
+  <si>
+    <t>Und ob du mich zuchtigst</t>
+  </si>
+  <si>
+    <t>Venez chantez</t>
+  </si>
+  <si>
+    <t>Vier trube Monden sind entfloh'n</t>
+  </si>
+  <si>
+    <t>Von allen dienen zarten Gaben</t>
+  </si>
+  <si>
+    <t>Von Himmel hoch</t>
+  </si>
+  <si>
+    <t>Weinend seh' ich in die Nacht</t>
+  </si>
+  <si>
+    <t>Weiter, rastlos atemlos voruber</t>
+  </si>
+  <si>
+    <t>Wie gross ist des Allmacht'gen Gute</t>
+  </si>
+  <si>
+    <t>Wie gross ist des Allmacht'gen Gute, chorale-prélude et 3 variations, pour orgue</t>
+  </si>
+  <si>
+    <t>Wiegenlied: Schlummre sanft</t>
+  </si>
+  <si>
+    <t>Worauf kommt es uberall an</t>
   </si>
   <si>
     <t>Vokalmusik
@@ -6825,7 +7338,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M522"/>
+  <dimension ref="A1:M677"/>
   <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="30" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="9.01801801801802" style="13" customWidth="1"/>
@@ -6834,7 +7347,7 @@
     <col min="4" max="4" width="10.0990990990991" style="15" customWidth="1"/>
     <col min="5" max="5" width="11.2792792792793" style="14" customWidth="1"/>
     <col min="6" max="6" width="10.3243243243243" style="14" customWidth="1"/>
-    <col min="7" max="7" width="33.2792792792793" style="12" customWidth="1"/>
+    <col min="7" max="7" width="54.1261261261261" style="12" customWidth="1"/>
     <col min="8" max="8" width="16.2072072072072" style="14" customWidth="1"/>
     <col min="9" max="9" width="13.1261261261261" style="16" customWidth="1"/>
     <col min="10" max="10" width="21.9279279279279" style="17" customWidth="1"/>
@@ -19882,300 +20395,286 @@
         <v>1416</v>
       </c>
       <c r="F380" s="14"/>
-      <c r="G380" s="12"/>
-      <c r="H380" s="12"/>
+      <c r="G380" s="12" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H380" s="14"/>
       <c r="I380" s="16"/>
-      <c r="J380" s="12"/>
-      <c r="K380" s="12"/>
-      <c r="L380" s="18"/>
     </row>
     <row r="381" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A381" s="13">
-        <v>999.05</v>
-      </c>
-      <c r="B381" s="14" t="s">
-        <v>1417</v>
-      </c>
-      <c r="C381" s="14" t="s">
-        <v>381</v>
-      </c>
-      <c r="D381" s="15">
-        <v>11</v>
-      </c>
+        <v>999.041</v>
+      </c>
+      <c r="B381" s="14"/>
+      <c r="C381" s="14"/>
+      <c r="D381" s="15"/>
       <c r="E381" s="14" t="s">
         <v>1418</v>
       </c>
       <c r="F381" s="14"/>
-      <c r="G381" s="12"/>
+      <c r="G381" s="12" t="s">
+        <v>1419</v>
+      </c>
       <c r="H381" s="14"/>
       <c r="I381" s="16"/>
     </row>
     <row r="382" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A382" s="13">
-        <v>999.06</v>
-      </c>
-      <c r="B382" s="14" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C382" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D382" s="15">
-        <v>141</v>
-      </c>
+        <v>999.042</v>
+      </c>
+      <c r="B382" s="14"/>
+      <c r="C382" s="14"/>
+      <c r="D382" s="15"/>
       <c r="E382" s="14" t="s">
         <v>1420</v>
       </c>
       <c r="F382" s="14"/>
-      <c r="G382" s="12"/>
+      <c r="G382" s="12" t="s">
+        <v>1421</v>
+      </c>
       <c r="H382" s="14"/>
       <c r="I382" s="16"/>
-      <c r="J382" s="17"/>
-      <c r="K382" s="12"/>
-      <c r="L382" s="18"/>
     </row>
     <row r="383" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A383" s="13">
-        <v>999.07</v>
+        <v>999.05</v>
       </c>
       <c r="B383" s="14" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C383" s="14" t="s">
-        <v>88</v>
+        <v>381</v>
       </c>
       <c r="D383" s="15">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="E383" s="14" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="F383" s="14"/>
-      <c r="G383" s="12"/>
+      <c r="G383" s="12" t="s">
+        <v>1424</v>
+      </c>
       <c r="H383" s="14"/>
       <c r="I383" s="16"/>
-      <c r="J383" s="17"/>
-      <c r="K383" s="12"/>
-      <c r="L383" s="18"/>
     </row>
     <row r="384" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A384" s="13">
-        <v>999.08</v>
+        <v>999.06</v>
       </c>
       <c r="B384" s="14" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="C384" s="14" t="s">
-        <v>661</v>
+        <v>38</v>
       </c>
       <c r="D384" s="15">
-        <v>25</v>
+        <v>141</v>
       </c>
       <c r="E384" s="14" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="F384" s="14"/>
       <c r="G384" s="12"/>
       <c r="H384" s="14"/>
       <c r="I384" s="16"/>
+      <c r="J384" s="17"/>
+      <c r="K384" s="12"/>
+      <c r="L384" s="18"/>
     </row>
     <row r="385" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A385" s="13">
-        <v>999.09</v>
+        <v>999.07</v>
       </c>
       <c r="B385" s="14" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="C385" s="14" t="s">
-        <v>782</v>
+        <v>88</v>
       </c>
       <c r="D385" s="15">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E385" s="14" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="F385" s="14"/>
-      <c r="G385" s="12"/>
+      <c r="G385" s="12" t="s">
+        <v>1429</v>
+      </c>
       <c r="H385" s="14"/>
       <c r="I385" s="16"/>
     </row>
     <row r="386" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A386" s="13">
-        <v>999.1</v>
+        <v>999.08</v>
       </c>
       <c r="B386" s="14" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="C386" s="14" t="s">
-        <v>38</v>
+        <v>661</v>
       </c>
       <c r="D386" s="15">
-        <v>136</v>
+        <v>25</v>
       </c>
       <c r="E386" s="14" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="F386" s="14"/>
-      <c r="G386" s="12"/>
+      <c r="G386" s="12" t="s">
+        <v>1432</v>
+      </c>
       <c r="H386" s="14"/>
       <c r="I386" s="16"/>
-      <c r="J386" s="17"/>
-      <c r="K386" s="12"/>
-      <c r="L386" s="18"/>
     </row>
     <row r="387" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A387" s="13">
-        <v>999.11</v>
-      </c>
-      <c r="B387" s="14"/>
-      <c r="C387" s="14"/>
-      <c r="D387" s="15"/>
+        <v>999.09</v>
+      </c>
+      <c r="B387" s="14" t="s">
+        <v>1433</v>
+      </c>
+      <c r="C387" s="14" t="s">
+        <v>782</v>
+      </c>
+      <c r="D387" s="15">
+        <v>4</v>
+      </c>
       <c r="E387" s="14" t="s">
-        <v>1429</v>
+        <v>1434</v>
       </c>
       <c r="F387" s="14"/>
-      <c r="G387" s="12"/>
+      <c r="G387" s="12" t="s">
+        <v>1435</v>
+      </c>
       <c r="H387" s="14"/>
       <c r="I387" s="16"/>
     </row>
     <row r="388" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A388" s="13">
-        <v>999.12</v>
+        <v>999.1</v>
       </c>
       <c r="B388" s="14" t="s">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="C388" s="14" t="s">
-        <v>317</v>
+        <v>38</v>
       </c>
       <c r="D388" s="15">
-        <v>27</v>
+        <v>136</v>
       </c>
       <c r="E388" s="14" t="s">
-        <v>1431</v>
+        <v>1437</v>
       </c>
       <c r="F388" s="14"/>
       <c r="G388" s="12"/>
-      <c r="H388" s="12"/>
+      <c r="H388" s="14"/>
       <c r="I388" s="16"/>
+      <c r="J388" s="17"/>
+      <c r="K388" s="12"/>
+      <c r="L388" s="18"/>
     </row>
     <row r="389" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A389" s="13">
-        <v>999.13</v>
-      </c>
-      <c r="B389" s="14" t="s">
-        <v>1432</v>
-      </c>
-      <c r="C389" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D389" s="15">
-        <v>157</v>
-      </c>
+        <v>999.11</v>
+      </c>
+      <c r="B389" s="14"/>
+      <c r="C389" s="14"/>
+      <c r="D389" s="15"/>
       <c r="E389" s="14" t="s">
-        <v>1433</v>
+        <v>1438</v>
       </c>
       <c r="F389" s="14"/>
-      <c r="G389" s="12"/>
+      <c r="G389" s="12" t="s">
+        <v>1439</v>
+      </c>
       <c r="H389" s="14"/>
       <c r="I389" s="16"/>
     </row>
     <row r="390" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A390" s="13">
-        <v>999.14</v>
-      </c>
-      <c r="B390" s="14" t="s">
-        <v>1434</v>
-      </c>
-      <c r="C390" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="D390" s="15">
-        <v>33</v>
-      </c>
+        <v>999.111</v>
+      </c>
+      <c r="B390" s="14"/>
+      <c r="C390" s="14"/>
+      <c r="D390" s="15"/>
       <c r="E390" s="14" t="s">
-        <v>1435</v>
+        <v>1440</v>
       </c>
       <c r="F390" s="14"/>
-      <c r="G390" s="12"/>
+      <c r="G390" s="12" t="s">
+        <v>1441</v>
+      </c>
       <c r="H390" s="14"/>
       <c r="I390" s="16"/>
-      <c r="J390" s="12"/>
-      <c r="K390" s="12"/>
-      <c r="L390" s="18" t="s">
-        <v>1436</v>
-      </c>
     </row>
     <row r="391" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A391" s="13">
-        <v>999.15</v>
-      </c>
-      <c r="B391" s="14" t="s">
-        <v>1437</v>
-      </c>
-      <c r="C391" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="D391" s="15">
-        <v>49</v>
-      </c>
+        <v>999.112</v>
+      </c>
+      <c r="B391" s="14"/>
+      <c r="C391" s="14"/>
+      <c r="D391" s="15"/>
       <c r="E391" s="14" t="s">
-        <v>1438</v>
+        <v>1442</v>
       </c>
       <c r="F391" s="14"/>
-      <c r="G391" s="12"/>
+      <c r="G391" s="12" t="s">
+        <v>1443</v>
+      </c>
       <c r="H391" s="14"/>
       <c r="I391" s="16"/>
-      <c r="J391" s="17"/>
-      <c r="K391" s="12"/>
-      <c r="L391" s="18"/>
     </row>
     <row r="392" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A392" s="13">
-        <v>999.16</v>
-      </c>
-      <c r="B392" s="14" t="s">
-        <v>1439</v>
-      </c>
-      <c r="C392" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D392" s="15">
-        <v>105</v>
-      </c>
+        <v>999.113</v>
+      </c>
+      <c r="B392" s="14"/>
+      <c r="C392" s="14"/>
+      <c r="D392" s="15"/>
       <c r="E392" s="14" t="s">
-        <v>1440</v>
+        <v>1444</v>
       </c>
       <c r="F392" s="14"/>
-      <c r="G392" s="12"/>
+      <c r="G392" s="12" t="s">
+        <v>1445</v>
+      </c>
       <c r="H392" s="14"/>
       <c r="I392" s="16"/>
     </row>
     <row r="393" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A393" s="13">
-        <v>999.17</v>
-      </c>
-      <c r="B393" s="14"/>
-      <c r="C393" s="14"/>
-      <c r="D393" s="15"/>
+        <v>999.12</v>
+      </c>
+      <c r="B393" s="14" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C393" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="D393" s="15">
+        <v>27</v>
+      </c>
       <c r="E393" s="14" t="s">
-        <v>1441</v>
+        <v>1447</v>
       </c>
       <c r="F393" s="14"/>
-      <c r="G393" s="12"/>
+      <c r="G393" s="12" t="s">
+        <v>1448</v>
+      </c>
       <c r="H393" s="14"/>
       <c r="I393" s="16"/>
     </row>
     <row r="394" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A394" s="13">
-        <v>999.18</v>
-      </c>
-      <c r="B394" s="14"/>
-      <c r="C394" s="14"/>
-      <c r="D394" s="15"/>
+        <v>999.12</v>
+      </c>
+      <c r="B394" s="12"/>
+      <c r="C394" s="12"/>
+      <c r="D394" s="12"/>
       <c r="E394" s="14" t="s">
-        <v>1442</v>
+        <v>1447</v>
       </c>
       <c r="F394" s="14"/>
       <c r="G394" s="12"/>
@@ -20184,608 +20683,536 @@
     </row>
     <row r="395" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A395" s="13">
-        <v>999.19</v>
-      </c>
-      <c r="B395" s="12"/>
-      <c r="C395" s="14"/>
-      <c r="D395" s="26"/>
+        <v>999.13</v>
+      </c>
+      <c r="B395" s="14" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C395" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D395" s="15">
+        <v>157</v>
+      </c>
       <c r="E395" s="14" t="s">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="F395" s="14"/>
-      <c r="G395" s="12" t="s">
-        <v>1444</v>
-      </c>
+      <c r="G395" s="12"/>
       <c r="H395" s="14"/>
       <c r="I395" s="16"/>
     </row>
     <row r="396" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A396" s="13">
-        <v>999.191</v>
+        <v>999.14</v>
       </c>
       <c r="B396" s="14" t="s">
-        <v>1445</v>
+        <v>1451</v>
       </c>
       <c r="C396" s="14" t="s">
-        <v>38</v>
+        <v>317</v>
       </c>
       <c r="D396" s="15">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="E396" s="14" t="s">
-        <v>1446</v>
+        <v>1452</v>
       </c>
       <c r="F396" s="14"/>
-      <c r="G396" s="12"/>
+      <c r="G396" s="12" t="s">
+        <v>1453</v>
+      </c>
       <c r="H396" s="14"/>
-      <c r="I396" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="J396" s="12" t="s">
-        <v>1447</v>
+      <c r="I396" s="16"/>
+      <c r="J396" s="12"/>
+      <c r="K396" s="12"/>
+      <c r="L396" s="18" t="s">
+        <v>1454</v>
       </c>
     </row>
     <row r="397" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A397" s="13">
-        <v>999.192</v>
+        <v>999.15</v>
       </c>
       <c r="B397" s="14" t="s">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="C397" s="14" t="s">
-        <v>38</v>
+        <v>317</v>
       </c>
       <c r="D397" s="15">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="E397" s="14" t="s">
-        <v>1449</v>
+        <v>1456</v>
       </c>
       <c r="F397" s="14"/>
-      <c r="G397" s="12"/>
+      <c r="G397" s="12" t="s">
+        <v>1457</v>
+      </c>
       <c r="H397" s="14"/>
-      <c r="I397" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="J397" s="12" t="s">
-        <v>271</v>
-      </c>
+      <c r="I397" s="16"/>
     </row>
     <row r="398" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A398" s="13">
-        <v>999.2</v>
+        <v>999.16</v>
       </c>
       <c r="B398" s="14" t="s">
-        <v>1450</v>
+        <v>1458</v>
       </c>
       <c r="C398" s="14" t="s">
         <v>88</v>
       </c>
       <c r="D398" s="15">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="E398" s="14" t="s">
-        <v>1451</v>
+        <v>1459</v>
       </c>
       <c r="F398" s="14"/>
-      <c r="G398" s="12"/>
-      <c r="H398" s="12"/>
+      <c r="G398" s="12" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H398" s="14"/>
       <c r="I398" s="16"/>
     </row>
     <row r="399" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A399" s="13">
-        <v>999.21</v>
-      </c>
-      <c r="B399" s="14" t="s">
-        <v>1452</v>
-      </c>
-      <c r="C399" s="14" t="s">
-        <v>661</v>
-      </c>
-      <c r="D399" s="15">
-        <v>29</v>
-      </c>
+        <v>999.17</v>
+      </c>
+      <c r="B399" s="14"/>
+      <c r="C399" s="14"/>
+      <c r="D399" s="15"/>
       <c r="E399" s="14" t="s">
-        <v>1453</v>
+        <v>1461</v>
       </c>
       <c r="F399" s="14"/>
-      <c r="G399" s="12"/>
+      <c r="G399" s="12" t="s">
+        <v>1462</v>
+      </c>
       <c r="H399" s="14"/>
       <c r="I399" s="16"/>
     </row>
     <row r="400" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A400" s="13">
-        <v>999.22</v>
-      </c>
-      <c r="B400" s="14" t="s">
-        <v>1454</v>
-      </c>
-      <c r="C400" s="14" t="s">
-        <v>661</v>
-      </c>
-      <c r="D400" s="15">
-        <v>32</v>
-      </c>
+        <v>999.171</v>
+      </c>
+      <c r="B400" s="14"/>
+      <c r="C400" s="14"/>
+      <c r="D400" s="15"/>
       <c r="E400" s="14" t="s">
-        <v>1455</v>
+        <v>1463</v>
       </c>
       <c r="F400" s="14"/>
-      <c r="G400" s="12"/>
+      <c r="G400" s="12" t="s">
+        <v>1464</v>
+      </c>
       <c r="H400" s="14"/>
       <c r="I400" s="16"/>
     </row>
     <row r="401" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A401" s="13">
-        <v>999.23</v>
-      </c>
-      <c r="B401" s="14" t="s">
-        <v>1456</v>
-      </c>
-      <c r="C401" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D401" s="15">
-        <v>25</v>
-      </c>
+        <v>999.172</v>
+      </c>
+      <c r="B401" s="14"/>
+      <c r="C401" s="14"/>
+      <c r="D401" s="15"/>
       <c r="E401" s="14" t="s">
-        <v>1457</v>
+        <v>1465</v>
       </c>
       <c r="F401" s="14"/>
-      <c r="G401" s="12"/>
+      <c r="G401" s="12" t="s">
+        <v>1466</v>
+      </c>
       <c r="H401" s="14"/>
       <c r="I401" s="16"/>
     </row>
     <row r="402" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A402" s="13">
-        <v>999.24</v>
-      </c>
-      <c r="B402" s="14" t="s">
-        <v>1458</v>
-      </c>
-      <c r="C402" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="D402" s="15" t="s">
-        <v>1459</v>
-      </c>
+        <v>999.18</v>
+      </c>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="15"/>
       <c r="E402" s="14" t="s">
-        <v>1460</v>
-      </c>
-      <c r="F402" s="14">
-        <v>1846</v>
-      </c>
+        <v>1467</v>
+      </c>
+      <c r="F402" s="14"/>
       <c r="G402" s="12" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H402" s="14"/>
       <c r="I402" s="16"/>
     </row>
     <row r="403" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A403" s="13">
-        <v>999.25</v>
-      </c>
-      <c r="B403" s="14" t="s">
-        <v>1462</v>
-      </c>
-      <c r="C403" s="14" t="s">
-        <v>307</v>
-      </c>
-      <c r="D403" s="15">
-        <v>9</v>
-      </c>
+        <v>999.181</v>
+      </c>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="15"/>
       <c r="E403" s="14" t="s">
-        <v>1463</v>
+        <v>1468</v>
       </c>
       <c r="F403" s="14"/>
       <c r="G403" s="12" t="s">
-        <v>1464</v>
+        <v>1469</v>
       </c>
       <c r="H403" s="14"/>
-      <c r="I403" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J403" s="12"/>
-      <c r="K403" s="12" t="s">
-        <v>1465</v>
-      </c>
-      <c r="L403" s="12" t="s">
-        <v>1466</v>
-      </c>
+      <c r="I403" s="16"/>
     </row>
     <row r="404" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A404" s="13">
-        <v>999.26</v>
+        <v>999.182</v>
       </c>
       <c r="B404" s="14"/>
       <c r="C404" s="14"/>
       <c r="D404" s="15"/>
       <c r="E404" s="14" t="s">
-        <v>1467</v>
-      </c>
-      <c r="F404" s="14">
-        <v>1846</v>
-      </c>
+        <v>1470</v>
+      </c>
+      <c r="F404" s="14"/>
       <c r="G404" s="12" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="H404" s="14"/>
-      <c r="I404" s="16" t="s">
-        <v>65</v>
-      </c>
+      <c r="I404" s="16"/>
     </row>
     <row r="405" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A405" s="13">
-        <v>999.27</v>
-      </c>
-      <c r="B405" s="14" t="s">
-        <v>1469</v>
-      </c>
-      <c r="C405" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="D405" s="15">
-        <v>47</v>
-      </c>
+        <v>999.19</v>
+      </c>
+      <c r="B405" s="12"/>
+      <c r="C405" s="14"/>
+      <c r="D405" s="26"/>
       <c r="E405" s="14" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F405" s="14">
-        <v>1844</v>
-      </c>
+        <v>1472</v>
+      </c>
+      <c r="F405" s="14"/>
       <c r="G405" s="12" t="s">
-        <v>1471</v>
-      </c>
-      <c r="H405" s="12"/>
-      <c r="I405" s="16" t="s">
-        <v>128</v>
-      </c>
+        <v>1473</v>
+      </c>
+      <c r="H405" s="14"/>
+      <c r="I405" s="16"/>
     </row>
     <row r="406" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A406" s="13">
-        <v>999.27</v>
+        <v>999.191</v>
       </c>
       <c r="B406" s="14" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C406" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="D406" s="15" t="s">
-        <v>1473</v>
+        <v>38</v>
+      </c>
+      <c r="D406" s="15">
+        <v>93</v>
       </c>
       <c r="E406" s="14" t="s">
-        <v>1470</v>
-      </c>
-      <c r="F406" s="14">
-        <v>1846</v>
-      </c>
-      <c r="G406" s="12" t="s">
-        <v>1474</v>
-      </c>
+        <v>1475</v>
+      </c>
+      <c r="F406" s="14"/>
+      <c r="G406" s="12"/>
       <c r="H406" s="14"/>
-      <c r="I406" s="16"/>
+      <c r="I406" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="J406" s="12" t="s">
+        <v>1476</v>
+      </c>
     </row>
     <row r="407" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A407" s="13">
-        <v>999.28</v>
+        <v>999.192</v>
       </c>
       <c r="B407" s="14" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C407" s="14" t="s">
-        <v>317</v>
+        <v>38</v>
       </c>
       <c r="D407" s="15">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="E407" s="14" t="s">
-        <v>1476</v>
-      </c>
-      <c r="F407" s="14" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G407" s="12" t="s">
-        <v>1477</v>
-      </c>
-      <c r="H407" s="14" t="s">
-        <v>384</v>
-      </c>
+        <v>1478</v>
+      </c>
+      <c r="F407" s="14"/>
+      <c r="G407" s="12"/>
+      <c r="H407" s="14"/>
       <c r="I407" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="J407" s="12"/>
-      <c r="K407" s="12"/>
-      <c r="L407" s="18"/>
+        <v>124</v>
+      </c>
+      <c r="J407" s="12" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="408" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A408" s="13">
-        <v>999.29</v>
+        <v>999.2</v>
       </c>
       <c r="B408" s="14" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="C408" s="14" t="s">
-        <v>317</v>
+        <v>88</v>
       </c>
       <c r="D408" s="15">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E408" s="14" t="s">
-        <v>1479</v>
-      </c>
-      <c r="F408" s="14">
-        <v>1832</v>
-      </c>
+        <v>1480</v>
+      </c>
+      <c r="F408" s="14"/>
       <c r="G408" s="12" t="s">
-        <v>1480</v>
-      </c>
-      <c r="H408" s="12"/>
+        <v>1481</v>
+      </c>
+      <c r="H408" s="14"/>
       <c r="I408" s="16"/>
     </row>
     <row r="409" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A409" s="13" t="s">
-        <v>1481</v>
+      <c r="A409" s="13">
+        <v>999.21</v>
       </c>
       <c r="B409" s="14" t="s">
         <v>1482</v>
       </c>
       <c r="C409" s="14" t="s">
-        <v>197</v>
+        <v>661</v>
       </c>
       <c r="D409" s="15">
-        <v>1</v>
-      </c>
-      <c r="E409" s="14"/>
+        <v>29</v>
+      </c>
+      <c r="E409" s="14" t="s">
+        <v>1483</v>
+      </c>
       <c r="F409" s="14"/>
-      <c r="G409" s="12"/>
-      <c r="H409" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I409" s="16" t="s">
+      <c r="G409" s="12" t="s">
+        <v>1484</v>
+      </c>
+      <c r="H409" s="14"/>
+      <c r="I409" s="16"/>
+    </row>
+    <row r="410" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A410" s="13">
+        <v>999.22</v>
+      </c>
+      <c r="B410" s="14" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C410" s="14" t="s">
+        <v>661</v>
+      </c>
+      <c r="D410" s="15">
+        <v>32</v>
+      </c>
+      <c r="E410" s="14" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F410" s="14"/>
+      <c r="G410" s="12" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H410" s="14"/>
+      <c r="I410" s="16"/>
+    </row>
+    <row r="411" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A411" s="13">
+        <v>999.23</v>
+      </c>
+      <c r="B411" s="14" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C411" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D411" s="15">
+        <v>25</v>
+      </c>
+      <c r="E411" s="14" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F411" s="14"/>
+      <c r="G411" s="12" t="s">
+        <v>1490</v>
+      </c>
+      <c r="H411" s="14"/>
+      <c r="I411" s="16"/>
+    </row>
+    <row r="412" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A412" s="13">
+        <v>999.24</v>
+      </c>
+      <c r="B412" s="14" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C412" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="D412" s="15" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E412" s="14" t="s">
+        <v>1493</v>
+      </c>
+      <c r="F412" s="14">
+        <v>1846</v>
+      </c>
+      <c r="G412" s="12" t="s">
+        <v>1494</v>
+      </c>
+      <c r="H412" s="14"/>
+      <c r="I412" s="16"/>
+    </row>
+    <row r="413" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A413" s="13">
+        <v>999.25</v>
+      </c>
+      <c r="B413" s="14" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C413" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D413" s="15">
+        <v>9</v>
+      </c>
+      <c r="E413" s="14" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F413" s="14"/>
+      <c r="G413" s="12" t="s">
+        <v>1497</v>
+      </c>
+      <c r="H413" s="14"/>
+      <c r="I413" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J413" s="12"/>
+      <c r="K413" s="12" t="s">
+        <v>1498</v>
+      </c>
+      <c r="L413" s="12" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="414" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A414" s="13">
+        <v>999.26</v>
+      </c>
+      <c r="B414" s="14"/>
+      <c r="C414" s="14"/>
+      <c r="D414" s="15"/>
+      <c r="E414" s="14" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F414" s="14">
+        <v>1846</v>
+      </c>
+      <c r="G414" s="12" t="s">
+        <v>1501</v>
+      </c>
+      <c r="H414" s="14"/>
+      <c r="I414" s="16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="415" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A415" s="13">
+        <v>999.27</v>
+      </c>
+      <c r="B415" s="14" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C415" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="D415" s="15">
+        <v>47</v>
+      </c>
+      <c r="E415" s="14" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F415" s="14">
+        <v>1844</v>
+      </c>
+      <c r="G415" s="12" t="s">
+        <v>1504</v>
+      </c>
+      <c r="H415" s="12"/>
+      <c r="I415" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="416" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A416" s="13">
+        <v>999.28</v>
+      </c>
+      <c r="B416" s="14" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C416" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="D416" s="15">
+        <v>45</v>
+      </c>
+      <c r="E416" s="14" t="s">
+        <v>1506</v>
+      </c>
+      <c r="F416" s="14" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G416" s="12" t="s">
+        <v>1507</v>
+      </c>
+      <c r="H416" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="I416" s="16" t="s">
         <v>333</v>
       </c>
-      <c r="J409" s="17"/>
-      <c r="K409" s="18" t="s">
-        <v>1483</v>
-      </c>
-      <c r="L409" s="18"/>
-    </row>
-    <row r="410" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A410" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B410" s="14" t="s">
-        <v>1484</v>
-      </c>
-      <c r="C410" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D410" s="15">
-        <v>2</v>
-      </c>
-      <c r="E410" s="14"/>
-      <c r="F410" s="14"/>
-      <c r="G410" s="12"/>
-      <c r="H410" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I410" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="J410" s="17"/>
-      <c r="K410" s="18" t="s">
-        <v>1483</v>
-      </c>
-      <c r="L410" s="18"/>
-    </row>
-    <row r="411" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A411" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B411" s="14" t="s">
-        <v>1485</v>
-      </c>
-      <c r="C411" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D411" s="15">
-        <v>3</v>
-      </c>
-      <c r="E411" s="14"/>
-      <c r="F411" s="14"/>
-      <c r="G411" s="12"/>
-      <c r="H411" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I411" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="J411" s="17"/>
-      <c r="K411" s="18" t="s">
-        <v>1483</v>
-      </c>
-      <c r="L411" s="18"/>
-    </row>
-    <row r="412" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A412" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B412" s="14" t="s">
-        <v>1486</v>
-      </c>
-      <c r="C412" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D412" s="15">
-        <v>4</v>
-      </c>
-      <c r="E412" s="14"/>
-      <c r="F412" s="14"/>
-      <c r="G412" s="12"/>
-      <c r="H412" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I412" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="J412" s="17"/>
-      <c r="K412" s="18" t="s">
-        <v>1483</v>
-      </c>
-      <c r="L412" s="18"/>
-    </row>
-    <row r="413" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A413" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B413" s="14" t="s">
-        <v>1487</v>
-      </c>
-      <c r="C413" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D413" s="15">
-        <v>5</v>
-      </c>
-      <c r="E413" s="14"/>
-      <c r="F413" s="14"/>
-      <c r="G413" s="12"/>
-      <c r="H413" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I413" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="J413" s="17"/>
-      <c r="K413" s="18" t="s">
-        <v>1483</v>
-      </c>
-      <c r="L413" s="18"/>
-    </row>
-    <row r="414" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A414" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B414" s="14" t="s">
-        <v>1488</v>
-      </c>
-      <c r="C414" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D414" s="15">
-        <v>6</v>
-      </c>
-      <c r="E414" s="14"/>
-      <c r="F414" s="14"/>
-      <c r="G414" s="12"/>
-      <c r="H414" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I414" s="16" t="s">
-        <v>128</v>
-      </c>
-      <c r="J414" s="17"/>
-      <c r="K414" s="18" t="s">
-        <v>1483</v>
-      </c>
-      <c r="L414" s="18"/>
-    </row>
-    <row r="415" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A415" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B415" s="14" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C415" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D415" s="15">
-        <v>7</v>
-      </c>
-      <c r="E415" s="14"/>
-      <c r="F415" s="14"/>
-      <c r="G415" s="12"/>
-      <c r="H415" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I415" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="J415" s="17"/>
-      <c r="K415" s="18" t="s">
-        <v>1483</v>
-      </c>
-      <c r="L415" s="18"/>
-    </row>
-    <row r="416" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A416" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B416" s="14" t="s">
-        <v>1490</v>
-      </c>
-      <c r="C416" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D416" s="15">
-        <v>8</v>
-      </c>
-      <c r="E416" s="14"/>
-      <c r="F416" s="14"/>
-      <c r="G416" s="12"/>
-      <c r="H416" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I416" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="J416" s="17"/>
-      <c r="K416" s="18" t="s">
-        <v>1483</v>
-      </c>
+      <c r="J416" s="12"/>
+      <c r="K416" s="12"/>
       <c r="L416" s="18"/>
     </row>
     <row r="417" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A417" s="13" t="s">
-        <v>1481</v>
+      <c r="A417" s="13">
+        <v>999.29</v>
       </c>
       <c r="B417" s="14" t="s">
-        <v>1491</v>
+        <v>1508</v>
       </c>
       <c r="C417" s="14" t="s">
-        <v>197</v>
+        <v>317</v>
       </c>
       <c r="D417" s="15">
-        <v>9</v>
-      </c>
-      <c r="E417" s="14"/>
-      <c r="F417" s="14"/>
-      <c r="G417" s="12"/>
-      <c r="H417" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I417" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="J417" s="17"/>
-      <c r="K417" s="18" t="s">
-        <v>1483</v>
-      </c>
-      <c r="L417" s="18"/>
+        <v>25</v>
+      </c>
+      <c r="E417" s="14" t="s">
+        <v>1509</v>
+      </c>
+      <c r="F417" s="14">
+        <v>1832</v>
+      </c>
+      <c r="G417" s="12" t="s">
+        <v>1510</v>
+      </c>
+      <c r="H417" s="12"/>
+      <c r="I417" s="16"/>
     </row>
     <row r="418" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A418" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B418" s="14" t="s">
-        <v>1492</v>
+        <v>1512</v>
       </c>
       <c r="C418" s="14" t="s">
         <v>197</v>
       </c>
       <c r="D418" s="15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E418" s="14"/>
       <c r="F418" s="14"/>
@@ -20794,26 +21221,26 @@
         <v>200</v>
       </c>
       <c r="I418" s="16" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="J418" s="17"/>
       <c r="K418" s="18" t="s">
-        <v>1483</v>
+        <v>1513</v>
       </c>
       <c r="L418" s="18"/>
     </row>
     <row r="419" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A419" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B419" s="14" t="s">
-        <v>1493</v>
+        <v>1514</v>
       </c>
       <c r="C419" s="14" t="s">
         <v>197</v>
       </c>
       <c r="D419" s="15">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E419" s="14"/>
       <c r="F419" s="14"/>
@@ -20822,26 +21249,26 @@
         <v>200</v>
       </c>
       <c r="I419" s="16" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="J419" s="17"/>
       <c r="K419" s="18" t="s">
-        <v>1483</v>
+        <v>1513</v>
       </c>
       <c r="L419" s="18"/>
     </row>
     <row r="420" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A420" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B420" s="14" t="s">
-        <v>1494</v>
+        <v>1515</v>
       </c>
       <c r="C420" s="14" t="s">
         <v>197</v>
       </c>
       <c r="D420" s="15">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E420" s="14"/>
       <c r="F420" s="14"/>
@@ -20850,26 +21277,26 @@
         <v>200</v>
       </c>
       <c r="I420" s="16" t="s">
-        <v>124</v>
+        <v>56</v>
       </c>
       <c r="J420" s="17"/>
       <c r="K420" s="18" t="s">
-        <v>1483</v>
+        <v>1513</v>
       </c>
       <c r="L420" s="18"/>
     </row>
     <row r="421" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A421" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B421" s="14" t="s">
-        <v>196</v>
+        <v>1516</v>
       </c>
       <c r="C421" s="14" t="s">
         <v>197</v>
       </c>
       <c r="D421" s="15">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E421" s="14"/>
       <c r="F421" s="14"/>
@@ -20882,239 +21309,293 @@
       </c>
       <c r="J421" s="17"/>
       <c r="K421" s="18" t="s">
-        <v>1483</v>
+        <v>1513</v>
       </c>
       <c r="L421" s="18"/>
     </row>
     <row r="422" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A422" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B422" s="14" t="s">
-        <v>1495</v>
+        <v>1517</v>
       </c>
       <c r="C422" s="14" t="s">
-        <v>14</v>
+        <v>197</v>
       </c>
       <c r="D422" s="15">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E422" s="14"/>
       <c r="F422" s="14"/>
-      <c r="G422" s="12" t="s">
-        <v>1496</v>
-      </c>
-      <c r="H422" s="14"/>
+      <c r="G422" s="12"/>
+      <c r="H422" s="14" t="s">
+        <v>200</v>
+      </c>
       <c r="I422" s="16" t="s">
         <v>465</v>
       </c>
       <c r="J422" s="17"/>
       <c r="K422" s="18" t="s">
-        <v>1497</v>
+        <v>1513</v>
       </c>
       <c r="L422" s="18"/>
     </row>
     <row r="423" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A423" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B423" s="14"/>
-      <c r="C423" s="14"/>
-      <c r="D423" s="15"/>
+        <v>1511</v>
+      </c>
+      <c r="B423" s="14" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C423" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D423" s="15">
+        <v>6</v>
+      </c>
       <c r="E423" s="14"/>
       <c r="F423" s="14"/>
       <c r="G423" s="12"/>
       <c r="H423" s="14" t="s">
-        <v>338</v>
+        <v>200</v>
       </c>
       <c r="I423" s="16" t="s">
-        <v>413</v>
+        <v>128</v>
       </c>
       <c r="J423" s="17"/>
       <c r="K423" s="18" t="s">
-        <v>1465</v>
+        <v>1513</v>
       </c>
       <c r="L423" s="18"/>
     </row>
     <row r="424" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A424" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B424" s="14"/>
-      <c r="C424" s="14"/>
-      <c r="D424" s="15"/>
+        <v>1511</v>
+      </c>
+      <c r="B424" s="14" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C424" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D424" s="15">
+        <v>7</v>
+      </c>
       <c r="E424" s="14"/>
       <c r="F424" s="14"/>
       <c r="G424" s="12"/>
       <c r="H424" s="14" t="s">
-        <v>338</v>
+        <v>200</v>
       </c>
       <c r="I424" s="16" t="s">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="J424" s="17"/>
       <c r="K424" s="18" t="s">
-        <v>1465</v>
+        <v>1513</v>
       </c>
       <c r="L424" s="18"/>
     </row>
     <row r="425" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A425" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B425" s="14"/>
-      <c r="C425" s="14"/>
-      <c r="D425" s="15"/>
+        <v>1511</v>
+      </c>
+      <c r="B425" s="14" t="s">
+        <v>1520</v>
+      </c>
+      <c r="C425" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D425" s="15">
+        <v>8</v>
+      </c>
       <c r="E425" s="14"/>
       <c r="F425" s="14"/>
       <c r="G425" s="12"/>
       <c r="H425" s="14" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="I425" s="16" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="J425" s="17"/>
       <c r="K425" s="18" t="s">
-        <v>1498</v>
+        <v>1513</v>
       </c>
       <c r="L425" s="18"/>
     </row>
     <row r="426" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A426" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B426" s="14"/>
-      <c r="C426" s="14"/>
-      <c r="D426" s="15"/>
+        <v>1511</v>
+      </c>
+      <c r="B426" s="14" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C426" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D426" s="15">
+        <v>9</v>
+      </c>
       <c r="E426" s="14"/>
       <c r="F426" s="14"/>
       <c r="G426" s="12"/>
       <c r="H426" s="14" t="s">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="I426" s="16" t="s">
-        <v>128</v>
+        <v>333</v>
       </c>
       <c r="J426" s="17"/>
       <c r="K426" s="18" t="s">
-        <v>1499</v>
+        <v>1513</v>
       </c>
       <c r="L426" s="18"/>
     </row>
     <row r="427" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A427" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B427" s="14"/>
-      <c r="C427" s="14"/>
-      <c r="D427" s="15"/>
+        <v>1511</v>
+      </c>
+      <c r="B427" s="14" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C427" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D427" s="15">
+        <v>10</v>
+      </c>
       <c r="E427" s="14"/>
       <c r="F427" s="14"/>
       <c r="G427" s="12"/>
       <c r="H427" s="14" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="I427" s="16" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="J427" s="17"/>
       <c r="K427" s="18" t="s">
-        <v>477</v>
+        <v>1513</v>
       </c>
       <c r="L427" s="18"/>
     </row>
     <row r="428" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A428" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B428" s="14"/>
-      <c r="C428" s="14"/>
-      <c r="D428" s="15"/>
+        <v>1511</v>
+      </c>
+      <c r="B428" s="14" t="s">
+        <v>1523</v>
+      </c>
+      <c r="C428" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D428" s="15">
+        <v>11</v>
+      </c>
       <c r="E428" s="14"/>
       <c r="F428" s="14"/>
       <c r="G428" s="12"/>
       <c r="H428" s="14" t="s">
-        <v>438</v>
+        <v>200</v>
       </c>
       <c r="I428" s="16" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="J428" s="17"/>
       <c r="K428" s="18" t="s">
-        <v>477</v>
+        <v>1513</v>
       </c>
       <c r="L428" s="18"/>
     </row>
     <row r="429" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A429" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B429" s="14"/>
-      <c r="C429" s="14"/>
-      <c r="D429" s="15"/>
+        <v>1511</v>
+      </c>
+      <c r="B429" s="14" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C429" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D429" s="15">
+        <v>12</v>
+      </c>
       <c r="E429" s="14"/>
       <c r="F429" s="14"/>
       <c r="G429" s="12"/>
       <c r="H429" s="14" t="s">
-        <v>438</v>
+        <v>200</v>
       </c>
       <c r="I429" s="16" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="J429" s="17"/>
       <c r="K429" s="18" t="s">
-        <v>477</v>
+        <v>1513</v>
       </c>
       <c r="L429" s="18"/>
     </row>
     <row r="430" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A430" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B430" s="14"/>
-      <c r="C430" s="14"/>
-      <c r="D430" s="15"/>
+        <v>1511</v>
+      </c>
+      <c r="B430" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C430" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D430" s="15">
+        <v>13</v>
+      </c>
       <c r="E430" s="14"/>
       <c r="F430" s="14"/>
       <c r="G430" s="12"/>
       <c r="H430" s="14" t="s">
-        <v>438</v>
+        <v>200</v>
       </c>
       <c r="I430" s="16" t="s">
-        <v>1500</v>
+        <v>17</v>
       </c>
       <c r="J430" s="17"/>
       <c r="K430" s="18" t="s">
-        <v>477</v>
+        <v>1513</v>
       </c>
       <c r="L430" s="18"/>
     </row>
     <row r="431" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A431" s="13" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B431" s="14"/>
-      <c r="C431" s="14"/>
-      <c r="D431" s="15"/>
+        <v>1511</v>
+      </c>
+      <c r="B431" s="14" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C431" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D431" s="15">
+        <v>20</v>
+      </c>
       <c r="E431" s="14"/>
       <c r="F431" s="14"/>
       <c r="G431" s="12" t="s">
-        <v>1501</v>
-      </c>
-      <c r="H431" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I431" s="16"/>
+        <v>1526</v>
+      </c>
+      <c r="H431" s="14"/>
+      <c r="I431" s="16" t="s">
+        <v>465</v>
+      </c>
       <c r="J431" s="17"/>
       <c r="K431" s="18" t="s">
-        <v>477</v>
+        <v>1527</v>
       </c>
       <c r="L431" s="18"/>
     </row>
     <row r="432" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A432" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B432" s="14"/>
       <c r="C432" s="14"/>
@@ -21122,21 +21603,19 @@
       <c r="E432" s="14"/>
       <c r="F432" s="14"/>
       <c r="G432" s="12" t="s">
-        <v>1502</v>
-      </c>
-      <c r="H432" s="14" t="s">
-        <v>52</v>
-      </c>
+        <v>1528</v>
+      </c>
+      <c r="H432" s="14"/>
       <c r="I432" s="16"/>
       <c r="J432" s="17"/>
       <c r="K432" s="18" t="s">
-        <v>477</v>
+        <v>1529</v>
       </c>
       <c r="L432" s="18"/>
     </row>
     <row r="433" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A433" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B433" s="14"/>
       <c r="C433" s="14"/>
@@ -21144,21 +21623,21 @@
       <c r="E433" s="14"/>
       <c r="F433" s="14"/>
       <c r="G433" s="12" t="s">
-        <v>1503</v>
+        <v>1530</v>
       </c>
       <c r="H433" s="14" t="s">
-        <v>52</v>
+        <v>1304</v>
       </c>
       <c r="I433" s="16"/>
       <c r="J433" s="17"/>
       <c r="K433" s="18" t="s">
-        <v>477</v>
+        <v>44</v>
       </c>
       <c r="L433" s="18"/>
     </row>
     <row r="434" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A434" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B434" s="14"/>
       <c r="C434" s="14"/>
@@ -21166,7 +21645,7 @@
       <c r="E434" s="14"/>
       <c r="F434" s="14"/>
       <c r="G434" s="12" t="s">
-        <v>1504</v>
+        <v>1531</v>
       </c>
       <c r="H434" s="14" t="s">
         <v>52</v>
@@ -21180,29 +21659,29 @@
     </row>
     <row r="435" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A435" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B435" s="14"/>
       <c r="C435" s="14"/>
       <c r="D435" s="15"/>
       <c r="E435" s="14"/>
       <c r="F435" s="14"/>
-      <c r="G435" s="12"/>
+      <c r="G435" s="12" t="s">
+        <v>1531</v>
+      </c>
       <c r="H435" s="14" t="s">
-        <v>1296</v>
-      </c>
-      <c r="I435" s="16" t="s">
-        <v>17</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="I435" s="16"/>
       <c r="J435" s="17"/>
       <c r="K435" s="18" t="s">
-        <v>477</v>
+        <v>44</v>
       </c>
       <c r="L435" s="18"/>
     </row>
     <row r="436" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A436" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B436" s="14"/>
       <c r="C436" s="14"/>
@@ -21210,21 +21689,21 @@
       <c r="E436" s="14"/>
       <c r="F436" s="14"/>
       <c r="G436" s="12" t="s">
-        <v>562</v>
-      </c>
-      <c r="H436" s="14"/>
-      <c r="I436" s="16" t="s">
-        <v>1500</v>
-      </c>
+        <v>1531</v>
+      </c>
+      <c r="H436" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I436" s="16"/>
       <c r="J436" s="17"/>
       <c r="K436" s="18" t="s">
-        <v>477</v>
+        <v>44</v>
       </c>
       <c r="L436" s="18"/>
     </row>
     <row r="437" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A437" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B437" s="14"/>
       <c r="C437" s="14"/>
@@ -21232,12 +21711,12 @@
       <c r="E437" s="14"/>
       <c r="F437" s="14"/>
       <c r="G437" s="12" t="s">
-        <v>1505</v>
-      </c>
-      <c r="H437" s="14"/>
-      <c r="I437" s="16" t="s">
-        <v>1500</v>
-      </c>
+        <v>1532</v>
+      </c>
+      <c r="H437" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I437" s="16"/>
       <c r="J437" s="17"/>
       <c r="K437" s="18" t="s">
         <v>477</v>
@@ -21246,7 +21725,7 @@
     </row>
     <row r="438" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A438" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B438" s="14"/>
       <c r="C438" s="14"/>
@@ -21254,21 +21733,21 @@
       <c r="E438" s="14"/>
       <c r="F438" s="14"/>
       <c r="G438" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="H438" s="14"/>
-      <c r="I438" s="16" t="s">
-        <v>65</v>
-      </c>
+        <v>1532</v>
+      </c>
+      <c r="H438" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I438" s="16"/>
       <c r="J438" s="17"/>
       <c r="K438" s="18" t="s">
-        <v>477</v>
+        <v>44</v>
       </c>
       <c r="L438" s="18"/>
     </row>
     <row r="439" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A439" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B439" s="14"/>
       <c r="C439" s="14"/>
@@ -21276,21 +21755,19 @@
       <c r="E439" s="14"/>
       <c r="F439" s="14"/>
       <c r="G439" s="12" t="s">
-        <v>1506</v>
+        <v>1533</v>
       </c>
       <c r="H439" s="14"/>
-      <c r="I439" s="16" t="s">
-        <v>413</v>
-      </c>
+      <c r="I439" s="16"/>
       <c r="J439" s="17"/>
       <c r="K439" s="18" t="s">
-        <v>477</v>
+        <v>44</v>
       </c>
       <c r="L439" s="18"/>
     </row>
     <row r="440" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A440" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B440" s="14"/>
       <c r="C440" s="14"/>
@@ -21298,12 +21775,12 @@
       <c r="E440" s="14"/>
       <c r="F440" s="14"/>
       <c r="G440" s="12" t="s">
-        <v>1506</v>
-      </c>
-      <c r="H440" s="14"/>
-      <c r="I440" s="16" t="s">
-        <v>65</v>
-      </c>
+        <v>1534</v>
+      </c>
+      <c r="H440" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I440" s="16"/>
       <c r="J440" s="17"/>
       <c r="K440" s="18" t="s">
         <v>477</v>
@@ -21312,7 +21789,7 @@
     </row>
     <row r="441" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A441" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B441" s="14"/>
       <c r="C441" s="14"/>
@@ -21320,19 +21797,21 @@
       <c r="E441" s="14"/>
       <c r="F441" s="14"/>
       <c r="G441" s="12" t="s">
-        <v>1507</v>
-      </c>
-      <c r="H441" s="14"/>
+        <v>1535</v>
+      </c>
+      <c r="H441" s="14" t="s">
+        <v>52</v>
+      </c>
       <c r="I441" s="16"/>
       <c r="J441" s="17"/>
       <c r="K441" s="18" t="s">
-        <v>477</v>
+        <v>44</v>
       </c>
       <c r="L441" s="18"/>
     </row>
     <row r="442" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A442" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B442" s="14"/>
       <c r="C442" s="14"/>
@@ -21340,55 +21819,55 @@
       <c r="E442" s="14"/>
       <c r="F442" s="14"/>
       <c r="G442" s="12" t="s">
-        <v>1508</v>
+        <v>1536</v>
       </c>
       <c r="H442" s="14" t="s">
-        <v>1304</v>
+        <v>52</v>
       </c>
       <c r="I442" s="16"/>
       <c r="J442" s="17"/>
       <c r="K442" s="18" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="L442" s="18"/>
     </row>
     <row r="443" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A443" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B443" s="14"/>
       <c r="C443" s="14"/>
       <c r="D443" s="15"/>
       <c r="E443" s="14"/>
       <c r="F443" s="14"/>
-      <c r="G443" s="12"/>
-      <c r="H443" s="14" t="s">
-        <v>1304</v>
-      </c>
+      <c r="G443" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="H443" s="14"/>
       <c r="I443" s="16" t="s">
-        <v>333</v>
+        <v>1537</v>
       </c>
       <c r="J443" s="17"/>
       <c r="K443" s="18" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="L443" s="18"/>
     </row>
     <row r="444" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A444" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B444" s="14"/>
       <c r="C444" s="14"/>
       <c r="D444" s="15"/>
       <c r="E444" s="14"/>
       <c r="F444" s="14"/>
-      <c r="G444" s="12"/>
-      <c r="H444" s="14" t="s">
-        <v>1304</v>
-      </c>
+      <c r="G444" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="H444" s="14"/>
       <c r="I444" s="16" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J444" s="17"/>
       <c r="K444" s="18" t="s">
@@ -21398,19 +21877,19 @@
     </row>
     <row r="445" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A445" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B445" s="14"/>
       <c r="C445" s="14"/>
       <c r="D445" s="15"/>
       <c r="E445" s="14"/>
       <c r="F445" s="14"/>
-      <c r="G445" s="12"/>
-      <c r="H445" s="14" t="s">
-        <v>220</v>
-      </c>
+      <c r="G445" s="12" t="s">
+        <v>562</v>
+      </c>
+      <c r="H445" s="14"/>
       <c r="I445" s="16" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="J445" s="17"/>
       <c r="K445" s="18" t="s">
@@ -21420,19 +21899,19 @@
     </row>
     <row r="446" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A446" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B446" s="14"/>
       <c r="C446" s="14"/>
       <c r="D446" s="15"/>
       <c r="E446" s="14"/>
       <c r="F446" s="14"/>
-      <c r="G446" s="12"/>
-      <c r="H446" s="14" t="s">
-        <v>438</v>
-      </c>
+      <c r="G446" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H446" s="14"/>
       <c r="I446" s="16" t="s">
-        <v>1509</v>
+        <v>91</v>
       </c>
       <c r="J446" s="17"/>
       <c r="K446" s="18" t="s">
@@ -21442,19 +21921,19 @@
     </row>
     <row r="447" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A447" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B447" s="14"/>
       <c r="C447" s="14"/>
       <c r="D447" s="15"/>
       <c r="E447" s="14"/>
       <c r="F447" s="14"/>
-      <c r="G447" s="12"/>
-      <c r="H447" s="14" t="s">
-        <v>438</v>
-      </c>
+      <c r="G447" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H447" s="14"/>
       <c r="I447" s="16" t="s">
-        <v>56</v>
+        <v>413</v>
       </c>
       <c r="J447" s="17"/>
       <c r="K447" s="18" t="s">
@@ -21464,7 +21943,7 @@
     </row>
     <row r="448" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A448" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B448" s="14"/>
       <c r="C448" s="14"/>
@@ -21472,13 +21951,11 @@
       <c r="E448" s="14"/>
       <c r="F448" s="14"/>
       <c r="G448" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H448" s="14" t="s">
-        <v>85</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="H448" s="14"/>
       <c r="I448" s="16" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="J448" s="17"/>
       <c r="K448" s="18" t="s">
@@ -21488,7 +21965,7 @@
     </row>
     <row r="449" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A449" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B449" s="14"/>
       <c r="C449" s="14"/>
@@ -21496,23 +21973,21 @@
       <c r="E449" s="14"/>
       <c r="F449" s="14"/>
       <c r="G449" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H449" s="14" t="s">
-        <v>85</v>
-      </c>
+        <v>1538</v>
+      </c>
+      <c r="H449" s="14"/>
       <c r="I449" s="16" t="s">
-        <v>69</v>
+        <v>1537</v>
       </c>
       <c r="J449" s="17"/>
       <c r="K449" s="18" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="L449" s="18"/>
     </row>
     <row r="450" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A450" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B450" s="14"/>
       <c r="C450" s="14"/>
@@ -21520,23 +21995,21 @@
       <c r="E450" s="14"/>
       <c r="F450" s="14"/>
       <c r="G450" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="H450" s="14" t="s">
-        <v>85</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="H450" s="14"/>
       <c r="I450" s="16" t="s">
         <v>65</v>
       </c>
       <c r="J450" s="17"/>
       <c r="K450" s="18" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="L450" s="18"/>
     </row>
     <row r="451" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A451" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B451" s="14"/>
       <c r="C451" s="14"/>
@@ -21550,7 +22023,7 @@
         <v>85</v>
       </c>
       <c r="I451" s="16" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="J451" s="17"/>
       <c r="K451" s="18" t="s">
@@ -21560,7 +22033,7 @@
     </row>
     <row r="452" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A452" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B452" s="14"/>
       <c r="C452" s="14"/>
@@ -21574,7 +22047,7 @@
         <v>85</v>
       </c>
       <c r="I452" s="16" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="J452" s="17"/>
       <c r="K452" s="18" t="s">
@@ -21584,7 +22057,7 @@
     </row>
     <row r="453" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A453" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B453" s="14"/>
       <c r="C453" s="14"/>
@@ -21592,12 +22065,14 @@
       <c r="E453" s="14"/>
       <c r="F453" s="14"/>
       <c r="G453" s="12" t="s">
-        <v>1501</v>
+        <v>273</v>
       </c>
       <c r="H453" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I453" s="16"/>
+        <v>85</v>
+      </c>
+      <c r="I453" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="J453" s="17"/>
       <c r="K453" s="18" t="s">
         <v>44</v>
@@ -21606,7 +22081,7 @@
     </row>
     <row r="454" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A454" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B454" s="14"/>
       <c r="C454" s="14"/>
@@ -21614,12 +22089,14 @@
       <c r="E454" s="14"/>
       <c r="F454" s="14"/>
       <c r="G454" s="12" t="s">
-        <v>1501</v>
+        <v>273</v>
       </c>
       <c r="H454" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I454" s="16"/>
+        <v>85</v>
+      </c>
+      <c r="I454" s="16" t="s">
+        <v>65</v>
+      </c>
       <c r="J454" s="17"/>
       <c r="K454" s="18" t="s">
         <v>44</v>
@@ -21628,7 +22105,7 @@
     </row>
     <row r="455" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A455" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B455" s="14"/>
       <c r="C455" s="14"/>
@@ -21636,12 +22113,14 @@
       <c r="E455" s="14"/>
       <c r="F455" s="14"/>
       <c r="G455" s="12" t="s">
-        <v>1502</v>
+        <v>273</v>
       </c>
       <c r="H455" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I455" s="16"/>
+        <v>85</v>
+      </c>
+      <c r="I455" s="16" t="s">
+        <v>95</v>
+      </c>
       <c r="J455" s="17"/>
       <c r="K455" s="18" t="s">
         <v>44</v>
@@ -21650,7 +22129,7 @@
     </row>
     <row r="456" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A456" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B456" s="14"/>
       <c r="C456" s="14"/>
@@ -21658,21 +22137,21 @@
       <c r="E456" s="14"/>
       <c r="F456" s="14"/>
       <c r="G456" s="12" t="s">
-        <v>1510</v>
-      </c>
-      <c r="H456" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="I456" s="16"/>
+        <v>1539</v>
+      </c>
+      <c r="H456" s="14"/>
+      <c r="I456" s="16" t="s">
+        <v>413</v>
+      </c>
       <c r="J456" s="17"/>
       <c r="K456" s="18" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="L456" s="18"/>
     </row>
     <row r="457" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A457" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B457" s="14"/>
       <c r="C457" s="14"/>
@@ -21680,35 +22159,33 @@
       <c r="E457" s="14"/>
       <c r="F457" s="14"/>
       <c r="G457" s="12" t="s">
-        <v>1511</v>
-      </c>
-      <c r="H457" s="14" t="s">
-        <v>52</v>
-      </c>
+        <v>1539</v>
+      </c>
+      <c r="H457" s="14"/>
       <c r="I457" s="16" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="J457" s="17"/>
       <c r="K457" s="18" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="L457" s="18"/>
     </row>
     <row r="458" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A458" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B458" s="14"/>
       <c r="C458" s="14"/>
       <c r="D458" s="15"/>
       <c r="E458" s="14"/>
       <c r="F458" s="14"/>
-      <c r="G458" s="12"/>
-      <c r="H458" s="14" t="s">
-        <v>1296</v>
-      </c>
+      <c r="G458" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H458" s="14"/>
       <c r="I458" s="16" t="s">
-        <v>23</v>
+        <v>367</v>
       </c>
       <c r="J458" s="17"/>
       <c r="K458" s="18" t="s">
@@ -21718,19 +22195,19 @@
     </row>
     <row r="459" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A459" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B459" s="14"/>
       <c r="C459" s="14"/>
       <c r="D459" s="15"/>
       <c r="E459" s="14"/>
       <c r="F459" s="14"/>
-      <c r="G459" s="12"/>
-      <c r="H459" s="14" t="s">
-        <v>34</v>
-      </c>
+      <c r="G459" s="12" t="s">
+        <v>1540</v>
+      </c>
+      <c r="H459" s="14"/>
       <c r="I459" s="16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J459" s="17"/>
       <c r="K459" s="18" t="s">
@@ -21740,19 +22217,19 @@
     </row>
     <row r="460" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A460" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B460" s="14"/>
       <c r="C460" s="14"/>
       <c r="D460" s="15"/>
       <c r="E460" s="14"/>
       <c r="F460" s="14"/>
-      <c r="G460" s="12"/>
-      <c r="H460" s="14" t="s">
-        <v>34</v>
-      </c>
+      <c r="G460" s="12" t="s">
+        <v>1541</v>
+      </c>
+      <c r="H460" s="14"/>
       <c r="I460" s="16" t="s">
-        <v>105</v>
+        <v>855</v>
       </c>
       <c r="J460" s="17"/>
       <c r="K460" s="18" t="s">
@@ -21762,29 +22239,29 @@
     </row>
     <row r="461" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A461" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B461" s="14"/>
       <c r="C461" s="14"/>
       <c r="D461" s="15"/>
       <c r="E461" s="14"/>
       <c r="F461" s="14"/>
-      <c r="G461" s="12"/>
-      <c r="H461" s="14" t="s">
-        <v>34</v>
-      </c>
+      <c r="G461" s="12" t="s">
+        <v>1542</v>
+      </c>
+      <c r="H461" s="14"/>
       <c r="I461" s="16" t="s">
-        <v>56</v>
+        <v>124</v>
       </c>
       <c r="J461" s="17"/>
       <c r="K461" s="18" t="s">
-        <v>44</v>
+        <v>1092</v>
       </c>
       <c r="L461" s="18"/>
     </row>
     <row r="462" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A462" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B462" s="14"/>
       <c r="C462" s="14"/>
@@ -21792,10 +22269,12 @@
       <c r="E462" s="14"/>
       <c r="F462" s="14"/>
       <c r="G462" s="12" t="s">
-        <v>1512</v>
+        <v>85</v>
       </c>
       <c r="H462" s="14"/>
-      <c r="I462" s="16"/>
+      <c r="I462" s="16" t="s">
+        <v>42</v>
+      </c>
       <c r="J462" s="17"/>
       <c r="K462" s="18" t="s">
         <v>44</v>
@@ -21804,7 +22283,7 @@
     </row>
     <row r="463" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A463" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B463" s="14"/>
       <c r="C463" s="14"/>
@@ -21812,11 +22291,13 @@
       <c r="E463" s="14"/>
       <c r="F463" s="14"/>
       <c r="G463" s="12" t="s">
-        <v>562</v>
-      </c>
-      <c r="H463" s="14"/>
+        <v>1543</v>
+      </c>
+      <c r="H463" s="14" t="s">
+        <v>52</v>
+      </c>
       <c r="I463" s="16" t="s">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="J463" s="17"/>
       <c r="K463" s="18" t="s">
@@ -21826,7 +22307,7 @@
     </row>
     <row r="464" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A464" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B464" s="14"/>
       <c r="C464" s="14"/>
@@ -21834,11 +22315,11 @@
       <c r="E464" s="14"/>
       <c r="F464" s="14"/>
       <c r="G464" s="12" t="s">
-        <v>562</v>
+        <v>81</v>
       </c>
       <c r="H464" s="14"/>
       <c r="I464" s="16" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="J464" s="17"/>
       <c r="K464" s="18" t="s">
@@ -21848,7 +22329,7 @@
     </row>
     <row r="465" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A465" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B465" s="14"/>
       <c r="C465" s="14"/>
@@ -21856,7 +22337,7 @@
       <c r="E465" s="14"/>
       <c r="F465" s="14"/>
       <c r="G465" s="12" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="H465" s="14"/>
       <c r="I465" s="16" t="s">
@@ -21864,13 +22345,13 @@
       </c>
       <c r="J465" s="17"/>
       <c r="K465" s="18" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="L465" s="18"/>
     </row>
     <row r="466" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A466" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B466" s="14"/>
       <c r="C466" s="14"/>
@@ -21878,11 +22359,11 @@
       <c r="E466" s="14"/>
       <c r="F466" s="14"/>
       <c r="G466" s="12" t="s">
-        <v>57</v>
+        <v>1544</v>
       </c>
       <c r="H466" s="14"/>
       <c r="I466" s="16" t="s">
-        <v>413</v>
+        <v>95</v>
       </c>
       <c r="J466" s="17"/>
       <c r="K466" s="18" t="s">
@@ -21892,7 +22373,7 @@
     </row>
     <row r="467" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A467" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B467" s="14"/>
       <c r="C467" s="14"/>
@@ -21900,153 +22381,151 @@
       <c r="E467" s="14"/>
       <c r="F467" s="14"/>
       <c r="G467" s="12" t="s">
-        <v>57</v>
+        <v>1545</v>
       </c>
       <c r="H467" s="14"/>
-      <c r="I467" s="16" t="s">
-        <v>69</v>
-      </c>
+      <c r="I467" s="16"/>
       <c r="J467" s="17"/>
       <c r="K467" s="18" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="L467" s="18"/>
     </row>
     <row r="468" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A468" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B468" s="14"/>
       <c r="C468" s="14"/>
       <c r="D468" s="15"/>
       <c r="E468" s="14"/>
       <c r="F468" s="14"/>
-      <c r="G468" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H468" s="14"/>
+      <c r="G468" s="12"/>
+      <c r="H468" s="14" t="s">
+        <v>338</v>
+      </c>
       <c r="I468" s="16" t="s">
-        <v>367</v>
+        <v>413</v>
       </c>
       <c r="J468" s="17"/>
       <c r="K468" s="18" t="s">
-        <v>44</v>
+        <v>1498</v>
       </c>
       <c r="L468" s="18"/>
     </row>
     <row r="469" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A469" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B469" s="14"/>
       <c r="C469" s="14"/>
       <c r="D469" s="15"/>
       <c r="E469" s="14"/>
       <c r="F469" s="14"/>
-      <c r="G469" s="12" t="s">
-        <v>1513</v>
-      </c>
-      <c r="H469" s="14"/>
+      <c r="G469" s="12"/>
+      <c r="H469" s="14" t="s">
+        <v>338</v>
+      </c>
       <c r="I469" s="16" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="J469" s="17"/>
       <c r="K469" s="18" t="s">
-        <v>44</v>
+        <v>1498</v>
       </c>
       <c r="L469" s="18"/>
     </row>
     <row r="470" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A470" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B470" s="14"/>
       <c r="C470" s="14"/>
       <c r="D470" s="15"/>
       <c r="E470" s="14"/>
       <c r="F470" s="14"/>
-      <c r="G470" s="12" t="s">
-        <v>1514</v>
-      </c>
-      <c r="H470" s="14"/>
+      <c r="G470" s="12"/>
+      <c r="H470" s="14" t="s">
+        <v>34</v>
+      </c>
       <c r="I470" s="16" t="s">
-        <v>855</v>
+        <v>17</v>
       </c>
       <c r="J470" s="17"/>
       <c r="K470" s="18" t="s">
-        <v>44</v>
+        <v>1546</v>
       </c>
       <c r="L470" s="18"/>
     </row>
     <row r="471" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A471" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B471" s="14"/>
       <c r="C471" s="14"/>
       <c r="D471" s="15"/>
       <c r="E471" s="14"/>
       <c r="F471" s="14"/>
-      <c r="G471" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="H471" s="14"/>
+      <c r="G471" s="12"/>
+      <c r="H471" s="14" t="s">
+        <v>34</v>
+      </c>
       <c r="I471" s="16" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="J471" s="17"/>
       <c r="K471" s="18" t="s">
-        <v>44</v>
+        <v>1547</v>
       </c>
       <c r="L471" s="18"/>
     </row>
     <row r="472" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A472" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B472" s="14"/>
       <c r="C472" s="14"/>
       <c r="D472" s="15"/>
       <c r="E472" s="14"/>
       <c r="F472" s="14"/>
-      <c r="G472" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H472" s="14"/>
+      <c r="G472" s="12"/>
+      <c r="H472" s="14" t="s">
+        <v>220</v>
+      </c>
       <c r="I472" s="16" t="s">
-        <v>17</v>
+        <v>124</v>
       </c>
       <c r="J472" s="17"/>
       <c r="K472" s="18" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="L472" s="18"/>
     </row>
     <row r="473" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A473" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B473" s="14"/>
       <c r="C473" s="14"/>
       <c r="D473" s="15"/>
       <c r="E473" s="14"/>
       <c r="F473" s="14"/>
-      <c r="G473" s="12" t="s">
-        <v>1515</v>
-      </c>
-      <c r="H473" s="14"/>
+      <c r="G473" s="12"/>
+      <c r="H473" s="14" t="s">
+        <v>438</v>
+      </c>
       <c r="I473" s="16" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="J473" s="17"/>
       <c r="K473" s="18" t="s">
-        <v>44</v>
+        <v>477</v>
       </c>
       <c r="L473" s="18"/>
     </row>
     <row r="474" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A474" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B474" s="14"/>
       <c r="C474" s="14"/>
@@ -22055,42 +22534,42 @@
       <c r="F474" s="14"/>
       <c r="G474" s="12"/>
       <c r="H474" s="14" t="s">
-        <v>220</v>
+        <v>438</v>
       </c>
       <c r="I474" s="16" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="J474" s="17"/>
       <c r="K474" s="18" t="s">
-        <v>1092</v>
+        <v>477</v>
       </c>
       <c r="L474" s="18"/>
     </row>
     <row r="475" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A475" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B475" s="14"/>
       <c r="C475" s="14"/>
       <c r="D475" s="15"/>
       <c r="E475" s="14"/>
       <c r="F475" s="14"/>
-      <c r="G475" s="12" t="s">
-        <v>1516</v>
-      </c>
-      <c r="H475" s="14"/>
+      <c r="G475" s="12"/>
+      <c r="H475" s="14" t="s">
+        <v>438</v>
+      </c>
       <c r="I475" s="16" t="s">
-        <v>124</v>
+        <v>1537</v>
       </c>
       <c r="J475" s="17"/>
       <c r="K475" s="18" t="s">
-        <v>1092</v>
+        <v>477</v>
       </c>
       <c r="L475" s="18"/>
     </row>
     <row r="476" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A476" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B476" s="14"/>
       <c r="C476" s="14"/>
@@ -22099,20 +22578,20 @@
       <c r="F476" s="14"/>
       <c r="G476" s="12"/>
       <c r="H476" s="14" t="s">
-        <v>338</v>
+        <v>1296</v>
       </c>
       <c r="I476" s="16" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="J476" s="17"/>
       <c r="K476" s="18" t="s">
-        <v>1517</v>
+        <v>477</v>
       </c>
       <c r="L476" s="18"/>
     </row>
     <row r="477" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A477" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B477" s="14"/>
       <c r="C477" s="14"/>
@@ -22121,20 +22600,20 @@
       <c r="F477" s="14"/>
       <c r="G477" s="12"/>
       <c r="H477" s="14" t="s">
-        <v>16</v>
+        <v>1304</v>
       </c>
       <c r="I477" s="16" t="s">
-        <v>95</v>
+        <v>333</v>
       </c>
       <c r="J477" s="17"/>
       <c r="K477" s="18" t="s">
-        <v>1518</v>
+        <v>44</v>
       </c>
       <c r="L477" s="18"/>
     </row>
     <row r="478" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A478" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B478" s="14"/>
       <c r="C478" s="14"/>
@@ -22143,20 +22622,20 @@
       <c r="F478" s="14"/>
       <c r="G478" s="12"/>
       <c r="H478" s="14" t="s">
-        <v>653</v>
+        <v>1304</v>
       </c>
       <c r="I478" s="16" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="J478" s="17"/>
       <c r="K478" s="18" t="s">
-        <v>1519</v>
+        <v>44</v>
       </c>
       <c r="L478" s="18"/>
     </row>
     <row r="479" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A479" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B479" s="14"/>
       <c r="C479" s="14"/>
@@ -22165,40 +22644,42 @@
       <c r="F479" s="14"/>
       <c r="G479" s="12"/>
       <c r="H479" s="14" t="s">
-        <v>438</v>
+        <v>220</v>
       </c>
       <c r="I479" s="16" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="J479" s="17"/>
       <c r="K479" s="18" t="s">
-        <v>1520</v>
+        <v>44</v>
       </c>
       <c r="L479" s="18"/>
     </row>
     <row r="480" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A480" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B480" s="14"/>
       <c r="C480" s="14"/>
       <c r="D480" s="15"/>
       <c r="E480" s="14"/>
       <c r="F480" s="14"/>
-      <c r="G480" s="12" t="s">
-        <v>1521</v>
-      </c>
-      <c r="H480" s="14"/>
-      <c r="I480" s="16"/>
+      <c r="G480" s="12"/>
+      <c r="H480" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I480" s="16" t="s">
+        <v>1548</v>
+      </c>
       <c r="J480" s="17"/>
       <c r="K480" s="18" t="s">
-        <v>1520</v>
+        <v>44</v>
       </c>
       <c r="L480" s="18"/>
     </row>
     <row r="481" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A481" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B481" s="14"/>
       <c r="C481" s="14"/>
@@ -22207,20 +22688,20 @@
       <c r="F481" s="14"/>
       <c r="G481" s="12"/>
       <c r="H481" s="14" t="s">
-        <v>16</v>
+        <v>438</v>
       </c>
       <c r="I481" s="16" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="J481" s="17"/>
       <c r="K481" s="18" t="s">
-        <v>1483</v>
+        <v>44</v>
       </c>
       <c r="L481" s="18"/>
     </row>
     <row r="482" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A482" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B482" s="14"/>
       <c r="C482" s="14"/>
@@ -22229,20 +22710,20 @@
       <c r="F482" s="14"/>
       <c r="G482" s="12"/>
       <c r="H482" s="14" t="s">
-        <v>34</v>
+        <v>1296</v>
       </c>
       <c r="I482" s="16" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="J482" s="17"/>
       <c r="K482" s="18" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L482" s="18"/>
     </row>
     <row r="483" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A483" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B483" s="14"/>
       <c r="C483" s="14"/>
@@ -22254,39 +22735,39 @@
         <v>34</v>
       </c>
       <c r="I483" s="16" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="J483" s="17"/>
       <c r="K483" s="18" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L483" s="18"/>
     </row>
     <row r="484" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A484" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B484" s="14"/>
       <c r="C484" s="14"/>
       <c r="D484" s="15"/>
       <c r="E484" s="14"/>
       <c r="F484" s="14"/>
-      <c r="G484" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H484" s="14"/>
+      <c r="G484" s="12"/>
+      <c r="H484" s="14" t="s">
+        <v>34</v>
+      </c>
       <c r="I484" s="16" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="J484" s="17"/>
       <c r="K484" s="18" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="L484" s="18"/>
     </row>
     <row r="485" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A485" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B485" s="14"/>
       <c r="C485" s="14"/>
@@ -22295,20 +22776,20 @@
       <c r="F485" s="14"/>
       <c r="G485" s="12"/>
       <c r="H485" s="14" t="s">
-        <v>338</v>
+        <v>34</v>
       </c>
       <c r="I485" s="16" t="s">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="J485" s="17"/>
       <c r="K485" s="18" t="s">
-        <v>1522</v>
+        <v>44</v>
       </c>
       <c r="L485" s="18"/>
     </row>
     <row r="486" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A486" s="13" t="s">
-        <v>1481</v>
+        <v>1511</v>
       </c>
       <c r="B486" s="14"/>
       <c r="C486" s="14"/>
@@ -22317,368 +22798,350 @@
       <c r="F486" s="14"/>
       <c r="G486" s="12"/>
       <c r="H486" s="14" t="s">
-        <v>338</v>
+        <v>220</v>
       </c>
       <c r="I486" s="16" t="s">
         <v>95</v>
       </c>
       <c r="J486" s="17"/>
       <c r="K486" s="18" t="s">
-        <v>1523</v>
+        <v>1092</v>
       </c>
       <c r="L486" s="18"/>
     </row>
     <row r="487" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A487" s="13"/>
-      <c r="B487" s="14" t="s">
-        <v>1524</v>
-      </c>
-      <c r="C487" s="14" t="s">
-        <v>317</v>
-      </c>
-      <c r="D487" s="15">
-        <v>57</v>
-      </c>
+      <c r="A487" s="13" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B487" s="14"/>
+      <c r="C487" s="14"/>
+      <c r="D487" s="15"/>
       <c r="E487" s="14"/>
-      <c r="F487" s="14">
-        <v>1846</v>
-      </c>
-      <c r="G487" s="12" t="s">
-        <v>1525</v>
-      </c>
-      <c r="H487" s="14"/>
-      <c r="I487" s="16"/>
+      <c r="F487" s="14"/>
+      <c r="G487" s="12"/>
+      <c r="H487" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="I487" s="16" t="s">
+        <v>105</v>
+      </c>
       <c r="J487" s="17"/>
-      <c r="K487" s="18"/>
+      <c r="K487" s="18" t="s">
+        <v>1549</v>
+      </c>
       <c r="L487" s="18"/>
     </row>
     <row r="488" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A488" s="13"/>
-      <c r="B488" s="14" t="s">
-        <v>1526</v>
-      </c>
-      <c r="C488" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D488" s="15">
-        <v>1</v>
-      </c>
+      <c r="A488" s="13" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B488" s="14"/>
+      <c r="C488" s="14"/>
+      <c r="D488" s="15"/>
       <c r="E488" s="14"/>
       <c r="F488" s="14"/>
-      <c r="G488" s="12" t="s">
-        <v>1527</v>
-      </c>
+      <c r="G488" s="12"/>
       <c r="H488" s="14" t="s">
-        <v>1528</v>
-      </c>
-      <c r="I488" s="16"/>
+        <v>16</v>
+      </c>
+      <c r="I488" s="16" t="s">
+        <v>95</v>
+      </c>
       <c r="J488" s="17"/>
-      <c r="K488" s="18"/>
+      <c r="K488" s="18" t="s">
+        <v>1550</v>
+      </c>
       <c r="L488" s="18"/>
     </row>
     <row r="489" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A489" s="13"/>
-      <c r="B489" s="14" t="s">
-        <v>1529</v>
-      </c>
-      <c r="C489" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D489" s="15">
-        <v>2</v>
-      </c>
+      <c r="A489" s="13" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B489" s="14"/>
+      <c r="C489" s="14"/>
+      <c r="D489" s="15"/>
       <c r="E489" s="14"/>
       <c r="F489" s="14"/>
-      <c r="G489" s="12" t="s">
-        <v>1530</v>
-      </c>
+      <c r="G489" s="12"/>
       <c r="H489" s="14" t="s">
-        <v>1531</v>
-      </c>
-      <c r="I489" s="16"/>
+        <v>653</v>
+      </c>
+      <c r="I489" s="16" t="s">
+        <v>17</v>
+      </c>
       <c r="J489" s="17"/>
-      <c r="K489" s="18"/>
+      <c r="K489" s="18" t="s">
+        <v>1551</v>
+      </c>
       <c r="L489" s="18"/>
     </row>
     <row r="490" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A490" s="13"/>
-      <c r="B490" s="14" t="s">
-        <v>1532</v>
-      </c>
-      <c r="C490" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D490" s="15">
-        <v>3</v>
-      </c>
+      <c r="A490" s="13" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B490" s="14"/>
+      <c r="C490" s="14"/>
+      <c r="D490" s="15"/>
       <c r="E490" s="14"/>
       <c r="F490" s="14"/>
-      <c r="G490" s="12" t="s">
-        <v>1533</v>
-      </c>
+      <c r="G490" s="12"/>
       <c r="H490" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="I490" s="16"/>
+        <v>438</v>
+      </c>
+      <c r="I490" s="16" t="s">
+        <v>128</v>
+      </c>
       <c r="J490" s="17"/>
-      <c r="K490" s="18"/>
+      <c r="K490" s="18" t="s">
+        <v>1529</v>
+      </c>
       <c r="L490" s="18"/>
     </row>
     <row r="491" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A491" s="13"/>
-      <c r="B491" s="14" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C491" s="14" t="s">
-        <v>190</v>
-      </c>
-      <c r="D491" s="15">
-        <v>4</v>
-      </c>
+      <c r="A491" s="13" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B491" s="14"/>
+      <c r="C491" s="14"/>
+      <c r="D491" s="15"/>
       <c r="E491" s="14"/>
       <c r="F491" s="14"/>
-      <c r="G491" s="12" t="s">
-        <v>1535</v>
-      </c>
+      <c r="G491" s="12"/>
       <c r="H491" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="I491" s="16"/>
+        <v>16</v>
+      </c>
+      <c r="I491" s="16" t="s">
+        <v>128</v>
+      </c>
       <c r="J491" s="17"/>
-      <c r="K491" s="18"/>
+      <c r="K491" s="18" t="s">
+        <v>1513</v>
+      </c>
       <c r="L491" s="18"/>
     </row>
     <row r="492" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A492" s="13"/>
-      <c r="B492" s="14" t="s">
-        <v>1536</v>
-      </c>
-      <c r="C492" s="14" t="s">
-        <v>714</v>
-      </c>
-      <c r="D492" s="15">
-        <v>1</v>
-      </c>
+      <c r="A492" s="13" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B492" s="14"/>
+      <c r="C492" s="14"/>
+      <c r="D492" s="15"/>
       <c r="E492" s="14"/>
       <c r="F492" s="14"/>
-      <c r="G492" s="12" t="s">
-        <v>1537</v>
-      </c>
+      <c r="G492" s="12"/>
       <c r="H492" s="14" t="s">
-        <v>717</v>
-      </c>
-      <c r="I492" s="16"/>
-      <c r="J492" s="22"/>
-      <c r="K492" s="18"/>
+        <v>34</v>
+      </c>
+      <c r="I492" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J492" s="17"/>
+      <c r="K492" s="18" t="s">
+        <v>36</v>
+      </c>
       <c r="L492" s="18"/>
     </row>
     <row r="493" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A493" s="13"/>
-      <c r="B493" s="14" t="s">
-        <v>1538</v>
-      </c>
-      <c r="C493" s="14" t="s">
-        <v>714</v>
-      </c>
-      <c r="D493" s="15">
-        <v>2</v>
-      </c>
+      <c r="A493" s="13" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B493" s="14"/>
+      <c r="C493" s="14"/>
+      <c r="D493" s="15"/>
       <c r="E493" s="14"/>
       <c r="F493" s="14"/>
-      <c r="G493" s="12" t="s">
-        <v>1539</v>
-      </c>
+      <c r="G493" s="12"/>
       <c r="H493" s="14" t="s">
-        <v>717</v>
-      </c>
-      <c r="I493" s="16"/>
-      <c r="J493" s="22"/>
-      <c r="K493" s="18"/>
+        <v>34</v>
+      </c>
+      <c r="I493" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="J493" s="17"/>
+      <c r="K493" s="18" t="s">
+        <v>36</v>
+      </c>
       <c r="L493" s="18"/>
     </row>
     <row r="494" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A494" s="13"/>
-      <c r="B494" s="14" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C494" s="14" t="s">
-        <v>714</v>
-      </c>
-      <c r="D494" s="15">
-        <v>3</v>
-      </c>
+      <c r="A494" s="13" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B494" s="14"/>
+      <c r="C494" s="14"/>
+      <c r="D494" s="15"/>
       <c r="E494" s="14"/>
       <c r="F494" s="14"/>
-      <c r="G494" s="12" t="s">
-        <v>1541</v>
-      </c>
+      <c r="G494" s="12"/>
       <c r="H494" s="14" t="s">
-        <v>717</v>
-      </c>
-      <c r="I494" s="16"/>
-      <c r="J494" s="22"/>
-      <c r="K494" s="18"/>
+        <v>338</v>
+      </c>
+      <c r="I494" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J494" s="17"/>
+      <c r="K494" s="18" t="s">
+        <v>1552</v>
+      </c>
       <c r="L494" s="18"/>
     </row>
     <row r="495" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A495" s="13"/>
-      <c r="B495" s="14" t="s">
-        <v>1542</v>
-      </c>
-      <c r="C495" s="14" t="s">
-        <v>714</v>
-      </c>
-      <c r="D495" s="15">
-        <v>4</v>
-      </c>
+      <c r="A495" s="13" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B495" s="14"/>
+      <c r="C495" s="14"/>
+      <c r="D495" s="15"/>
       <c r="E495" s="14"/>
       <c r="F495" s="14"/>
-      <c r="G495" s="12" t="s">
-        <v>1543</v>
-      </c>
+      <c r="G495" s="12"/>
       <c r="H495" s="14" t="s">
-        <v>717</v>
-      </c>
-      <c r="I495" s="16"/>
-      <c r="J495" s="22"/>
-      <c r="K495" s="18"/>
+        <v>338</v>
+      </c>
+      <c r="I495" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J495" s="17"/>
+      <c r="K495" s="18" t="s">
+        <v>1553</v>
+      </c>
       <c r="L495" s="18"/>
     </row>
     <row r="496" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A496" s="13"/>
       <c r="B496" s="14" t="s">
-        <v>1544</v>
+        <v>1554</v>
       </c>
       <c r="C496" s="14" t="s">
-        <v>714</v>
+        <v>317</v>
       </c>
       <c r="D496" s="15">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="E496" s="14"/>
-      <c r="F496" s="14"/>
+      <c r="F496" s="14">
+        <v>1846</v>
+      </c>
       <c r="G496" s="12" t="s">
-        <v>1545</v>
-      </c>
-      <c r="H496" s="14" t="s">
-        <v>717</v>
-      </c>
+        <v>1555</v>
+      </c>
+      <c r="H496" s="14"/>
       <c r="I496" s="16"/>
-      <c r="J496" s="22"/>
+      <c r="J496" s="17"/>
       <c r="K496" s="18"/>
       <c r="L496" s="18"/>
     </row>
     <row r="497" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A497" s="13"/>
       <c r="B497" s="14" t="s">
-        <v>1546</v>
+        <v>1556</v>
       </c>
       <c r="C497" s="14" t="s">
-        <v>714</v>
+        <v>190</v>
       </c>
       <c r="D497" s="15">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E497" s="14"/>
       <c r="F497" s="14"/>
       <c r="G497" s="12" t="s">
-        <v>1547</v>
+        <v>1557</v>
       </c>
       <c r="H497" s="14" t="s">
-        <v>717</v>
+        <v>1558</v>
       </c>
       <c r="I497" s="16"/>
-      <c r="J497" s="22"/>
+      <c r="J497" s="17"/>
       <c r="K497" s="18"/>
       <c r="L497" s="18"/>
     </row>
     <row r="498" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A498" s="13"/>
       <c r="B498" s="14" t="s">
-        <v>1548</v>
+        <v>1559</v>
       </c>
       <c r="C498" s="14" t="s">
-        <v>714</v>
+        <v>190</v>
       </c>
       <c r="D498" s="15">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E498" s="14"/>
       <c r="F498" s="14"/>
       <c r="G498" s="12" t="s">
-        <v>1549</v>
+        <v>1560</v>
       </c>
       <c r="H498" s="14" t="s">
-        <v>717</v>
+        <v>1561</v>
       </c>
       <c r="I498" s="16"/>
-      <c r="J498" s="22"/>
+      <c r="J498" s="17"/>
       <c r="K498" s="18"/>
       <c r="L498" s="18"/>
     </row>
     <row r="499" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A499" s="13"/>
       <c r="B499" s="14" t="s">
-        <v>1550</v>
+        <v>1562</v>
       </c>
       <c r="C499" s="14" t="s">
-        <v>714</v>
+        <v>190</v>
       </c>
       <c r="D499" s="15">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E499" s="14"/>
       <c r="F499" s="14"/>
       <c r="G499" s="12" t="s">
-        <v>1551</v>
+        <v>1563</v>
       </c>
       <c r="H499" s="14" t="s">
-        <v>717</v>
+        <v>193</v>
       </c>
       <c r="I499" s="16"/>
-      <c r="J499" s="22"/>
+      <c r="J499" s="17"/>
       <c r="K499" s="18"/>
       <c r="L499" s="18"/>
     </row>
     <row r="500" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A500" s="13"/>
       <c r="B500" s="14" t="s">
-        <v>1552</v>
+        <v>1564</v>
       </c>
       <c r="C500" s="14" t="s">
-        <v>714</v>
+        <v>190</v>
       </c>
       <c r="D500" s="15">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E500" s="14"/>
       <c r="F500" s="14"/>
       <c r="G500" s="12" t="s">
-        <v>1553</v>
+        <v>1565</v>
       </c>
       <c r="H500" s="14" t="s">
-        <v>717</v>
+        <v>193</v>
       </c>
       <c r="I500" s="16"/>
-      <c r="J500" s="22"/>
+      <c r="J500" s="17"/>
       <c r="K500" s="18"/>
       <c r="L500" s="18"/>
     </row>
     <row r="501" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A501" s="13"/>
       <c r="B501" s="14" t="s">
-        <v>1554</v>
+        <v>1566</v>
       </c>
       <c r="C501" s="14" t="s">
         <v>714</v>
       </c>
       <c r="D501" s="15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E501" s="14"/>
       <c r="F501" s="14"/>
       <c r="G501" s="12" t="s">
-        <v>1555</v>
+        <v>1567</v>
       </c>
       <c r="H501" s="14" t="s">
         <v>717</v>
@@ -22691,18 +23154,18 @@
     <row r="502" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A502" s="13"/>
       <c r="B502" s="14" t="s">
-        <v>1556</v>
+        <v>1568</v>
       </c>
       <c r="C502" s="14" t="s">
         <v>714</v>
       </c>
       <c r="D502" s="15">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E502" s="14"/>
       <c r="F502" s="14"/>
       <c r="G502" s="12" t="s">
-        <v>1557</v>
+        <v>1569</v>
       </c>
       <c r="H502" s="14" t="s">
         <v>717</v>
@@ -22715,18 +23178,18 @@
     <row r="503" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A503" s="13"/>
       <c r="B503" s="14" t="s">
-        <v>1558</v>
+        <v>1570</v>
       </c>
       <c r="C503" s="14" t="s">
         <v>714</v>
       </c>
       <c r="D503" s="15">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E503" s="14"/>
       <c r="F503" s="14"/>
       <c r="G503" s="12" t="s">
-        <v>1559</v>
+        <v>1571</v>
       </c>
       <c r="H503" s="14" t="s">
         <v>717</v>
@@ -22739,23 +23202,23 @@
     <row r="504" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A504" s="13"/>
       <c r="B504" s="14" t="s">
-        <v>1560</v>
+        <v>1572</v>
       </c>
       <c r="C504" s="14" t="s">
-        <v>197</v>
+        <v>714</v>
       </c>
       <c r="D504" s="15">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="E504" s="14"/>
       <c r="F504" s="14"/>
-      <c r="G504" s="12"/>
+      <c r="G504" s="12" t="s">
+        <v>1573</v>
+      </c>
       <c r="H504" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I504" s="16" t="s">
-        <v>465</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="I504" s="16"/>
       <c r="J504" s="22"/>
       <c r="K504" s="18"/>
       <c r="L504" s="18"/>
@@ -22763,23 +23226,23 @@
     <row r="505" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A505" s="13"/>
       <c r="B505" s="14" t="s">
-        <v>1561</v>
+        <v>1574</v>
       </c>
       <c r="C505" s="14" t="s">
-        <v>197</v>
+        <v>714</v>
       </c>
       <c r="D505" s="15">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E505" s="14"/>
       <c r="F505" s="14"/>
-      <c r="G505" s="12"/>
+      <c r="G505" s="12" t="s">
+        <v>1575</v>
+      </c>
       <c r="H505" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="I505" s="16" t="s">
-        <v>333</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="I505" s="16"/>
       <c r="J505" s="22"/>
       <c r="K505" s="18"/>
       <c r="L505" s="18"/>
@@ -22787,23 +23250,23 @@
     <row r="506" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A506" s="13"/>
       <c r="B506" s="14" t="s">
-        <v>1562</v>
+        <v>1576</v>
       </c>
       <c r="C506" s="14" t="s">
-        <v>307</v>
+        <v>714</v>
       </c>
       <c r="D506" s="15">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E506" s="14"/>
       <c r="F506" s="14"/>
       <c r="G506" s="12" t="s">
-        <v>1563</v>
-      </c>
-      <c r="H506" s="14"/>
-      <c r="I506" s="16" t="s">
-        <v>95</v>
-      </c>
+        <v>1577</v>
+      </c>
+      <c r="H506" s="14" t="s">
+        <v>717</v>
+      </c>
+      <c r="I506" s="16"/>
       <c r="J506" s="22"/>
       <c r="K506" s="18"/>
       <c r="L506" s="18"/>
@@ -22811,383 +23274,3113 @@
     <row r="507" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A507" s="13"/>
       <c r="B507" s="14" t="s">
-        <v>1564</v>
+        <v>1578</v>
       </c>
       <c r="C507" s="14" t="s">
-        <v>307</v>
+        <v>714</v>
       </c>
       <c r="D507" s="15">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E507" s="14"/>
       <c r="F507" s="14"/>
-      <c r="G507" s="12"/>
+      <c r="G507" s="12" t="s">
+        <v>1579</v>
+      </c>
       <c r="H507" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="I507" s="16" t="s">
-        <v>105</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="I507" s="16"/>
       <c r="J507" s="22"/>
-      <c r="K507" s="18" t="s">
-        <v>1518</v>
-      </c>
+      <c r="K507" s="18"/>
       <c r="L507" s="18"/>
     </row>
     <row r="508" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A508" s="13"/>
       <c r="B508" s="14" t="s">
-        <v>1565</v>
+        <v>1580</v>
       </c>
       <c r="C508" s="14" t="s">
-        <v>307</v>
+        <v>714</v>
       </c>
       <c r="D508" s="15">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E508" s="14"/>
       <c r="F508" s="14"/>
-      <c r="G508" s="12"/>
+      <c r="G508" s="12" t="s">
+        <v>1581</v>
+      </c>
       <c r="H508" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="I508" s="16" t="s">
-        <v>95</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="I508" s="16"/>
       <c r="J508" s="22"/>
-      <c r="K508" s="18" t="s">
-        <v>1523</v>
-      </c>
+      <c r="K508" s="18"/>
       <c r="L508" s="18"/>
     </row>
     <row r="509" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A509" s="13"/>
       <c r="B509" s="14" t="s">
-        <v>1566</v>
+        <v>1582</v>
       </c>
       <c r="C509" s="14" t="s">
-        <v>307</v>
+        <v>714</v>
       </c>
       <c r="D509" s="15">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E509" s="14"/>
       <c r="F509" s="14"/>
-      <c r="G509" s="12"/>
+      <c r="G509" s="12" t="s">
+        <v>1583</v>
+      </c>
       <c r="H509" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="I509" s="16" t="s">
-        <v>95</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="I509" s="16"/>
       <c r="J509" s="22"/>
-      <c r="K509" s="18" t="s">
-        <v>1567</v>
-      </c>
+      <c r="K509" s="18"/>
       <c r="L509" s="18"/>
     </row>
     <row r="510" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A510" s="13"/>
       <c r="B510" s="14" t="s">
-        <v>1568</v>
+        <v>1584</v>
       </c>
       <c r="C510" s="14" t="s">
-        <v>307</v>
+        <v>714</v>
       </c>
       <c r="D510" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E510" s="14"/>
       <c r="F510" s="14"/>
-      <c r="G510" s="12"/>
+      <c r="G510" s="12" t="s">
+        <v>1585</v>
+      </c>
       <c r="H510" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="I510" s="16" t="s">
-        <v>47</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="I510" s="16"/>
       <c r="J510" s="22"/>
-      <c r="K510" s="18" t="s">
-        <v>1465</v>
-      </c>
+      <c r="K510" s="18"/>
       <c r="L510" s="18"/>
     </row>
     <row r="511" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A511" s="13"/>
       <c r="B511" s="14" t="s">
-        <v>1569</v>
+        <v>1586</v>
       </c>
       <c r="C511" s="14" t="s">
-        <v>307</v>
+        <v>714</v>
       </c>
       <c r="D511" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E511" s="14"/>
       <c r="F511" s="14"/>
-      <c r="G511" s="12"/>
+      <c r="G511" s="12" t="s">
+        <v>1587</v>
+      </c>
       <c r="H511" s="14" t="s">
-        <v>338</v>
-      </c>
-      <c r="I511" s="16" t="s">
-        <v>413</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="I511" s="16"/>
       <c r="J511" s="22"/>
-      <c r="K511" s="18" t="s">
-        <v>1465</v>
-      </c>
+      <c r="K511" s="18"/>
       <c r="L511" s="18"/>
     </row>
     <row r="512" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A512" s="13"/>
       <c r="B512" s="14" t="s">
-        <v>1570</v>
+        <v>1588</v>
       </c>
       <c r="C512" s="14" t="s">
-        <v>307</v>
+        <v>714</v>
       </c>
       <c r="D512" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E512" s="14"/>
       <c r="F512" s="14"/>
-      <c r="G512" s="12"/>
-      <c r="H512" s="14"/>
-      <c r="I512" s="16" t="s">
-        <v>56</v>
-      </c>
+      <c r="G512" s="12" t="s">
+        <v>1589</v>
+      </c>
+      <c r="H512" s="14" t="s">
+        <v>717</v>
+      </c>
+      <c r="I512" s="16"/>
       <c r="J512" s="22"/>
-      <c r="K512" s="22" t="s">
-        <v>1517</v>
-      </c>
+      <c r="K512" s="18"/>
       <c r="L512" s="18"/>
     </row>
     <row r="513" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A513" s="13"/>
       <c r="B513" s="14" t="s">
-        <v>1571</v>
+        <v>1590</v>
       </c>
       <c r="C513" s="14" t="s">
-        <v>298</v>
+        <v>197</v>
       </c>
       <c r="D513" s="15">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E513" s="14"/>
       <c r="F513" s="14"/>
-      <c r="G513" s="12" t="s">
-        <v>1572</v>
-      </c>
-      <c r="H513" s="14"/>
-      <c r="I513" s="16"/>
-      <c r="J513" s="17"/>
+      <c r="G513" s="12"/>
+      <c r="H513" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="I513" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="J513" s="22"/>
       <c r="K513" s="18"/>
-      <c r="L513" s="22"/>
+      <c r="L513" s="18"/>
     </row>
     <row r="514" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A514" s="13"/>
       <c r="B514" s="14" t="s">
-        <v>1573</v>
+        <v>1591</v>
       </c>
       <c r="C514" s="14" t="s">
-        <v>298</v>
+        <v>197</v>
       </c>
       <c r="D514" s="15">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E514" s="14"/>
       <c r="F514" s="14"/>
-      <c r="G514" s="12" t="s">
-        <v>1572</v>
-      </c>
-      <c r="H514" s="14"/>
-      <c r="I514" s="16"/>
-      <c r="J514" s="17"/>
+      <c r="G514" s="12"/>
+      <c r="H514" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="I514" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="J514" s="22"/>
       <c r="K514" s="18"/>
-      <c r="L514" s="22"/>
+      <c r="L514" s="18"/>
     </row>
     <row r="515" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A515" s="13"/>
       <c r="B515" s="14" t="s">
-        <v>1574</v>
+        <v>1592</v>
       </c>
       <c r="C515" s="14" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D515" s="15">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E515" s="14"/>
       <c r="F515" s="14"/>
       <c r="G515" s="12" t="s">
-        <v>1575</v>
+        <v>1593</v>
       </c>
       <c r="H515" s="14"/>
-      <c r="I515" s="16"/>
-      <c r="J515" s="17"/>
+      <c r="I515" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J515" s="22"/>
       <c r="K515" s="18"/>
-      <c r="L515" s="22"/>
+      <c r="L515" s="18"/>
     </row>
     <row r="516" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A516" s="13"/>
       <c r="B516" s="14" t="s">
-        <v>1576</v>
+        <v>1594</v>
       </c>
       <c r="C516" s="14" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D516" s="15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E516" s="14"/>
       <c r="F516" s="14"/>
-      <c r="G516" s="12" t="s">
-        <v>1577</v>
-      </c>
-      <c r="H516" s="14"/>
-      <c r="I516" s="16"/>
-      <c r="J516" s="17"/>
-      <c r="K516" s="18"/>
-      <c r="L516" s="22"/>
+      <c r="G516" s="12"/>
+      <c r="H516" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="I516" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="J516" s="22"/>
+      <c r="K516" s="18" t="s">
+        <v>1550</v>
+      </c>
+      <c r="L516" s="18"/>
     </row>
     <row r="517" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A517" s="13"/>
       <c r="B517" s="14" t="s">
-        <v>1578</v>
+        <v>1595</v>
       </c>
       <c r="C517" s="14" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D517" s="15">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E517" s="14"/>
       <c r="F517" s="14"/>
-      <c r="G517" s="12" t="s">
-        <v>1579</v>
-      </c>
-      <c r="H517" s="14"/>
-      <c r="I517" s="16"/>
-      <c r="J517" s="17"/>
-      <c r="K517" s="18"/>
-      <c r="L517" s="22"/>
+      <c r="G517" s="12"/>
+      <c r="H517" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="I517" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J517" s="22"/>
+      <c r="K517" s="18" t="s">
+        <v>1553</v>
+      </c>
+      <c r="L517" s="18"/>
     </row>
     <row r="518" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A518" s="13"/>
       <c r="B518" s="14" t="s">
-        <v>1580</v>
+        <v>1596</v>
       </c>
       <c r="C518" s="14" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D518" s="15">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E518" s="14"/>
       <c r="F518" s="14"/>
-      <c r="G518" s="12" t="s">
-        <v>1579</v>
-      </c>
-      <c r="H518" s="14"/>
-      <c r="I518" s="16"/>
-      <c r="J518" s="17"/>
-      <c r="K518" s="18"/>
-      <c r="L518" s="22"/>
+      <c r="G518" s="12"/>
+      <c r="H518" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="I518" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="J518" s="22"/>
+      <c r="K518" s="18" t="s">
+        <v>1597</v>
+      </c>
+      <c r="L518" s="18"/>
     </row>
     <row r="519" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A519" s="13"/>
       <c r="B519" s="14" t="s">
-        <v>1581</v>
+        <v>1598</v>
       </c>
       <c r="C519" s="14" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D519" s="15">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E519" s="14"/>
-      <c r="F519" s="16"/>
-      <c r="G519" s="24"/>
+      <c r="F519" s="14"/>
+      <c r="G519" s="12"/>
       <c r="H519" s="14" t="s">
-        <v>1288</v>
-      </c>
-      <c r="I519" s="16"/>
+        <v>338</v>
+      </c>
+      <c r="I519" s="16" t="s">
+        <v>47</v>
+      </c>
       <c r="J519" s="22"/>
-      <c r="K519" s="18"/>
-      <c r="L519" s="25"/>
+      <c r="K519" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="L519" s="18"/>
     </row>
     <row r="520" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A520" s="13"/>
       <c r="B520" s="14" t="s">
-        <v>1582</v>
+        <v>1599</v>
       </c>
       <c r="C520" s="14" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D520" s="15">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E520" s="14"/>
-      <c r="F520" s="16"/>
-      <c r="G520" s="24"/>
+      <c r="F520" s="14"/>
+      <c r="G520" s="12"/>
       <c r="H520" s="14" t="s">
-        <v>1288</v>
-      </c>
-      <c r="I520" s="16"/>
+        <v>338</v>
+      </c>
+      <c r="I520" s="16" t="s">
+        <v>413</v>
+      </c>
       <c r="J520" s="22"/>
-      <c r="K520" s="18"/>
-      <c r="L520" s="25"/>
+      <c r="K520" s="18" t="s">
+        <v>1498</v>
+      </c>
+      <c r="L520" s="18"/>
     </row>
     <row r="521" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A521" s="13"/>
       <c r="B521" s="14" t="s">
-        <v>1583</v>
+        <v>1600</v>
       </c>
       <c r="C521" s="14" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="D521" s="15">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E521" s="14"/>
-      <c r="F521" s="16"/>
-      <c r="G521" s="12" t="s">
-        <v>1579</v>
-      </c>
-      <c r="H521" s="14" t="s">
-        <v>1288</v>
-      </c>
-      <c r="I521" s="16"/>
+      <c r="F521" s="14"/>
+      <c r="G521" s="12"/>
+      <c r="H521" s="14"/>
+      <c r="I521" s="16" t="s">
+        <v>56</v>
+      </c>
       <c r="J521" s="22"/>
-      <c r="K521" s="18"/>
-      <c r="L521" s="25"/>
+      <c r="K521" s="22" t="s">
+        <v>1549</v>
+      </c>
+      <c r="L521" s="18"/>
     </row>
     <row r="522" s="12" customFormat="1" customHeight="1" spans="1:12">
       <c r="A522" s="13"/>
       <c r="B522" s="14" t="s">
-        <v>1584</v>
+        <v>1601</v>
       </c>
       <c r="C522" s="14" t="s">
-        <v>38</v>
+        <v>298</v>
       </c>
       <c r="D522" s="15">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="E522" s="14"/>
       <c r="F522" s="14"/>
-      <c r="G522" s="12"/>
+      <c r="G522" s="12" t="s">
+        <v>1602</v>
+      </c>
       <c r="H522" s="14"/>
       <c r="I522" s="16"/>
+      <c r="J522" s="17"/>
+      <c r="K522" s="18"/>
+      <c r="L522" s="22"/>
+    </row>
+    <row r="523" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A523" s="13"/>
+      <c r="B523" s="14" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C523" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D523" s="15">
+        <v>8</v>
+      </c>
+      <c r="E523" s="14"/>
+      <c r="F523" s="14"/>
+      <c r="G523" s="12" t="s">
+        <v>1602</v>
+      </c>
+      <c r="H523" s="14"/>
+      <c r="I523" s="16"/>
+      <c r="J523" s="17"/>
+      <c r="K523" s="18"/>
+      <c r="L523" s="22"/>
+    </row>
+    <row r="524" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A524" s="13"/>
+      <c r="B524" s="14" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C524" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D524" s="15">
+        <v>9</v>
+      </c>
+      <c r="E524" s="14"/>
+      <c r="F524" s="14"/>
+      <c r="G524" s="12" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H524" s="14"/>
+      <c r="I524" s="16"/>
+      <c r="J524" s="17"/>
+      <c r="K524" s="18"/>
+      <c r="L524" s="22"/>
+    </row>
+    <row r="525" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A525" s="13"/>
+      <c r="B525" s="14" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C525" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D525" s="15">
+        <v>10</v>
+      </c>
+      <c r="E525" s="14"/>
+      <c r="F525" s="14"/>
+      <c r="G525" s="12" t="s">
+        <v>1607</v>
+      </c>
+      <c r="H525" s="14"/>
+      <c r="I525" s="16"/>
+      <c r="J525" s="17"/>
+      <c r="K525" s="18"/>
+      <c r="L525" s="22"/>
+    </row>
+    <row r="526" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A526" s="13"/>
+      <c r="B526" s="14" t="s">
+        <v>1608</v>
+      </c>
+      <c r="C526" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D526" s="15">
+        <v>11</v>
+      </c>
+      <c r="E526" s="14"/>
+      <c r="F526" s="14"/>
+      <c r="G526" s="12" t="s">
+        <v>1609</v>
+      </c>
+      <c r="H526" s="14"/>
+      <c r="I526" s="16"/>
+      <c r="J526" s="17"/>
+      <c r="K526" s="18"/>
+      <c r="L526" s="22"/>
+    </row>
+    <row r="527" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A527" s="13"/>
+      <c r="B527" s="14" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C527" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D527" s="15">
+        <v>13</v>
+      </c>
+      <c r="E527" s="14"/>
+      <c r="F527" s="14"/>
+      <c r="G527" s="12" t="s">
+        <v>1609</v>
+      </c>
+      <c r="H527" s="14"/>
+      <c r="I527" s="16"/>
+      <c r="J527" s="17"/>
+      <c r="K527" s="18"/>
+      <c r="L527" s="22"/>
+    </row>
+    <row r="528" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A528" s="13"/>
+      <c r="B528" s="14" t="s">
+        <v>1611</v>
+      </c>
+      <c r="C528" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D528" s="15">
+        <v>17</v>
+      </c>
+      <c r="E528" s="14"/>
+      <c r="F528" s="16"/>
+      <c r="G528" s="24"/>
+      <c r="H528" s="14" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I528" s="16"/>
+      <c r="J528" s="22"/>
+      <c r="K528" s="18"/>
+      <c r="L528" s="25"/>
+    </row>
+    <row r="529" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A529" s="13"/>
+      <c r="B529" s="14" t="s">
+        <v>1612</v>
+      </c>
+      <c r="C529" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D529" s="15">
+        <v>18</v>
+      </c>
+      <c r="E529" s="14"/>
+      <c r="F529" s="16"/>
+      <c r="G529" s="24"/>
+      <c r="H529" s="14" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I529" s="16"/>
+      <c r="J529" s="22"/>
+      <c r="K529" s="18"/>
+      <c r="L529" s="25"/>
+    </row>
+    <row r="530" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A530" s="13"/>
+      <c r="B530" s="14" t="s">
+        <v>1613</v>
+      </c>
+      <c r="C530" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="D530" s="15">
+        <v>19</v>
+      </c>
+      <c r="E530" s="14"/>
+      <c r="F530" s="16"/>
+      <c r="G530" s="12" t="s">
+        <v>1609</v>
+      </c>
+      <c r="H530" s="14" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I530" s="16"/>
+      <c r="J530" s="22"/>
+      <c r="K530" s="18"/>
+      <c r="L530" s="25"/>
+    </row>
+    <row r="531" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A531" s="13"/>
+      <c r="B531" s="14" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C531" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D531" s="15">
+        <v>65</v>
+      </c>
+      <c r="E531" s="14"/>
+      <c r="F531" s="14"/>
+      <c r="G531" s="12"/>
+      <c r="H531" s="14"/>
+      <c r="I531" s="16"/>
+    </row>
+    <row r="532" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A532" s="13"/>
+      <c r="B532" s="14"/>
+      <c r="C532" s="14"/>
+      <c r="D532" s="15"/>
+      <c r="E532" s="14"/>
+      <c r="F532" s="14"/>
+      <c r="G532" s="12" t="s">
+        <v>1615</v>
+      </c>
+      <c r="H532" s="14" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I532" s="16"/>
+    </row>
+    <row r="533" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A533" s="13"/>
+      <c r="B533" s="14"/>
+      <c r="C533" s="14"/>
+      <c r="D533" s="15"/>
+      <c r="E533" s="14"/>
+      <c r="F533" s="14"/>
+      <c r="G533" s="12" t="s">
+        <v>1616</v>
+      </c>
+      <c r="H533" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I533" s="16"/>
+    </row>
+    <row r="534" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A534" s="13"/>
+      <c r="B534" s="14"/>
+      <c r="C534" s="14"/>
+      <c r="D534" s="15"/>
+      <c r="E534" s="14"/>
+      <c r="F534" s="14"/>
+      <c r="G534" s="12" t="s">
+        <v>1616</v>
+      </c>
+      <c r="H534" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I534" s="16"/>
+    </row>
+    <row r="535" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A535" s="13"/>
+      <c r="B535" s="14"/>
+      <c r="C535" s="14"/>
+      <c r="D535" s="15"/>
+      <c r="E535" s="14"/>
+      <c r="F535" s="14"/>
+      <c r="G535" s="12" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H535" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I535" s="16"/>
+    </row>
+    <row r="536" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A536" s="13"/>
+      <c r="B536" s="14"/>
+      <c r="C536" s="14"/>
+      <c r="D536" s="15"/>
+      <c r="E536" s="14"/>
+      <c r="F536" s="14"/>
+      <c r="G536" s="12" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H536" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I536" s="16"/>
+    </row>
+    <row r="537" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A537" s="13"/>
+      <c r="B537" s="14"/>
+      <c r="C537" s="14"/>
+      <c r="D537" s="15"/>
+      <c r="E537" s="14"/>
+      <c r="F537" s="14"/>
+      <c r="G537" s="12" t="s">
+        <v>1619</v>
+      </c>
+      <c r="H537" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I537" s="16"/>
+    </row>
+    <row r="538" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A538" s="13"/>
+      <c r="B538" s="14"/>
+      <c r="C538" s="14"/>
+      <c r="D538" s="15"/>
+      <c r="E538" s="14"/>
+      <c r="F538" s="14"/>
+      <c r="G538" s="12" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H538" s="14"/>
+      <c r="I538" s="16"/>
+    </row>
+    <row r="539" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A539" s="13"/>
+      <c r="B539" s="14"/>
+      <c r="C539" s="14"/>
+      <c r="D539" s="15"/>
+      <c r="E539" s="14"/>
+      <c r="F539" s="14"/>
+      <c r="G539" s="12" t="s">
+        <v>1621</v>
+      </c>
+      <c r="H539" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I539" s="16"/>
+    </row>
+    <row r="540" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A540" s="13"/>
+      <c r="B540" s="14"/>
+      <c r="C540" s="14"/>
+      <c r="D540" s="15"/>
+      <c r="E540" s="14"/>
+      <c r="F540" s="14"/>
+      <c r="G540" s="12" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H540" s="14"/>
+      <c r="I540" s="16"/>
+    </row>
+    <row r="541" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A541" s="13"/>
+      <c r="B541" s="14"/>
+      <c r="C541" s="14"/>
+      <c r="D541" s="15"/>
+      <c r="E541" s="14"/>
+      <c r="F541" s="14"/>
+      <c r="G541" s="12" t="s">
+        <v>1623</v>
+      </c>
+      <c r="H541" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I541" s="16"/>
+    </row>
+    <row r="542" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A542" s="13"/>
+      <c r="B542" s="14"/>
+      <c r="C542" s="14"/>
+      <c r="D542" s="15"/>
+      <c r="E542" s="14"/>
+      <c r="F542" s="14"/>
+      <c r="G542" s="12" t="s">
+        <v>1624</v>
+      </c>
+      <c r="H542" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I542" s="16"/>
+    </row>
+    <row r="543" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A543" s="13"/>
+      <c r="B543" s="14"/>
+      <c r="C543" s="14"/>
+      <c r="D543" s="15"/>
+      <c r="E543" s="14"/>
+      <c r="F543" s="14"/>
+      <c r="G543" s="12" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H543" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I543" s="16"/>
+    </row>
+    <row r="544" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A544" s="13"/>
+      <c r="B544" s="14"/>
+      <c r="C544" s="14"/>
+      <c r="D544" s="15"/>
+      <c r="E544" s="14"/>
+      <c r="F544" s="14"/>
+      <c r="G544" s="12" t="s">
+        <v>1626</v>
+      </c>
+      <c r="H544" s="14"/>
+      <c r="I544" s="16"/>
+    </row>
+    <row r="545" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A545" s="13"/>
+      <c r="B545" s="14"/>
+      <c r="C545" s="14"/>
+      <c r="D545" s="15"/>
+      <c r="E545" s="14"/>
+      <c r="F545" s="14"/>
+      <c r="G545" s="12" t="s">
+        <v>1627</v>
+      </c>
+      <c r="H545" s="14"/>
+      <c r="I545" s="16"/>
+    </row>
+    <row r="546" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A546" s="13"/>
+      <c r="B546" s="14"/>
+      <c r="C546" s="14"/>
+      <c r="D546" s="15"/>
+      <c r="E546" s="14"/>
+      <c r="F546" s="14"/>
+      <c r="G546" s="12" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H546" s="14"/>
+      <c r="I546" s="16"/>
+    </row>
+    <row r="547" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A547" s="13"/>
+      <c r="B547" s="14"/>
+      <c r="C547" s="14"/>
+      <c r="D547" s="15"/>
+      <c r="E547" s="14"/>
+      <c r="F547" s="14"/>
+      <c r="G547" s="12" t="s">
+        <v>1629</v>
+      </c>
+      <c r="H547" s="14"/>
+      <c r="I547" s="16"/>
+    </row>
+    <row r="548" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A548" s="13"/>
+      <c r="B548" s="14"/>
+      <c r="C548" s="14"/>
+      <c r="D548" s="15"/>
+      <c r="E548" s="14"/>
+      <c r="F548" s="14"/>
+      <c r="G548" s="12" t="s">
+        <v>1630</v>
+      </c>
+      <c r="H548" s="14"/>
+      <c r="I548" s="16"/>
+    </row>
+    <row r="549" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A549" s="13"/>
+      <c r="B549" s="14"/>
+      <c r="C549" s="14"/>
+      <c r="D549" s="15"/>
+      <c r="E549" s="14"/>
+      <c r="F549" s="14"/>
+      <c r="G549" s="12" t="s">
+        <v>1631</v>
+      </c>
+      <c r="H549" s="14"/>
+      <c r="I549" s="16"/>
+    </row>
+    <row r="550" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A550" s="13"/>
+      <c r="B550" s="14"/>
+      <c r="C550" s="14"/>
+      <c r="D550" s="15"/>
+      <c r="E550" s="14"/>
+      <c r="F550" s="14"/>
+      <c r="G550" s="12" t="s">
+        <v>1632</v>
+      </c>
+      <c r="H550" s="14"/>
+      <c r="I550" s="16"/>
+    </row>
+    <row r="551" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A551" s="13"/>
+      <c r="B551" s="14"/>
+      <c r="C551" s="14"/>
+      <c r="D551" s="15"/>
+      <c r="E551" s="14"/>
+      <c r="F551" s="14"/>
+      <c r="G551" s="12" t="s">
+        <v>1633</v>
+      </c>
+      <c r="H551" s="14"/>
+      <c r="I551" s="16"/>
+    </row>
+    <row r="552" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A552" s="13"/>
+      <c r="B552" s="14"/>
+      <c r="C552" s="14"/>
+      <c r="D552" s="15"/>
+      <c r="E552" s="14"/>
+      <c r="F552" s="14"/>
+      <c r="G552" s="12" t="s">
+        <v>1634</v>
+      </c>
+      <c r="H552" s="14"/>
+      <c r="I552" s="16"/>
+    </row>
+    <row r="553" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A553" s="13"/>
+      <c r="B553" s="14"/>
+      <c r="C553" s="14"/>
+      <c r="D553" s="15"/>
+      <c r="E553" s="14"/>
+      <c r="F553" s="14"/>
+      <c r="G553" s="12" t="s">
+        <v>1635</v>
+      </c>
+      <c r="H553" s="14"/>
+      <c r="I553" s="16"/>
+    </row>
+    <row r="554" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A554" s="13"/>
+      <c r="B554" s="14"/>
+      <c r="C554" s="14"/>
+      <c r="D554" s="15"/>
+      <c r="E554" s="14"/>
+      <c r="F554" s="14"/>
+      <c r="G554" s="12" t="s">
+        <v>1636</v>
+      </c>
+      <c r="H554" s="14"/>
+      <c r="I554" s="16"/>
+    </row>
+    <row r="555" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A555" s="13"/>
+      <c r="B555" s="14"/>
+      <c r="C555" s="14"/>
+      <c r="D555" s="15"/>
+      <c r="E555" s="14"/>
+      <c r="F555" s="14"/>
+      <c r="G555" s="12" t="s">
+        <v>1637</v>
+      </c>
+      <c r="H555" s="14"/>
+      <c r="I555" s="16"/>
+    </row>
+    <row r="556" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A556" s="13"/>
+      <c r="B556" s="14"/>
+      <c r="C556" s="14"/>
+      <c r="D556" s="15"/>
+      <c r="E556" s="14"/>
+      <c r="F556" s="14"/>
+      <c r="G556" s="12" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H556" s="14"/>
+      <c r="I556" s="16"/>
+    </row>
+    <row r="557" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A557" s="13"/>
+      <c r="B557" s="14"/>
+      <c r="C557" s="14"/>
+      <c r="D557" s="15"/>
+      <c r="E557" s="14"/>
+      <c r="F557" s="14"/>
+      <c r="G557" s="12" t="s">
+        <v>1639</v>
+      </c>
+      <c r="H557" s="14"/>
+      <c r="I557" s="16"/>
+    </row>
+    <row r="558" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A558" s="13"/>
+      <c r="B558" s="14"/>
+      <c r="C558" s="14"/>
+      <c r="D558" s="15"/>
+      <c r="E558" s="14"/>
+      <c r="F558" s="14"/>
+      <c r="G558" s="12" t="s">
+        <v>1640</v>
+      </c>
+      <c r="H558" s="14"/>
+      <c r="I558" s="16"/>
+    </row>
+    <row r="559" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A559" s="13"/>
+      <c r="B559" s="14"/>
+      <c r="C559" s="14"/>
+      <c r="D559" s="15"/>
+      <c r="E559" s="14"/>
+      <c r="F559" s="14"/>
+      <c r="G559" s="12" t="s">
+        <v>1641</v>
+      </c>
+      <c r="H559" s="14"/>
+      <c r="I559" s="16"/>
+    </row>
+    <row r="560" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A560" s="13"/>
+      <c r="B560" s="14"/>
+      <c r="C560" s="14"/>
+      <c r="D560" s="15"/>
+      <c r="E560" s="14"/>
+      <c r="F560" s="14"/>
+      <c r="G560" s="12" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H560" s="14" t="s">
+        <v>1643</v>
+      </c>
+      <c r="I560" s="16"/>
+    </row>
+    <row r="561" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A561" s="13"/>
+      <c r="B561" s="14"/>
+      <c r="C561" s="14"/>
+      <c r="D561" s="15"/>
+      <c r="E561" s="14"/>
+      <c r="F561" s="14"/>
+      <c r="G561" s="12" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H561" s="14"/>
+      <c r="I561" s="16"/>
+    </row>
+    <row r="562" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A562" s="13"/>
+      <c r="B562" s="14"/>
+      <c r="C562" s="14"/>
+      <c r="D562" s="15"/>
+      <c r="E562" s="14"/>
+      <c r="F562" s="14"/>
+      <c r="G562" s="12" t="s">
+        <v>1644</v>
+      </c>
+      <c r="H562" s="14"/>
+      <c r="I562" s="16"/>
+    </row>
+    <row r="563" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A563" s="13"/>
+      <c r="B563" s="14"/>
+      <c r="C563" s="14"/>
+      <c r="D563" s="15"/>
+      <c r="E563" s="14"/>
+      <c r="F563" s="14"/>
+      <c r="G563" s="12" t="s">
+        <v>1645</v>
+      </c>
+      <c r="H563" s="14" t="s">
+        <v>1643</v>
+      </c>
+      <c r="I563" s="16"/>
+    </row>
+    <row r="564" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A564" s="13"/>
+      <c r="B564" s="14"/>
+      <c r="C564" s="14"/>
+      <c r="D564" s="15"/>
+      <c r="E564" s="14"/>
+      <c r="F564" s="14"/>
+      <c r="G564" s="12" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H564" s="14" t="s">
+        <v>1643</v>
+      </c>
+      <c r="I564" s="16"/>
+    </row>
+    <row r="565" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A565" s="13"/>
+      <c r="B565" s="14"/>
+      <c r="C565" s="14"/>
+      <c r="D565" s="15"/>
+      <c r="E565" s="14"/>
+      <c r="F565" s="14"/>
+      <c r="G565" s="12" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H565" s="14"/>
+      <c r="I565" s="16"/>
+    </row>
+    <row r="566" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A566" s="13"/>
+      <c r="B566" s="14"/>
+      <c r="C566" s="14"/>
+      <c r="D566" s="15"/>
+      <c r="E566" s="14"/>
+      <c r="F566" s="14"/>
+      <c r="G566" s="12" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H566" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I566" s="16"/>
+    </row>
+    <row r="567" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A567" s="13"/>
+      <c r="B567" s="14"/>
+      <c r="C567" s="14"/>
+      <c r="D567" s="15"/>
+      <c r="E567" s="14"/>
+      <c r="F567" s="14"/>
+      <c r="G567" s="12" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H567" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I567" s="16"/>
+    </row>
+    <row r="568" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A568" s="13"/>
+      <c r="B568" s="14"/>
+      <c r="C568" s="14"/>
+      <c r="D568" s="15"/>
+      <c r="E568" s="14"/>
+      <c r="F568" s="14"/>
+      <c r="G568" s="12" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H568" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I568" s="16"/>
+    </row>
+    <row r="569" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A569" s="13"/>
+      <c r="B569" s="14"/>
+      <c r="C569" s="14"/>
+      <c r="D569" s="15"/>
+      <c r="E569" s="14"/>
+      <c r="F569" s="14"/>
+      <c r="G569" s="12" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H569" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I569" s="16"/>
+    </row>
+    <row r="570" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A570" s="13"/>
+      <c r="B570" s="14"/>
+      <c r="C570" s="14"/>
+      <c r="D570" s="15"/>
+      <c r="E570" s="14"/>
+      <c r="F570" s="14"/>
+      <c r="G570" s="12" t="s">
+        <v>1651</v>
+      </c>
+      <c r="H570" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="I570" s="16"/>
+    </row>
+    <row r="571" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A571" s="13"/>
+      <c r="B571" s="14"/>
+      <c r="C571" s="14"/>
+      <c r="D571" s="15"/>
+      <c r="E571" s="14"/>
+      <c r="F571" s="14"/>
+      <c r="G571" s="12" t="s">
+        <v>1652</v>
+      </c>
+      <c r="H571" s="14"/>
+      <c r="I571" s="16"/>
+    </row>
+    <row r="572" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A572" s="13"/>
+      <c r="B572" s="14"/>
+      <c r="C572" s="14"/>
+      <c r="D572" s="15"/>
+      <c r="E572" s="14"/>
+      <c r="F572" s="14"/>
+      <c r="G572" s="12" t="s">
+        <v>1653</v>
+      </c>
+      <c r="H572" s="14"/>
+      <c r="I572" s="16"/>
+    </row>
+    <row r="573" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A573" s="13"/>
+      <c r="B573" s="14"/>
+      <c r="C573" s="14"/>
+      <c r="D573" s="15"/>
+      <c r="E573" s="14"/>
+      <c r="F573" s="14"/>
+      <c r="G573" s="12" t="s">
+        <v>1654</v>
+      </c>
+      <c r="H573" s="14"/>
+      <c r="I573" s="16"/>
+    </row>
+    <row r="574" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A574" s="13"/>
+      <c r="B574" s="14"/>
+      <c r="C574" s="14"/>
+      <c r="D574" s="15"/>
+      <c r="E574" s="14"/>
+      <c r="F574" s="14"/>
+      <c r="G574" s="12" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H574" s="14"/>
+      <c r="I574" s="16"/>
+    </row>
+    <row r="575" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A575" s="13"/>
+      <c r="B575" s="14"/>
+      <c r="C575" s="14"/>
+      <c r="D575" s="15"/>
+      <c r="E575" s="14"/>
+      <c r="F575" s="14"/>
+      <c r="G575" s="12" t="s">
+        <v>1656</v>
+      </c>
+      <c r="H575" s="14"/>
+      <c r="I575" s="16"/>
+    </row>
+    <row r="576" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A576" s="13"/>
+      <c r="B576" s="14"/>
+      <c r="C576" s="14"/>
+      <c r="D576" s="15"/>
+      <c r="E576" s="14"/>
+      <c r="F576" s="14"/>
+      <c r="G576" s="12" t="s">
+        <v>1657</v>
+      </c>
+      <c r="H576" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="I576" s="16"/>
+    </row>
+    <row r="577" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A577" s="13"/>
+      <c r="B577" s="14"/>
+      <c r="C577" s="14"/>
+      <c r="D577" s="15"/>
+      <c r="E577" s="14"/>
+      <c r="F577" s="14"/>
+      <c r="G577" s="12" t="s">
+        <v>1658</v>
+      </c>
+      <c r="H577" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="I577" s="16"/>
+    </row>
+    <row r="578" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A578" s="13"/>
+      <c r="B578" s="14"/>
+      <c r="C578" s="14"/>
+      <c r="D578" s="15"/>
+      <c r="E578" s="14"/>
+      <c r="F578" s="14"/>
+      <c r="G578" s="12" t="s">
+        <v>1659</v>
+      </c>
+      <c r="H578" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="I578" s="16"/>
+    </row>
+    <row r="579" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A579" s="13"/>
+      <c r="B579" s="14"/>
+      <c r="C579" s="14"/>
+      <c r="D579" s="15"/>
+      <c r="E579" s="14"/>
+      <c r="F579" s="14"/>
+      <c r="G579" s="12" t="s">
+        <v>1660</v>
+      </c>
+      <c r="H579" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="I579" s="16"/>
+    </row>
+    <row r="580" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A580" s="13"/>
+      <c r="B580" s="14"/>
+      <c r="C580" s="14"/>
+      <c r="D580" s="15"/>
+      <c r="E580" s="14"/>
+      <c r="F580" s="14"/>
+      <c r="G580" s="12" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H580" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="I580" s="16"/>
+    </row>
+    <row r="581" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A581" s="13"/>
+      <c r="B581" s="14"/>
+      <c r="C581" s="14"/>
+      <c r="D581" s="15"/>
+      <c r="E581" s="14"/>
+      <c r="F581" s="14"/>
+      <c r="G581" s="12" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H581" s="14"/>
+      <c r="I581" s="16"/>
+    </row>
+    <row r="582" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A582" s="13"/>
+      <c r="B582" s="14"/>
+      <c r="C582" s="14"/>
+      <c r="D582" s="15"/>
+      <c r="E582" s="14"/>
+      <c r="F582" s="14"/>
+      <c r="G582" s="12" t="s">
+        <v>1663</v>
+      </c>
+      <c r="H582" s="14"/>
+      <c r="I582" s="16"/>
+    </row>
+    <row r="583" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A583" s="13"/>
+      <c r="B583" s="14"/>
+      <c r="C583" s="14"/>
+      <c r="D583" s="15"/>
+      <c r="E583" s="14"/>
+      <c r="F583" s="14"/>
+      <c r="G583" s="12" t="s">
+        <v>1664</v>
+      </c>
+      <c r="H583" s="14"/>
+      <c r="I583" s="16"/>
+    </row>
+    <row r="584" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A584" s="13"/>
+      <c r="B584" s="14"/>
+      <c r="C584" s="14"/>
+      <c r="D584" s="15"/>
+      <c r="E584" s="14"/>
+      <c r="F584" s="14"/>
+      <c r="G584" s="12" t="s">
+        <v>1665</v>
+      </c>
+      <c r="H584" s="14"/>
+      <c r="I584" s="16"/>
+    </row>
+    <row r="585" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A585" s="13"/>
+      <c r="B585" s="14"/>
+      <c r="C585" s="14"/>
+      <c r="D585" s="15"/>
+      <c r="E585" s="14"/>
+      <c r="F585" s="14"/>
+      <c r="G585" s="12" t="s">
+        <v>1666</v>
+      </c>
+      <c r="H585" s="14"/>
+      <c r="I585" s="16"/>
+    </row>
+    <row r="586" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A586" s="13"/>
+      <c r="B586" s="14"/>
+      <c r="C586" s="14"/>
+      <c r="D586" s="15"/>
+      <c r="E586" s="14"/>
+      <c r="F586" s="14"/>
+      <c r="G586" s="12" t="s">
+        <v>1667</v>
+      </c>
+      <c r="H586" s="14"/>
+      <c r="I586" s="16"/>
+    </row>
+    <row r="587" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A587" s="13"/>
+      <c r="B587" s="14"/>
+      <c r="C587" s="14"/>
+      <c r="D587" s="15"/>
+      <c r="E587" s="14"/>
+      <c r="F587" s="14"/>
+      <c r="G587" s="12" t="s">
+        <v>1668</v>
+      </c>
+      <c r="H587" s="14"/>
+      <c r="I587" s="16"/>
+    </row>
+    <row r="588" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A588" s="13"/>
+      <c r="B588" s="14"/>
+      <c r="C588" s="14"/>
+      <c r="D588" s="15"/>
+      <c r="E588" s="14"/>
+      <c r="F588" s="14"/>
+      <c r="G588" s="12" t="s">
+        <v>1669</v>
+      </c>
+      <c r="H588" s="14"/>
+      <c r="I588" s="16"/>
+    </row>
+    <row r="589" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A589" s="13"/>
+      <c r="B589" s="14"/>
+      <c r="C589" s="14"/>
+      <c r="D589" s="15"/>
+      <c r="E589" s="14"/>
+      <c r="F589" s="14"/>
+      <c r="G589" s="12" t="s">
+        <v>1670</v>
+      </c>
+      <c r="H589" s="14"/>
+      <c r="I589" s="16"/>
+    </row>
+    <row r="590" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A590" s="13"/>
+      <c r="B590" s="14"/>
+      <c r="C590" s="14"/>
+      <c r="D590" s="15"/>
+      <c r="E590" s="14"/>
+      <c r="F590" s="14"/>
+      <c r="G590" s="12" t="s">
+        <v>1671</v>
+      </c>
+      <c r="H590" s="14"/>
+      <c r="I590" s="16"/>
+    </row>
+    <row r="591" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A591" s="13"/>
+      <c r="B591" s="14"/>
+      <c r="C591" s="14"/>
+      <c r="D591" s="15"/>
+      <c r="E591" s="14"/>
+      <c r="F591" s="14"/>
+      <c r="G591" s="12" t="s">
+        <v>1672</v>
+      </c>
+      <c r="H591" s="14"/>
+      <c r="I591" s="16"/>
+    </row>
+    <row r="592" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A592" s="13"/>
+      <c r="B592" s="14"/>
+      <c r="C592" s="14"/>
+      <c r="D592" s="15"/>
+      <c r="E592" s="14"/>
+      <c r="F592" s="14"/>
+      <c r="G592" s="12" t="s">
+        <v>1673</v>
+      </c>
+      <c r="H592" s="14"/>
+      <c r="I592" s="16"/>
+    </row>
+    <row r="593" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A593" s="13"/>
+      <c r="B593" s="14"/>
+      <c r="C593" s="14"/>
+      <c r="D593" s="15"/>
+      <c r="E593" s="14"/>
+      <c r="F593" s="14"/>
+      <c r="G593" s="12" t="s">
+        <v>1673</v>
+      </c>
+      <c r="H593" s="14"/>
+      <c r="I593" s="16"/>
+    </row>
+    <row r="594" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A594" s="13"/>
+      <c r="B594" s="14"/>
+      <c r="C594" s="14"/>
+      <c r="D594" s="15"/>
+      <c r="E594" s="14"/>
+      <c r="F594" s="14"/>
+      <c r="G594" s="12" t="s">
+        <v>1674</v>
+      </c>
+      <c r="H594" s="14"/>
+      <c r="I594" s="16"/>
+    </row>
+    <row r="595" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A595" s="13"/>
+      <c r="B595" s="14"/>
+      <c r="C595" s="14"/>
+      <c r="D595" s="15"/>
+      <c r="E595" s="14"/>
+      <c r="F595" s="14"/>
+      <c r="G595" s="12" t="s">
+        <v>1675</v>
+      </c>
+      <c r="H595" s="14"/>
+      <c r="I595" s="16"/>
+    </row>
+    <row r="596" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A596" s="13"/>
+      <c r="B596" s="14"/>
+      <c r="C596" s="14"/>
+      <c r="D596" s="15"/>
+      <c r="E596" s="14"/>
+      <c r="F596" s="14"/>
+      <c r="G596" s="12" t="s">
+        <v>1676</v>
+      </c>
+      <c r="H596" s="14"/>
+      <c r="I596" s="16"/>
+    </row>
+    <row r="597" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A597" s="13"/>
+      <c r="B597" s="14"/>
+      <c r="C597" s="14"/>
+      <c r="D597" s="15"/>
+      <c r="E597" s="14"/>
+      <c r="F597" s="14"/>
+      <c r="G597" s="12" t="s">
+        <v>1677</v>
+      </c>
+      <c r="H597" s="14"/>
+      <c r="I597" s="16"/>
+    </row>
+    <row r="598" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A598" s="13"/>
+      <c r="B598" s="14"/>
+      <c r="C598" s="14"/>
+      <c r="D598" s="15"/>
+      <c r="E598" s="14"/>
+      <c r="F598" s="14"/>
+      <c r="G598" s="12" t="s">
+        <v>1678</v>
+      </c>
+      <c r="H598" s="14"/>
+      <c r="I598" s="16"/>
+    </row>
+    <row r="599" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A599" s="13"/>
+      <c r="B599" s="14"/>
+      <c r="C599" s="14"/>
+      <c r="D599" s="15"/>
+      <c r="E599" s="14"/>
+      <c r="F599" s="14"/>
+      <c r="G599" s="12" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H599" s="14"/>
+      <c r="I599" s="16"/>
+    </row>
+    <row r="600" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A600" s="13"/>
+      <c r="B600" s="14"/>
+      <c r="C600" s="14"/>
+      <c r="D600" s="15"/>
+      <c r="E600" s="14"/>
+      <c r="F600" s="14"/>
+      <c r="G600" s="12" t="s">
+        <v>1680</v>
+      </c>
+      <c r="H600" s="14"/>
+      <c r="I600" s="16"/>
+    </row>
+    <row r="601" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A601" s="13"/>
+      <c r="B601" s="14"/>
+      <c r="C601" s="14"/>
+      <c r="D601" s="15"/>
+      <c r="E601" s="14"/>
+      <c r="F601" s="14"/>
+      <c r="G601" s="12" t="s">
+        <v>1681</v>
+      </c>
+      <c r="H601" s="14" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I601" s="16"/>
+    </row>
+    <row r="602" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A602" s="13"/>
+      <c r="B602" s="14"/>
+      <c r="C602" s="14"/>
+      <c r="D602" s="15"/>
+      <c r="E602" s="14"/>
+      <c r="F602" s="14"/>
+      <c r="G602" s="12" t="s">
+        <v>1682</v>
+      </c>
+      <c r="H602" s="14" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I602" s="16"/>
+    </row>
+    <row r="603" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A603" s="13"/>
+      <c r="B603" s="14"/>
+      <c r="C603" s="14"/>
+      <c r="D603" s="15"/>
+      <c r="E603" s="14"/>
+      <c r="F603" s="14"/>
+      <c r="G603" s="12" t="s">
+        <v>1683</v>
+      </c>
+      <c r="H603" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I603" s="16"/>
+    </row>
+    <row r="604" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A604" s="13"/>
+      <c r="B604" s="14"/>
+      <c r="C604" s="14"/>
+      <c r="D604" s="15"/>
+      <c r="E604" s="14"/>
+      <c r="F604" s="14"/>
+      <c r="G604" s="12" t="s">
+        <v>1684</v>
+      </c>
+      <c r="H604" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I604" s="16"/>
+    </row>
+    <row r="605" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A605" s="13"/>
+      <c r="B605" s="14"/>
+      <c r="C605" s="14"/>
+      <c r="D605" s="15"/>
+      <c r="E605" s="14"/>
+      <c r="F605" s="14"/>
+      <c r="G605" s="12" t="s">
+        <v>1685</v>
+      </c>
+      <c r="H605" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="I605" s="16"/>
+    </row>
+    <row r="606" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A606" s="13"/>
+      <c r="B606" s="14"/>
+      <c r="C606" s="14"/>
+      <c r="D606" s="15"/>
+      <c r="E606" s="14"/>
+      <c r="F606" s="14"/>
+      <c r="G606" s="12" t="s">
+        <v>1686</v>
+      </c>
+      <c r="H606" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I606" s="16"/>
+    </row>
+    <row r="607" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A607" s="13"/>
+      <c r="B607" s="14"/>
+      <c r="C607" s="14"/>
+      <c r="D607" s="15"/>
+      <c r="E607" s="14"/>
+      <c r="F607" s="14"/>
+      <c r="G607" s="12" t="s">
+        <v>1687</v>
+      </c>
+      <c r="H607" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I607" s="16"/>
+    </row>
+    <row r="608" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A608" s="13"/>
+      <c r="B608" s="14"/>
+      <c r="C608" s="14"/>
+      <c r="D608" s="15"/>
+      <c r="E608" s="14"/>
+      <c r="F608" s="14"/>
+      <c r="G608" s="12" t="s">
+        <v>1688</v>
+      </c>
+      <c r="H608" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I608" s="16"/>
+    </row>
+    <row r="609" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A609" s="13"/>
+      <c r="B609" s="14"/>
+      <c r="C609" s="14"/>
+      <c r="D609" s="15"/>
+      <c r="E609" s="14"/>
+      <c r="F609" s="14"/>
+      <c r="G609" s="12" t="s">
+        <v>1689</v>
+      </c>
+      <c r="H609" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I609" s="16"/>
+    </row>
+    <row r="610" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A610" s="13"/>
+      <c r="B610" s="14"/>
+      <c r="C610" s="14"/>
+      <c r="D610" s="15"/>
+      <c r="E610" s="14"/>
+      <c r="F610" s="14"/>
+      <c r="G610" s="12" t="s">
+        <v>1690</v>
+      </c>
+      <c r="H610" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I610" s="16"/>
+    </row>
+    <row r="611" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A611" s="13"/>
+      <c r="B611" s="14"/>
+      <c r="C611" s="14"/>
+      <c r="D611" s="15"/>
+      <c r="E611" s="14"/>
+      <c r="F611" s="14"/>
+      <c r="G611" s="12" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H611" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="I611" s="16"/>
+    </row>
+    <row r="612" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A612" s="13"/>
+      <c r="B612" s="14"/>
+      <c r="C612" s="14"/>
+      <c r="D612" s="15"/>
+      <c r="E612" s="14"/>
+      <c r="F612" s="14"/>
+      <c r="G612" s="12" t="s">
+        <v>1692</v>
+      </c>
+      <c r="H612" s="14"/>
+      <c r="I612" s="16"/>
+    </row>
+    <row r="613" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A613" s="13"/>
+      <c r="B613" s="14"/>
+      <c r="C613" s="14"/>
+      <c r="D613" s="15"/>
+      <c r="E613" s="14"/>
+      <c r="F613" s="14"/>
+      <c r="G613" s="12" t="s">
+        <v>1693</v>
+      </c>
+      <c r="H613" s="14"/>
+      <c r="I613" s="16"/>
+    </row>
+    <row r="614" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A614" s="13"/>
+      <c r="B614" s="14"/>
+      <c r="C614" s="14"/>
+      <c r="D614" s="15"/>
+      <c r="E614" s="14"/>
+      <c r="F614" s="14"/>
+      <c r="G614" s="12" t="s">
+        <v>1694</v>
+      </c>
+      <c r="H614" s="14"/>
+      <c r="I614" s="16"/>
+    </row>
+    <row r="615" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A615" s="13"/>
+      <c r="B615" s="14"/>
+      <c r="C615" s="14"/>
+      <c r="D615" s="15"/>
+      <c r="E615" s="14"/>
+      <c r="F615" s="14"/>
+      <c r="G615" s="12" t="s">
+        <v>1695</v>
+      </c>
+      <c r="H615" s="14"/>
+      <c r="I615" s="16"/>
+    </row>
+    <row r="616" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A616" s="13"/>
+      <c r="B616" s="14"/>
+      <c r="C616" s="14"/>
+      <c r="D616" s="15"/>
+      <c r="E616" s="14"/>
+      <c r="F616" s="14"/>
+      <c r="G616" s="12" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H616" s="14"/>
+      <c r="I616" s="16"/>
+    </row>
+    <row r="617" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A617" s="13"/>
+      <c r="B617" s="14"/>
+      <c r="C617" s="14"/>
+      <c r="D617" s="15"/>
+      <c r="E617" s="14"/>
+      <c r="F617" s="14"/>
+      <c r="G617" s="12" t="s">
+        <v>1697</v>
+      </c>
+      <c r="H617" s="14"/>
+      <c r="I617" s="16"/>
+    </row>
+    <row r="618" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A618" s="13"/>
+      <c r="B618" s="14"/>
+      <c r="C618" s="14"/>
+      <c r="D618" s="15"/>
+      <c r="E618" s="14"/>
+      <c r="F618" s="14"/>
+      <c r="G618" s="12" t="s">
+        <v>1698</v>
+      </c>
+      <c r="H618" s="14"/>
+      <c r="I618" s="16"/>
+    </row>
+    <row r="619" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A619" s="13"/>
+      <c r="B619" s="14"/>
+      <c r="C619" s="14"/>
+      <c r="D619" s="15"/>
+      <c r="E619" s="14"/>
+      <c r="F619" s="14"/>
+      <c r="G619" s="12" t="s">
+        <v>1699</v>
+      </c>
+      <c r="H619" s="14"/>
+      <c r="I619" s="16"/>
+    </row>
+    <row r="620" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A620" s="13"/>
+      <c r="B620" s="14"/>
+      <c r="C620" s="14"/>
+      <c r="D620" s="15"/>
+      <c r="E620" s="14"/>
+      <c r="F620" s="14"/>
+      <c r="G620" s="12" t="s">
+        <v>1700</v>
+      </c>
+      <c r="H620" s="14"/>
+      <c r="I620" s="16"/>
+    </row>
+    <row r="621" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A621" s="13"/>
+      <c r="B621" s="14"/>
+      <c r="C621" s="14"/>
+      <c r="D621" s="15"/>
+      <c r="E621" s="14"/>
+      <c r="F621" s="14"/>
+      <c r="G621" s="12" t="s">
+        <v>1701</v>
+      </c>
+      <c r="H621" s="14"/>
+      <c r="I621" s="16"/>
+    </row>
+    <row r="622" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A622" s="13"/>
+      <c r="B622" s="14"/>
+      <c r="C622" s="14"/>
+      <c r="D622" s="15"/>
+      <c r="E622" s="14"/>
+      <c r="F622" s="14"/>
+      <c r="G622" s="12" t="s">
+        <v>1702</v>
+      </c>
+      <c r="H622" s="14"/>
+      <c r="I622" s="16"/>
+    </row>
+    <row r="623" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A623" s="13"/>
+      <c r="B623" s="14"/>
+      <c r="C623" s="14"/>
+      <c r="D623" s="15"/>
+      <c r="E623" s="14"/>
+      <c r="F623" s="14"/>
+      <c r="G623" s="12" t="s">
+        <v>1703</v>
+      </c>
+      <c r="H623" s="14"/>
+      <c r="I623" s="16"/>
+    </row>
+    <row r="624" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A624" s="13"/>
+      <c r="B624" s="14"/>
+      <c r="C624" s="14"/>
+      <c r="D624" s="15"/>
+      <c r="E624" s="14"/>
+      <c r="F624" s="14"/>
+      <c r="G624" s="12" t="s">
+        <v>1704</v>
+      </c>
+      <c r="H624" s="14"/>
+      <c r="I624" s="16"/>
+    </row>
+    <row r="625" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A625" s="13"/>
+      <c r="B625" s="14"/>
+      <c r="C625" s="14"/>
+      <c r="D625" s="15"/>
+      <c r="E625" s="14"/>
+      <c r="F625" s="14"/>
+      <c r="G625" s="12" t="s">
+        <v>1705</v>
+      </c>
+      <c r="H625" s="14"/>
+      <c r="I625" s="16"/>
+    </row>
+    <row r="626" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A626" s="13"/>
+      <c r="B626" s="14"/>
+      <c r="C626" s="14"/>
+      <c r="D626" s="15"/>
+      <c r="E626" s="14"/>
+      <c r="F626" s="14"/>
+      <c r="G626" s="12" t="s">
+        <v>1706</v>
+      </c>
+      <c r="H626" s="14"/>
+      <c r="I626" s="16"/>
+    </row>
+    <row r="627" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A627" s="13"/>
+      <c r="B627" s="14"/>
+      <c r="C627" s="14"/>
+      <c r="D627" s="15"/>
+      <c r="E627" s="14"/>
+      <c r="F627" s="14"/>
+      <c r="G627" s="12" t="s">
+        <v>1707</v>
+      </c>
+      <c r="H627" s="14"/>
+      <c r="I627" s="16"/>
+    </row>
+    <row r="628" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A628" s="13"/>
+      <c r="B628" s="14"/>
+      <c r="C628" s="14"/>
+      <c r="D628" s="15"/>
+      <c r="E628" s="14"/>
+      <c r="F628" s="14"/>
+      <c r="G628" s="12" t="s">
+        <v>1708</v>
+      </c>
+      <c r="H628" s="14"/>
+      <c r="I628" s="16"/>
+    </row>
+    <row r="629" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A629" s="13"/>
+      <c r="B629" s="14"/>
+      <c r="C629" s="14"/>
+      <c r="D629" s="15"/>
+      <c r="E629" s="14"/>
+      <c r="F629" s="14"/>
+      <c r="G629" s="12" t="s">
+        <v>1708</v>
+      </c>
+      <c r="H629" s="14"/>
+      <c r="I629" s="16"/>
+    </row>
+    <row r="630" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A630" s="13"/>
+      <c r="B630" s="14"/>
+      <c r="C630" s="14"/>
+      <c r="D630" s="15"/>
+      <c r="E630" s="14"/>
+      <c r="F630" s="14"/>
+      <c r="G630" s="12" t="s">
+        <v>1709</v>
+      </c>
+      <c r="H630" s="14"/>
+      <c r="I630" s="16"/>
+    </row>
+    <row r="631" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A631" s="13"/>
+      <c r="B631" s="14"/>
+      <c r="C631" s="14"/>
+      <c r="D631" s="15"/>
+      <c r="E631" s="14"/>
+      <c r="F631" s="14"/>
+      <c r="G631" s="12" t="s">
+        <v>1710</v>
+      </c>
+      <c r="H631" s="14"/>
+      <c r="I631" s="16"/>
+    </row>
+    <row r="632" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A632" s="13"/>
+      <c r="B632" s="14"/>
+      <c r="C632" s="14"/>
+      <c r="D632" s="15"/>
+      <c r="E632" s="14"/>
+      <c r="F632" s="14"/>
+      <c r="G632" s="12" t="s">
+        <v>1711</v>
+      </c>
+      <c r="H632" s="14"/>
+      <c r="I632" s="16"/>
+    </row>
+    <row r="633" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A633" s="13"/>
+      <c r="B633" s="14"/>
+      <c r="C633" s="14"/>
+      <c r="D633" s="15"/>
+      <c r="E633" s="14"/>
+      <c r="F633" s="14"/>
+      <c r="G633" s="12" t="s">
+        <v>1712</v>
+      </c>
+      <c r="H633" s="14"/>
+      <c r="I633" s="16"/>
+    </row>
+    <row r="634" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A634" s="13"/>
+      <c r="B634" s="14"/>
+      <c r="C634" s="14"/>
+      <c r="D634" s="15"/>
+      <c r="E634" s="14"/>
+      <c r="F634" s="14"/>
+      <c r="G634" s="12" t="s">
+        <v>1713</v>
+      </c>
+      <c r="H634" s="14"/>
+      <c r="I634" s="16"/>
+    </row>
+    <row r="635" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A635" s="13"/>
+      <c r="B635" s="14"/>
+      <c r="C635" s="14"/>
+      <c r="D635" s="15"/>
+      <c r="E635" s="14"/>
+      <c r="F635" s="14"/>
+      <c r="G635" s="12" t="s">
+        <v>1714</v>
+      </c>
+      <c r="H635" s="14"/>
+      <c r="I635" s="16"/>
+    </row>
+    <row r="636" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A636" s="13"/>
+      <c r="B636" s="14"/>
+      <c r="C636" s="14"/>
+      <c r="D636" s="15"/>
+      <c r="E636" s="14"/>
+      <c r="F636" s="14"/>
+      <c r="G636" s="12" t="s">
+        <v>1715</v>
+      </c>
+      <c r="H636" s="14"/>
+      <c r="I636" s="16"/>
+    </row>
+    <row r="637" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A637" s="13"/>
+      <c r="B637" s="14"/>
+      <c r="C637" s="14"/>
+      <c r="D637" s="15"/>
+      <c r="E637" s="14"/>
+      <c r="F637" s="14"/>
+      <c r="G637" s="12" t="s">
+        <v>1716</v>
+      </c>
+      <c r="H637" s="14"/>
+      <c r="I637" s="16"/>
+    </row>
+    <row r="638" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A638" s="13"/>
+      <c r="B638" s="14"/>
+      <c r="C638" s="14"/>
+      <c r="D638" s="15"/>
+      <c r="E638" s="14"/>
+      <c r="F638" s="14"/>
+      <c r="G638" s="12" t="s">
+        <v>1717</v>
+      </c>
+      <c r="H638" s="14"/>
+      <c r="I638" s="16"/>
+    </row>
+    <row r="639" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A639" s="13"/>
+      <c r="B639" s="14"/>
+      <c r="C639" s="14"/>
+      <c r="D639" s="15"/>
+      <c r="E639" s="14"/>
+      <c r="F639" s="14"/>
+      <c r="G639" s="12" t="s">
+        <v>1718</v>
+      </c>
+      <c r="H639" s="14"/>
+      <c r="I639" s="16"/>
+    </row>
+    <row r="640" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A640" s="13"/>
+      <c r="B640" s="14"/>
+      <c r="C640" s="14"/>
+      <c r="D640" s="15"/>
+      <c r="E640" s="14"/>
+      <c r="F640" s="14"/>
+      <c r="G640" s="12" t="s">
+        <v>1719</v>
+      </c>
+      <c r="H640" s="14"/>
+      <c r="I640" s="16"/>
+    </row>
+    <row r="641" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A641" s="13"/>
+      <c r="B641" s="14"/>
+      <c r="C641" s="14"/>
+      <c r="D641" s="15"/>
+      <c r="E641" s="14"/>
+      <c r="F641" s="14"/>
+      <c r="G641" s="12" t="s">
+        <v>1720</v>
+      </c>
+      <c r="H641" s="14"/>
+      <c r="I641" s="16"/>
+    </row>
+    <row r="642" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A642" s="13"/>
+      <c r="B642" s="14"/>
+      <c r="C642" s="14"/>
+      <c r="D642" s="15"/>
+      <c r="E642" s="14"/>
+      <c r="F642" s="14"/>
+      <c r="G642" s="12" t="s">
+        <v>1721</v>
+      </c>
+      <c r="H642" s="14"/>
+      <c r="I642" s="16"/>
+    </row>
+    <row r="643" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A643" s="13"/>
+      <c r="B643" s="14"/>
+      <c r="C643" s="14"/>
+      <c r="D643" s="15"/>
+      <c r="E643" s="14"/>
+      <c r="F643" s="14"/>
+      <c r="G643" s="12" t="s">
+        <v>1722</v>
+      </c>
+      <c r="H643" s="14"/>
+      <c r="I643" s="16"/>
+    </row>
+    <row r="644" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A644" s="13"/>
+      <c r="B644" s="14"/>
+      <c r="C644" s="14"/>
+      <c r="D644" s="15"/>
+      <c r="E644" s="14"/>
+      <c r="F644" s="14"/>
+      <c r="G644" s="12" t="s">
+        <v>1723</v>
+      </c>
+      <c r="H644" s="14"/>
+      <c r="I644" s="16"/>
+    </row>
+    <row r="645" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A645" s="13"/>
+      <c r="B645" s="14"/>
+      <c r="C645" s="14"/>
+      <c r="D645" s="15"/>
+      <c r="E645" s="14"/>
+      <c r="F645" s="14"/>
+      <c r="G645" s="12" t="s">
+        <v>1724</v>
+      </c>
+      <c r="H645" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I645" s="16"/>
+    </row>
+    <row r="646" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A646" s="13"/>
+      <c r="B646" s="14"/>
+      <c r="C646" s="14"/>
+      <c r="D646" s="15"/>
+      <c r="E646" s="14"/>
+      <c r="F646" s="14"/>
+      <c r="G646" s="12" t="s">
+        <v>1725</v>
+      </c>
+      <c r="H646" s="14" t="s">
+        <v>1296</v>
+      </c>
+      <c r="I646" s="16"/>
+    </row>
+    <row r="647" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A647" s="13"/>
+      <c r="B647" s="14"/>
+      <c r="C647" s="14"/>
+      <c r="D647" s="15"/>
+      <c r="E647" s="14"/>
+      <c r="F647" s="14"/>
+      <c r="G647" s="12" t="s">
+        <v>1726</v>
+      </c>
+      <c r="H647" s="14" t="s">
+        <v>1296</v>
+      </c>
+      <c r="I647" s="16"/>
+    </row>
+    <row r="648" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A648" s="13"/>
+      <c r="B648" s="14"/>
+      <c r="C648" s="14"/>
+      <c r="D648" s="15"/>
+      <c r="E648" s="14"/>
+      <c r="F648" s="14"/>
+      <c r="G648" s="12" t="s">
+        <v>1727</v>
+      </c>
+      <c r="H648" s="14"/>
+      <c r="I648" s="16"/>
+    </row>
+    <row r="649" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A649" s="13"/>
+      <c r="B649" s="14"/>
+      <c r="C649" s="14"/>
+      <c r="D649" s="15"/>
+      <c r="E649" s="14"/>
+      <c r="F649" s="14"/>
+      <c r="G649" s="12" t="s">
+        <v>1728</v>
+      </c>
+      <c r="H649" s="14"/>
+      <c r="I649" s="16"/>
+    </row>
+    <row r="650" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A650" s="13"/>
+      <c r="B650" s="14"/>
+      <c r="C650" s="14"/>
+      <c r="D650" s="15"/>
+      <c r="E650" s="14"/>
+      <c r="F650" s="14"/>
+      <c r="G650" s="12" t="s">
+        <v>1729</v>
+      </c>
+      <c r="H650" s="14"/>
+      <c r="I650" s="16"/>
+    </row>
+    <row r="651" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A651" s="13"/>
+      <c r="B651" s="14"/>
+      <c r="C651" s="14"/>
+      <c r="D651" s="15"/>
+      <c r="E651" s="14"/>
+      <c r="F651" s="14"/>
+      <c r="G651" s="12" t="s">
+        <v>1730</v>
+      </c>
+      <c r="H651" s="14"/>
+      <c r="I651" s="16"/>
+    </row>
+    <row r="652" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A652" s="13"/>
+      <c r="B652" s="14"/>
+      <c r="C652" s="14"/>
+      <c r="D652" s="15"/>
+      <c r="E652" s="14"/>
+      <c r="F652" s="14"/>
+      <c r="G652" s="12" t="s">
+        <v>1731</v>
+      </c>
+      <c r="H652" s="14"/>
+      <c r="I652" s="16"/>
+    </row>
+    <row r="653" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A653" s="13"/>
+      <c r="B653" s="14"/>
+      <c r="C653" s="14"/>
+      <c r="D653" s="15"/>
+      <c r="E653" s="14"/>
+      <c r="F653" s="14"/>
+      <c r="G653" s="12" t="s">
+        <v>1732</v>
+      </c>
+      <c r="H653" s="14"/>
+      <c r="I653" s="16"/>
+    </row>
+    <row r="654" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A654" s="13"/>
+      <c r="B654" s="14"/>
+      <c r="C654" s="14"/>
+      <c r="D654" s="15"/>
+      <c r="E654" s="14"/>
+      <c r="F654" s="14"/>
+      <c r="G654" s="12" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H654" s="14"/>
+      <c r="I654" s="16"/>
+    </row>
+    <row r="655" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A655" s="13"/>
+      <c r="B655" s="14"/>
+      <c r="C655" s="14"/>
+      <c r="D655" s="15"/>
+      <c r="E655" s="14"/>
+      <c r="F655" s="14"/>
+      <c r="G655" s="12" t="s">
+        <v>1734</v>
+      </c>
+      <c r="H655" s="14"/>
+      <c r="I655" s="16"/>
+    </row>
+    <row r="656" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A656" s="13"/>
+      <c r="B656" s="14"/>
+      <c r="C656" s="14"/>
+      <c r="D656" s="15"/>
+      <c r="E656" s="14"/>
+      <c r="F656" s="14"/>
+      <c r="G656" s="12" t="s">
+        <v>1735</v>
+      </c>
+      <c r="H656" s="14"/>
+      <c r="I656" s="16"/>
+    </row>
+    <row r="657" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A657" s="13"/>
+      <c r="B657" s="14"/>
+      <c r="C657" s="14"/>
+      <c r="D657" s="15"/>
+      <c r="E657" s="14"/>
+      <c r="F657" s="14"/>
+      <c r="G657" s="12" t="s">
+        <v>1736</v>
+      </c>
+      <c r="H657" s="14"/>
+      <c r="I657" s="16"/>
+    </row>
+    <row r="658" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A658" s="13"/>
+      <c r="B658" s="14"/>
+      <c r="C658" s="14"/>
+      <c r="D658" s="15"/>
+      <c r="E658" s="14"/>
+      <c r="F658" s="14"/>
+      <c r="G658" s="12" t="s">
+        <v>1737</v>
+      </c>
+      <c r="H658" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I658" s="16"/>
+    </row>
+    <row r="659" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A659" s="13"/>
+      <c r="B659" s="14"/>
+      <c r="C659" s="14"/>
+      <c r="D659" s="15"/>
+      <c r="E659" s="14"/>
+      <c r="F659" s="14"/>
+      <c r="G659" s="12" t="s">
+        <v>1737</v>
+      </c>
+      <c r="H659" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I659" s="16"/>
+    </row>
+    <row r="660" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A660" s="13"/>
+      <c r="B660" s="14"/>
+      <c r="C660" s="14"/>
+      <c r="D660" s="15"/>
+      <c r="E660" s="14"/>
+      <c r="F660" s="14"/>
+      <c r="G660" s="12" t="s">
+        <v>1738</v>
+      </c>
+      <c r="H660" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I660" s="16"/>
+    </row>
+    <row r="661" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A661" s="13"/>
+      <c r="B661" s="14"/>
+      <c r="C661" s="14"/>
+      <c r="D661" s="15"/>
+      <c r="E661" s="14"/>
+      <c r="F661" s="14"/>
+      <c r="G661" s="12" t="s">
+        <v>1739</v>
+      </c>
+      <c r="H661" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I661" s="16"/>
+    </row>
+    <row r="662" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A662" s="13"/>
+      <c r="B662" s="14"/>
+      <c r="C662" s="14"/>
+      <c r="D662" s="15"/>
+      <c r="E662" s="14"/>
+      <c r="F662" s="14"/>
+      <c r="G662" s="12" t="s">
+        <v>1740</v>
+      </c>
+      <c r="H662" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I662" s="16"/>
+    </row>
+    <row r="663" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A663" s="13"/>
+      <c r="B663" s="14"/>
+      <c r="C663" s="14"/>
+      <c r="D663" s="15"/>
+      <c r="E663" s="14"/>
+      <c r="F663" s="14"/>
+      <c r="G663" s="12" t="s">
+        <v>1741</v>
+      </c>
+      <c r="H663" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I663" s="16"/>
+    </row>
+    <row r="664" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A664" s="13"/>
+      <c r="B664" s="14"/>
+      <c r="C664" s="14"/>
+      <c r="D664" s="15"/>
+      <c r="E664" s="14"/>
+      <c r="F664" s="14"/>
+      <c r="G664" s="12" t="s">
+        <v>1742</v>
+      </c>
+      <c r="H664" s="14"/>
+      <c r="I664" s="16"/>
+    </row>
+    <row r="665" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A665" s="13"/>
+      <c r="B665" s="14"/>
+      <c r="C665" s="14"/>
+      <c r="D665" s="15"/>
+      <c r="E665" s="14"/>
+      <c r="F665" s="14"/>
+      <c r="G665" s="12" t="s">
+        <v>1743</v>
+      </c>
+      <c r="H665" s="14"/>
+      <c r="I665" s="16"/>
+    </row>
+    <row r="666" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A666" s="13"/>
+      <c r="B666" s="14"/>
+      <c r="C666" s="14"/>
+      <c r="D666" s="15"/>
+      <c r="E666" s="14"/>
+      <c r="F666" s="14"/>
+      <c r="G666" s="12" t="s">
+        <v>1744</v>
+      </c>
+      <c r="H666" s="14" t="s">
+        <v>653</v>
+      </c>
+      <c r="I666" s="16"/>
+    </row>
+    <row r="667" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A667" s="13"/>
+      <c r="B667" s="14"/>
+      <c r="C667" s="14"/>
+      <c r="D667" s="15"/>
+      <c r="E667" s="14"/>
+      <c r="F667" s="14"/>
+      <c r="G667" s="12" t="s">
+        <v>1745</v>
+      </c>
+      <c r="H667" s="14"/>
+      <c r="I667" s="16"/>
+    </row>
+    <row r="668" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A668" s="13"/>
+      <c r="B668" s="14"/>
+      <c r="C668" s="14"/>
+      <c r="D668" s="15"/>
+      <c r="E668" s="14"/>
+      <c r="F668" s="14"/>
+      <c r="G668" s="12" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H668" s="14"/>
+      <c r="I668" s="16"/>
+    </row>
+    <row r="669" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A669" s="13"/>
+      <c r="B669" s="14"/>
+      <c r="C669" s="14"/>
+      <c r="D669" s="15"/>
+      <c r="E669" s="14"/>
+      <c r="F669" s="14"/>
+      <c r="G669" s="12" t="s">
+        <v>1747</v>
+      </c>
+      <c r="H669" s="14"/>
+      <c r="I669" s="16"/>
+    </row>
+    <row r="670" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A670" s="13"/>
+      <c r="B670" s="14"/>
+      <c r="C670" s="14"/>
+      <c r="D670" s="15"/>
+      <c r="E670" s="14"/>
+      <c r="F670" s="14"/>
+      <c r="G670" s="12" t="s">
+        <v>1748</v>
+      </c>
+      <c r="H670" s="14"/>
+      <c r="I670" s="16"/>
+    </row>
+    <row r="671" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A671" s="13"/>
+      <c r="B671" s="14"/>
+      <c r="C671" s="14"/>
+      <c r="D671" s="15"/>
+      <c r="E671" s="14"/>
+      <c r="F671" s="14"/>
+      <c r="G671" s="12" t="s">
+        <v>1749</v>
+      </c>
+      <c r="H671" s="14"/>
+      <c r="I671" s="16"/>
+    </row>
+    <row r="672" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A672" s="13"/>
+      <c r="B672" s="14"/>
+      <c r="C672" s="14"/>
+      <c r="D672" s="15"/>
+      <c r="E672" s="14"/>
+      <c r="F672" s="14"/>
+      <c r="G672" s="12" t="s">
+        <v>1750</v>
+      </c>
+      <c r="H672" s="14"/>
+      <c r="I672" s="16"/>
+    </row>
+    <row r="673" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A673" s="13"/>
+      <c r="B673" s="14"/>
+      <c r="C673" s="14"/>
+      <c r="D673" s="15"/>
+      <c r="E673" s="14"/>
+      <c r="F673" s="14"/>
+      <c r="G673" s="12" t="s">
+        <v>1751</v>
+      </c>
+      <c r="H673" s="14"/>
+      <c r="I673" s="16"/>
+    </row>
+    <row r="674" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A674" s="13"/>
+      <c r="B674" s="14"/>
+      <c r="C674" s="14"/>
+      <c r="D674" s="15"/>
+      <c r="E674" s="14"/>
+      <c r="F674" s="14"/>
+      <c r="G674" s="12" t="s">
+        <v>1752</v>
+      </c>
+      <c r="H674" s="14"/>
+      <c r="I674" s="16"/>
+    </row>
+    <row r="675" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A675" s="13"/>
+      <c r="B675" s="14"/>
+      <c r="C675" s="14"/>
+      <c r="D675" s="15"/>
+      <c r="E675" s="14"/>
+      <c r="F675" s="14"/>
+      <c r="G675" s="12" t="s">
+        <v>1753</v>
+      </c>
+      <c r="H675" s="14"/>
+      <c r="I675" s="16"/>
+    </row>
+    <row r="676" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A676" s="13"/>
+      <c r="B676" s="14"/>
+      <c r="C676" s="14"/>
+      <c r="D676" s="15"/>
+      <c r="E676" s="14"/>
+      <c r="F676" s="14"/>
+      <c r="G676" s="12" t="s">
+        <v>1754</v>
+      </c>
+      <c r="H676" s="14"/>
+      <c r="I676" s="16"/>
+    </row>
+    <row r="677" s="12" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A677" s="13"/>
+      <c r="B677" s="14"/>
+      <c r="C677" s="14"/>
+      <c r="D677" s="15"/>
+      <c r="E677" s="14"/>
+      <c r="F677" s="14"/>
+      <c r="G677" s="12" t="s">
+        <v>1755</v>
+      </c>
+      <c r="H677" s="14"/>
+      <c r="I677" s="16"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M522" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:M522">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M677" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:M677">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
   </autoFilter>
-  <conditionalFormatting sqref="K$1:K$1048576">
+  <conditionalFormatting sqref="K502">
+    <cfRule type="duplicateValues" dxfId="0" priority="177"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K503">
+    <cfRule type="duplicateValues" dxfId="0" priority="176"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K504">
+    <cfRule type="duplicateValues" dxfId="0" priority="175"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K505">
+    <cfRule type="duplicateValues" dxfId="0" priority="174"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K506">
+    <cfRule type="duplicateValues" dxfId="0" priority="173"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K507">
+    <cfRule type="duplicateValues" dxfId="0" priority="172"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K508">
+    <cfRule type="duplicateValues" dxfId="0" priority="171"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K509">
+    <cfRule type="duplicateValues" dxfId="0" priority="170"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K510">
+    <cfRule type="duplicateValues" dxfId="0" priority="169"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K511">
+    <cfRule type="duplicateValues" dxfId="0" priority="168"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K512">
+    <cfRule type="duplicateValues" dxfId="0" priority="167"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K513">
+    <cfRule type="duplicateValues" dxfId="0" priority="166"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K514">
+    <cfRule type="duplicateValues" dxfId="0" priority="165"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K515">
+    <cfRule type="duplicateValues" dxfId="0" priority="164"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K516">
+    <cfRule type="duplicateValues" dxfId="0" priority="163"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K517">
+    <cfRule type="duplicateValues" dxfId="0" priority="162"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K518">
+    <cfRule type="duplicateValues" dxfId="0" priority="161"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K519">
+    <cfRule type="duplicateValues" dxfId="0" priority="160"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K520">
+    <cfRule type="duplicateValues" dxfId="0" priority="159"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K521">
+    <cfRule type="duplicateValues" dxfId="0" priority="158"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K522">
+    <cfRule type="duplicateValues" dxfId="0" priority="157"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K523">
+    <cfRule type="duplicateValues" dxfId="0" priority="156"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K524">
+    <cfRule type="duplicateValues" dxfId="0" priority="155"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K525">
+    <cfRule type="duplicateValues" dxfId="0" priority="154"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K526">
+    <cfRule type="duplicateValues" dxfId="0" priority="153"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K527">
+    <cfRule type="duplicateValues" dxfId="0" priority="152"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K528">
+    <cfRule type="duplicateValues" dxfId="0" priority="151"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K529">
+    <cfRule type="duplicateValues" dxfId="0" priority="150"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K530">
+    <cfRule type="duplicateValues" dxfId="0" priority="149"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K531">
+    <cfRule type="duplicateValues" dxfId="0" priority="148"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K532">
+    <cfRule type="duplicateValues" dxfId="0" priority="147"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K533">
+    <cfRule type="duplicateValues" dxfId="0" priority="146"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K534">
+    <cfRule type="duplicateValues" dxfId="0" priority="144"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K535">
+    <cfRule type="duplicateValues" dxfId="0" priority="143"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K536">
+    <cfRule type="duplicateValues" dxfId="0" priority="142"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K537">
+    <cfRule type="duplicateValues" dxfId="0" priority="141"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K538">
+    <cfRule type="duplicateValues" dxfId="0" priority="140"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K539">
+    <cfRule type="duplicateValues" dxfId="0" priority="139"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K540">
+    <cfRule type="duplicateValues" dxfId="0" priority="138"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K541">
+    <cfRule type="duplicateValues" dxfId="0" priority="137"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K542">
+    <cfRule type="duplicateValues" dxfId="0" priority="136"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K543">
+    <cfRule type="duplicateValues" dxfId="0" priority="135"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K544">
+    <cfRule type="duplicateValues" dxfId="0" priority="134"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K545">
+    <cfRule type="duplicateValues" dxfId="0" priority="133"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K546">
+    <cfRule type="duplicateValues" dxfId="0" priority="132"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K547">
+    <cfRule type="duplicateValues" dxfId="0" priority="131"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K548">
+    <cfRule type="duplicateValues" dxfId="0" priority="130"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K549">
+    <cfRule type="duplicateValues" dxfId="0" priority="129"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K550">
+    <cfRule type="duplicateValues" dxfId="0" priority="128"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K551">
+    <cfRule type="duplicateValues" dxfId="0" priority="127"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K552">
+    <cfRule type="duplicateValues" dxfId="0" priority="126"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K553">
+    <cfRule type="duplicateValues" dxfId="0" priority="125"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K554">
+    <cfRule type="duplicateValues" dxfId="0" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K555">
+    <cfRule type="duplicateValues" dxfId="0" priority="123"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K556">
+    <cfRule type="duplicateValues" dxfId="0" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K557">
+    <cfRule type="duplicateValues" dxfId="0" priority="121"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K558">
+    <cfRule type="duplicateValues" dxfId="0" priority="120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K559">
+    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K560">
+    <cfRule type="duplicateValues" dxfId="0" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K561">
+    <cfRule type="duplicateValues" dxfId="0" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K562">
+    <cfRule type="duplicateValues" dxfId="0" priority="116"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K563">
+    <cfRule type="duplicateValues" dxfId="0" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K564">
+    <cfRule type="duplicateValues" dxfId="0" priority="114"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K565">
+    <cfRule type="duplicateValues" dxfId="0" priority="113"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K566">
+    <cfRule type="duplicateValues" dxfId="0" priority="112"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K567">
+    <cfRule type="duplicateValues" dxfId="0" priority="111"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K568">
+    <cfRule type="duplicateValues" dxfId="0" priority="110"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K569">
+    <cfRule type="duplicateValues" dxfId="0" priority="109"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K570">
+    <cfRule type="duplicateValues" dxfId="0" priority="108"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K571">
+    <cfRule type="duplicateValues" dxfId="0" priority="107"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K572">
+    <cfRule type="duplicateValues" dxfId="0" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K573">
+    <cfRule type="duplicateValues" dxfId="0" priority="105"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K574">
+    <cfRule type="duplicateValues" dxfId="0" priority="104"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K575">
+    <cfRule type="duplicateValues" dxfId="0" priority="103"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K576">
+    <cfRule type="duplicateValues" dxfId="0" priority="102"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K577">
+    <cfRule type="duplicateValues" dxfId="0" priority="101"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K578">
+    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K579">
+    <cfRule type="duplicateValues" dxfId="0" priority="99"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K580">
+    <cfRule type="duplicateValues" dxfId="0" priority="98"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K581">
+    <cfRule type="duplicateValues" dxfId="0" priority="97"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K582">
+    <cfRule type="duplicateValues" dxfId="0" priority="96"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K583">
+    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K584">
+    <cfRule type="duplicateValues" dxfId="0" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K585">
+    <cfRule type="duplicateValues" dxfId="0" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K586">
+    <cfRule type="duplicateValues" dxfId="0" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K587">
+    <cfRule type="duplicateValues" dxfId="0" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K588">
+    <cfRule type="duplicateValues" dxfId="0" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K589">
+    <cfRule type="duplicateValues" dxfId="0" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K590">
+    <cfRule type="duplicateValues" dxfId="0" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K591">
+    <cfRule type="duplicateValues" dxfId="0" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K592">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K593">
+    <cfRule type="duplicateValues" dxfId="0" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K594">
+    <cfRule type="duplicateValues" dxfId="0" priority="84"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K595">
+    <cfRule type="duplicateValues" dxfId="0" priority="83"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K596">
+    <cfRule type="duplicateValues" dxfId="0" priority="82"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K597">
+    <cfRule type="duplicateValues" dxfId="0" priority="81"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K598">
+    <cfRule type="duplicateValues" dxfId="0" priority="80"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K599">
+    <cfRule type="duplicateValues" dxfId="0" priority="79"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K600">
+    <cfRule type="duplicateValues" dxfId="0" priority="78"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K601">
+    <cfRule type="duplicateValues" dxfId="0" priority="77"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K602">
+    <cfRule type="duplicateValues" dxfId="0" priority="76"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K603">
+    <cfRule type="duplicateValues" dxfId="0" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K604">
+    <cfRule type="duplicateValues" dxfId="0" priority="74"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K605">
+    <cfRule type="duplicateValues" dxfId="0" priority="73"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K606">
+    <cfRule type="duplicateValues" dxfId="0" priority="72"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K607">
+    <cfRule type="duplicateValues" dxfId="0" priority="71"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K608">
+    <cfRule type="duplicateValues" dxfId="0" priority="70"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K609">
+    <cfRule type="duplicateValues" dxfId="0" priority="69"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K610">
+    <cfRule type="duplicateValues" dxfId="0" priority="68"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K611">
+    <cfRule type="duplicateValues" dxfId="0" priority="67"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K612">
+    <cfRule type="duplicateValues" dxfId="0" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K613">
+    <cfRule type="duplicateValues" dxfId="0" priority="65"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K614">
+    <cfRule type="duplicateValues" dxfId="0" priority="64"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K615">
+    <cfRule type="duplicateValues" dxfId="0" priority="63"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K616">
+    <cfRule type="duplicateValues" dxfId="0" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K617">
+    <cfRule type="duplicateValues" dxfId="0" priority="61"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K618">
+    <cfRule type="duplicateValues" dxfId="0" priority="60"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K619">
+    <cfRule type="duplicateValues" dxfId="0" priority="59"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K620">
+    <cfRule type="duplicateValues" dxfId="0" priority="58"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K621">
+    <cfRule type="duplicateValues" dxfId="0" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K622">
+    <cfRule type="duplicateValues" dxfId="0" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K623">
+    <cfRule type="duplicateValues" dxfId="0" priority="55"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K624">
+    <cfRule type="duplicateValues" dxfId="0" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K625">
+    <cfRule type="duplicateValues" dxfId="0" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K626">
+    <cfRule type="duplicateValues" dxfId="0" priority="52"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K627">
+    <cfRule type="duplicateValues" dxfId="0" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K628">
+    <cfRule type="duplicateValues" dxfId="0" priority="50"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K629">
+    <cfRule type="duplicateValues" dxfId="0" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K630">
+    <cfRule type="duplicateValues" dxfId="0" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K631">
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K632">
+    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K633">
+    <cfRule type="duplicateValues" dxfId="0" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K634">
+    <cfRule type="duplicateValues" dxfId="0" priority="44"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K635">
+    <cfRule type="duplicateValues" dxfId="0" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K636">
+    <cfRule type="duplicateValues" dxfId="0" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K637">
+    <cfRule type="duplicateValues" dxfId="0" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K638">
+    <cfRule type="duplicateValues" dxfId="0" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K639">
+    <cfRule type="duplicateValues" dxfId="0" priority="39"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K640">
+    <cfRule type="duplicateValues" dxfId="0" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K641">
+    <cfRule type="duplicateValues" dxfId="0" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K642">
+    <cfRule type="duplicateValues" dxfId="0" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K643">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K644">
+    <cfRule type="duplicateValues" dxfId="0" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K645">
+    <cfRule type="duplicateValues" dxfId="0" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K646">
+    <cfRule type="duplicateValues" dxfId="0" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K647">
+    <cfRule type="duplicateValues" dxfId="0" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K648">
+    <cfRule type="duplicateValues" dxfId="0" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K649">
+    <cfRule type="duplicateValues" dxfId="0" priority="29"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K650">
+    <cfRule type="duplicateValues" dxfId="0" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K651">
+    <cfRule type="duplicateValues" dxfId="0" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K652">
+    <cfRule type="duplicateValues" dxfId="0" priority="26"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K653">
+    <cfRule type="duplicateValues" dxfId="0" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K654">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K655">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K656">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K657">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K658">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K659">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K660">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K661">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K662">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K663">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K664">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K665">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K666">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K667">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K668">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K669">
+    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K670">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K671">
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K672">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K673">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K674">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K675">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K676">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K677">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K1:K501 K678:K1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="178"/>
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="M69" r:id="rId1" display="https://open.spotify.com/track/44rDdbTIyoXJyWxAnUv5ys?si=e1c832cba0ca418b"/>
@@ -23218,28 +26411,28 @@
   <sheetData>
     <row r="1" ht="29.15" spans="1:9">
       <c r="A1" s="5" t="s">
-        <v>1585</v>
+        <v>1756</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>1586</v>
+        <v>1757</v>
       </c>
       <c r="C1" s="6" t="s">
         <v>381</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>1587</v>
+        <v>1758</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>1588</v>
+        <v>1759</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>1589</v>
+        <v>1760</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>197</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>1590</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="2" ht="43.7" spans="1:9">
@@ -23249,7 +26442,7 @@
         <v>317</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1591</v>
+        <v>1762</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="5"/>
@@ -23257,17 +26450,17 @@
         <v>307</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>1592</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="3" ht="14.55" spans="1:9">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6" t="s">
-        <v>1593</v>
+        <v>1764</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>1594</v>
+        <v>1765</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="5"/>
@@ -23275,39 +26468,39 @@
         <v>298</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>1595</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="4" ht="29.15" spans="1:9">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
-        <v>1596</v>
+        <v>1767</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>782</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>1597</v>
+        <v>1768</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="5" t="s">
-        <v>1598</v>
+        <v>1769</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>14</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>1599</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="5" ht="29.15" spans="1:9">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="6" t="s">
-        <v>1600</v>
+        <v>1771</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>1601</v>
+        <v>1772</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="5"/>
@@ -23315,29 +26508,29 @@
         <v>204</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>1602</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="6" ht="14.55" spans="1:9">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
-        <v>1603</v>
+        <v>1774</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>540</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>1604</v>
+        <v>1775</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="5" t="s">
-        <v>1605</v>
+        <v>1776</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>1606</v>
+        <v>1777</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>1607</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="7" ht="14.55" spans="1:9">
@@ -23347,7 +26540,7 @@
         <v>661</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>1608</v>
+        <v>1779</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="5"/>
@@ -23355,19 +26548,19 @@
         <v>1188</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>1609</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="8" ht="14.55" spans="1:9">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
-        <v>1610</v>
+        <v>1781</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1196</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>1611</v>
+        <v>1782</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="5"/>
@@ -23375,39 +26568,39 @@
         <v>38</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>1612</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="9" ht="14.55" spans="1:9">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="6" t="s">
-        <v>1613</v>
+        <v>1784</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>1614</v>
+        <v>1785</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5" t="s">
-        <v>1615</v>
+        <v>1786</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>1616</v>
+        <v>1787</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>1617</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="10" ht="14.55" spans="1:9">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
-        <v>1618</v>
+        <v>1789</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>817</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>1619</v>
+        <v>1790</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="5"/>
@@ -23415,7 +26608,7 @@
         <v>479</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>1620</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:9">
@@ -23425,39 +26618,39 @@
         <v>88</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>1621</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="12" ht="14.55" spans="1:9">
       <c r="F12" s="8" t="s">
-        <v>1622</v>
+        <v>1793</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="6" t="s">
-        <v>1623</v>
+        <v>1794</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>1624</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="13" ht="14.55" spans="1:9">
       <c r="A13" s="5" t="s">
-        <v>1625</v>
+        <v>1796</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="6" t="s">
         <v>190</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>1626</v>
+        <v>1797</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="7"/>
       <c r="H13" s="6" t="s">
-        <v>1627</v>
+        <v>1798</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>1628</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="14" ht="14.55" spans="1:9">
@@ -23467,15 +26660,15 @@
         <v>714</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>1629</v>
+        <v>1800</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="7"/>
       <c r="H14" s="6" t="s">
-        <v>1630</v>
+        <v>1801</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>1631</v>
+        <v>1802</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/MWV.xlsx
+++ b/xlsx/MWV.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21925" windowHeight="9582"/>
+    <workbookView windowWidth="21942" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="MWV" sheetId="1" r:id="rId1"/>
@@ -5666,6 +5666,89 @@
     <t>Piccolo, Flute, 4 Clarinets, 2 Oboes, 2 Basset Horns, 2 Bassoons, Contrabassoon, 4 Horns, 2 Trumpets, 3 Trombones, Tambourine, Triangle, Bass Drum, Cymbals</t>
   </si>
   <si>
+    <t>MWV P2</t>
+  </si>
+  <si>
+    <t>op. 101</t>
+  </si>
+  <si>
+    <t>Ouverture "Trumpet"</t>
+  </si>
+  <si>
+    <t>2 Flutes, 2 Oboes, 2 Clarinets, 2 Bassoons, 2 Horns, 2 Trumpets, 3 trombones, Timpani, 2 Violins, Viola, Cello, Double Bass</t>
+  </si>
+  <si>
+    <t>MWV P3</t>
+  </si>
+  <si>
+    <t>op. 21</t>
+  </si>
+  <si>
+    <t>Ein Sommernachstraum</t>
+  </si>
+  <si>
+    <t>Allegro di molto</t>
+  </si>
+  <si>
+    <t>2 Flutes, 2 Oboes, 2 Clarinets, 2 Bassoons, 2 Horns, 2 Trumpets, ophicleïde, Timpani, 2 Violins, Viola, Cello, Double Bass</t>
+  </si>
+  <si>
+    <t>Ouverture No. 1, in "A Midsummer Night's Dream", op. 61</t>
+  </si>
+  <si>
+    <t>https://open.spotify.com/track/44rDdbTIyoXJyWxAnUv5ys?si=e1c832cba0ca418b</t>
+  </si>
+  <si>
+    <t>MWV P5</t>
+  </si>
+  <si>
+    <t>op. 27</t>
+  </si>
+  <si>
+    <t>Meeresstille und gluckliche Fahrt</t>
+  </si>
+  <si>
+    <t>Adagio / Molto Allegro e vivace / Allegro maestoso</t>
+  </si>
+  <si>
+    <t>Piccolo, 2 Flutes, 2 Oboes, 2 Clarinets, 2 Bassoons, contreBassoon, serpentin, 2 Horns, 3 Trumpets, Timpani, 2 Violins, Viola, Cello, Double Bass</t>
+  </si>
+  <si>
+    <t>Ouverture No. 3
+after 2 poems by Johann Wolfgang von Goethe</t>
+  </si>
+  <si>
+    <t>MWV P6</t>
+  </si>
+  <si>
+    <t>Kindersinfonie</t>
+  </si>
+  <si>
+    <t>MWV P7</t>
+  </si>
+  <si>
+    <t>op. 26</t>
+  </si>
+  <si>
+    <t>1830-1832</t>
+  </si>
+  <si>
+    <t>Die Hebriden "Fingals Hohle"</t>
+  </si>
+  <si>
+    <t>Ouverture No. 2
+[1st version: 1830; 2nd version: 1832 - based on "Die einsame Insel" (1829)]</t>
+  </si>
+  <si>
+    <t>MWV P8</t>
+  </si>
+  <si>
+    <t>MWV P9</t>
+  </si>
+  <si>
+    <t>Militärstück</t>
+  </si>
+  <si>
     <t>MWV P10</t>
   </si>
   <si>
@@ -5760,93 +5843,58 @@
     <t>MWV P19</t>
   </si>
   <si>
-    <t>MWV P2</t>
-  </si>
-  <si>
-    <t>op. 101</t>
-  </si>
-  <si>
-    <t>Ouverture "Trumpet"</t>
-  </si>
-  <si>
-    <t>2 Flutes, 2 Oboes, 2 Clarinets, 2 Bassoons, 2 Horns, 2 Trumpets, 3 trombones, Timpani, 2 Violins, Viola, Cello, Double Bass</t>
-  </si>
-  <si>
-    <t>MWV P3</t>
-  </si>
-  <si>
-    <t>op. 21</t>
-  </si>
-  <si>
-    <t>Ein Sommernachstraum</t>
-  </si>
-  <si>
-    <t>Allegro di molto</t>
-  </si>
-  <si>
-    <t>2 Flutes, 2 Oboes, 2 Clarinets, 2 Bassoons, 2 Horns, 2 Trumpets, ophicleïde, Timpani, 2 Violins, Viola, Cello, Double Bass</t>
-  </si>
-  <si>
-    <t>Ouverture No. 1, in "A Midsummer Night's Dream", op. 61</t>
-  </si>
-  <si>
-    <t>https://open.spotify.com/track/44rDdbTIyoXJyWxAnUv5ys?si=e1c832cba0ca418b</t>
-  </si>
-  <si>
-    <t>MWV P5</t>
-  </si>
-  <si>
-    <t>op. 27</t>
-  </si>
-  <si>
-    <t>Meeresstille und gluckliche Fahrt</t>
-  </si>
-  <si>
-    <t>Adagio / Molto Allegro e vivace / Allegro maestoso</t>
-  </si>
-  <si>
-    <t>Piccolo, 2 Flutes, 2 Oboes, 2 Clarinets, 2 Bassoons, contreBassoon, serpentin, 2 Horns, 3 Trumpets, Timpani, 2 Violins, Viola, Cello, Double Bass</t>
-  </si>
-  <si>
-    <t>Ouverture No. 3
-after 2 poems by Johann Wolfgang von Goethe</t>
-  </si>
-  <si>
-    <t>MWV P6</t>
-  </si>
-  <si>
-    <t>Kindersinfonie</t>
-  </si>
-  <si>
-    <t>MWV P7</t>
-  </si>
-  <si>
-    <t>op. 26</t>
-  </si>
-  <si>
-    <t>1830-1832</t>
-  </si>
-  <si>
-    <t>Die Hebriden "Fingals Hohle"</t>
-  </si>
-  <si>
-    <t>Ouverture No. 2
-[1st version: 1830; 2nd version: 1832 - based on "Die einsame Insel" (1829)]</t>
-  </si>
-  <si>
-    <t>MWV P8</t>
-  </si>
-  <si>
-    <t>MWV P9</t>
-  </si>
-  <si>
-    <t>Militärstück</t>
-  </si>
-  <si>
     <t>MWV Q1</t>
   </si>
   <si>
     <t>Fragment A-Dur für Violine und Klavier</t>
+  </si>
+  <si>
+    <t>MWV Q2</t>
+  </si>
+  <si>
+    <t>Sonate F-Dur für Violine und Klavier, Fragment</t>
+  </si>
+  <si>
+    <t>MWV Q3</t>
+  </si>
+  <si>
+    <t>Trio c-Moll für Klavier, Violine und Viola</t>
+  </si>
+  <si>
+    <t>MWV Q4</t>
+  </si>
+  <si>
+    <t>Andante d-Moll für Violine und Klavier</t>
+  </si>
+  <si>
+    <t>MWV Q5</t>
+  </si>
+  <si>
+    <t>Fuge d-Moll für Violine und Klavier</t>
+  </si>
+  <si>
+    <t>MWV Q6</t>
+  </si>
+  <si>
+    <t>Fragment C-Dur für Violine und Klavier</t>
+  </si>
+  <si>
+    <t>MWV Q7</t>
+  </si>
+  <si>
+    <t>Sonate F-Dur für Violine und Klavier</t>
+  </si>
+  <si>
+    <t>MWV Q8</t>
+  </si>
+  <si>
+    <t>Menuett G-Dur für Violine und Klavier</t>
+  </si>
+  <si>
+    <t>MWV Q9</t>
+  </si>
+  <si>
+    <t>Sonate d-Moll für Violine und Klavier, Fragment</t>
   </si>
   <si>
     <t>MWV Q10</t>
@@ -5985,12 +6033,6 @@
     <t>Piano, Cello</t>
   </si>
   <si>
-    <t>MWV Q2</t>
-  </si>
-  <si>
-    <t>Sonate F-Dur für Violine und Klavier, Fragment</t>
-  </si>
-  <si>
     <t>MWV Q20</t>
   </si>
   <si>
@@ -6075,12 +6117,6 @@
     <t>Piano Trio No. 1</t>
   </si>
   <si>
-    <t>MWV Q3</t>
-  </si>
-  <si>
-    <t>Trio c-Moll für Klavier, Violine und Viola</t>
-  </si>
-  <si>
     <t>MWV Q32</t>
   </si>
   <si>
@@ -6126,48 +6162,48 @@
     <t>Chant sans parole</t>
   </si>
   <si>
-    <t>MWV Q4</t>
-  </si>
-  <si>
-    <t>Andante d-Moll für Violine und Klavier</t>
-  </si>
-  <si>
-    <t>MWV Q5</t>
-  </si>
-  <si>
-    <t>Fuge d-Moll für Violine und Klavier</t>
-  </si>
-  <si>
-    <t>MWV Q6</t>
-  </si>
-  <si>
-    <t>Fragment C-Dur für Violine und Klavier</t>
-  </si>
-  <si>
-    <t>MWV Q7</t>
-  </si>
-  <si>
-    <t>Sonate F-Dur für Violine und Klavier</t>
-  </si>
-  <si>
-    <t>MWV Q8</t>
-  </si>
-  <si>
-    <t>Menuett G-Dur für Violine und Klavier</t>
-  </si>
-  <si>
-    <t>MWV Q9</t>
-  </si>
-  <si>
-    <t>Sonate d-Moll für Violine und Klavier, Fragment</t>
-  </si>
-  <si>
     <t>MWV R1</t>
   </si>
   <si>
     <t>Fuge d-Moll für zwei Violinen, Viola und Violoncello</t>
   </si>
   <si>
+    <t>MWV R2</t>
+  </si>
+  <si>
+    <t>Fuge C-Dur für zwei Violinen, Viola und Violoncello</t>
+  </si>
+  <si>
+    <t>MWV R3</t>
+  </si>
+  <si>
+    <t>MWV R4</t>
+  </si>
+  <si>
+    <t>MWV R5</t>
+  </si>
+  <si>
+    <t>Fuge c-Moll für zwei Violinen, Viola und Violoncello</t>
+  </si>
+  <si>
+    <t>MWV R6</t>
+  </si>
+  <si>
+    <t>MWV R7</t>
+  </si>
+  <si>
+    <t>MWV R8</t>
+  </si>
+  <si>
+    <t>Fuge Es-Dur für zwei Violinen, Viola und Violoncello</t>
+  </si>
+  <si>
+    <t>MWV R9</t>
+  </si>
+  <si>
+    <t>Fuge C-Dur für zwei Violinen, Viola und Violoncello, Fragment</t>
+  </si>
+  <si>
     <t>MWV R10</t>
   </si>
   <si>
@@ -6210,9 +6246,6 @@
     <t>MWV R17</t>
   </si>
   <si>
-    <t>Fuge C-Dur für zwei Violinen, Viola und Violoncello</t>
-  </si>
-  <si>
     <t>MWV R18</t>
   </si>
   <si>
@@ -6223,9 +6256,6 @@
   </si>
   <si>
     <t>Duo d-Moll für zwei Violinen</t>
-  </si>
-  <si>
-    <t>MWV R2</t>
   </si>
   <si>
     <t>MWV R20</t>
@@ -6399,9 +6429,6 @@
     <t>Andante B-Dur für Violine und Violoncello</t>
   </si>
   <si>
-    <t>MWV R3</t>
-  </si>
-  <si>
     <t>MWV R30</t>
   </si>
   <si>
@@ -6498,33 +6525,6 @@
     <t>String Quartet No. 6</t>
   </si>
   <si>
-    <t>MWV R4</t>
-  </si>
-  <si>
-    <t>MWV R5</t>
-  </si>
-  <si>
-    <t>Fuge c-Moll für zwei Violinen, Viola und Violoncello</t>
-  </si>
-  <si>
-    <t>MWV R6</t>
-  </si>
-  <si>
-    <t>MWV R7</t>
-  </si>
-  <si>
-    <t>MWV R8</t>
-  </si>
-  <si>
-    <t>Fuge Es-Dur für zwei Violinen, Viola und Violoncello</t>
-  </si>
-  <si>
-    <t>MWV R9</t>
-  </si>
-  <si>
-    <t>Fuge C-Dur für zwei Violinen, Viola und Violoncello, Fragment</t>
-  </si>
-  <si>
     <t>MWV S1</t>
   </si>
   <si>
@@ -6567,6 +6567,382 @@
     <t>Piano Four Hands</t>
   </si>
   <si>
+    <t>MWV U30</t>
+  </si>
+  <si>
+    <t>op. 105</t>
+  </si>
+  <si>
+    <t>Violin Sonata in G minor</t>
+  </si>
+  <si>
+    <t>1. Allegro (sol mineur)
+2. Adagio cantabile e lento (do mineur)
+3. Presto (sol mineur)</t>
+  </si>
+  <si>
+    <t>Piano</t>
+  </si>
+  <si>
+    <t>Piano Sonata No. 2</t>
+  </si>
+  <si>
+    <t>MWV U44</t>
+  </si>
+  <si>
+    <t>op. 7/2</t>
+  </si>
+  <si>
+    <t>Mit heftiger Bewegung</t>
+  </si>
+  <si>
+    <t>MWV U50</t>
+  </si>
+  <si>
+    <t>op. 5</t>
+  </si>
+  <si>
+    <t>Cappricio in F-sharp minor</t>
+  </si>
+  <si>
+    <t>Prestissimo</t>
+  </si>
+  <si>
+    <t>MWV U54</t>
+  </si>
+  <si>
+    <t>op. 6</t>
+  </si>
+  <si>
+    <t>Piano Sonata in E major</t>
+  </si>
+  <si>
+    <t>1. Allegretto con espressione (mi majeur)
+2. Tempo di Menuetto (fa dièse mineur)
+3. Recitativo. Adagio e senza tempo (la mineur)
+4. Molto Allegro vivace (mi majeur)</t>
+  </si>
+  <si>
+    <t>Piano Sonata No. 1</t>
+  </si>
+  <si>
+    <t>MWV U55</t>
+  </si>
+  <si>
+    <t>op. 7/4</t>
+  </si>
+  <si>
+    <t>Schnell und beweglich</t>
+  </si>
+  <si>
+    <t>MWV U56</t>
+  </si>
+  <si>
+    <t>op. 7/1</t>
+  </si>
+  <si>
+    <t>Sanft und mit Empfindung</t>
+  </si>
+  <si>
+    <t>MWV U58</t>
+  </si>
+  <si>
+    <t>op. 119</t>
+  </si>
+  <si>
+    <t>Perpetuum mobile</t>
+  </si>
+  <si>
+    <t>MWV U59</t>
+  </si>
+  <si>
+    <t>op. 7/3</t>
+  </si>
+  <si>
+    <t>Kraftig und feurig</t>
+  </si>
+  <si>
+    <t>MWV U60</t>
+  </si>
+  <si>
+    <t>op. 7/5</t>
+  </si>
+  <si>
+    <t>Ernst und mit steigender Lebhaftigkeit</t>
+  </si>
+  <si>
+    <t>Fuga</t>
+  </si>
+  <si>
+    <t>MWV U61</t>
+  </si>
+  <si>
+    <t>op. 7/6</t>
+  </si>
+  <si>
+    <t>Sensuchtig</t>
+  </si>
+  <si>
+    <t>MWV U62</t>
+  </si>
+  <si>
+    <t>op. 7/7</t>
+  </si>
+  <si>
+    <t>Leicht und luftig</t>
+  </si>
+  <si>
+    <t>MWV U64</t>
+  </si>
+  <si>
+    <t>op. 106</t>
+  </si>
+  <si>
+    <t>Piano Sonata in B-flat major</t>
+  </si>
+  <si>
+    <t>1. Allegro vivace (si bémol majeur)
+2. Scherzo. Allegro non troppo (ré bémol majeur)
+3. Andante quasi Allegretto (mi majeur)
+4. Allegro molto (si bémol majeur) / Allegro moderato</t>
+  </si>
+  <si>
+    <t>Piano Sonata No. 3</t>
+  </si>
+  <si>
+    <t>MWV U65</t>
+  </si>
+  <si>
+    <t>MWV U66</t>
+  </si>
+  <si>
+    <t>op. 35/1b</t>
+  </si>
+  <si>
+    <t>Fugue in E minor</t>
+  </si>
+  <si>
+    <t>Andante espressivo</t>
+  </si>
+  <si>
+    <t>MWV U67</t>
+  </si>
+  <si>
+    <t>op. 14</t>
+  </si>
+  <si>
+    <t>Rondo capriccioso in E major</t>
+  </si>
+  <si>
+    <t>1. Andante (mi majeur)
+2. Presto (mi mineur)</t>
+  </si>
+  <si>
+    <t>MWV U69</t>
+  </si>
+  <si>
+    <t>WoO 2</t>
+  </si>
+  <si>
+    <t>Scherzo in B minor</t>
+  </si>
+  <si>
+    <t>[Publié dans "Berliner allgemeine musikalische Zeitung"]</t>
+  </si>
+  <si>
+    <t>MWV U70</t>
+  </si>
+  <si>
+    <t>op. 16/1</t>
+  </si>
+  <si>
+    <t>Fantaisia in A minor</t>
+  </si>
+  <si>
+    <t>Fantaisia</t>
+  </si>
+  <si>
+    <t>1. Andante con moto (la mineur)
+2. Allegro vivace (la majeur)</t>
+  </si>
+  <si>
+    <t>MWV U71</t>
+  </si>
+  <si>
+    <t>op. 16/2</t>
+  </si>
+  <si>
+    <t>Caprice in E minor</t>
+  </si>
+  <si>
+    <t>Scherzo. Presto</t>
+  </si>
+  <si>
+    <t>MWV U72</t>
+  </si>
+  <si>
+    <t>op. 16/3</t>
+  </si>
+  <si>
+    <t>Fantaisie in E major "The Rivulet"</t>
+  </si>
+  <si>
+    <t>MWV U73</t>
+  </si>
+  <si>
+    <t>op. 19b/4</t>
+  </si>
+  <si>
+    <t>Moderato</t>
+  </si>
+  <si>
+    <t>MWV U74</t>
+  </si>
+  <si>
+    <t>op. 15</t>
+  </si>
+  <si>
+    <t>Fantaisie sur le lied irlandais "The Last Rose"</t>
+  </si>
+  <si>
+    <t>1. Adagio (mi majeur)
+2. Presto agitato (mi mineur)
+3. Andante (mi majeur)
+4. Presto come prima (mi majeur / mi mineur)
+5. Andante con moto (mi majeur)</t>
+  </si>
+  <si>
+    <t>MWV U77</t>
+  </si>
+  <si>
+    <t>op. 30/2</t>
+  </si>
+  <si>
+    <t>B-flat minor</t>
+  </si>
+  <si>
+    <t>MWV U78</t>
+  </si>
+  <si>
+    <t>op. 19b/6</t>
+  </si>
+  <si>
+    <t>Andante sostenuto "Venerianisches Gondellied"</t>
+  </si>
+  <si>
+    <t>MWV U80</t>
+  </si>
+  <si>
+    <t>op. 19b/2</t>
+  </si>
+  <si>
+    <t>MWV U86</t>
+  </si>
+  <si>
+    <t>op. 19b/1</t>
+  </si>
+  <si>
+    <t>MWV U89</t>
+  </si>
+  <si>
+    <t>op. 19b/3</t>
+  </si>
+  <si>
+    <t>Molto Allegro e vivace "Jagerlied"</t>
+  </si>
+  <si>
+    <t>MWV U90</t>
+  </si>
+  <si>
+    <t>op. 19b/5</t>
+  </si>
+  <si>
+    <t>Poco agitato</t>
+  </si>
+  <si>
+    <t>MWV U91</t>
+  </si>
+  <si>
+    <t>op. 35/3b</t>
+  </si>
+  <si>
+    <t>Fugue in B minor</t>
+  </si>
+  <si>
+    <t>Allegro con brio</t>
+  </si>
+  <si>
+    <t>MWV U92</t>
+  </si>
+  <si>
+    <t>op. 28</t>
+  </si>
+  <si>
+    <t>Fantaisie in F-sharp minor "Sonate écossaise"</t>
+  </si>
+  <si>
+    <t>1. Con moto agitato / Andante / Con moto agitato
+2. Allegro con moto (la majeur / ré majeur)
+3. Presto (fa dièse mineur)</t>
+  </si>
+  <si>
+    <t>MWV U93</t>
+  </si>
+  <si>
+    <t>WoO 19/1</t>
+  </si>
+  <si>
+    <t>Andante cantabile</t>
+  </si>
+  <si>
+    <t>MWV U94</t>
+  </si>
+  <si>
+    <t>WoO 19/2</t>
+  </si>
+  <si>
+    <t>MWV U95</t>
+  </si>
+  <si>
+    <t>op. 33/3</t>
+  </si>
+  <si>
+    <t>Caprice in B-flat minor</t>
+  </si>
+  <si>
+    <t>Adagio / Presto con fuoco</t>
+  </si>
+  <si>
+    <t>MWV U97</t>
+  </si>
+  <si>
+    <t>op. 30/5</t>
+  </si>
+  <si>
+    <t>Andante grazioso</t>
+  </si>
+  <si>
+    <t>MWV U98</t>
+  </si>
+  <si>
+    <t>op. 30/4</t>
+  </si>
+  <si>
+    <t>Agitato e con fuoco</t>
+  </si>
+  <si>
+    <t>MWV U99</t>
+  </si>
+  <si>
+    <t>op. 33/1</t>
+  </si>
+  <si>
+    <t>Caprice in A minor</t>
+  </si>
+  <si>
+    <t>Adagio quasi Fantasia / Presto agitato</t>
+  </si>
+  <si>
     <t>MWV U100</t>
   </si>
   <si>
@@ -6579,9 +6955,6 @@
     <t>Etude</t>
   </si>
   <si>
-    <t>Piano</t>
-  </si>
-  <si>
     <t>MWV U101</t>
   </si>
   <si>
@@ -6600,9 +6973,6 @@
     <t>op. 30/1</t>
   </si>
   <si>
-    <t>Andante espressivo</t>
-  </si>
-  <si>
     <t>MWV U104</t>
   </si>
   <si>
@@ -6744,9 +7114,6 @@
     <t>Etude in B-flat minor</t>
   </si>
   <si>
-    <t>B-flat minor</t>
-  </si>
-  <si>
     <t>MWV U119</t>
   </si>
   <si>
@@ -6835,9 +7202,6 @@
   </si>
   <si>
     <t>Fugue in B-flat major</t>
-  </si>
-  <si>
-    <t>Allegro con brio</t>
   </si>
   <si>
     <t>MWV U129</t>
@@ -7151,9 +7515,6 @@
   </si>
   <si>
     <t>op. 67/5</t>
-  </si>
-  <si>
-    <t>Moderato</t>
   </si>
   <si>
     <t>MWV U185</t>
@@ -7249,367 +7610,6 @@
     <t>Fuge a-Moll</t>
   </si>
   <si>
-    <t>MWV U30</t>
-  </si>
-  <si>
-    <t>op. 105</t>
-  </si>
-  <si>
-    <t>Violin Sonata in G minor</t>
-  </si>
-  <si>
-    <t>1. Allegro (sol mineur)
-2. Adagio cantabile e lento (do mineur)
-3. Presto (sol mineur)</t>
-  </si>
-  <si>
-    <t>Piano Sonata No. 2</t>
-  </si>
-  <si>
-    <t>MWV U44</t>
-  </si>
-  <si>
-    <t>op. 7/2</t>
-  </si>
-  <si>
-    <t>Mit heftiger Bewegung</t>
-  </si>
-  <si>
-    <t>MWV U50</t>
-  </si>
-  <si>
-    <t>op. 5</t>
-  </si>
-  <si>
-    <t>Cappricio in F-sharp minor</t>
-  </si>
-  <si>
-    <t>Prestissimo</t>
-  </si>
-  <si>
-    <t>MWV U54</t>
-  </si>
-  <si>
-    <t>op. 6</t>
-  </si>
-  <si>
-    <t>Piano Sonata in E major</t>
-  </si>
-  <si>
-    <t>1. Allegretto con espressione (mi majeur)
-2. Tempo di Menuetto (fa dièse mineur)
-3. Recitativo. Adagio e senza tempo (la mineur)
-4. Molto Allegro vivace (mi majeur)</t>
-  </si>
-  <si>
-    <t>Piano Sonata No. 1</t>
-  </si>
-  <si>
-    <t>MWV U55</t>
-  </si>
-  <si>
-    <t>op. 7/4</t>
-  </si>
-  <si>
-    <t>Schnell und beweglich</t>
-  </si>
-  <si>
-    <t>MWV U56</t>
-  </si>
-  <si>
-    <t>op. 7/1</t>
-  </si>
-  <si>
-    <t>Sanft und mit Empfindung</t>
-  </si>
-  <si>
-    <t>MWV U58</t>
-  </si>
-  <si>
-    <t>op. 119</t>
-  </si>
-  <si>
-    <t>Perpetuum mobile</t>
-  </si>
-  <si>
-    <t>MWV U59</t>
-  </si>
-  <si>
-    <t>op. 7/3</t>
-  </si>
-  <si>
-    <t>Kraftig und feurig</t>
-  </si>
-  <si>
-    <t>MWV U60</t>
-  </si>
-  <si>
-    <t>op. 7/5</t>
-  </si>
-  <si>
-    <t>Ernst und mit steigender Lebhaftigkeit</t>
-  </si>
-  <si>
-    <t>Fuga</t>
-  </si>
-  <si>
-    <t>MWV U61</t>
-  </si>
-  <si>
-    <t>op. 7/6</t>
-  </si>
-  <si>
-    <t>Sensuchtig</t>
-  </si>
-  <si>
-    <t>MWV U62</t>
-  </si>
-  <si>
-    <t>op. 7/7</t>
-  </si>
-  <si>
-    <t>Leicht und luftig</t>
-  </si>
-  <si>
-    <t>MWV U64</t>
-  </si>
-  <si>
-    <t>op. 106</t>
-  </si>
-  <si>
-    <t>Piano Sonata in B-flat major</t>
-  </si>
-  <si>
-    <t>1. Allegro vivace (si bémol majeur)
-2. Scherzo. Allegro non troppo (ré bémol majeur)
-3. Andante quasi Allegretto (mi majeur)
-4. Allegro molto (si bémol majeur) / Allegro moderato</t>
-  </si>
-  <si>
-    <t>Piano Sonata No. 3</t>
-  </si>
-  <si>
-    <t>MWV U65</t>
-  </si>
-  <si>
-    <t>MWV U66</t>
-  </si>
-  <si>
-    <t>op. 35/1b</t>
-  </si>
-  <si>
-    <t>Fugue in E minor</t>
-  </si>
-  <si>
-    <t>MWV U67</t>
-  </si>
-  <si>
-    <t>op. 14</t>
-  </si>
-  <si>
-    <t>Rondo capriccioso in E major</t>
-  </si>
-  <si>
-    <t>1. Andante (mi majeur)
-2. Presto (mi mineur)</t>
-  </si>
-  <si>
-    <t>MWV U69</t>
-  </si>
-  <si>
-    <t>WoO 2</t>
-  </si>
-  <si>
-    <t>Scherzo in B minor</t>
-  </si>
-  <si>
-    <t>[Publié dans "Berliner allgemeine musikalische Zeitung"]</t>
-  </si>
-  <si>
-    <t>MWV U70</t>
-  </si>
-  <si>
-    <t>op. 16/1</t>
-  </si>
-  <si>
-    <t>Fantaisia in A minor</t>
-  </si>
-  <si>
-    <t>Fantaisia</t>
-  </si>
-  <si>
-    <t>1. Andante con moto (la mineur)
-2. Allegro vivace (la majeur)</t>
-  </si>
-  <si>
-    <t>MWV U71</t>
-  </si>
-  <si>
-    <t>op. 16/2</t>
-  </si>
-  <si>
-    <t>Caprice in E minor</t>
-  </si>
-  <si>
-    <t>Scherzo. Presto</t>
-  </si>
-  <si>
-    <t>MWV U72</t>
-  </si>
-  <si>
-    <t>op. 16/3</t>
-  </si>
-  <si>
-    <t>Fantaisie in E major "The Rivulet"</t>
-  </si>
-  <si>
-    <t>MWV U73</t>
-  </si>
-  <si>
-    <t>op. 19b/4</t>
-  </si>
-  <si>
-    <t>MWV U74</t>
-  </si>
-  <si>
-    <t>op. 15</t>
-  </si>
-  <si>
-    <t>Fantaisie sur le lied irlandais "The Last Rose"</t>
-  </si>
-  <si>
-    <t>1. Adagio (mi majeur)
-2. Presto agitato (mi mineur)
-3. Andante (mi majeur)
-4. Presto come prima (mi majeur / mi mineur)
-5. Andante con moto (mi majeur)</t>
-  </si>
-  <si>
-    <t>MWV U77</t>
-  </si>
-  <si>
-    <t>op. 30/2</t>
-  </si>
-  <si>
-    <t>MWV U78</t>
-  </si>
-  <si>
-    <t>op. 19b/6</t>
-  </si>
-  <si>
-    <t>Andante sostenuto "Venerianisches Gondellied"</t>
-  </si>
-  <si>
-    <t>MWV U80</t>
-  </si>
-  <si>
-    <t>op. 19b/2</t>
-  </si>
-  <si>
-    <t>MWV U86</t>
-  </si>
-  <si>
-    <t>op. 19b/1</t>
-  </si>
-  <si>
-    <t>MWV U89</t>
-  </si>
-  <si>
-    <t>op. 19b/3</t>
-  </si>
-  <si>
-    <t>Molto Allegro e vivace "Jagerlied"</t>
-  </si>
-  <si>
-    <t>MWV U90</t>
-  </si>
-  <si>
-    <t>op. 19b/5</t>
-  </si>
-  <si>
-    <t>Poco agitato</t>
-  </si>
-  <si>
-    <t>MWV U91</t>
-  </si>
-  <si>
-    <t>op. 35/3b</t>
-  </si>
-  <si>
-    <t>Fugue in B minor</t>
-  </si>
-  <si>
-    <t>MWV U92</t>
-  </si>
-  <si>
-    <t>op. 28</t>
-  </si>
-  <si>
-    <t>Fantaisie in F-sharp minor "Sonate écossaise"</t>
-  </si>
-  <si>
-    <t>1. Con moto agitato / Andante / Con moto agitato
-2. Allegro con moto (la majeur / ré majeur)
-3. Presto (fa dièse mineur)</t>
-  </si>
-  <si>
-    <t>MWV U93</t>
-  </si>
-  <si>
-    <t>WoO 19/1</t>
-  </si>
-  <si>
-    <t>Andante cantabile</t>
-  </si>
-  <si>
-    <t>MWV U94</t>
-  </si>
-  <si>
-    <t>WoO 19/2</t>
-  </si>
-  <si>
-    <t>MWV U95</t>
-  </si>
-  <si>
-    <t>op. 33/3</t>
-  </si>
-  <si>
-    <t>Caprice in B-flat minor</t>
-  </si>
-  <si>
-    <t>Adagio / Presto con fuoco</t>
-  </si>
-  <si>
-    <t>MWV U97</t>
-  </si>
-  <si>
-    <t>op. 30/5</t>
-  </si>
-  <si>
-    <t>Andante grazioso</t>
-  </si>
-  <si>
-    <t>MWV U98</t>
-  </si>
-  <si>
-    <t>op. 30/4</t>
-  </si>
-  <si>
-    <t>Agitato e con fuoco</t>
-  </si>
-  <si>
-    <t>MWV U99</t>
-  </si>
-  <si>
-    <t>op. 33/1</t>
-  </si>
-  <si>
-    <t>Caprice in A minor</t>
-  </si>
-  <si>
-    <t>Adagio quasi Fantasia / Presto agitato</t>
-  </si>
-  <si>
     <t>MWV V1</t>
   </si>
   <si>
@@ -7775,6 +7775,54 @@
     <t>„Gesegnete Mahlzeit“</t>
   </si>
   <si>
+    <t>MWV X2</t>
+  </si>
+  <si>
+    <t>„Ich will Dienstag kommen“</t>
+  </si>
+  <si>
+    <t>MWV X3</t>
+  </si>
+  <si>
+    <t>„Wohl ihm“</t>
+  </si>
+  <si>
+    <t>MWV X4</t>
+  </si>
+  <si>
+    <t>„Ach, liebe Fanny, verzeih“</t>
+  </si>
+  <si>
+    <t>MWV X5</t>
+  </si>
+  <si>
+    <t>„Denn ach, sie sind Philister“</t>
+  </si>
+  <si>
+    <t>MWV X6</t>
+  </si>
+  <si>
+    <t>„Ein genialer Geist frägt nicht“</t>
+  </si>
+  <si>
+    <t>MWV X7</t>
+  </si>
+  <si>
+    <t>„Sohn, Schmidt, Bendemann“</t>
+  </si>
+  <si>
+    <t>MWV X8</t>
+  </si>
+  <si>
+    <t>„Mit Vergnügen werd ich kommen“</t>
+  </si>
+  <si>
+    <t>MWV X9</t>
+  </si>
+  <si>
+    <t>„Und ob du mich züchtigest, Herr“</t>
+  </si>
+  <si>
     <t>MWV X10</t>
   </si>
   <si>
@@ -7823,60 +7871,78 @@
     <t>„Gott fürchten, ist die Weisheit“</t>
   </si>
   <si>
-    <t>MWV X2</t>
-  </si>
-  <si>
-    <t>„Ich will Dienstag kommen“</t>
-  </si>
-  <si>
-    <t>MWV X3</t>
-  </si>
-  <si>
-    <t>„Wohl ihm“</t>
-  </si>
-  <si>
-    <t>MWV X4</t>
-  </si>
-  <si>
-    <t>„Ach, liebe Fanny, verzeih“</t>
-  </si>
-  <si>
-    <t>MWV X5</t>
-  </si>
-  <si>
-    <t>„Denn ach, sie sind Philister“</t>
-  </si>
-  <si>
-    <t>MWV X6</t>
-  </si>
-  <si>
-    <t>„Ein genialer Geist frägt nicht“</t>
-  </si>
-  <si>
-    <t>MWV X7</t>
-  </si>
-  <si>
-    <t>„Sohn, Schmidt, Bendemann“</t>
-  </si>
-  <si>
-    <t>MWV X8</t>
-  </si>
-  <si>
-    <t>„Mit Vergnügen werd ich kommen“</t>
-  </si>
-  <si>
-    <t>MWV X9</t>
-  </si>
-  <si>
-    <t>„Und ob du mich züchtigest, Herr“</t>
-  </si>
-  <si>
     <t>MWV Y1</t>
   </si>
   <si>
     <t>Kanon A-Dur für drei Stimmen</t>
   </si>
   <si>
+    <t>MWV Y2</t>
+  </si>
+  <si>
+    <t>Kanon F-Dur für drei Stimmen</t>
+  </si>
+  <si>
+    <t>MWV Y3</t>
+  </si>
+  <si>
+    <t>Kanon F-Dur für sechs Stimmen und Bassbegleitung</t>
+  </si>
+  <si>
+    <t>MWV Y4</t>
+  </si>
+  <si>
+    <r>
+      <t>Kurzgefasste Übersicht des canonischen Rechts</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>für drei Violinen</t>
+    </r>
+  </si>
+  <si>
+    <t>MWV Y5</t>
+  </si>
+  <si>
+    <t>Kanon h-Moll für drei Stimmen und Bassbegleitung</t>
+  </si>
+  <si>
+    <t>MWV Y6</t>
+  </si>
+  <si>
+    <t>Kanon a-Moll für drei Stimmen</t>
+  </si>
+  <si>
+    <t>MWV Y7</t>
+  </si>
+  <si>
+    <t>Kanon Es-Dur für zwei Violen</t>
+  </si>
+  <si>
+    <t>MWV Y8</t>
+  </si>
+  <si>
+    <t>Kanon h-Moll für drei Stimmen</t>
+  </si>
+  <si>
+    <t>MWV Y9</t>
+  </si>
+  <si>
     <t>MWV Y10</t>
   </si>
   <si>
@@ -7926,9 +7992,6 @@
   </si>
   <si>
     <t>MWV Y18</t>
-  </si>
-  <si>
-    <t>Kanon h-Moll für drei Stimmen</t>
   </si>
   <si>
     <t>MWV Y19</t>
@@ -7958,12 +8021,6 @@
     </r>
   </si>
   <si>
-    <t>MWV Y2</t>
-  </si>
-  <si>
-    <t>Kanon F-Dur für drei Stimmen</t>
-  </si>
-  <si>
     <t>MWV Y20</t>
   </si>
   <si>
@@ -7974,63 +8031,6 @@
   </si>
   <si>
     <t>Kanon G-Dur für zwei Stimmen und eine Oberstimme</t>
-  </si>
-  <si>
-    <t>MWV Y3</t>
-  </si>
-  <si>
-    <t>Kanon F-Dur für sechs Stimmen und Bassbegleitung</t>
-  </si>
-  <si>
-    <t>MWV Y4</t>
-  </si>
-  <si>
-    <r>
-      <t>Kurzgefasste Übersicht des canonischen Rechts</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="13.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13.5"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>für drei Violinen</t>
-    </r>
-  </si>
-  <si>
-    <t>MWV Y5</t>
-  </si>
-  <si>
-    <t>Kanon h-Moll für drei Stimmen und Bassbegleitung</t>
-  </si>
-  <si>
-    <t>MWV Y6</t>
-  </si>
-  <si>
-    <t>Kanon a-Moll für drei Stimmen</t>
-  </si>
-  <si>
-    <t>MWV Y7</t>
-  </si>
-  <si>
-    <t>Kanon Es-Dur für zwei Violen</t>
-  </si>
-  <si>
-    <t>MWV Y8</t>
-  </si>
-  <si>
-    <t>MWV Y9</t>
   </si>
   <si>
     <t>MWV Z1</t>
@@ -9037,7 +9037,7 @@
   </si>
   <si>
     <t>Weltliche Vokalmusik
-(D bis K)</t>
+(D bis E)</t>
   </si>
   <si>
     <t>D</t>
@@ -9930,7 +9930,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="J368" s="18"/>
     </row>
-    <row r="369" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="369" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A369" s="13">
         <v>15009</v>
       </c>
@@ -19456,7 +19456,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="370" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="370" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A370" s="13">
         <v>15010</v>
       </c>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="J370" s="18"/>
     </row>
-    <row r="371" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="371" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A371" s="13">
         <v>15011</v>
       </c>
@@ -19516,7 +19516,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="372" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="372" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A372" s="13">
         <v>15012</v>
       </c>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="J372" s="18"/>
     </row>
-    <row r="373" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="373" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A373" s="13">
         <v>15013</v>
       </c>
@@ -19564,7 +19564,7 @@
       </c>
       <c r="J373" s="18"/>
     </row>
-    <row r="374" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="374" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A374" s="13">
         <v>15014</v>
       </c>
@@ -19594,7 +19594,7 @@
       </c>
       <c r="J374" s="18"/>
     </row>
-    <row r="375" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="375" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A375" s="13">
         <v>16001</v>
       </c>
@@ -19624,428 +19624,428 @@
       </c>
       <c r="J375" s="18"/>
     </row>
-    <row r="376" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="376" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A376" s="13">
-        <v>16010</v>
+        <v>16002</v>
       </c>
       <c r="B376" s="14" t="s">
         <v>1181</v>
       </c>
-      <c r="C376" s="15"/>
-      <c r="D376" s="15"/>
+      <c r="C376" s="15" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D376" s="15">
+        <v>1826</v>
+      </c>
       <c r="E376" s="12" t="s">
-        <v>1182</v>
-      </c>
-      <c r="F376" s="15"/>
-      <c r="G376" s="16"/>
-      <c r="H376" s="17"/>
-      <c r="I376" s="18"/>
-      <c r="J376" s="23"/>
-    </row>
-    <row r="377" s="12" customFormat="1" customHeight="1" spans="1:10">
+        <v>1183</v>
+      </c>
+      <c r="F376" s="15" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G376" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="H376" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="I376" s="18" t="s">
+        <v>1184</v>
+      </c>
+      <c r="J376" s="18"/>
+    </row>
+    <row r="377" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A377" s="13">
-        <v>16011</v>
+        <v>16003</v>
       </c>
       <c r="B377" s="14" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C377" s="15"/>
-      <c r="D377" s="15"/>
+        <v>1185</v>
+      </c>
+      <c r="C377" s="15" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D377" s="15">
+        <v>1826</v>
+      </c>
       <c r="E377" s="12" t="s">
-        <v>1184</v>
+        <v>1187</v>
       </c>
       <c r="F377" s="15" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G377" s="16"/>
-      <c r="H377" s="17"/>
-      <c r="I377" s="18"/>
-      <c r="J377" s="23"/>
-    </row>
-    <row r="378" s="12" customFormat="1" customHeight="1" spans="1:10">
+        <v>1178</v>
+      </c>
+      <c r="G377" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="H377" s="17" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I377" s="18" t="s">
+        <v>1189</v>
+      </c>
+      <c r="J377" s="18" t="s">
+        <v>1190</v>
+      </c>
+      <c r="K377" s="26" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="378" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A378" s="13">
-        <v>16012</v>
+        <v>16005</v>
       </c>
       <c r="B378" s="14" t="s">
-        <v>1186</v>
+        <v>1192</v>
       </c>
       <c r="C378" s="15" t="s">
-        <v>1187</v>
+        <v>1193</v>
       </c>
       <c r="D378" s="15">
-        <v>1833</v>
+        <v>1828</v>
       </c>
       <c r="E378" s="12" t="s">
-        <v>1188</v>
+        <v>1194</v>
       </c>
       <c r="F378" s="15" t="s">
         <v>1178</v>
       </c>
       <c r="G378" s="16" t="s">
-        <v>433</v>
+        <v>191</v>
       </c>
       <c r="H378" s="17" t="s">
-        <v>611</v>
+        <v>1195</v>
       </c>
       <c r="I378" s="18" t="s">
-        <v>1189</v>
+        <v>1196</v>
       </c>
       <c r="J378" s="23" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="379" s="12" customFormat="1" customHeight="1" spans="1:10">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="379" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A379" s="13">
-        <v>16013</v>
+        <v>16006</v>
       </c>
       <c r="B379" s="14" t="s">
-        <v>1191</v>
+        <v>1198</v>
       </c>
       <c r="C379" s="15"/>
       <c r="D379" s="15"/>
       <c r="E379" s="12" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F379" s="15" t="s">
-        <v>1185</v>
-      </c>
+        <v>1199</v>
+      </c>
+      <c r="F379" s="15"/>
       <c r="G379" s="16"/>
       <c r="H379" s="17"/>
       <c r="I379" s="18"/>
       <c r="J379" s="23"/>
     </row>
-    <row r="380" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="380" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A380" s="13">
-        <v>16014</v>
+        <v>16007</v>
       </c>
       <c r="B380" s="14" t="s">
-        <v>1192</v>
+        <v>1200</v>
       </c>
       <c r="C380" s="15" t="s">
-        <v>1193</v>
-      </c>
-      <c r="D380" s="15">
-        <v>1836</v>
+        <v>1201</v>
+      </c>
+      <c r="D380" s="15" t="s">
+        <v>1202</v>
       </c>
       <c r="E380" s="12" t="s">
-        <v>1194</v>
+        <v>1203</v>
       </c>
       <c r="F380" s="15" t="s">
-        <v>1185</v>
+        <v>1178</v>
       </c>
       <c r="G380" s="16" t="s">
-        <v>349</v>
+        <v>508</v>
       </c>
       <c r="H380" s="17" t="s">
-        <v>1195</v>
+        <v>229</v>
       </c>
       <c r="I380" s="18" t="s">
-        <v>1196</v>
-      </c>
-      <c r="J380" s="18" t="s">
-        <v>1197</v>
-      </c>
-    </row>
-    <row r="381" s="12" customFormat="1" customHeight="1" spans="1:10">
+        <v>1103</v>
+      </c>
+      <c r="J380" s="23" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="381" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A381" s="13">
-        <v>16015</v>
+        <v>16008</v>
       </c>
       <c r="B381" s="14" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C381" s="15" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C381" s="15"/>
+      <c r="D381" s="15"/>
+      <c r="E381" s="12" t="s">
         <v>1199</v>
       </c>
-      <c r="D381" s="15">
-        <v>1839</v>
-      </c>
-      <c r="E381" s="12" t="s">
-        <v>1200</v>
-      </c>
-      <c r="F381" s="15" t="s">
-        <v>1178</v>
-      </c>
-      <c r="G381" s="16" t="s">
-        <v>1201</v>
-      </c>
-      <c r="H381" s="17" t="s">
-        <v>1202</v>
-      </c>
-      <c r="I381" s="18" t="s">
-        <v>1203</v>
-      </c>
-      <c r="J381" s="18"/>
-    </row>
-    <row r="382" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="F381" s="15"/>
+      <c r="G381" s="16"/>
+      <c r="H381" s="17"/>
+      <c r="I381" s="18"/>
+      <c r="J381" s="23"/>
+    </row>
+    <row r="382" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A382" s="13">
-        <v>16016</v>
+        <v>16009</v>
       </c>
       <c r="B382" s="14" t="s">
-        <v>1204</v>
-      </c>
-      <c r="C382" s="15" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D382" s="16">
-        <v>1841</v>
-      </c>
-      <c r="E382" s="27"/>
-      <c r="F382" s="15" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G382" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H382" s="23" t="s">
         <v>1206</v>
       </c>
-      <c r="I382" s="18" t="s">
+      <c r="C382" s="15"/>
+      <c r="D382" s="15"/>
+      <c r="E382" s="12" t="s">
         <v>1207</v>
       </c>
-      <c r="J382" s="28" t="s">
+      <c r="F382" s="15"/>
+      <c r="G382" s="16"/>
+      <c r="H382" s="17"/>
+      <c r="I382" s="18"/>
+      <c r="J382" s="23"/>
+    </row>
+    <row r="383" s="12" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A383" s="13">
+        <v>16010</v>
+      </c>
+      <c r="B383" s="14" t="s">
         <v>1208</v>
       </c>
-    </row>
-    <row r="383" s="12" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A383" s="13">
-        <v>16017</v>
-      </c>
-      <c r="B383" s="14" t="s">
+      <c r="C383" s="15"/>
+      <c r="D383" s="15"/>
+      <c r="E383" s="12" t="s">
         <v>1209</v>
       </c>
-      <c r="C383" s="15"/>
-      <c r="D383" s="16"/>
-      <c r="E383" s="27"/>
-      <c r="F383" s="15" t="s">
-        <v>1185</v>
-      </c>
+      <c r="F383" s="15"/>
       <c r="G383" s="16"/>
-      <c r="H383" s="23"/>
+      <c r="H383" s="17"/>
       <c r="I383" s="18"/>
-      <c r="J383" s="28"/>
-    </row>
-    <row r="384" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J383" s="23"/>
+    </row>
+    <row r="384" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A384" s="13">
-        <v>16018</v>
+        <v>16011</v>
       </c>
       <c r="B384" s="14" t="s">
         <v>1210</v>
       </c>
       <c r="C384" s="15"/>
-      <c r="D384" s="16"/>
-      <c r="E384" s="27"/>
+      <c r="D384" s="15"/>
+      <c r="E384" s="12" t="s">
+        <v>1211</v>
+      </c>
       <c r="F384" s="15" t="s">
-        <v>1185</v>
+        <v>1212</v>
       </c>
       <c r="G384" s="16"/>
-      <c r="H384" s="23"/>
+      <c r="H384" s="17"/>
       <c r="I384" s="18"/>
-      <c r="J384" s="28"/>
-    </row>
-    <row r="385" s="12" customFormat="1" customHeight="1" spans="1:11">
+      <c r="J384" s="23"/>
+    </row>
+    <row r="385" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A385" s="13">
-        <v>16019</v>
+        <v>16012</v>
       </c>
       <c r="B385" s="14" t="s">
+        <v>1213</v>
+      </c>
+      <c r="C385" s="15" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D385" s="15">
+        <v>1833</v>
+      </c>
+      <c r="E385" s="12" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F385" s="15" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G385" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="H385" s="17" t="s">
+        <v>611</v>
+      </c>
+      <c r="I385" s="18" t="s">
+        <v>1216</v>
+      </c>
+      <c r="J385" s="23" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="386" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A386" s="13">
+        <v>16013</v>
+      </c>
+      <c r="B386" s="14" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C386" s="15"/>
+      <c r="D386" s="15"/>
+      <c r="E386" s="12" t="s">
         <v>1211</v>
       </c>
-      <c r="C385" s="15"/>
-      <c r="D385" s="16"/>
-      <c r="E385" s="12" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F385" s="15" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G385" s="16"/>
-      <c r="H385" s="23"/>
-      <c r="I385" s="18"/>
-      <c r="J385" s="28"/>
-    </row>
-    <row r="386" s="12" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A386" s="13">
-        <v>16002</v>
-      </c>
-      <c r="B386" s="14" t="s">
+      <c r="F386" s="15" t="s">
         <v>1212</v>
       </c>
-      <c r="C386" s="15" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D386" s="15">
-        <v>1826</v>
-      </c>
-      <c r="E386" s="12" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F386" s="15" t="s">
-        <v>1178</v>
-      </c>
-      <c r="G386" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="H386" s="17" t="s">
-        <v>192</v>
-      </c>
-      <c r="I386" s="18" t="s">
-        <v>1215</v>
-      </c>
-      <c r="J386" s="18"/>
-    </row>
-    <row r="387" s="12" customFormat="1" customHeight="1" spans="1:11">
+      <c r="G386" s="16"/>
+      <c r="H386" s="17"/>
+      <c r="I386" s="18"/>
+      <c r="J386" s="23"/>
+    </row>
+    <row r="387" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A387" s="13">
-        <v>16003</v>
+        <v>16014</v>
       </c>
       <c r="B387" s="14" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="C387" s="15" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="D387" s="15">
-        <v>1826</v>
+        <v>1836</v>
       </c>
       <c r="E387" s="12" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="F387" s="15" t="s">
-        <v>1178</v>
+        <v>1212</v>
       </c>
       <c r="G387" s="16" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="H387" s="17" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="I387" s="18" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="J387" s="18" t="s">
-        <v>1221</v>
-      </c>
-      <c r="K387" s="26" t="s">
-        <v>1222</v>
-      </c>
-    </row>
-    <row r="388" s="12" customFormat="1" customHeight="1" spans="1:11">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="388" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A388" s="13">
-        <v>16005</v>
+        <v>16015</v>
       </c>
       <c r="B388" s="14" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="C388" s="15" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="D388" s="15">
-        <v>1828</v>
+        <v>1839</v>
       </c>
       <c r="E388" s="12" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="F388" s="15" t="s">
         <v>1178</v>
       </c>
       <c r="G388" s="16" t="s">
+        <v>1228</v>
+      </c>
+      <c r="H388" s="17" t="s">
+        <v>1229</v>
+      </c>
+      <c r="I388" s="18" t="s">
+        <v>1230</v>
+      </c>
+      <c r="J388" s="18"/>
+    </row>
+    <row r="389" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A389" s="13">
+        <v>16016</v>
+      </c>
+      <c r="B389" s="14" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C389" s="15" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D389" s="16">
+        <v>1841</v>
+      </c>
+      <c r="E389" s="27"/>
+      <c r="F389" s="15" t="s">
+        <v>1212</v>
+      </c>
+      <c r="G389" s="16" t="s">
         <v>191</v>
       </c>
-      <c r="H388" s="17" t="s">
-        <v>1226</v>
-      </c>
-      <c r="I388" s="18" t="s">
-        <v>1227</v>
-      </c>
-      <c r="J388" s="23" t="s">
-        <v>1228</v>
-      </c>
-    </row>
-    <row r="389" s="12" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A389" s="13">
-        <v>16006</v>
-      </c>
-      <c r="B389" s="14" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C389" s="15"/>
-      <c r="D389" s="15"/>
-      <c r="E389" s="12" t="s">
-        <v>1230</v>
-      </c>
-      <c r="F389" s="15"/>
-      <c r="G389" s="16"/>
-      <c r="H389" s="17"/>
-      <c r="I389" s="18"/>
-      <c r="J389" s="23"/>
-    </row>
-    <row r="390" s="12" customFormat="1" customHeight="1" spans="1:11">
+      <c r="H389" s="23" t="s">
+        <v>1233</v>
+      </c>
+      <c r="I389" s="18" t="s">
+        <v>1234</v>
+      </c>
+      <c r="J389" s="28" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="390" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A390" s="13">
-        <v>16007</v>
+        <v>16017</v>
       </c>
       <c r="B390" s="14" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C390" s="15" t="s">
-        <v>1232</v>
-      </c>
-      <c r="D390" s="15" t="s">
-        <v>1233</v>
-      </c>
-      <c r="E390" s="12" t="s">
-        <v>1234</v>
-      </c>
+        <v>1236</v>
+      </c>
+      <c r="C390" s="15"/>
+      <c r="D390" s="16"/>
+      <c r="E390" s="27"/>
       <c r="F390" s="15" t="s">
-        <v>1178</v>
-      </c>
-      <c r="G390" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="H390" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="I390" s="18" t="s">
-        <v>1103</v>
-      </c>
-      <c r="J390" s="23" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="391" s="12" customFormat="1" customHeight="1" spans="1:11">
+        <v>1212</v>
+      </c>
+      <c r="G390" s="16"/>
+      <c r="H390" s="23"/>
+      <c r="I390" s="18"/>
+      <c r="J390" s="28"/>
+    </row>
+    <row r="391" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A391" s="13">
-        <v>16008</v>
+        <v>16018</v>
       </c>
       <c r="B391" s="14" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C391" s="15"/>
-      <c r="D391" s="15"/>
-      <c r="E391" s="12" t="s">
-        <v>1230</v>
-      </c>
-      <c r="F391" s="15"/>
+      <c r="D391" s="16"/>
+      <c r="E391" s="27"/>
+      <c r="F391" s="15" t="s">
+        <v>1212</v>
+      </c>
       <c r="G391" s="16"/>
-      <c r="H391" s="17"/>
+      <c r="H391" s="23"/>
       <c r="I391" s="18"/>
-      <c r="J391" s="23"/>
-    </row>
-    <row r="392" s="12" customFormat="1" customHeight="1" spans="1:11">
+      <c r="J391" s="28"/>
+    </row>
+    <row r="392" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A392" s="13">
-        <v>16009</v>
+        <v>16019</v>
       </c>
       <c r="B392" s="14" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C392" s="15"/>
-      <c r="D392" s="15"/>
+      <c r="D392" s="16"/>
       <c r="E392" s="12" t="s">
-        <v>1238</v>
-      </c>
-      <c r="F392" s="15"/>
+        <v>1211</v>
+      </c>
+      <c r="F392" s="15" t="s">
+        <v>1212</v>
+      </c>
       <c r="G392" s="16"/>
-      <c r="H392" s="17"/>
+      <c r="H392" s="23"/>
       <c r="I392" s="18"/>
-      <c r="J392" s="23"/>
-    </row>
-    <row r="393" s="12" customFormat="1" customHeight="1" spans="1:11">
+      <c r="J392" s="28"/>
+    </row>
+    <row r="393" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A393" s="13">
         <v>17001</v>
       </c>
@@ -20063,9 +20063,9 @@
       <c r="I393" s="18"/>
       <c r="J393" s="23"/>
     </row>
-    <row r="394" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="394" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A394" s="13">
-        <v>17010</v>
+        <v>17002</v>
       </c>
       <c r="B394" s="14" t="s">
         <v>1241</v>
@@ -20081,201 +20081,125 @@
       <c r="I394" s="18"/>
       <c r="J394" s="23"/>
     </row>
-    <row r="395" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="395" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A395" s="13">
-        <v>17011</v>
+        <v>17003</v>
       </c>
       <c r="B395" s="14" t="s">
         <v>1243</v>
       </c>
-      <c r="C395" s="15" t="s">
+      <c r="C395" s="15"/>
+      <c r="D395" s="15"/>
+      <c r="E395" s="24" t="s">
         <v>1244</v>
       </c>
-      <c r="D395" s="15">
-        <v>1822</v>
-      </c>
-      <c r="E395" s="12" t="s">
+      <c r="F395" s="15"/>
+      <c r="G395" s="16"/>
+      <c r="H395" s="17"/>
+      <c r="I395" s="18"/>
+      <c r="J395" s="23"/>
+    </row>
+    <row r="396" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A396" s="13">
+        <v>17004</v>
+      </c>
+      <c r="B396" s="14" t="s">
         <v>1245</v>
       </c>
-      <c r="F395" s="15" t="s">
+      <c r="C396" s="15"/>
+      <c r="D396" s="15"/>
+      <c r="E396" s="24" t="s">
         <v>1246</v>
       </c>
-      <c r="G395" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="H395" s="23" t="s">
+      <c r="F396" s="15"/>
+      <c r="G396" s="16"/>
+      <c r="H396" s="17"/>
+      <c r="I396" s="18"/>
+      <c r="J396" s="23"/>
+    </row>
+    <row r="397" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A397" s="13">
+        <v>17005</v>
+      </c>
+      <c r="B397" s="14" t="s">
         <v>1247</v>
       </c>
-      <c r="I395" s="18" t="s">
+      <c r="C397" s="15"/>
+      <c r="D397" s="15"/>
+      <c r="E397" s="24" t="s">
         <v>1248</v>
       </c>
-      <c r="J395" s="18" t="s">
+      <c r="F397" s="15"/>
+      <c r="G397" s="16"/>
+      <c r="H397" s="17"/>
+      <c r="I397" s="18"/>
+      <c r="J397" s="23"/>
+    </row>
+    <row r="398" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A398" s="13">
+        <v>17006</v>
+      </c>
+      <c r="B398" s="14" t="s">
         <v>1249</v>
       </c>
-    </row>
-    <row r="396" s="12" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A396" s="13">
-        <v>17012</v>
-      </c>
-      <c r="B396" s="14" t="s">
+      <c r="C398" s="15"/>
+      <c r="D398" s="15"/>
+      <c r="E398" s="24" t="s">
         <v>1250</v>
       </c>
-      <c r="C396" s="15" t="s">
+      <c r="F398" s="15"/>
+      <c r="G398" s="16"/>
+      <c r="H398" s="17"/>
+      <c r="I398" s="18"/>
+      <c r="J398" s="23"/>
+    </row>
+    <row r="399" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A399" s="13">
+        <v>17007</v>
+      </c>
+      <c r="B399" s="14" t="s">
         <v>1251</v>
       </c>
-      <c r="D396" s="15">
-        <v>1825</v>
-      </c>
-      <c r="E396" s="12" t="s">
+      <c r="C399" s="15"/>
+      <c r="D399" s="15"/>
+      <c r="E399" s="24" t="s">
         <v>1252</v>
       </c>
-      <c r="F396" s="15" t="s">
+      <c r="F399" s="15"/>
+      <c r="G399" s="16"/>
+      <c r="H399" s="17"/>
+      <c r="I399" s="18"/>
+      <c r="J399" s="23"/>
+    </row>
+    <row r="400" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A400" s="13">
+        <v>17008</v>
+      </c>
+      <c r="B400" s="14" t="s">
         <v>1253</v>
       </c>
-      <c r="G396" s="16" t="s">
+      <c r="C400" s="15"/>
+      <c r="D400" s="15"/>
+      <c r="E400" s="24" t="s">
         <v>1254</v>
       </c>
-      <c r="H396" s="23" t="s">
-        <v>1255</v>
-      </c>
-      <c r="I396" s="18" t="s">
-        <v>1256</v>
-      </c>
-      <c r="J396" s="18"/>
-    </row>
-    <row r="397" s="12" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A397" s="13">
-        <v>17013</v>
-      </c>
-      <c r="B397" s="14" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C397" s="15" t="s">
-        <v>1258</v>
-      </c>
-      <c r="D397" s="15">
-        <v>1823</v>
-      </c>
-      <c r="E397" s="12" t="s">
-        <v>1259</v>
-      </c>
-      <c r="F397" s="15" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G397" s="16" t="s">
-        <v>1254</v>
-      </c>
-      <c r="H397" s="23" t="s">
-        <v>1260</v>
-      </c>
-      <c r="I397" s="18" t="s">
-        <v>1248</v>
-      </c>
-      <c r="J397" s="18" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="398" s="12" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A398" s="13">
-        <v>17014</v>
-      </c>
-      <c r="B398" s="14" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C398" s="15" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D398" s="16">
-        <v>1824</v>
-      </c>
-      <c r="E398" s="12" t="s">
-        <v>1264</v>
-      </c>
-      <c r="F398" s="15" t="s">
-        <v>1265</v>
-      </c>
-      <c r="G398" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H398" s="23" t="s">
-        <v>1266</v>
-      </c>
-      <c r="I398" s="18" t="s">
-        <v>1267</v>
-      </c>
-      <c r="J398" s="18"/>
-    </row>
-    <row r="399" s="12" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A399" s="13">
-        <v>17015</v>
-      </c>
-      <c r="B399" s="14" t="s">
-        <v>1268</v>
-      </c>
-      <c r="C399" s="15" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D399" s="15" t="s">
-        <v>1270</v>
-      </c>
-      <c r="E399" s="12" t="s">
-        <v>1271</v>
-      </c>
-      <c r="F399" s="15" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G399" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="H399" s="23" t="s">
-        <v>1272</v>
-      </c>
-      <c r="I399" s="18" t="s">
-        <v>1248</v>
-      </c>
-      <c r="J399" s="18" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="400" s="12" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A400" s="13">
-        <v>17016</v>
-      </c>
-      <c r="B400" s="14" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C400" s="15" t="s">
-        <v>1275</v>
-      </c>
-      <c r="D400" s="15">
-        <v>1829</v>
-      </c>
-      <c r="E400" s="12" t="s">
-        <v>1276</v>
-      </c>
       <c r="F400" s="15"/>
-      <c r="G400" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H400" s="23" t="s">
-        <v>1277</v>
-      </c>
-      <c r="I400" s="18" t="s">
-        <v>1278</v>
-      </c>
-      <c r="J400" s="18"/>
+      <c r="G400" s="16"/>
+      <c r="H400" s="17"/>
+      <c r="I400" s="18"/>
+      <c r="J400" s="23"/>
     </row>
     <row r="401" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A401" s="13">
-        <v>17002</v>
+        <v>17009</v>
       </c>
       <c r="B401" s="14" t="s">
-        <v>1279</v>
+        <v>1255</v>
       </c>
       <c r="C401" s="15"/>
       <c r="D401" s="15"/>
       <c r="E401" s="24" t="s">
-        <v>1280</v>
+        <v>1256</v>
       </c>
       <c r="F401" s="15"/>
       <c r="G401" s="16"/>
@@ -20285,365 +20209,441 @@
     </row>
     <row r="402" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A402" s="13">
-        <v>17020</v>
+        <v>17010</v>
       </c>
       <c r="B402" s="14" t="s">
-        <v>1281</v>
+        <v>1257</v>
       </c>
       <c r="C402" s="15"/>
       <c r="D402" s="15"/>
-      <c r="E402" s="12" t="s">
-        <v>1282</v>
+      <c r="E402" s="24" t="s">
+        <v>1258</v>
       </c>
       <c r="F402" s="15"/>
-      <c r="G402" s="16" t="s">
-        <v>70</v>
-      </c>
+      <c r="G402" s="16"/>
       <c r="H402" s="17"/>
-      <c r="I402" s="18" t="s">
-        <v>1283</v>
-      </c>
-      <c r="J402" s="18"/>
+      <c r="I402" s="18"/>
+      <c r="J402" s="23"/>
     </row>
     <row r="403" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A403" s="13">
-        <v>17023</v>
+        <v>17011</v>
       </c>
       <c r="B403" s="14" t="s">
-        <v>1284</v>
+        <v>1259</v>
       </c>
       <c r="C403" s="15" t="s">
-        <v>1285</v>
+        <v>1260</v>
       </c>
       <c r="D403" s="15">
-        <v>1833</v>
+        <v>1822</v>
       </c>
       <c r="E403" s="12" t="s">
-        <v>1286</v>
-      </c>
-      <c r="F403" s="15"/>
+        <v>1261</v>
+      </c>
+      <c r="F403" s="15" t="s">
+        <v>1262</v>
+      </c>
       <c r="G403" s="16" t="s">
-        <v>1254</v>
+        <v>154</v>
       </c>
       <c r="H403" s="23" t="s">
-        <v>1287</v>
+        <v>1263</v>
       </c>
       <c r="I403" s="18" t="s">
-        <v>1288</v>
-      </c>
-      <c r="J403" s="18"/>
+        <v>1264</v>
+      </c>
+      <c r="J403" s="18" t="s">
+        <v>1265</v>
+      </c>
     </row>
     <row r="404" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A404" s="13">
-        <v>17024</v>
+        <v>17012</v>
       </c>
       <c r="B404" s="14" t="s">
-        <v>1289</v>
+        <v>1266</v>
       </c>
       <c r="C404" s="15" t="s">
-        <v>1290</v>
+        <v>1267</v>
       </c>
       <c r="D404" s="15">
-        <v>1833</v>
+        <v>1825</v>
       </c>
       <c r="E404" s="12" t="s">
-        <v>1291</v>
-      </c>
-      <c r="F404" s="15"/>
+        <v>1268</v>
+      </c>
+      <c r="F404" s="15" t="s">
+        <v>1269</v>
+      </c>
       <c r="G404" s="16" t="s">
-        <v>237</v>
+        <v>1270</v>
       </c>
       <c r="H404" s="23" t="s">
-        <v>1292</v>
+        <v>1271</v>
       </c>
       <c r="I404" s="18" t="s">
-        <v>1288</v>
+        <v>1272</v>
       </c>
       <c r="J404" s="18"/>
     </row>
     <row r="405" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A405" s="13">
-        <v>17027</v>
+        <v>17013</v>
       </c>
       <c r="B405" s="14" t="s">
-        <v>1293</v>
+        <v>1273</v>
       </c>
       <c r="C405" s="15" t="s">
-        <v>1294</v>
+        <v>1274</v>
       </c>
       <c r="D405" s="15">
-        <v>1838</v>
+        <v>1823</v>
       </c>
       <c r="E405" s="12" t="s">
-        <v>1295</v>
+        <v>1275</v>
       </c>
       <c r="F405" s="15" t="s">
-        <v>1253</v>
+        <v>1262</v>
       </c>
       <c r="G405" s="16" t="s">
-        <v>70</v>
+        <v>1270</v>
       </c>
       <c r="H405" s="23" t="s">
-        <v>1296</v>
+        <v>1276</v>
       </c>
       <c r="I405" s="18" t="s">
-        <v>1297</v>
+        <v>1264</v>
       </c>
       <c r="J405" s="18" t="s">
-        <v>1298</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="406" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A406" s="13">
-        <v>17029</v>
+        <v>17014</v>
       </c>
       <c r="B406" s="14" t="s">
-        <v>1299</v>
+        <v>1278</v>
       </c>
       <c r="C406" s="15" t="s">
-        <v>1300</v>
-      </c>
-      <c r="D406" s="15">
-        <v>1839</v>
+        <v>1279</v>
+      </c>
+      <c r="D406" s="16">
+        <v>1824</v>
       </c>
       <c r="E406" s="12" t="s">
-        <v>1301</v>
+        <v>1280</v>
       </c>
       <c r="F406" s="15" t="s">
-        <v>1302</v>
+        <v>1281</v>
       </c>
       <c r="G406" s="16" t="s">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="H406" s="23" t="s">
-        <v>1303</v>
+        <v>1282</v>
       </c>
       <c r="I406" s="18" t="s">
-        <v>1304</v>
-      </c>
-      <c r="J406" s="18" t="s">
-        <v>1305</v>
-      </c>
+        <v>1283</v>
+      </c>
+      <c r="J406" s="18"/>
     </row>
     <row r="407" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A407" s="13">
-        <v>17003</v>
+        <v>17015</v>
       </c>
       <c r="B407" s="14" t="s">
-        <v>1306</v>
-      </c>
-      <c r="C407" s="15"/>
-      <c r="D407" s="15"/>
-      <c r="E407" s="24" t="s">
-        <v>1307</v>
-      </c>
-      <c r="F407" s="15"/>
-      <c r="G407" s="16"/>
-      <c r="H407" s="17"/>
-      <c r="I407" s="18"/>
-      <c r="J407" s="23"/>
+        <v>1284</v>
+      </c>
+      <c r="C407" s="15" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D407" s="15" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E407" s="12" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F407" s="15" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G407" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="H407" s="23" t="s">
+        <v>1288</v>
+      </c>
+      <c r="I407" s="18" t="s">
+        <v>1264</v>
+      </c>
+      <c r="J407" s="18" t="s">
+        <v>1289</v>
+      </c>
     </row>
     <row r="408" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A408" s="13">
-        <v>17032</v>
+        <v>17016</v>
       </c>
       <c r="B408" s="14" t="s">
-        <v>1308</v>
+        <v>1290</v>
       </c>
       <c r="C408" s="15" t="s">
-        <v>1309</v>
+        <v>1291</v>
       </c>
       <c r="D408" s="15">
-        <v>1843</v>
+        <v>1829</v>
       </c>
       <c r="E408" s="12" t="s">
-        <v>1310</v>
-      </c>
-      <c r="F408" s="15" t="s">
-        <v>1253</v>
-      </c>
+        <v>1292</v>
+      </c>
+      <c r="F408" s="15"/>
       <c r="G408" s="16" t="s">
         <v>191</v>
       </c>
       <c r="H408" s="23" t="s">
-        <v>1311</v>
+        <v>1293</v>
       </c>
       <c r="I408" s="18" t="s">
-        <v>1297</v>
-      </c>
-      <c r="J408" s="18" t="s">
-        <v>1312</v>
-      </c>
+        <v>1294</v>
+      </c>
+      <c r="J408" s="18"/>
     </row>
     <row r="409" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A409" s="13">
-        <v>17033</v>
+        <v>17020</v>
       </c>
       <c r="B409" s="14" t="s">
-        <v>1313</v>
-      </c>
-      <c r="C409" s="15" t="s">
-        <v>1314</v>
-      </c>
-      <c r="D409" s="15">
-        <v>1845</v>
-      </c>
+        <v>1295</v>
+      </c>
+      <c r="C409" s="15"/>
+      <c r="D409" s="15"/>
       <c r="E409" s="12" t="s">
-        <v>1315</v>
-      </c>
-      <c r="F409" s="15" t="s">
-        <v>1302</v>
-      </c>
+        <v>1296</v>
+      </c>
+      <c r="F409" s="15"/>
       <c r="G409" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="H409" s="23" t="s">
-        <v>1316</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H409" s="17"/>
       <c r="I409" s="18" t="s">
-        <v>1304</v>
-      </c>
-      <c r="J409" s="18" t="s">
-        <v>1317</v>
-      </c>
+        <v>1297</v>
+      </c>
+      <c r="J409" s="18"/>
     </row>
     <row r="410" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A410" s="13">
-        <v>17034</v>
+        <v>17023</v>
       </c>
       <c r="B410" s="14" t="s">
-        <v>1318</v>
+        <v>1298</v>
       </c>
       <c r="C410" s="15" t="s">
-        <v>1319</v>
-      </c>
-      <c r="D410" s="16">
-        <v>1845</v>
+        <v>1299</v>
+      </c>
+      <c r="D410" s="15">
+        <v>1833</v>
       </c>
       <c r="E410" s="12" t="s">
-        <v>1320</v>
-      </c>
-      <c r="F410" s="15" t="s">
-        <v>204</v>
-      </c>
+        <v>1300</v>
+      </c>
+      <c r="F410" s="15"/>
       <c r="G410" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H410" s="17" t="s">
-        <v>144</v>
+        <v>1270</v>
+      </c>
+      <c r="H410" s="23" t="s">
+        <v>1301</v>
       </c>
       <c r="I410" s="18" t="s">
-        <v>1297</v>
+        <v>1302</v>
       </c>
       <c r="J410" s="18"/>
     </row>
     <row r="411" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A411" s="13">
-        <v>17004</v>
+        <v>17024</v>
       </c>
       <c r="B411" s="14" t="s">
-        <v>1321</v>
-      </c>
-      <c r="C411" s="15"/>
-      <c r="D411" s="15"/>
-      <c r="E411" s="24" t="s">
-        <v>1322</v>
+        <v>1303</v>
+      </c>
+      <c r="C411" s="15" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D411" s="15">
+        <v>1833</v>
+      </c>
+      <c r="E411" s="12" t="s">
+        <v>1305</v>
       </c>
       <c r="F411" s="15"/>
-      <c r="G411" s="16"/>
-      <c r="H411" s="17"/>
-      <c r="I411" s="18"/>
-      <c r="J411" s="23"/>
+      <c r="G411" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="H411" s="23" t="s">
+        <v>1306</v>
+      </c>
+      <c r="I411" s="18" t="s">
+        <v>1302</v>
+      </c>
+      <c r="J411" s="18"/>
     </row>
     <row r="412" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A412" s="13">
-        <v>17005</v>
+        <v>17027</v>
       </c>
       <c r="B412" s="14" t="s">
-        <v>1323</v>
-      </c>
-      <c r="C412" s="15"/>
-      <c r="D412" s="15"/>
-      <c r="E412" s="24" t="s">
-        <v>1324</v>
-      </c>
-      <c r="F412" s="15"/>
-      <c r="G412" s="16"/>
-      <c r="H412" s="17"/>
-      <c r="I412" s="18"/>
-      <c r="J412" s="23"/>
+        <v>1307</v>
+      </c>
+      <c r="C412" s="15" t="s">
+        <v>1308</v>
+      </c>
+      <c r="D412" s="15">
+        <v>1838</v>
+      </c>
+      <c r="E412" s="12" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F412" s="15" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G412" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H412" s="23" t="s">
+        <v>1310</v>
+      </c>
+      <c r="I412" s="18" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J412" s="18" t="s">
+        <v>1312</v>
+      </c>
     </row>
     <row r="413" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A413" s="13">
-        <v>17006</v>
+        <v>17029</v>
       </c>
       <c r="B413" s="14" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C413" s="15"/>
-      <c r="D413" s="15"/>
-      <c r="E413" s="24" t="s">
-        <v>1326</v>
-      </c>
-      <c r="F413" s="15"/>
-      <c r="G413" s="16"/>
-      <c r="H413" s="17"/>
-      <c r="I413" s="18"/>
-      <c r="J413" s="23"/>
+        <v>1313</v>
+      </c>
+      <c r="C413" s="15" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D413" s="15">
+        <v>1839</v>
+      </c>
+      <c r="E413" s="12" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F413" s="15" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G413" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="H413" s="23" t="s">
+        <v>1317</v>
+      </c>
+      <c r="I413" s="18" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J413" s="18" t="s">
+        <v>1319</v>
+      </c>
     </row>
     <row r="414" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A414" s="13">
-        <v>17007</v>
+        <v>17032</v>
       </c>
       <c r="B414" s="14" t="s">
-        <v>1327</v>
-      </c>
-      <c r="C414" s="15"/>
-      <c r="D414" s="15"/>
-      <c r="E414" s="24" t="s">
-        <v>1328</v>
-      </c>
-      <c r="F414" s="15"/>
-      <c r="G414" s="16"/>
-      <c r="H414" s="17"/>
-      <c r="I414" s="18"/>
-      <c r="J414" s="23"/>
+        <v>1320</v>
+      </c>
+      <c r="C414" s="15" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D414" s="15">
+        <v>1843</v>
+      </c>
+      <c r="E414" s="12" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F414" s="15" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G414" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="H414" s="23" t="s">
+        <v>1323</v>
+      </c>
+      <c r="I414" s="18" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J414" s="18" t="s">
+        <v>1324</v>
+      </c>
     </row>
     <row r="415" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A415" s="13">
-        <v>17008</v>
+        <v>17033</v>
       </c>
       <c r="B415" s="14" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C415" s="15" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D415" s="15">
+        <v>1845</v>
+      </c>
+      <c r="E415" s="12" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F415" s="15" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G415" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="H415" s="23" t="s">
+        <v>1328</v>
+      </c>
+      <c r="I415" s="18" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J415" s="18" t="s">
         <v>1329</v>
       </c>
-      <c r="C415" s="15"/>
-      <c r="D415" s="15"/>
-      <c r="E415" s="24" t="s">
-        <v>1330</v>
-      </c>
-      <c r="F415" s="15"/>
-      <c r="G415" s="16"/>
-      <c r="H415" s="17"/>
-      <c r="I415" s="18"/>
-      <c r="J415" s="23"/>
     </row>
     <row r="416" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A416" s="13">
-        <v>17009</v>
+        <v>17034</v>
       </c>
       <c r="B416" s="14" t="s">
+        <v>1330</v>
+      </c>
+      <c r="C416" s="15" t="s">
         <v>1331</v>
       </c>
-      <c r="C416" s="15"/>
-      <c r="D416" s="15"/>
-      <c r="E416" s="24" t="s">
+      <c r="D416" s="16">
+        <v>1845</v>
+      </c>
+      <c r="E416" s="12" t="s">
         <v>1332</v>
       </c>
-      <c r="F416" s="15"/>
-      <c r="G416" s="16"/>
-      <c r="H416" s="17"/>
-      <c r="I416" s="18"/>
-      <c r="J416" s="23"/>
+      <c r="F416" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G416" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="H416" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="I416" s="18" t="s">
+        <v>1311</v>
+      </c>
+      <c r="J416" s="18"/>
     </row>
     <row r="417" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A417" s="13">
@@ -20665,7 +20665,7 @@
     </row>
     <row r="418" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A418" s="13">
-        <v>18010</v>
+        <v>18002</v>
       </c>
       <c r="B418" s="14" t="s">
         <v>1335</v>
@@ -20683,7 +20683,7 @@
     </row>
     <row r="419" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A419" s="13">
-        <v>18011</v>
+        <v>18003</v>
       </c>
       <c r="B419" s="14" t="s">
         <v>1337</v>
@@ -20691,7 +20691,7 @@
       <c r="C419" s="15"/>
       <c r="D419" s="16"/>
       <c r="E419" s="24" t="s">
-        <v>1338</v>
+        <v>1334</v>
       </c>
       <c r="F419" s="15"/>
       <c r="G419" s="16"/>
@@ -20701,15 +20701,15 @@
     </row>
     <row r="420" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A420" s="13">
-        <v>18012</v>
+        <v>18004</v>
       </c>
       <c r="B420" s="14" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="C420" s="15"/>
       <c r="D420" s="16"/>
       <c r="E420" s="24" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="F420" s="15"/>
       <c r="G420" s="16"/>
@@ -20719,15 +20719,15 @@
     </row>
     <row r="421" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A421" s="13">
-        <v>18013</v>
+        <v>18005</v>
       </c>
       <c r="B421" s="14" t="s">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C421" s="15"/>
       <c r="D421" s="16"/>
       <c r="E421" s="24" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="F421" s="15"/>
       <c r="G421" s="16"/>
@@ -20737,15 +20737,15 @@
     </row>
     <row r="422" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A422" s="13">
-        <v>18014</v>
+        <v>18006</v>
       </c>
       <c r="B422" s="14" t="s">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="C422" s="15"/>
       <c r="D422" s="16"/>
       <c r="E422" s="24" t="s">
-        <v>1344</v>
+        <v>1334</v>
       </c>
       <c r="F422" s="15"/>
       <c r="G422" s="16"/>
@@ -20755,15 +20755,15 @@
     </row>
     <row r="423" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A423" s="13">
-        <v>18015</v>
+        <v>18007</v>
       </c>
       <c r="B423" s="14" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="C423" s="15"/>
       <c r="D423" s="16"/>
       <c r="E423" s="24" t="s">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="F423" s="15"/>
       <c r="G423" s="16"/>
@@ -20773,15 +20773,15 @@
     </row>
     <row r="424" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A424" s="13">
-        <v>18016</v>
+        <v>18008</v>
       </c>
       <c r="B424" s="14" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="C424" s="15"/>
       <c r="D424" s="16"/>
       <c r="E424" s="24" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="F424" s="15"/>
       <c r="G424" s="16"/>
@@ -20791,15 +20791,15 @@
     </row>
     <row r="425" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A425" s="13">
-        <v>18017</v>
+        <v>18009</v>
       </c>
       <c r="B425" s="14" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="C425" s="15"/>
       <c r="D425" s="16"/>
       <c r="E425" s="24" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="F425" s="15"/>
       <c r="G425" s="16"/>
@@ -20809,15 +20809,15 @@
     </row>
     <row r="426" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A426" s="13">
-        <v>18018</v>
+        <v>18010</v>
       </c>
       <c r="B426" s="14" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="C426" s="15"/>
       <c r="D426" s="16"/>
       <c r="E426" s="24" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="F426" s="15"/>
       <c r="G426" s="16"/>
@@ -20827,15 +20827,15 @@
     </row>
     <row r="427" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A427" s="13">
-        <v>18019</v>
+        <v>18011</v>
       </c>
       <c r="B427" s="14" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="C427" s="15"/>
       <c r="D427" s="16"/>
       <c r="E427" s="24" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="F427" s="15"/>
       <c r="G427" s="16"/>
@@ -20845,15 +20845,15 @@
     </row>
     <row r="428" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A428" s="13">
-        <v>18002</v>
+        <v>18012</v>
       </c>
       <c r="B428" s="14" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
       <c r="C428" s="15"/>
       <c r="D428" s="16"/>
       <c r="E428" s="24" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="F428" s="15"/>
       <c r="G428" s="16"/>
@@ -20863,623 +20863,623 @@
     </row>
     <row r="429" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A429" s="13">
-        <v>18020</v>
+        <v>18013</v>
       </c>
       <c r="B429" s="14" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C429" s="15" t="s">
-        <v>1356</v>
-      </c>
-      <c r="D429" s="15">
-        <v>1825</v>
-      </c>
-      <c r="E429" s="12"/>
-      <c r="F429" s="15" t="s">
-        <v>1357</v>
-      </c>
-      <c r="G429" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H429" s="23" t="s">
-        <v>1358</v>
-      </c>
-      <c r="I429" s="18" t="s">
-        <v>1359</v>
-      </c>
+        <v>1353</v>
+      </c>
+      <c r="C429" s="15"/>
+      <c r="D429" s="16"/>
+      <c r="E429" s="24" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F429" s="15"/>
+      <c r="G429" s="16"/>
+      <c r="H429" s="17"/>
+      <c r="I429" s="18"/>
       <c r="J429" s="18"/>
     </row>
     <row r="430" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A430" s="13">
-        <v>18021</v>
+        <v>18014</v>
       </c>
       <c r="B430" s="14" t="s">
-        <v>1360</v>
-      </c>
-      <c r="C430" s="15" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D430" s="15" t="s">
-        <v>1362</v>
-      </c>
-      <c r="E430" s="12" t="s">
-        <v>1363</v>
-      </c>
-      <c r="F430" s="15" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G430" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H430" s="23" t="s">
-        <v>1365</v>
-      </c>
-      <c r="I430" s="18" t="s">
-        <v>1366</v>
-      </c>
-      <c r="J430" s="18" t="s">
-        <v>1367</v>
-      </c>
+        <v>1355</v>
+      </c>
+      <c r="C430" s="15"/>
+      <c r="D430" s="16"/>
+      <c r="E430" s="24" t="s">
+        <v>1356</v>
+      </c>
+      <c r="F430" s="15"/>
+      <c r="G430" s="16"/>
+      <c r="H430" s="17"/>
+      <c r="I430" s="18"/>
+      <c r="J430" s="18"/>
     </row>
     <row r="431" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A431" s="13">
-        <v>18022</v>
+        <v>18015</v>
       </c>
       <c r="B431" s="14" t="s">
-        <v>1368</v>
-      </c>
-      <c r="C431" s="15" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D431" s="15">
-        <v>1827</v>
-      </c>
-      <c r="E431" s="12" t="s">
-        <v>1370</v>
-      </c>
-      <c r="F431" s="15" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G431" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H431" s="23" t="s">
-        <v>1371</v>
-      </c>
-      <c r="I431" s="18" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J431" s="18" t="s">
-        <v>1373</v>
-      </c>
+        <v>1357</v>
+      </c>
+      <c r="C431" s="15"/>
+      <c r="D431" s="16"/>
+      <c r="E431" s="24" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F431" s="15"/>
+      <c r="G431" s="16"/>
+      <c r="H431" s="17"/>
+      <c r="I431" s="18"/>
+      <c r="J431" s="18"/>
     </row>
     <row r="432" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A432" s="13">
-        <v>18023</v>
+        <v>18016</v>
       </c>
       <c r="B432" s="14" t="s">
-        <v>1374</v>
-      </c>
-      <c r="C432" s="15" t="s">
-        <v>1375</v>
-      </c>
-      <c r="D432" s="15">
-        <v>1827</v>
-      </c>
-      <c r="E432" s="12" t="s">
-        <v>1376</v>
-      </c>
-      <c r="F432" s="15" t="s">
-        <v>1377</v>
-      </c>
-      <c r="G432" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H432" s="17" t="s">
-        <v>1378</v>
-      </c>
-      <c r="I432" s="23" t="s">
-        <v>1372</v>
-      </c>
+        <v>1358</v>
+      </c>
+      <c r="C432" s="15"/>
+      <c r="D432" s="16"/>
+      <c r="E432" s="24" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F432" s="15"/>
+      <c r="G432" s="16"/>
+      <c r="H432" s="17"/>
+      <c r="I432" s="18"/>
       <c r="J432" s="18"/>
     </row>
     <row r="433" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A433" s="13">
-        <v>18024</v>
+        <v>18017</v>
       </c>
       <c r="B433" s="14" t="s">
-        <v>1379</v>
+        <v>1360</v>
       </c>
       <c r="C433" s="15"/>
-      <c r="D433" s="15"/>
-      <c r="E433" s="22" t="s">
-        <v>1380</v>
+      <c r="D433" s="16"/>
+      <c r="E433" s="24" t="s">
+        <v>1336</v>
       </c>
       <c r="F433" s="15"/>
       <c r="G433" s="16"/>
       <c r="H433" s="17"/>
-      <c r="I433" s="23"/>
+      <c r="I433" s="18"/>
       <c r="J433" s="18"/>
     </row>
     <row r="434" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A434" s="13">
-        <v>18025</v>
+        <v>18018</v>
       </c>
       <c r="B434" s="14" t="s">
-        <v>1381</v>
-      </c>
-      <c r="C434" s="15" t="s">
-        <v>1382</v>
-      </c>
-      <c r="D434" s="15">
-        <v>1829</v>
-      </c>
-      <c r="E434" s="12" t="s">
-        <v>1383</v>
-      </c>
-      <c r="F434" s="15" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G434" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H434" s="23" t="s">
-        <v>1384</v>
-      </c>
-      <c r="I434" s="18" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J434" s="18" t="s">
-        <v>1385</v>
-      </c>
+        <v>1361</v>
+      </c>
+      <c r="C434" s="15"/>
+      <c r="D434" s="16"/>
+      <c r="E434" s="24" t="s">
+        <v>1362</v>
+      </c>
+      <c r="F434" s="15"/>
+      <c r="G434" s="16"/>
+      <c r="H434" s="17"/>
+      <c r="I434" s="18"/>
+      <c r="J434" s="18"/>
     </row>
     <row r="435" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A435" s="13">
-        <v>18026</v>
+        <v>18019</v>
       </c>
       <c r="B435" s="14" t="s">
-        <v>1386</v>
-      </c>
-      <c r="C435" s="15" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D435" s="15">
-        <v>1837</v>
-      </c>
-      <c r="E435" s="12" t="s">
-        <v>1388</v>
-      </c>
-      <c r="F435" s="15" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G435" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="H435" s="23" t="s">
-        <v>1389</v>
-      </c>
-      <c r="I435" s="18" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J435" s="18" t="s">
-        <v>1390</v>
-      </c>
+        <v>1363</v>
+      </c>
+      <c r="C435" s="15"/>
+      <c r="D435" s="16"/>
+      <c r="E435" s="24" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F435" s="15"/>
+      <c r="G435" s="16"/>
+      <c r="H435" s="17"/>
+      <c r="I435" s="18"/>
+      <c r="J435" s="18"/>
     </row>
     <row r="436" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A436" s="13">
-        <v>18027</v>
+        <v>18020</v>
       </c>
       <c r="B436" s="14" t="s">
-        <v>1391</v>
-      </c>
-      <c r="C436" s="15"/>
-      <c r="D436" s="15"/>
-      <c r="E436" s="24" t="s">
-        <v>1392</v>
-      </c>
-      <c r="F436" s="15"/>
-      <c r="G436" s="16"/>
-      <c r="H436" s="23"/>
-      <c r="I436" s="18"/>
+        <v>1365</v>
+      </c>
+      <c r="C436" s="15" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D436" s="15">
+        <v>1825</v>
+      </c>
+      <c r="E436" s="12"/>
+      <c r="F436" s="15" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G436" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="H436" s="23" t="s">
+        <v>1368</v>
+      </c>
+      <c r="I436" s="18" t="s">
+        <v>1369</v>
+      </c>
       <c r="J436" s="18"/>
     </row>
     <row r="437" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A437" s="13">
-        <v>18028</v>
+        <v>18021</v>
       </c>
       <c r="B437" s="14" t="s">
-        <v>1393</v>
+        <v>1370</v>
       </c>
       <c r="C437" s="15" t="s">
-        <v>1394</v>
-      </c>
-      <c r="D437" s="15">
-        <v>1838</v>
+        <v>1371</v>
+      </c>
+      <c r="D437" s="15" t="s">
+        <v>1372</v>
       </c>
       <c r="E437" s="12" t="s">
-        <v>1383</v>
+        <v>1373</v>
       </c>
       <c r="F437" s="15" t="s">
-        <v>1246</v>
+        <v>1374</v>
       </c>
       <c r="G437" s="16" t="s">
-        <v>249</v>
+        <v>21</v>
       </c>
       <c r="H437" s="23" t="s">
-        <v>1395</v>
+        <v>1375</v>
       </c>
       <c r="I437" s="18" t="s">
-        <v>1372</v>
+        <v>1376</v>
       </c>
       <c r="J437" s="18" t="s">
-        <v>1396</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="438" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A438" s="13">
-        <v>18029</v>
+        <v>18022</v>
       </c>
       <c r="B438" s="14" t="s">
-        <v>1397</v>
-      </c>
-      <c r="C438" s="15"/>
-      <c r="D438" s="15"/>
-      <c r="E438" s="24" t="s">
-        <v>1398</v>
-      </c>
-      <c r="F438" s="15"/>
-      <c r="G438" s="16"/>
-      <c r="H438" s="23"/>
-      <c r="I438" s="18"/>
-      <c r="J438" s="18"/>
+        <v>1378</v>
+      </c>
+      <c r="C438" s="15" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D438" s="15">
+        <v>1827</v>
+      </c>
+      <c r="E438" s="12" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F438" s="15" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G438" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H438" s="23" t="s">
+        <v>1381</v>
+      </c>
+      <c r="I438" s="18" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J438" s="18" t="s">
+        <v>1383</v>
+      </c>
     </row>
     <row r="439" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A439" s="13">
-        <v>18003</v>
+        <v>18023</v>
       </c>
       <c r="B439" s="14" t="s">
-        <v>1399</v>
-      </c>
-      <c r="C439" s="15"/>
-      <c r="D439" s="16"/>
-      <c r="E439" s="24" t="s">
-        <v>1334</v>
-      </c>
-      <c r="F439" s="15"/>
-      <c r="G439" s="16"/>
-      <c r="H439" s="17"/>
-      <c r="I439" s="18"/>
+        <v>1384</v>
+      </c>
+      <c r="C439" s="15" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D439" s="15">
+        <v>1827</v>
+      </c>
+      <c r="E439" s="12" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F439" s="15" t="s">
+        <v>1387</v>
+      </c>
+      <c r="G439" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="H439" s="17" t="s">
+        <v>1388</v>
+      </c>
+      <c r="I439" s="23" t="s">
+        <v>1382</v>
+      </c>
       <c r="J439" s="18"/>
     </row>
     <row r="440" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A440" s="13">
-        <v>18030</v>
+        <v>18024</v>
       </c>
       <c r="B440" s="14" t="s">
-        <v>1400</v>
-      </c>
-      <c r="C440" s="15" t="s">
-        <v>1401</v>
-      </c>
-      <c r="D440" s="15">
-        <v>1838</v>
-      </c>
-      <c r="E440" s="12" t="s">
-        <v>1402</v>
-      </c>
-      <c r="F440" s="15" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G440" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H440" s="23" t="s">
-        <v>1403</v>
-      </c>
-      <c r="I440" s="18" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J440" s="18" t="s">
-        <v>1404</v>
-      </c>
+        <v>1389</v>
+      </c>
+      <c r="C440" s="15"/>
+      <c r="D440" s="15"/>
+      <c r="E440" s="22" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F440" s="15"/>
+      <c r="G440" s="16"/>
+      <c r="H440" s="17"/>
+      <c r="I440" s="23"/>
+      <c r="J440" s="18"/>
     </row>
     <row r="441" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A441" s="13">
-        <v>18031</v>
+        <v>18025</v>
       </c>
       <c r="B441" s="14" t="s">
-        <v>1405</v>
-      </c>
-      <c r="C441" s="15"/>
-      <c r="D441" s="15"/>
-      <c r="E441" s="24" t="s">
-        <v>1406</v>
-      </c>
-      <c r="F441" s="15"/>
-      <c r="G441" s="16"/>
-      <c r="H441" s="23"/>
-      <c r="I441" s="18"/>
-      <c r="J441" s="18"/>
+        <v>1391</v>
+      </c>
+      <c r="C441" s="15" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D441" s="15">
+        <v>1829</v>
+      </c>
+      <c r="E441" s="12" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F441" s="15" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G441" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="H441" s="23" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I441" s="18" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J441" s="18" t="s">
+        <v>1395</v>
+      </c>
     </row>
     <row r="442" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A442" s="13">
-        <v>18032</v>
+        <v>18026</v>
       </c>
       <c r="B442" s="14" t="s">
-        <v>1407</v>
+        <v>1396</v>
       </c>
       <c r="C442" s="15" t="s">
-        <v>1408</v>
+        <v>1397</v>
       </c>
       <c r="D442" s="15">
-        <v>1843</v>
+        <v>1837</v>
       </c>
       <c r="E442" s="12" t="s">
-        <v>1409</v>
+        <v>1398</v>
       </c>
       <c r="F442" s="15" t="s">
-        <v>143</v>
+        <v>1262</v>
       </c>
       <c r="G442" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="H442" s="17" t="s">
-        <v>1410</v>
-      </c>
-      <c r="I442" s="23" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J442" s="18"/>
+      <c r="H442" s="23" t="s">
+        <v>1399</v>
+      </c>
+      <c r="I442" s="18" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J442" s="18" t="s">
+        <v>1400</v>
+      </c>
     </row>
     <row r="443" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A443" s="13">
-        <v>18033</v>
+        <v>18027</v>
       </c>
       <c r="B443" s="14" t="s">
-        <v>1411</v>
-      </c>
-      <c r="C443" s="15" t="s">
-        <v>1412</v>
-      </c>
-      <c r="D443" s="15">
-        <v>1845</v>
-      </c>
-      <c r="E443" s="12" t="s">
-        <v>1413</v>
-      </c>
-      <c r="F443" s="15" t="s">
-        <v>1364</v>
-      </c>
-      <c r="G443" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H443" s="23" t="s">
-        <v>1414</v>
-      </c>
-      <c r="I443" s="18" t="s">
-        <v>1366</v>
-      </c>
-      <c r="J443" s="18" t="s">
-        <v>1415</v>
-      </c>
+        <v>1401</v>
+      </c>
+      <c r="C443" s="15"/>
+      <c r="D443" s="15"/>
+      <c r="E443" s="24" t="s">
+        <v>1402</v>
+      </c>
+      <c r="F443" s="15"/>
+      <c r="G443" s="16"/>
+      <c r="H443" s="23"/>
+      <c r="I443" s="18"/>
+      <c r="J443" s="18"/>
     </row>
     <row r="444" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A444" s="13">
-        <v>18034</v>
+        <v>18028</v>
       </c>
       <c r="B444" s="14" t="s">
-        <v>1416</v>
+        <v>1403</v>
       </c>
       <c r="C444" s="15" t="s">
-        <v>1417</v>
+        <v>1404</v>
       </c>
       <c r="D444" s="15">
-        <v>1847</v>
+        <v>1838</v>
       </c>
       <c r="E444" s="12" t="s">
-        <v>186</v>
+        <v>1393</v>
       </c>
       <c r="F444" s="15" t="s">
-        <v>143</v>
+        <v>1262</v>
       </c>
       <c r="G444" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H444" s="17" t="s">
-        <v>1418</v>
-      </c>
-      <c r="I444" s="23" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J444" s="18"/>
+        <v>249</v>
+      </c>
+      <c r="H444" s="23" t="s">
+        <v>1405</v>
+      </c>
+      <c r="I444" s="18" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J444" s="18" t="s">
+        <v>1406</v>
+      </c>
     </row>
     <row r="445" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A445" s="13">
-        <v>18035</v>
+        <v>18029</v>
       </c>
       <c r="B445" s="14" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C445" s="15" t="s">
-        <v>1420</v>
-      </c>
-      <c r="D445" s="15">
-        <v>1847</v>
-      </c>
-      <c r="E445" s="12" t="s">
-        <v>1421</v>
-      </c>
-      <c r="F445" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G445" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="H445" s="17" t="s">
-        <v>1422</v>
-      </c>
-      <c r="I445" s="23" t="s">
-        <v>1372</v>
-      </c>
+        <v>1407</v>
+      </c>
+      <c r="C445" s="15"/>
+      <c r="D445" s="15"/>
+      <c r="E445" s="24" t="s">
+        <v>1408</v>
+      </c>
+      <c r="F445" s="15"/>
+      <c r="G445" s="16"/>
+      <c r="H445" s="23"/>
+      <c r="I445" s="18"/>
       <c r="J445" s="18"/>
     </row>
     <row r="446" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A446" s="13">
-        <v>18036</v>
+        <v>18030</v>
       </c>
       <c r="B446" s="14" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C446" s="15"/>
-      <c r="D446" s="15"/>
-      <c r="E446" s="24" t="s">
-        <v>1424</v>
-      </c>
-      <c r="F446" s="15"/>
-      <c r="G446" s="16"/>
-      <c r="H446" s="17"/>
-      <c r="I446" s="23"/>
-      <c r="J446" s="18"/>
+        <v>1409</v>
+      </c>
+      <c r="C446" s="15" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D446" s="15">
+        <v>1838</v>
+      </c>
+      <c r="E446" s="12" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F446" s="15" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G446" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="H446" s="23" t="s">
+        <v>1412</v>
+      </c>
+      <c r="I446" s="18" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J446" s="18" t="s">
+        <v>1413</v>
+      </c>
     </row>
     <row r="447" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A447" s="13">
-        <v>18037</v>
+        <v>18031</v>
       </c>
       <c r="B447" s="14" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C447" s="15" t="s">
-        <v>1426</v>
-      </c>
-      <c r="D447" s="15">
-        <v>1847</v>
-      </c>
-      <c r="E447" s="12" t="s">
-        <v>1259</v>
-      </c>
-      <c r="F447" s="15" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G447" s="16" t="s">
-        <v>1254</v>
-      </c>
-      <c r="H447" s="23" t="s">
-        <v>1427</v>
-      </c>
-      <c r="I447" s="18" t="s">
-        <v>1372</v>
-      </c>
-      <c r="J447" s="18" t="s">
-        <v>1428</v>
-      </c>
+        <v>1414</v>
+      </c>
+      <c r="C447" s="15"/>
+      <c r="D447" s="15"/>
+      <c r="E447" s="24" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F447" s="15"/>
+      <c r="G447" s="16"/>
+      <c r="H447" s="23"/>
+      <c r="I447" s="18"/>
+      <c r="J447" s="18"/>
     </row>
     <row r="448" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A448" s="13">
-        <v>18004</v>
+        <v>18032</v>
       </c>
       <c r="B448" s="14" t="s">
-        <v>1429</v>
-      </c>
-      <c r="C448" s="15"/>
-      <c r="D448" s="16"/>
-      <c r="E448" s="24" t="s">
-        <v>1334</v>
-      </c>
-      <c r="F448" s="15"/>
-      <c r="G448" s="16"/>
-      <c r="H448" s="17"/>
-      <c r="I448" s="18"/>
+        <v>1416</v>
+      </c>
+      <c r="C448" s="15" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D448" s="15">
+        <v>1843</v>
+      </c>
+      <c r="E448" s="12" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F448" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G448" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="H448" s="17" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I448" s="23" t="s">
+        <v>1382</v>
+      </c>
       <c r="J448" s="18"/>
     </row>
     <row r="449" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A449" s="13">
-        <v>18005</v>
+        <v>18033</v>
       </c>
       <c r="B449" s="14" t="s">
-        <v>1430</v>
-      </c>
-      <c r="C449" s="15"/>
-      <c r="D449" s="16"/>
-      <c r="E449" s="24" t="s">
-        <v>1431</v>
-      </c>
-      <c r="F449" s="15"/>
-      <c r="G449" s="16"/>
-      <c r="H449" s="17"/>
-      <c r="I449" s="18"/>
-      <c r="J449" s="18"/>
+        <v>1420</v>
+      </c>
+      <c r="C449" s="15" t="s">
+        <v>1421</v>
+      </c>
+      <c r="D449" s="15">
+        <v>1845</v>
+      </c>
+      <c r="E449" s="12" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F449" s="15" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G449" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H449" s="23" t="s">
+        <v>1423</v>
+      </c>
+      <c r="I449" s="18" t="s">
+        <v>1376</v>
+      </c>
+      <c r="J449" s="18" t="s">
+        <v>1424</v>
+      </c>
     </row>
     <row r="450" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A450" s="13">
-        <v>18006</v>
+        <v>18034</v>
       </c>
       <c r="B450" s="14" t="s">
-        <v>1432</v>
-      </c>
-      <c r="C450" s="15"/>
-      <c r="D450" s="16"/>
-      <c r="E450" s="24" t="s">
-        <v>1334</v>
-      </c>
-      <c r="F450" s="15"/>
-      <c r="G450" s="16"/>
-      <c r="H450" s="17"/>
-      <c r="I450" s="18"/>
+        <v>1425</v>
+      </c>
+      <c r="C450" s="15" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D450" s="15">
+        <v>1847</v>
+      </c>
+      <c r="E450" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="F450" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G450" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="H450" s="17" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I450" s="23" t="s">
+        <v>1382</v>
+      </c>
       <c r="J450" s="18"/>
     </row>
     <row r="451" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A451" s="13">
-        <v>18007</v>
+        <v>18035</v>
       </c>
       <c r="B451" s="14" t="s">
-        <v>1433</v>
-      </c>
-      <c r="C451" s="15"/>
-      <c r="D451" s="16"/>
-      <c r="E451" s="24" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C451" s="15" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D451" s="15">
+        <v>1847</v>
+      </c>
+      <c r="E451" s="12" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F451" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G451" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="H451" s="17" t="s">
         <v>1431</v>
       </c>
-      <c r="F451" s="15"/>
-      <c r="G451" s="16"/>
-      <c r="H451" s="17"/>
-      <c r="I451" s="18"/>
+      <c r="I451" s="23" t="s">
+        <v>1382</v>
+      </c>
       <c r="J451" s="18"/>
     </row>
     <row r="452" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A452" s="13">
-        <v>18008</v>
+        <v>18036</v>
       </c>
       <c r="B452" s="14" t="s">
-        <v>1434</v>
+        <v>1432</v>
       </c>
       <c r="C452" s="15"/>
-      <c r="D452" s="16"/>
+      <c r="D452" s="15"/>
       <c r="E452" s="24" t="s">
-        <v>1435</v>
+        <v>1433</v>
       </c>
       <c r="F452" s="15"/>
       <c r="G452" s="16"/>
       <c r="H452" s="17"/>
-      <c r="I452" s="18"/>
+      <c r="I452" s="23"/>
       <c r="J452" s="18"/>
     </row>
     <row r="453" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A453" s="13">
-        <v>18009</v>
+        <v>18037</v>
       </c>
       <c r="B453" s="14" t="s">
+        <v>1434</v>
+      </c>
+      <c r="C453" s="15" t="s">
+        <v>1435</v>
+      </c>
+      <c r="D453" s="15">
+        <v>1847</v>
+      </c>
+      <c r="E453" s="12" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F453" s="15" t="s">
+        <v>1262</v>
+      </c>
+      <c r="G453" s="16" t="s">
+        <v>1270</v>
+      </c>
+      <c r="H453" s="23" t="s">
         <v>1436</v>
       </c>
-      <c r="C453" s="15"/>
-      <c r="D453" s="16"/>
-      <c r="E453" s="24" t="s">
+      <c r="I453" s="18" t="s">
+        <v>1382</v>
+      </c>
+      <c r="J453" s="18" t="s">
         <v>1437</v>
       </c>
-      <c r="F453" s="15"/>
-      <c r="G453" s="16"/>
-      <c r="H453" s="17"/>
-      <c r="I453" s="18"/>
-      <c r="J453" s="18"/>
     </row>
     <row r="454" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A454" s="13">
@@ -21601,7 +21601,7 @@
     </row>
     <row r="460" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A460" s="13">
-        <v>21100</v>
+        <v>21030</v>
       </c>
       <c r="B460" s="14" t="s">
         <v>1452</v>
@@ -21610,48 +21610,52 @@
         <v>1453</v>
       </c>
       <c r="D460" s="15">
-        <v>1834</v>
+        <v>1821</v>
       </c>
       <c r="E460" s="12" t="s">
         <v>1454</v>
       </c>
       <c r="F460" s="15" t="s">
+        <v>1269</v>
+      </c>
+      <c r="G460" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="H460" s="23" t="s">
         <v>1455</v>
-      </c>
-      <c r="G460" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="H460" s="17" t="s">
-        <v>611</v>
       </c>
       <c r="I460" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J460" s="18"/>
+      <c r="J460" s="18" t="s">
+        <v>1457</v>
+      </c>
     </row>
     <row r="461" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A461" s="13">
-        <v>21101</v>
+        <v>21044</v>
       </c>
       <c r="B461" s="14" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C461" s="15" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D461" s="15">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E461" s="12" t="s">
-        <v>636</v>
+        <v>1460</v>
       </c>
       <c r="F461" s="15" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="G461" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="H461" s="17"/>
+        <v>508</v>
+      </c>
+      <c r="H461" s="17" t="s">
+        <v>192</v>
+      </c>
       <c r="I461" s="18" t="s">
         <v>1456</v>
       </c>
@@ -21659,27 +21663,29 @@
     </row>
     <row r="462" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A462" s="13">
-        <v>21102</v>
+        <v>21050</v>
       </c>
       <c r="B462" s="14" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="C462" s="15" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="D462" s="15">
-        <v>1845</v>
+        <v>1825</v>
       </c>
       <c r="E462" s="12" t="s">
-        <v>879</v>
+        <v>1463</v>
       </c>
       <c r="F462" s="15" t="s">
-        <v>204</v>
+        <v>1150</v>
       </c>
       <c r="G462" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H462" s="17"/>
+        <v>635</v>
+      </c>
+      <c r="H462" s="17" t="s">
+        <v>1464</v>
+      </c>
       <c r="I462" s="18" t="s">
         <v>1456</v>
       </c>
@@ -21687,55 +21693,61 @@
     </row>
     <row r="463" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A463" s="13">
-        <v>21103</v>
+        <v>21054</v>
       </c>
       <c r="B463" s="14" t="s">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="C463" s="15" t="s">
-        <v>1462</v>
+        <v>1466</v>
       </c>
       <c r="D463" s="15">
-        <v>1834</v>
+        <v>1826</v>
       </c>
       <c r="E463" s="12" t="s">
-        <v>1463</v>
+        <v>1467</v>
       </c>
       <c r="F463" s="15" t="s">
-        <v>204</v>
+        <v>1269</v>
       </c>
       <c r="G463" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H463" s="17"/>
+        <v>343</v>
+      </c>
+      <c r="H463" s="23" t="s">
+        <v>1468</v>
+      </c>
       <c r="I463" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J463" s="18"/>
+      <c r="J463" s="18" t="s">
+        <v>1469</v>
+      </c>
     </row>
     <row r="464" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A464" s="13">
-        <v>21104</v>
+        <v>21055</v>
       </c>
       <c r="B464" s="14" t="s">
-        <v>1464</v>
+        <v>1470</v>
       </c>
       <c r="C464" s="15" t="s">
-        <v>1465</v>
+        <v>1471</v>
       </c>
       <c r="D464" s="15">
-        <v>1834</v>
+        <v>1827</v>
       </c>
       <c r="E464" s="12" t="s">
-        <v>1466</v>
+        <v>1472</v>
       </c>
       <c r="F464" s="15" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="G464" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H464" s="17"/>
+        <v>21</v>
+      </c>
+      <c r="H464" s="17" t="s">
+        <v>439</v>
+      </c>
       <c r="I464" s="18" t="s">
         <v>1456</v>
       </c>
@@ -21743,79 +21755,85 @@
     </row>
     <row r="465" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A465" s="13">
-        <v>21105</v>
+        <v>21056</v>
       </c>
       <c r="B465" s="14" t="s">
-        <v>1467</v>
+        <v>1473</v>
       </c>
       <c r="C465" s="15" t="s">
-        <v>1468</v>
-      </c>
-      <c r="D465" s="15"/>
+        <v>1474</v>
+      </c>
+      <c r="D465" s="15">
+        <v>1827</v>
+      </c>
       <c r="E465" s="12" t="s">
-        <v>1469</v>
+        <v>1475</v>
       </c>
       <c r="F465" s="15" t="s">
-        <v>1377</v>
+        <v>143</v>
       </c>
       <c r="G465" s="16" t="s">
-        <v>191</v>
+        <v>262</v>
       </c>
       <c r="H465" s="17" t="s">
-        <v>1470</v>
-      </c>
-      <c r="I465" s="18"/>
+        <v>144</v>
+      </c>
+      <c r="I465" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J465" s="18"/>
     </row>
     <row r="466" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A466" s="13">
-        <v>21106</v>
+        <v>21058</v>
       </c>
       <c r="B466" s="14" t="s">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="C466" s="15" t="s">
-        <v>1472</v>
+        <v>1477</v>
       </c>
       <c r="D466" s="15"/>
       <c r="E466" s="12" t="s">
-        <v>1473</v>
-      </c>
-      <c r="F466" s="15" t="s">
-        <v>1377</v>
-      </c>
+        <v>1478</v>
+      </c>
+      <c r="F466" s="15"/>
       <c r="G466" s="16" t="s">
-        <v>1254</v>
+        <v>185</v>
       </c>
       <c r="H466" s="17" t="s">
-        <v>1474</v>
-      </c>
-      <c r="I466" s="18"/>
+        <v>1464</v>
+      </c>
+      <c r="I466" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J466" s="18"/>
     </row>
     <row r="467" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A467" s="13">
-        <v>21107</v>
+        <v>21059</v>
       </c>
       <c r="B467" s="14" t="s">
-        <v>1475</v>
+        <v>1479</v>
       </c>
       <c r="C467" s="15" t="s">
-        <v>1476</v>
+        <v>1480</v>
       </c>
       <c r="D467" s="15">
-        <v>1837</v>
+        <v>1827</v>
       </c>
       <c r="E467" s="12" t="s">
-        <v>1477</v>
+        <v>1481</v>
       </c>
       <c r="F467" s="15" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="G467" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H467" s="17"/>
+        <v>191</v>
+      </c>
+      <c r="H467" s="17" t="s">
+        <v>192</v>
+      </c>
       <c r="I467" s="18" t="s">
         <v>1456</v>
       </c>
@@ -21823,53 +21841,59 @@
     </row>
     <row r="468" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A468" s="13">
-        <v>21108</v>
+        <v>21060</v>
       </c>
       <c r="B468" s="14" t="s">
-        <v>1478</v>
+        <v>1482</v>
       </c>
       <c r="C468" s="15" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D468" s="15"/>
+        <v>1483</v>
+      </c>
+      <c r="D468" s="15">
+        <v>1827</v>
+      </c>
       <c r="E468" s="12" t="s">
-        <v>1480</v>
+        <v>1484</v>
       </c>
       <c r="F468" s="15" t="s">
-        <v>1377</v>
+        <v>143</v>
       </c>
       <c r="G468" s="16" t="s">
-        <v>878</v>
+        <v>21</v>
       </c>
       <c r="H468" s="17" t="s">
-        <v>1481</v>
-      </c>
-      <c r="I468" s="18"/>
+        <v>1485</v>
+      </c>
+      <c r="I468" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J468" s="18"/>
     </row>
     <row r="469" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A469" s="13">
-        <v>21109</v>
+        <v>21061</v>
       </c>
       <c r="B469" s="14" t="s">
-        <v>1482</v>
+        <v>1486</v>
       </c>
       <c r="C469" s="15" t="s">
-        <v>1483</v>
+        <v>1487</v>
       </c>
       <c r="D469" s="15">
-        <v>1839</v>
+        <v>1827</v>
       </c>
       <c r="E469" s="12" t="s">
-        <v>571</v>
+        <v>1488</v>
       </c>
       <c r="F469" s="15" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="G469" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H469" s="17"/>
+        <v>262</v>
+      </c>
+      <c r="H469" s="17" t="s">
+        <v>144</v>
+      </c>
       <c r="I469" s="18" t="s">
         <v>1456</v>
       </c>
@@ -21877,27 +21901,29 @@
     </row>
     <row r="470" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A470" s="13">
-        <v>21110</v>
+        <v>21062</v>
       </c>
       <c r="B470" s="14" t="s">
-        <v>1484</v>
+        <v>1489</v>
       </c>
       <c r="C470" s="15" t="s">
-        <v>1485</v>
+        <v>1490</v>
       </c>
       <c r="D470" s="15">
-        <v>1833</v>
+        <v>1827</v>
       </c>
       <c r="E470" s="12" t="s">
-        <v>1486</v>
+        <v>1491</v>
       </c>
       <c r="F470" s="15" t="s">
-        <v>204</v>
+        <v>143</v>
       </c>
       <c r="G470" s="16" t="s">
-        <v>635</v>
-      </c>
-      <c r="H470" s="17"/>
+        <v>343</v>
+      </c>
+      <c r="H470" s="17" t="s">
+        <v>522</v>
+      </c>
       <c r="I470" s="18" t="s">
         <v>1456</v>
       </c>
@@ -21905,115 +21931,100 @@
     </row>
     <row r="471" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A471" s="13">
-        <v>21111</v>
+        <v>21064</v>
       </c>
       <c r="B471" s="14" t="s">
-        <v>1487</v>
+        <v>1492</v>
       </c>
       <c r="C471" s="15" t="s">
-        <v>1488</v>
+        <v>1493</v>
       </c>
       <c r="D471" s="15">
-        <v>1835</v>
+        <v>1827</v>
       </c>
       <c r="E471" s="12" t="s">
-        <v>522</v>
+        <v>1494</v>
       </c>
       <c r="F471" s="15" t="s">
-        <v>204</v>
+        <v>1269</v>
       </c>
       <c r="G471" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H471" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="H471" s="23" t="s">
+        <v>1495</v>
+      </c>
       <c r="I471" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J471" s="18"/>
+      <c r="J471" s="18" t="s">
+        <v>1496</v>
+      </c>
     </row>
     <row r="472" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A472" s="13">
-        <v>21112</v>
+        <v>21065</v>
       </c>
       <c r="B472" s="14" t="s">
-        <v>1489</v>
-      </c>
-      <c r="C472" s="15" t="s">
-        <v>1490</v>
-      </c>
-      <c r="D472" s="15">
-        <v>1835</v>
-      </c>
-      <c r="E472" s="12" t="s">
-        <v>1491</v>
-      </c>
-      <c r="F472" s="15" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G472" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H472" s="17" t="s">
-        <v>1492</v>
-      </c>
-      <c r="I472" s="18" t="s">
-        <v>1456</v>
-      </c>
-      <c r="J472" s="18"/>
+        <v>1497</v>
+      </c>
+      <c r="C472" s="15"/>
+      <c r="D472" s="15"/>
+      <c r="E472" s="12"/>
+      <c r="F472" s="15"/>
+      <c r="G472" s="16"/>
     </row>
     <row r="473" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A473" s="13">
-        <v>21113</v>
+        <v>21066</v>
       </c>
       <c r="B473" s="14" t="s">
-        <v>1493</v>
+        <v>1498</v>
       </c>
       <c r="C473" s="15" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D473" s="15" t="s">
-        <v>1495</v>
-      </c>
+        <v>1499</v>
+      </c>
+      <c r="D473" s="15"/>
       <c r="E473" s="12" t="s">
-        <v>1496</v>
-      </c>
-      <c r="F473" s="15"/>
+        <v>1500</v>
+      </c>
+      <c r="F473" s="15" t="s">
+        <v>1387</v>
+      </c>
       <c r="G473" s="16" t="s">
-        <v>635</v>
+        <v>262</v>
       </c>
       <c r="H473" s="17" t="s">
-        <v>1497</v>
-      </c>
-      <c r="I473" s="18" t="s">
-        <v>1456</v>
-      </c>
-      <c r="J473" s="18" t="s">
-        <v>1498</v>
-      </c>
+        <v>1501</v>
+      </c>
+      <c r="I473" s="18"/>
+      <c r="J473" s="18"/>
     </row>
     <row r="474" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A474" s="13">
-        <v>21114</v>
+        <v>21067</v>
       </c>
       <c r="B474" s="14" t="s">
-        <v>1499</v>
+        <v>1502</v>
       </c>
       <c r="C474" s="15" t="s">
-        <v>1500</v>
+        <v>1503</v>
       </c>
       <c r="D474" s="15">
-        <v>1841</v>
+        <v>1824</v>
       </c>
       <c r="E474" s="12" t="s">
-        <v>395</v>
+        <v>1504</v>
       </c>
       <c r="F474" s="15" t="s">
-        <v>204</v>
+        <v>1150</v>
       </c>
       <c r="G474" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="H474" s="17"/>
+        <v>343</v>
+      </c>
+      <c r="H474" s="23" t="s">
+        <v>1505</v>
+      </c>
       <c r="I474" s="18" t="s">
         <v>1456</v>
       </c>
@@ -22021,56 +22032,58 @@
     </row>
     <row r="475" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A475" s="13">
-        <v>21115</v>
+        <v>21069</v>
       </c>
       <c r="B475" s="14" t="s">
-        <v>1501</v>
+        <v>1506</v>
       </c>
       <c r="C475" s="15" t="s">
-        <v>1502</v>
+        <v>1507</v>
       </c>
       <c r="D475" s="15">
-        <v>1837</v>
+        <v>1829</v>
       </c>
       <c r="E475" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="F475" s="15" t="s">
-        <v>204</v>
-      </c>
+        <v>1508</v>
+      </c>
+      <c r="F475" s="15"/>
       <c r="G475" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="H475" s="17"/>
+        <v>508</v>
+      </c>
+      <c r="H475" s="17" t="s">
+        <v>1464</v>
+      </c>
       <c r="I475" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J475" s="18"/>
+      <c r="J475" s="18" t="s">
+        <v>1509</v>
+      </c>
     </row>
     <row r="476" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A476" s="13">
-        <v>21116</v>
+        <v>21070</v>
       </c>
       <c r="B476" s="14" t="s">
-        <v>1503</v>
+        <v>1510</v>
       </c>
       <c r="C476" s="15" t="s">
-        <v>1504</v>
+        <v>1511</v>
       </c>
       <c r="D476" s="15">
-        <v>1837</v>
+        <v>1829</v>
       </c>
       <c r="E476" s="12" t="s">
-        <v>1505</v>
+        <v>1512</v>
       </c>
       <c r="F476" s="15" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="G476" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="H476" s="17" t="s">
-        <v>1507</v>
+        <v>349</v>
+      </c>
+      <c r="H476" s="23" t="s">
+        <v>1514</v>
       </c>
       <c r="I476" s="18" t="s">
         <v>1456</v>
@@ -22079,28 +22092,28 @@
     </row>
     <row r="477" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A477" s="13">
-        <v>21117</v>
+        <v>21071</v>
       </c>
       <c r="B477" s="14" t="s">
-        <v>1508</v>
+        <v>1515</v>
       </c>
       <c r="C477" s="15" t="s">
-        <v>1509</v>
+        <v>1516</v>
       </c>
       <c r="D477" s="15">
-        <v>1836</v>
+        <v>1829</v>
       </c>
       <c r="E477" s="12" t="s">
-        <v>1510</v>
+        <v>1517</v>
       </c>
       <c r="F477" s="15" t="s">
-        <v>1455</v>
+        <v>1150</v>
       </c>
       <c r="G477" s="16" t="s">
-        <v>1511</v>
+        <v>262</v>
       </c>
       <c r="H477" s="17" t="s">
-        <v>522</v>
+        <v>1518</v>
       </c>
       <c r="I477" s="18" t="s">
         <v>1456</v>
@@ -22109,27 +22122,29 @@
     </row>
     <row r="478" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A478" s="13">
-        <v>21119</v>
+        <v>21072</v>
       </c>
       <c r="B478" s="14" t="s">
-        <v>1512</v>
+        <v>1519</v>
       </c>
       <c r="C478" s="15" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D478" s="15">
+        <v>1829</v>
+      </c>
+      <c r="E478" s="12" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F478" s="15" t="s">
         <v>1513</v>
       </c>
-      <c r="D478" s="15">
-        <v>1836</v>
-      </c>
-      <c r="E478" s="12" t="s">
-        <v>1514</v>
-      </c>
-      <c r="F478" s="15" t="s">
-        <v>204</v>
-      </c>
       <c r="G478" s="16" t="s">
-        <v>878</v>
-      </c>
-      <c r="H478" s="17"/>
+        <v>343</v>
+      </c>
+      <c r="H478" s="23" t="s">
+        <v>144</v>
+      </c>
       <c r="I478" s="18" t="s">
         <v>1456</v>
       </c>
@@ -22137,19 +22152,19 @@
     </row>
     <row r="479" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A479" s="13">
-        <v>21120</v>
+        <v>21073</v>
       </c>
       <c r="B479" s="14" t="s">
-        <v>1515</v>
+        <v>1522</v>
       </c>
       <c r="C479" s="15" t="s">
-        <v>1516</v>
+        <v>1523</v>
       </c>
       <c r="D479" s="15">
-        <v>1837</v>
+        <v>1829</v>
       </c>
       <c r="E479" s="12" t="s">
-        <v>144</v>
+        <v>1524</v>
       </c>
       <c r="F479" s="15" t="s">
         <v>204</v>
@@ -22165,27 +22180,29 @@
     </row>
     <row r="480" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A480" s="13">
-        <v>21121</v>
+        <v>21074</v>
       </c>
       <c r="B480" s="14" t="s">
-        <v>1517</v>
+        <v>1525</v>
       </c>
       <c r="C480" s="15" t="s">
-        <v>1518</v>
+        <v>1526</v>
       </c>
       <c r="D480" s="15">
-        <v>1837</v>
+        <v>1827</v>
       </c>
       <c r="E480" s="12" t="s">
-        <v>439</v>
+        <v>1527</v>
       </c>
       <c r="F480" s="15" t="s">
-        <v>204</v>
+        <v>1513</v>
       </c>
       <c r="G480" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H480" s="17"/>
+        <v>343</v>
+      </c>
+      <c r="H480" s="23" t="s">
+        <v>1528</v>
+      </c>
       <c r="I480" s="18" t="s">
         <v>1456</v>
       </c>
@@ -22193,29 +22210,27 @@
     </row>
     <row r="481" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A481" s="13">
-        <v>21122</v>
+        <v>21077</v>
       </c>
       <c r="B481" s="14" t="s">
-        <v>1519</v>
+        <v>1529</v>
       </c>
       <c r="C481" s="15" t="s">
-        <v>1520</v>
-      </c>
-      <c r="D481" s="15" t="s">
-        <v>1521</v>
+        <v>1530</v>
+      </c>
+      <c r="D481" s="15">
+        <v>1834</v>
       </c>
       <c r="E481" s="12" t="s">
-        <v>1522</v>
+        <v>1188</v>
       </c>
       <c r="F481" s="15" t="s">
-        <v>1506</v>
+        <v>204</v>
       </c>
       <c r="G481" s="16" t="s">
-        <v>878</v>
-      </c>
-      <c r="H481" s="17" t="s">
-        <v>1523</v>
-      </c>
+        <v>1531</v>
+      </c>
+      <c r="H481" s="17"/>
       <c r="I481" s="18" t="s">
         <v>1456</v>
       </c>
@@ -22223,29 +22238,27 @@
     </row>
     <row r="482" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A482" s="13">
-        <v>21123</v>
+        <v>21078</v>
       </c>
       <c r="B482" s="14" t="s">
-        <v>1524</v>
+        <v>1532</v>
       </c>
       <c r="C482" s="15" t="s">
-        <v>1525</v>
+        <v>1533</v>
       </c>
       <c r="D482" s="15">
-        <v>1836</v>
+        <v>1830</v>
       </c>
       <c r="E482" s="12" t="s">
-        <v>1526</v>
+        <v>1534</v>
       </c>
       <c r="F482" s="15" t="s">
-        <v>1506</v>
+        <v>204</v>
       </c>
       <c r="G482" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="H482" s="17" t="s">
-        <v>636</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="H482" s="17"/>
       <c r="I482" s="18" t="s">
         <v>1456</v>
       </c>
@@ -22253,61 +22266,55 @@
     </row>
     <row r="483" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A483" s="13">
-        <v>21125</v>
+        <v>21080</v>
       </c>
       <c r="B483" s="14" t="s">
-        <v>1527</v>
+        <v>1535</v>
       </c>
       <c r="C483" s="15" t="s">
-        <v>1528</v>
+        <v>1536</v>
       </c>
       <c r="D483" s="15">
-        <v>1826</v>
+        <v>1829</v>
       </c>
       <c r="E483" s="12" t="s">
-        <v>1529</v>
+        <v>1501</v>
       </c>
       <c r="F483" s="15" t="s">
-        <v>1455</v>
+        <v>204</v>
       </c>
       <c r="G483" s="16" t="s">
-        <v>1254</v>
-      </c>
-      <c r="H483" s="17" t="s">
-        <v>815</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="H483" s="17"/>
       <c r="I483" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J483" s="18" t="s">
-        <v>1530</v>
-      </c>
+      <c r="J483" s="18"/>
     </row>
     <row r="484" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A484" s="13">
-        <v>21126</v>
+        <v>21086</v>
       </c>
       <c r="B484" s="14" t="s">
-        <v>1531</v>
+        <v>1537</v>
       </c>
       <c r="C484" s="15" t="s">
-        <v>1532</v>
-      </c>
-      <c r="D484" s="15" t="s">
-        <v>1533</v>
+        <v>1538</v>
+      </c>
+      <c r="D484" s="15">
+        <v>1829</v>
       </c>
       <c r="E484" s="12" t="s">
-        <v>1534</v>
+        <v>365</v>
       </c>
       <c r="F484" s="15" t="s">
-        <v>1506</v>
+        <v>204</v>
       </c>
       <c r="G484" s="16" t="s">
-        <v>1254</v>
-      </c>
-      <c r="H484" s="17" t="s">
-        <v>1535</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="H484" s="17"/>
       <c r="I484" s="18" t="s">
         <v>1456</v>
       </c>
@@ -22315,29 +22322,27 @@
     </row>
     <row r="485" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A485" s="13">
-        <v>21127</v>
+        <v>21089</v>
       </c>
       <c r="B485" s="14" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="C485" s="15" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
       <c r="D485" s="15">
-        <v>1836</v>
+        <v>1829</v>
       </c>
       <c r="E485" s="12" t="s">
-        <v>1538</v>
+        <v>1541</v>
       </c>
       <c r="F485" s="15" t="s">
-        <v>1506</v>
+        <v>204</v>
       </c>
       <c r="G485" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H485" s="17" t="s">
-        <v>192</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H485" s="17"/>
       <c r="I485" s="18" t="s">
         <v>1456</v>
       </c>
@@ -22345,84 +22350,82 @@
     </row>
     <row r="486" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A486" s="13">
-        <v>21128</v>
+        <v>21090</v>
       </c>
       <c r="B486" s="14" t="s">
-        <v>1539</v>
+        <v>1542</v>
       </c>
       <c r="C486" s="15" t="s">
-        <v>1540</v>
-      </c>
-      <c r="D486" s="15"/>
+        <v>1543</v>
+      </c>
+      <c r="D486" s="15">
+        <v>1830</v>
+      </c>
       <c r="E486" s="12" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="F486" s="15" t="s">
-        <v>1377</v>
+        <v>204</v>
       </c>
       <c r="G486" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H486" s="17" t="s">
-        <v>1542</v>
-      </c>
-      <c r="I486" s="18"/>
+        <v>635</v>
+      </c>
+      <c r="H486" s="17"/>
+      <c r="I486" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J486" s="18"/>
     </row>
     <row r="487" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A487" s="13">
-        <v>21129</v>
+        <v>21091</v>
       </c>
       <c r="B487" s="14" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="C487" s="15" t="s">
-        <v>1544</v>
-      </c>
-      <c r="D487" s="15" t="s">
-        <v>1521</v>
-      </c>
+        <v>1546</v>
+      </c>
+      <c r="D487" s="15"/>
       <c r="E487" s="12" t="s">
-        <v>1538</v>
+        <v>1547</v>
       </c>
       <c r="F487" s="15" t="s">
-        <v>1506</v>
+        <v>1387</v>
       </c>
       <c r="G487" s="16" t="s">
-        <v>191</v>
+        <v>508</v>
       </c>
       <c r="H487" s="17" t="s">
-        <v>1545</v>
-      </c>
-      <c r="I487" s="18" t="s">
-        <v>1456</v>
-      </c>
+        <v>1548</v>
+      </c>
+      <c r="I487" s="18"/>
       <c r="J487" s="18"/>
     </row>
     <row r="488" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A488" s="13">
-        <v>21131</v>
+        <v>21092</v>
       </c>
       <c r="B488" s="14" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
       <c r="C488" s="15" t="s">
-        <v>1547</v>
-      </c>
-      <c r="D488" s="15" t="s">
-        <v>1521</v>
+        <v>1550</v>
+      </c>
+      <c r="D488" s="15">
+        <v>1833</v>
       </c>
       <c r="E488" s="12" t="s">
-        <v>1526</v>
+        <v>1551</v>
       </c>
       <c r="F488" s="15" t="s">
-        <v>1506</v>
+        <v>1513</v>
       </c>
       <c r="G488" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="H488" s="17" t="s">
-        <v>1548</v>
+        <v>635</v>
+      </c>
+      <c r="H488" s="23" t="s">
+        <v>1552</v>
       </c>
       <c r="I488" s="18" t="s">
         <v>1456</v>
@@ -22431,88 +22434,67 @@
     </row>
     <row r="489" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A489" s="13">
-        <v>21132</v>
+        <v>21093</v>
       </c>
       <c r="B489" s="14" t="s">
-        <v>1549</v>
+        <v>1553</v>
       </c>
       <c r="C489" s="15" t="s">
-        <v>1550</v>
-      </c>
-      <c r="D489" s="15">
-        <v>1836</v>
-      </c>
+        <v>1554</v>
+      </c>
+      <c r="D489" s="15"/>
       <c r="E489" s="12" t="s">
-        <v>1551</v>
-      </c>
-      <c r="F489" s="15" t="s">
-        <v>1506</v>
-      </c>
+        <v>1555</v>
+      </c>
+      <c r="F489" s="15"/>
       <c r="G489" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="H489" s="17" t="s">
-        <v>1552</v>
-      </c>
-      <c r="I489" s="18" t="s">
-        <v>1456</v>
-      </c>
-      <c r="J489" s="18"/>
     </row>
     <row r="490" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A490" s="13">
-        <v>21134</v>
+        <v>21094</v>
       </c>
       <c r="B490" s="14" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="C490" s="15" t="s">
-        <v>1554</v>
-      </c>
-      <c r="D490" s="15">
-        <v>1837</v>
-      </c>
-      <c r="E490" s="12" t="s">
-        <v>1555</v>
-      </c>
-      <c r="F490" s="15" t="s">
-        <v>204</v>
-      </c>
+        <v>1557</v>
+      </c>
+      <c r="D490" s="15"/>
+      <c r="E490" s="12"/>
+      <c r="F490" s="15"/>
       <c r="G490" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="H490" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="I490" s="18" t="s">
-        <v>1456</v>
-      </c>
-      <c r="J490" s="18"/>
+        <v>167</v>
+      </c>
+      <c r="H490" s="12" t="s">
+        <v>815</v>
+      </c>
     </row>
     <row r="491" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A491" s="13">
-        <v>21135</v>
+        <v>21095</v>
       </c>
       <c r="B491" s="14" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="C491" s="15" t="s">
-        <v>1557</v>
-      </c>
-      <c r="D491" s="15" t="s">
-        <v>1521</v>
+        <v>1559</v>
+      </c>
+      <c r="D491" s="15">
+        <v>1833</v>
       </c>
       <c r="E491" s="12" t="s">
-        <v>1551</v>
+        <v>1560</v>
       </c>
       <c r="F491" s="15" t="s">
-        <v>1506</v>
+        <v>1150</v>
       </c>
       <c r="G491" s="16" t="s">
-        <v>70</v>
+        <v>1531</v>
       </c>
       <c r="H491" s="17" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="I491" s="18" t="s">
         <v>1456</v>
@@ -22521,43 +22503,53 @@
     </row>
     <row r="492" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A492" s="13">
-        <v>21136</v>
+        <v>21096</v>
       </c>
       <c r="B492" s="14" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
       <c r="C492" s="15" t="s">
-        <v>1560</v>
-      </c>
-      <c r="D492" s="15"/>
-      <c r="E492" s="12"/>
-      <c r="F492" s="15"/>
-      <c r="G492" s="16"/>
+        <v>1563</v>
+      </c>
+      <c r="D492" s="15">
+        <v>1833</v>
+      </c>
+      <c r="E492" s="12" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F492" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G492" s="16" t="s">
+        <v>191</v>
+      </c>
       <c r="H492" s="17"/>
-      <c r="I492" s="12"/>
+      <c r="I492" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J492" s="18"/>
     </row>
     <row r="493" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A493" s="13">
-        <v>21137</v>
+        <v>21097</v>
       </c>
       <c r="B493" s="14" t="s">
-        <v>1561</v>
+        <v>1565</v>
       </c>
       <c r="C493" s="15" t="s">
-        <v>1562</v>
+        <v>1566</v>
       </c>
       <c r="D493" s="15">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="E493" s="12" t="s">
-        <v>1563</v>
+        <v>1567</v>
       </c>
       <c r="F493" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G493" s="16" t="s">
-        <v>349</v>
+        <v>508</v>
       </c>
       <c r="H493" s="17"/>
       <c r="I493" s="18" t="s">
@@ -22567,28 +22559,28 @@
     </row>
     <row r="494" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A494" s="13">
-        <v>21139</v>
+        <v>21098</v>
       </c>
       <c r="B494" s="14" t="s">
-        <v>1564</v>
+        <v>1568</v>
       </c>
       <c r="C494" s="15" t="s">
-        <v>1565</v>
+        <v>1569</v>
       </c>
       <c r="D494" s="15">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="E494" s="12" t="s">
-        <v>1566</v>
+        <v>1570</v>
       </c>
       <c r="F494" s="15" t="s">
         <v>1150</v>
       </c>
       <c r="G494" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H494" s="23" t="s">
-        <v>1567</v>
+        <v>349</v>
+      </c>
+      <c r="H494" s="17" t="s">
+        <v>1571</v>
       </c>
       <c r="I494" s="18" t="s">
         <v>1456</v>
@@ -22597,73 +22589,83 @@
     </row>
     <row r="495" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A495" s="13">
-        <v>21141</v>
+        <v>21100</v>
       </c>
       <c r="B495" s="14" t="s">
-        <v>1568</v>
+        <v>1572</v>
       </c>
       <c r="C495" s="15" t="s">
-        <v>1569</v>
-      </c>
-      <c r="D495" s="15"/>
-      <c r="E495" s="12"/>
-      <c r="F495" s="15"/>
-      <c r="G495" s="16"/>
-      <c r="H495" s="17"/>
-      <c r="I495" s="12"/>
+        <v>1573</v>
+      </c>
+      <c r="D495" s="15">
+        <v>1834</v>
+      </c>
+      <c r="E495" s="12" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F495" s="15" t="s">
+        <v>1575</v>
+      </c>
+      <c r="G495" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="H495" s="17" t="s">
+        <v>611</v>
+      </c>
+      <c r="I495" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J495" s="18"/>
     </row>
     <row r="496" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A496" s="13">
-        <v>21142</v>
+        <v>21101</v>
       </c>
       <c r="B496" s="14" t="s">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="C496" s="15" t="s">
-        <v>1571</v>
+        <v>1577</v>
       </c>
       <c r="D496" s="15">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="E496" s="12" t="s">
-        <v>1572</v>
+        <v>636</v>
       </c>
       <c r="F496" s="15" t="s">
-        <v>1455</v>
+        <v>204</v>
       </c>
       <c r="G496" s="16" t="s">
         <v>349</v>
       </c>
-      <c r="H496" s="17" t="s">
-        <v>192</v>
-      </c>
+      <c r="H496" s="17"/>
       <c r="I496" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J496" s="18"/>
     </row>
-    <row r="497" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="497" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A497" s="13">
-        <v>21143</v>
+        <v>21102</v>
       </c>
       <c r="B497" s="14" t="s">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="C497" s="15" t="s">
-        <v>1574</v>
+        <v>1579</v>
       </c>
       <c r="D497" s="15">
-        <v>1839</v>
+        <v>1845</v>
       </c>
       <c r="E497" s="12" t="s">
-        <v>365</v>
+        <v>879</v>
       </c>
       <c r="F497" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G497" s="16" t="s">
-        <v>878</v>
+        <v>70</v>
       </c>
       <c r="H497" s="17"/>
       <c r="I497" s="18" t="s">
@@ -22671,27 +22673,27 @@
       </c>
       <c r="J497" s="18"/>
     </row>
-    <row r="498" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="498" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A498" s="13">
-        <v>21144</v>
+        <v>21103</v>
       </c>
       <c r="B498" s="14" t="s">
-        <v>1575</v>
+        <v>1580</v>
       </c>
       <c r="C498" s="15" t="s">
-        <v>1576</v>
+        <v>1581</v>
       </c>
       <c r="D498" s="15">
-        <v>1839</v>
+        <v>1834</v>
       </c>
       <c r="E498" s="12" t="s">
-        <v>815</v>
+        <v>1501</v>
       </c>
       <c r="F498" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G498" s="16" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="H498" s="17"/>
       <c r="I498" s="18" t="s">
@@ -22699,27 +22701,27 @@
       </c>
       <c r="J498" s="18"/>
     </row>
-    <row r="499" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="499" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A499" s="13">
-        <v>21145</v>
+        <v>21104</v>
       </c>
       <c r="B499" s="14" t="s">
-        <v>1577</v>
+        <v>1582</v>
       </c>
       <c r="C499" s="15" t="s">
-        <v>1578</v>
+        <v>1583</v>
       </c>
       <c r="D499" s="15">
-        <v>1845</v>
+        <v>1834</v>
       </c>
       <c r="E499" s="12" t="s">
-        <v>1422</v>
+        <v>1584</v>
       </c>
       <c r="F499" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G499" s="16" t="s">
-        <v>635</v>
+        <v>343</v>
       </c>
       <c r="H499" s="17"/>
       <c r="I499" s="18" t="s">
@@ -22727,83 +22729,79 @@
       </c>
       <c r="J499" s="18"/>
     </row>
-    <row r="500" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="500" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A500" s="13">
-        <v>21150</v>
+        <v>21105</v>
       </c>
       <c r="B500" s="14" t="s">
-        <v>1579</v>
+        <v>1585</v>
       </c>
       <c r="C500" s="15" t="s">
-        <v>1580</v>
-      </c>
-      <c r="D500" s="15">
-        <v>1834</v>
-      </c>
+        <v>1586</v>
+      </c>
+      <c r="D500" s="15"/>
       <c r="E500" s="12" t="s">
-        <v>1463</v>
+        <v>1587</v>
       </c>
       <c r="F500" s="15" t="s">
-        <v>204</v>
+        <v>1387</v>
       </c>
       <c r="G500" s="16" t="s">
-        <v>433</v>
-      </c>
-      <c r="H500" s="17"/>
-      <c r="I500" s="18" t="s">
-        <v>1456</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="H500" s="17" t="s">
+        <v>1588</v>
+      </c>
+      <c r="I500" s="18"/>
       <c r="J500" s="18"/>
     </row>
-    <row r="501" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="501" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A501" s="13">
-        <v>21151</v>
+        <v>21106</v>
       </c>
       <c r="B501" s="14" t="s">
-        <v>1581</v>
+        <v>1589</v>
       </c>
       <c r="C501" s="15" t="s">
-        <v>1582</v>
-      </c>
-      <c r="D501" s="15">
-        <v>1842</v>
-      </c>
+        <v>1590</v>
+      </c>
+      <c r="D501" s="15"/>
       <c r="E501" s="12" t="s">
-        <v>1583</v>
+        <v>1591</v>
       </c>
       <c r="F501" s="15" t="s">
-        <v>204</v>
+        <v>1387</v>
       </c>
       <c r="G501" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="H501" s="17"/>
-      <c r="I501" s="18" t="s">
-        <v>1456</v>
-      </c>
+        <v>1270</v>
+      </c>
+      <c r="H501" s="17" t="s">
+        <v>1592</v>
+      </c>
+      <c r="I501" s="18"/>
       <c r="J501" s="18"/>
     </row>
-    <row r="502" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="502" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A502" s="13">
-        <v>21152</v>
+        <v>21107</v>
       </c>
       <c r="B502" s="14" t="s">
-        <v>1584</v>
+        <v>1593</v>
       </c>
       <c r="C502" s="15" t="s">
-        <v>1585</v>
+        <v>1594</v>
       </c>
       <c r="D502" s="15">
-        <v>1845</v>
+        <v>1837</v>
       </c>
       <c r="E502" s="12" t="s">
-        <v>1586</v>
+        <v>1595</v>
       </c>
       <c r="F502" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G502" s="16" t="s">
-        <v>167</v>
+        <v>343</v>
       </c>
       <c r="H502" s="17"/>
       <c r="I502" s="18" t="s">
@@ -22811,55 +22809,53 @@
       </c>
       <c r="J502" s="18"/>
     </row>
-    <row r="503" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="503" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A503" s="13">
-        <v>21153</v>
+        <v>21108</v>
       </c>
       <c r="B503" s="14" t="s">
-        <v>1587</v>
+        <v>1596</v>
       </c>
       <c r="C503" s="15" t="s">
-        <v>1588</v>
-      </c>
-      <c r="D503" s="15">
-        <v>1841</v>
-      </c>
+        <v>1597</v>
+      </c>
+      <c r="D503" s="15"/>
       <c r="E503" s="12" t="s">
-        <v>1589</v>
+        <v>1598</v>
       </c>
       <c r="F503" s="15" t="s">
-        <v>204</v>
+        <v>1387</v>
       </c>
       <c r="G503" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="H503" s="17"/>
-      <c r="I503" s="18" t="s">
-        <v>1456</v>
-      </c>
+        <v>878</v>
+      </c>
+      <c r="H503" s="17" t="s">
+        <v>1599</v>
+      </c>
+      <c r="I503" s="18"/>
       <c r="J503" s="18"/>
     </row>
-    <row r="504" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="504" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A504" s="13">
-        <v>21154</v>
+        <v>21109</v>
       </c>
       <c r="B504" s="14" t="s">
-        <v>1590</v>
+        <v>1600</v>
       </c>
       <c r="C504" s="15" t="s">
-        <v>1591</v>
+        <v>1601</v>
       </c>
       <c r="D504" s="15">
-        <v>1841</v>
+        <v>1839</v>
       </c>
       <c r="E504" s="12" t="s">
-        <v>973</v>
+        <v>571</v>
       </c>
       <c r="F504" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G504" s="16" t="s">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="H504" s="17"/>
       <c r="I504" s="18" t="s">
@@ -22867,27 +22863,27 @@
       </c>
       <c r="J504" s="18"/>
     </row>
-    <row r="505" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="505" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A505" s="13">
-        <v>21155</v>
+        <v>21110</v>
       </c>
       <c r="B505" s="14" t="s">
-        <v>1592</v>
+        <v>1602</v>
       </c>
       <c r="C505" s="15" t="s">
-        <v>1593</v>
+        <v>1603</v>
       </c>
       <c r="D505" s="15">
-        <v>1841</v>
+        <v>1833</v>
       </c>
       <c r="E505" s="12" t="s">
-        <v>1594</v>
+        <v>1604</v>
       </c>
       <c r="F505" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G505" s="16" t="s">
-        <v>70</v>
+        <v>635</v>
       </c>
       <c r="H505" s="17"/>
       <c r="I505" s="18" t="s">
@@ -22895,125 +22891,143 @@
       </c>
       <c r="J505" s="18"/>
     </row>
-    <row r="506" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="506" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A506" s="13">
-        <v>21156</v>
+        <v>21111</v>
       </c>
       <c r="B506" s="14" t="s">
-        <v>1595</v>
+        <v>1605</v>
       </c>
       <c r="C506" s="15" t="s">
-        <v>1596</v>
+        <v>1606</v>
       </c>
       <c r="D506" s="15">
-        <v>1841</v>
+        <v>1835</v>
       </c>
       <c r="E506" s="12" t="s">
-        <v>1597</v>
-      </c>
-      <c r="F506" s="15"/>
-      <c r="G506" s="16"/>
+        <v>522</v>
+      </c>
+      <c r="F506" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G506" s="16" t="s">
+        <v>249</v>
+      </c>
       <c r="H506" s="17"/>
       <c r="I506" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J506" s="18"/>
     </row>
-    <row r="507" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="507" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A507" s="13">
-        <v>21157</v>
+        <v>21112</v>
       </c>
       <c r="B507" s="14" t="s">
-        <v>1598</v>
+        <v>1607</v>
       </c>
       <c r="C507" s="15" t="s">
-        <v>1599</v>
-      </c>
-      <c r="D507" s="15"/>
-      <c r="E507" s="12"/>
-      <c r="F507" s="15"/>
-      <c r="G507" s="16"/>
-    </row>
-    <row r="508" s="12" customFormat="1" customHeight="1" spans="1:11">
+        <v>1608</v>
+      </c>
+      <c r="D507" s="15">
+        <v>1835</v>
+      </c>
+      <c r="E507" s="12" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F507" s="15" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G507" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="H507" s="17" t="s">
+        <v>1610</v>
+      </c>
+      <c r="I507" s="18" t="s">
+        <v>1456</v>
+      </c>
+      <c r="J507" s="18"/>
+    </row>
+    <row r="508" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A508" s="13">
-        <v>21158</v>
+        <v>21113</v>
       </c>
       <c r="B508" s="14" t="s">
-        <v>1600</v>
+        <v>1611</v>
       </c>
       <c r="C508" s="15" t="s">
-        <v>1601</v>
-      </c>
-      <c r="D508" s="15">
-        <v>1841</v>
+        <v>1612</v>
+      </c>
+      <c r="D508" s="15" t="s">
+        <v>1613</v>
       </c>
       <c r="E508" s="12" t="s">
-        <v>1602</v>
+        <v>1614</v>
       </c>
       <c r="F508" s="15"/>
       <c r="G508" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H508" s="23" t="s">
-        <v>1603</v>
+        <v>635</v>
+      </c>
+      <c r="H508" s="17" t="s">
+        <v>1615</v>
       </c>
       <c r="I508" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J508" s="18"/>
-    </row>
-    <row r="509" s="12" customFormat="1" customHeight="1" spans="1:11">
+      <c r="J508" s="18" t="s">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="509" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A509" s="13">
-        <v>21159</v>
+        <v>21114</v>
       </c>
       <c r="B509" s="14" t="s">
-        <v>1604</v>
+        <v>1617</v>
       </c>
       <c r="C509" s="15" t="s">
-        <v>1605</v>
+        <v>1618</v>
       </c>
       <c r="D509" s="15">
         <v>1841</v>
       </c>
       <c r="E509" s="12" t="s">
-        <v>1602</v>
-      </c>
-      <c r="F509" s="15"/>
+        <v>395</v>
+      </c>
+      <c r="F509" s="15" t="s">
+        <v>204</v>
+      </c>
       <c r="G509" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H509" s="23" t="s">
-        <v>1606</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="H509" s="17"/>
       <c r="I509" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J509" s="18"/>
-      <c r="K509" s="17" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="510" s="12" customFormat="1" customHeight="1" spans="1:11">
+    </row>
+    <row r="510" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A510" s="13">
-        <v>21161</v>
+        <v>21115</v>
       </c>
       <c r="B510" s="14" t="s">
-        <v>1608</v>
+        <v>1619</v>
       </c>
       <c r="C510" s="15" t="s">
-        <v>1609</v>
+        <v>1620</v>
       </c>
       <c r="D510" s="15">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="E510" s="12" t="s">
-        <v>1610</v>
+        <v>571</v>
       </c>
       <c r="F510" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G510" s="16" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="H510" s="17"/>
       <c r="I510" s="18" t="s">
@@ -23021,57 +23035,61 @@
       </c>
       <c r="J510" s="18"/>
     </row>
-    <row r="511" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="511" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A511" s="13">
-        <v>21162</v>
+        <v>21116</v>
       </c>
       <c r="B511" s="14" t="s">
-        <v>1611</v>
+        <v>1621</v>
       </c>
       <c r="C511" s="15" t="s">
-        <v>1612</v>
+        <v>1622</v>
       </c>
       <c r="D511" s="15">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="E511" s="12" t="s">
-        <v>1613</v>
+        <v>1623</v>
       </c>
       <c r="F511" s="15" t="s">
-        <v>204</v>
+        <v>1624</v>
       </c>
       <c r="G511" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="H511" s="17"/>
+      <c r="H511" s="17" t="s">
+        <v>1625</v>
+      </c>
       <c r="I511" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J511" s="18"/>
     </row>
-    <row r="512" s="12" customFormat="1" customHeight="1" spans="1:11">
+    <row r="512" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A512" s="13">
-        <v>21164</v>
+        <v>21117</v>
       </c>
       <c r="B512" s="14" t="s">
-        <v>1614</v>
+        <v>1626</v>
       </c>
       <c r="C512" s="15" t="s">
-        <v>1615</v>
+        <v>1627</v>
       </c>
       <c r="D512" s="15">
-        <v>1842</v>
+        <v>1836</v>
       </c>
       <c r="E512" s="12" t="s">
-        <v>400</v>
+        <v>1628</v>
       </c>
       <c r="F512" s="15" t="s">
-        <v>143</v>
+        <v>1575</v>
       </c>
       <c r="G512" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H512" s="17"/>
+        <v>1531</v>
+      </c>
+      <c r="H512" s="17" t="s">
+        <v>522</v>
+      </c>
       <c r="I512" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23079,25 +23097,25 @@
     </row>
     <row r="513" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A513" s="13">
-        <v>21166</v>
+        <v>21119</v>
       </c>
       <c r="B513" s="14" t="s">
-        <v>1616</v>
+        <v>1629</v>
       </c>
       <c r="C513" s="15" t="s">
-        <v>1617</v>
+        <v>1630</v>
       </c>
       <c r="D513" s="15">
-        <v>1842</v>
+        <v>1836</v>
       </c>
       <c r="E513" s="12" t="s">
-        <v>434</v>
+        <v>1631</v>
       </c>
       <c r="F513" s="15" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="G513" s="16" t="s">
-        <v>167</v>
+        <v>878</v>
       </c>
       <c r="H513" s="17"/>
       <c r="I513" s="18" t="s">
@@ -23107,25 +23125,25 @@
     </row>
     <row r="514" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A514" s="13">
-        <v>21168</v>
+        <v>21120</v>
       </c>
       <c r="B514" s="14" t="s">
-        <v>1618</v>
+        <v>1632</v>
       </c>
       <c r="C514" s="15" t="s">
-        <v>1619</v>
+        <v>1633</v>
       </c>
       <c r="D514" s="15">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="E514" s="12" t="s">
-        <v>1206</v>
+        <v>144</v>
       </c>
       <c r="F514" s="15" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="G514" s="16" t="s">
-        <v>433</v>
+        <v>21</v>
       </c>
       <c r="H514" s="17"/>
       <c r="I514" s="18" t="s">
@@ -23135,25 +23153,25 @@
     </row>
     <row r="515" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A515" s="13">
-        <v>21169</v>
+        <v>21121</v>
       </c>
       <c r="B515" s="14" t="s">
-        <v>1620</v>
+        <v>1634</v>
       </c>
       <c r="C515" s="15" t="s">
-        <v>1621</v>
+        <v>1635</v>
       </c>
       <c r="D515" s="15">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="E515" s="12" t="s">
-        <v>365</v>
+        <v>439</v>
       </c>
       <c r="F515" s="15" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="G515" s="16" t="s">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="H515" s="17"/>
       <c r="I515" s="18" t="s">
@@ -23163,27 +23181,29 @@
     </row>
     <row r="516" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A516" s="13">
-        <v>21170</v>
+        <v>21122</v>
       </c>
       <c r="B516" s="14" t="s">
-        <v>1622</v>
+        <v>1636</v>
       </c>
       <c r="C516" s="15" t="s">
-        <v>1623</v>
-      </c>
-      <c r="D516" s="15">
-        <v>1842</v>
+        <v>1637</v>
+      </c>
+      <c r="D516" s="15" t="s">
+        <v>1638</v>
       </c>
       <c r="E516" s="12" t="s">
-        <v>186</v>
+        <v>1639</v>
       </c>
       <c r="F516" s="15" t="s">
-        <v>143</v>
+        <v>1624</v>
       </c>
       <c r="G516" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H516" s="17"/>
+        <v>878</v>
+      </c>
+      <c r="H516" s="17" t="s">
+        <v>1640</v>
+      </c>
       <c r="I516" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23191,27 +23211,29 @@
     </row>
     <row r="517" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A517" s="13">
-        <v>21171</v>
+        <v>21123</v>
       </c>
       <c r="B517" s="14" t="s">
+        <v>1641</v>
+      </c>
+      <c r="C517" s="15" t="s">
+        <v>1642</v>
+      </c>
+      <c r="D517" s="15">
+        <v>1836</v>
+      </c>
+      <c r="E517" s="12" t="s">
+        <v>1643</v>
+      </c>
+      <c r="F517" s="15" t="s">
         <v>1624</v>
       </c>
-      <c r="C517" s="15" t="s">
-        <v>1625</v>
-      </c>
-      <c r="D517" s="15">
-        <v>1842</v>
-      </c>
-      <c r="E517" s="12" t="s">
-        <v>571</v>
-      </c>
-      <c r="F517" s="15" t="s">
-        <v>143</v>
-      </c>
       <c r="G517" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H517" s="17"/>
+        <v>508</v>
+      </c>
+      <c r="H517" s="17" t="s">
+        <v>636</v>
+      </c>
       <c r="I517" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23219,55 +23241,61 @@
     </row>
     <row r="518" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A518" s="13">
-        <v>21172</v>
+        <v>21125</v>
       </c>
       <c r="B518" s="14" t="s">
-        <v>1626</v>
+        <v>1644</v>
       </c>
       <c r="C518" s="15" t="s">
-        <v>1627</v>
+        <v>1645</v>
       </c>
       <c r="D518" s="15">
-        <v>1845</v>
+        <v>1826</v>
       </c>
       <c r="E518" s="12" t="s">
-        <v>1628</v>
+        <v>1646</v>
       </c>
       <c r="F518" s="15" t="s">
-        <v>204</v>
+        <v>1575</v>
       </c>
       <c r="G518" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H518" s="17"/>
+        <v>1270</v>
+      </c>
+      <c r="H518" s="17" t="s">
+        <v>815</v>
+      </c>
       <c r="I518" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J518" s="18"/>
+      <c r="J518" s="18" t="s">
+        <v>1647</v>
+      </c>
     </row>
     <row r="519" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A519" s="13">
-        <v>21175</v>
+        <v>21126</v>
       </c>
       <c r="B519" s="14" t="s">
-        <v>1629</v>
+        <v>1648</v>
       </c>
       <c r="C519" s="15" t="s">
-        <v>1630</v>
-      </c>
-      <c r="D519" s="15">
-        <v>1842</v>
+        <v>1649</v>
+      </c>
+      <c r="D519" s="15" t="s">
+        <v>1650</v>
       </c>
       <c r="E519" s="12" t="s">
-        <v>1631</v>
+        <v>1651</v>
       </c>
       <c r="F519" s="15" t="s">
-        <v>204</v>
+        <v>1624</v>
       </c>
       <c r="G519" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H519" s="17"/>
+        <v>1270</v>
+      </c>
+      <c r="H519" s="17" t="s">
+        <v>1652</v>
+      </c>
       <c r="I519" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23275,27 +23303,29 @@
     </row>
     <row r="520" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A520" s="13">
-        <v>21177</v>
+        <v>21127</v>
       </c>
       <c r="B520" s="14" t="s">
-        <v>1632</v>
+        <v>1653</v>
       </c>
       <c r="C520" s="15" t="s">
-        <v>1633</v>
+        <v>1654</v>
       </c>
       <c r="D520" s="15">
-        <v>1843</v>
+        <v>1836</v>
       </c>
       <c r="E520" s="12" t="s">
-        <v>1634</v>
+        <v>1655</v>
       </c>
       <c r="F520" s="15" t="s">
-        <v>204</v>
+        <v>1624</v>
       </c>
       <c r="G520" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="H520" s="17"/>
+        <v>191</v>
+      </c>
+      <c r="H520" s="17" t="s">
+        <v>192</v>
+      </c>
       <c r="I520" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23303,55 +23333,55 @@
     </row>
     <row r="521" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A521" s="13">
-        <v>21180</v>
+        <v>21128</v>
       </c>
       <c r="B521" s="14" t="s">
-        <v>1635</v>
+        <v>1656</v>
       </c>
       <c r="C521" s="15" t="s">
-        <v>1636</v>
-      </c>
-      <c r="D521" s="15">
-        <v>1843</v>
-      </c>
+        <v>1657</v>
+      </c>
+      <c r="D521" s="15"/>
       <c r="E521" s="12" t="s">
-        <v>144</v>
+        <v>1658</v>
       </c>
       <c r="F521" s="15" t="s">
-        <v>204</v>
+        <v>1387</v>
       </c>
       <c r="G521" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="H521" s="17"/>
-      <c r="I521" s="18" t="s">
-        <v>1456</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H521" s="17" t="s">
+        <v>1548</v>
+      </c>
+      <c r="I521" s="18"/>
       <c r="J521" s="18"/>
     </row>
     <row r="522" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A522" s="13">
-        <v>21181</v>
+        <v>21129</v>
       </c>
       <c r="B522" s="14" t="s">
-        <v>1637</v>
+        <v>1659</v>
       </c>
       <c r="C522" s="15" t="s">
+        <v>1660</v>
+      </c>
+      <c r="D522" s="15" t="s">
         <v>1638</v>
       </c>
-      <c r="D522" s="15">
-        <v>1843</v>
-      </c>
       <c r="E522" s="12" t="s">
-        <v>1474</v>
+        <v>1655</v>
       </c>
       <c r="F522" s="15" t="s">
-        <v>204</v>
+        <v>1624</v>
       </c>
       <c r="G522" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H522" s="17"/>
+        <v>191</v>
+      </c>
+      <c r="H522" s="17" t="s">
+        <v>1661</v>
+      </c>
       <c r="I522" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23359,27 +23389,29 @@
     </row>
     <row r="523" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A523" s="13">
-        <v>21182</v>
+        <v>21131</v>
       </c>
       <c r="B523" s="14" t="s">
-        <v>1639</v>
+        <v>1662</v>
       </c>
       <c r="C523" s="15" t="s">
-        <v>1640</v>
-      </c>
-      <c r="D523" s="15">
-        <v>1845</v>
+        <v>1663</v>
+      </c>
+      <c r="D523" s="15" t="s">
+        <v>1638</v>
       </c>
       <c r="E523" s="12" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="F523" s="15" t="s">
-        <v>204</v>
+        <v>1624</v>
       </c>
       <c r="G523" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="H523" s="17"/>
+        <v>508</v>
+      </c>
+      <c r="H523" s="17" t="s">
+        <v>1664</v>
+      </c>
       <c r="I523" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23387,27 +23419,29 @@
     </row>
     <row r="524" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A524" s="13">
-        <v>21184</v>
+        <v>21132</v>
       </c>
       <c r="B524" s="14" t="s">
-        <v>1642</v>
+        <v>1665</v>
       </c>
       <c r="C524" s="15" t="s">
-        <v>1643</v>
+        <v>1666</v>
       </c>
       <c r="D524" s="15">
-        <v>1844</v>
+        <v>1836</v>
       </c>
       <c r="E524" s="12" t="s">
-        <v>1644</v>
+        <v>1667</v>
       </c>
       <c r="F524" s="15" t="s">
-        <v>204</v>
+        <v>1624</v>
       </c>
       <c r="G524" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="H524" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="H524" s="17" t="s">
+        <v>1668</v>
+      </c>
       <c r="I524" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23415,27 +23449,29 @@
     </row>
     <row r="525" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A525" s="13">
-        <v>21185</v>
+        <v>21134</v>
       </c>
       <c r="B525" s="14" t="s">
-        <v>1645</v>
+        <v>1669</v>
       </c>
       <c r="C525" s="15" t="s">
-        <v>1646</v>
+        <v>1670</v>
       </c>
       <c r="D525" s="15">
-        <v>1844</v>
+        <v>1837</v>
       </c>
       <c r="E525" s="12" t="s">
-        <v>1463</v>
+        <v>1671</v>
       </c>
       <c r="F525" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G525" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="H525" s="17"/>
+        <v>262</v>
+      </c>
+      <c r="H525" s="17" t="s">
+        <v>360</v>
+      </c>
       <c r="I525" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23443,27 +23479,29 @@
     </row>
     <row r="526" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A526" s="13">
-        <v>21188</v>
+        <v>21135</v>
       </c>
       <c r="B526" s="14" t="s">
-        <v>1647</v>
+        <v>1672</v>
       </c>
       <c r="C526" s="15" t="s">
-        <v>1648</v>
-      </c>
-      <c r="D526" s="15">
-        <v>1844</v>
+        <v>1673</v>
+      </c>
+      <c r="D526" s="15" t="s">
+        <v>1638</v>
       </c>
       <c r="E526" s="12" t="s">
-        <v>571</v>
+        <v>1667</v>
       </c>
       <c r="F526" s="15" t="s">
-        <v>204</v>
+        <v>1624</v>
       </c>
       <c r="G526" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H526" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="H526" s="17" t="s">
+        <v>1674</v>
+      </c>
       <c r="I526" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23471,53 +23509,43 @@
     </row>
     <row r="527" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A527" s="13">
-        <v>21190</v>
+        <v>21136</v>
       </c>
       <c r="B527" s="14" t="s">
-        <v>1649</v>
+        <v>1675</v>
       </c>
       <c r="C527" s="15" t="s">
-        <v>1650</v>
-      </c>
-      <c r="D527" s="15">
-        <v>1835</v>
-      </c>
-      <c r="E527" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="F527" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="G527" s="16" t="s">
-        <v>191</v>
-      </c>
+        <v>1676</v>
+      </c>
+      <c r="D527" s="15"/>
+      <c r="E527" s="12"/>
+      <c r="F527" s="15"/>
+      <c r="G527" s="16"/>
       <c r="H527" s="17"/>
-      <c r="I527" s="18" t="s">
-        <v>1456</v>
-      </c>
+      <c r="I527" s="12"/>
       <c r="J527" s="18"/>
     </row>
     <row r="528" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A528" s="13">
-        <v>21191</v>
+        <v>21137</v>
       </c>
       <c r="B528" s="14" t="s">
-        <v>1651</v>
+        <v>1677</v>
       </c>
       <c r="C528" s="15" t="s">
-        <v>1652</v>
+        <v>1678</v>
       </c>
       <c r="D528" s="15">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="E528" s="12" t="s">
-        <v>400</v>
+        <v>1679</v>
       </c>
       <c r="F528" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G528" s="16" t="s">
-        <v>21</v>
+        <v>349</v>
       </c>
       <c r="H528" s="17"/>
       <c r="I528" s="18" t="s">
@@ -23525,101 +23553,105 @@
       </c>
       <c r="J528" s="18"/>
     </row>
-    <row r="529" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="529" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A529" s="13">
-        <v>21192</v>
+        <v>21139</v>
       </c>
       <c r="B529" s="14" t="s">
-        <v>1653</v>
+        <v>1680</v>
       </c>
       <c r="C529" s="15" t="s">
-        <v>1654</v>
+        <v>1681</v>
       </c>
       <c r="D529" s="15">
-        <v>1845</v>
+        <v>1837</v>
       </c>
       <c r="E529" s="12" t="s">
-        <v>395</v>
+        <v>1682</v>
       </c>
       <c r="F529" s="15" t="s">
-        <v>204</v>
+        <v>1150</v>
       </c>
       <c r="G529" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H529" s="17"/>
+        <v>343</v>
+      </c>
+      <c r="H529" s="23" t="s">
+        <v>1683</v>
+      </c>
       <c r="I529" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J529" s="18"/>
     </row>
-    <row r="530" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="530" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A530" s="13">
-        <v>21193</v>
+        <v>21141</v>
       </c>
       <c r="B530" s="14" t="s">
-        <v>1655</v>
-      </c>
-      <c r="C530" s="15"/>
+        <v>1684</v>
+      </c>
+      <c r="C530" s="15" t="s">
+        <v>1685</v>
+      </c>
       <c r="D530" s="15"/>
-      <c r="E530" s="24" t="s">
-        <v>1656</v>
-      </c>
+      <c r="E530" s="12"/>
       <c r="F530" s="15"/>
       <c r="G530" s="16"/>
       <c r="H530" s="17"/>
-      <c r="I530" s="18"/>
+      <c r="I530" s="12"/>
       <c r="J530" s="18"/>
     </row>
-    <row r="531" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="531" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A531" s="13">
-        <v>21194</v>
+        <v>21142</v>
       </c>
       <c r="B531" s="14" t="s">
-        <v>1657</v>
+        <v>1686</v>
       </c>
       <c r="C531" s="15" t="s">
-        <v>1658</v>
+        <v>1687</v>
       </c>
       <c r="D531" s="15">
-        <v>1845</v>
+        <v>1838</v>
       </c>
       <c r="E531" s="12" t="s">
-        <v>1628</v>
+        <v>1688</v>
       </c>
       <c r="F531" s="15" t="s">
-        <v>204</v>
+        <v>1575</v>
       </c>
       <c r="G531" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H531" s="17"/>
+        <v>349</v>
+      </c>
+      <c r="H531" s="17" t="s">
+        <v>192</v>
+      </c>
       <c r="I531" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J531" s="18"/>
     </row>
-    <row r="532" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="532" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A532" s="13">
-        <v>21195</v>
+        <v>21143</v>
       </c>
       <c r="B532" s="14" t="s">
-        <v>1659</v>
+        <v>1689</v>
       </c>
       <c r="C532" s="15" t="s">
-        <v>1660</v>
+        <v>1690</v>
       </c>
       <c r="D532" s="15">
-        <v>1845</v>
+        <v>1839</v>
       </c>
       <c r="E532" s="12" t="s">
-        <v>522</v>
+        <v>365</v>
       </c>
       <c r="F532" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G532" s="16" t="s">
-        <v>185</v>
+        <v>878</v>
       </c>
       <c r="H532" s="17"/>
       <c r="I532" s="18" t="s">
@@ -23627,343 +23659,351 @@
       </c>
       <c r="J532" s="18"/>
     </row>
-    <row r="533" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="533" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A533" s="13">
-        <v>21196</v>
+        <v>21144</v>
       </c>
       <c r="B533" s="14" t="s">
-        <v>1661</v>
-      </c>
-      <c r="C533" s="15"/>
-      <c r="D533" s="15"/>
-      <c r="E533" s="22" t="s">
-        <v>1662</v>
-      </c>
-      <c r="F533" s="15"/>
-      <c r="G533" s="16"/>
+        <v>1691</v>
+      </c>
+      <c r="C533" s="15" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D533" s="15">
+        <v>1839</v>
+      </c>
+      <c r="E533" s="12" t="s">
+        <v>815</v>
+      </c>
+      <c r="F533" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G533" s="16" t="s">
+        <v>167</v>
+      </c>
       <c r="H533" s="17"/>
-      <c r="I533" s="18"/>
+      <c r="I533" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J533" s="18"/>
     </row>
-    <row r="534" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="534" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A534" s="13">
-        <v>21197</v>
+        <v>21145</v>
       </c>
       <c r="B534" s="14" t="s">
-        <v>1663</v>
-      </c>
-      <c r="C534" s="15"/>
-      <c r="D534" s="15"/>
-      <c r="E534" s="25" t="s">
-        <v>1664</v>
-      </c>
-      <c r="F534" s="15"/>
-      <c r="G534" s="16"/>
+        <v>1693</v>
+      </c>
+      <c r="C534" s="15" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D534" s="15">
+        <v>1845</v>
+      </c>
+      <c r="E534" s="12" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F534" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G534" s="16" t="s">
+        <v>635</v>
+      </c>
       <c r="H534" s="17"/>
-      <c r="I534" s="18"/>
+      <c r="I534" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J534" s="18"/>
     </row>
-    <row r="535" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="535" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A535" s="13">
-        <v>21198</v>
+        <v>21150</v>
       </c>
       <c r="B535" s="14" t="s">
-        <v>1665</v>
-      </c>
-      <c r="C535" s="15"/>
-      <c r="D535" s="15"/>
-      <c r="E535" s="24" t="s">
-        <v>1666</v>
-      </c>
-      <c r="F535" s="15"/>
-      <c r="G535" s="16"/>
+        <v>1695</v>
+      </c>
+      <c r="C535" s="15" t="s">
+        <v>1696</v>
+      </c>
+      <c r="D535" s="15">
+        <v>1834</v>
+      </c>
+      <c r="E535" s="12" t="s">
+        <v>1501</v>
+      </c>
+      <c r="F535" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G535" s="16" t="s">
+        <v>433</v>
+      </c>
       <c r="H535" s="17"/>
-      <c r="I535" s="18"/>
+      <c r="I535" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J535" s="18"/>
     </row>
-    <row r="536" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="536" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A536" s="13">
-        <v>21199</v>
+        <v>21151</v>
       </c>
       <c r="B536" s="14" t="s">
-        <v>1667</v>
-      </c>
-      <c r="C536" s="15"/>
-      <c r="D536" s="15"/>
-      <c r="E536" s="25" t="s">
-        <v>1668</v>
-      </c>
-      <c r="F536" s="15"/>
-      <c r="G536" s="16"/>
+        <v>1697</v>
+      </c>
+      <c r="C536" s="15" t="s">
+        <v>1698</v>
+      </c>
+      <c r="D536" s="15">
+        <v>1842</v>
+      </c>
+      <c r="E536" s="12" t="s">
+        <v>1699</v>
+      </c>
+      <c r="F536" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G536" s="16" t="s">
+        <v>349</v>
+      </c>
       <c r="H536" s="17"/>
-      <c r="I536" s="18"/>
+      <c r="I536" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J536" s="18"/>
     </row>
-    <row r="537" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="537" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A537" s="13">
-        <v>21030</v>
+        <v>21152</v>
       </c>
       <c r="B537" s="14" t="s">
-        <v>1669</v>
+        <v>1700</v>
       </c>
       <c r="C537" s="15" t="s">
-        <v>1670</v>
+        <v>1701</v>
       </c>
       <c r="D537" s="15">
-        <v>1821</v>
+        <v>1845</v>
       </c>
       <c r="E537" s="12" t="s">
-        <v>1671</v>
+        <v>1702</v>
       </c>
       <c r="F537" s="15" t="s">
-        <v>1253</v>
+        <v>204</v>
       </c>
       <c r="G537" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="H537" s="23" t="s">
-        <v>1672</v>
-      </c>
+      <c r="H537" s="17"/>
       <c r="I537" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J537" s="18" t="s">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="538" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J537" s="18"/>
+    </row>
+    <row r="538" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A538" s="13">
-        <v>21044</v>
+        <v>21153</v>
       </c>
       <c r="B538" s="14" t="s">
-        <v>1674</v>
+        <v>1703</v>
       </c>
       <c r="C538" s="15" t="s">
-        <v>1675</v>
+        <v>1704</v>
       </c>
       <c r="D538" s="15">
-        <v>1827</v>
+        <v>1841</v>
       </c>
       <c r="E538" s="12" t="s">
-        <v>1676</v>
+        <v>1705</v>
       </c>
       <c r="F538" s="15" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="G538" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="H538" s="17" t="s">
-        <v>192</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="H538" s="17"/>
       <c r="I538" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J538" s="18"/>
     </row>
-    <row r="539" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="539" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A539" s="13">
-        <v>21050</v>
+        <v>21154</v>
       </c>
       <c r="B539" s="14" t="s">
-        <v>1677</v>
+        <v>1706</v>
       </c>
       <c r="C539" s="15" t="s">
-        <v>1678</v>
+        <v>1707</v>
       </c>
       <c r="D539" s="15">
-        <v>1825</v>
+        <v>1841</v>
       </c>
       <c r="E539" s="12" t="s">
-        <v>1679</v>
+        <v>973</v>
       </c>
       <c r="F539" s="15" t="s">
-        <v>1150</v>
+        <v>204</v>
       </c>
       <c r="G539" s="16" t="s">
-        <v>635</v>
-      </c>
-      <c r="H539" s="17" t="s">
-        <v>1680</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H539" s="17"/>
       <c r="I539" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J539" s="18"/>
     </row>
-    <row r="540" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="540" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A540" s="13">
-        <v>21054</v>
+        <v>21155</v>
       </c>
       <c r="B540" s="14" t="s">
-        <v>1681</v>
+        <v>1708</v>
       </c>
       <c r="C540" s="15" t="s">
-        <v>1682</v>
+        <v>1709</v>
       </c>
       <c r="D540" s="15">
-        <v>1826</v>
+        <v>1841</v>
       </c>
       <c r="E540" s="12" t="s">
-        <v>1683</v>
+        <v>1710</v>
       </c>
       <c r="F540" s="15" t="s">
-        <v>1253</v>
+        <v>204</v>
       </c>
       <c r="G540" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H540" s="23" t="s">
-        <v>1684</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H540" s="17"/>
       <c r="I540" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J540" s="18" t="s">
-        <v>1685</v>
-      </c>
-    </row>
-    <row r="541" s="12" customFormat="1" customHeight="1" spans="1:10">
+      <c r="J540" s="18"/>
+    </row>
+    <row r="541" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A541" s="13">
-        <v>21055</v>
+        <v>21156</v>
       </c>
       <c r="B541" s="14" t="s">
-        <v>1686</v>
+        <v>1711</v>
       </c>
       <c r="C541" s="15" t="s">
-        <v>1687</v>
+        <v>1712</v>
       </c>
       <c r="D541" s="15">
-        <v>1827</v>
+        <v>1841</v>
       </c>
       <c r="E541" s="12" t="s">
-        <v>1688</v>
-      </c>
-      <c r="F541" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G541" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H541" s="17" t="s">
-        <v>439</v>
-      </c>
+        <v>1713</v>
+      </c>
+      <c r="F541" s="15"/>
+      <c r="G541" s="16"/>
+      <c r="H541" s="17"/>
       <c r="I541" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J541" s="18"/>
     </row>
-    <row r="542" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="542" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A542" s="13">
-        <v>21056</v>
+        <v>21157</v>
       </c>
       <c r="B542" s="14" t="s">
-        <v>1689</v>
+        <v>1714</v>
       </c>
       <c r="C542" s="15" t="s">
-        <v>1690</v>
-      </c>
-      <c r="D542" s="15">
-        <v>1827</v>
-      </c>
-      <c r="E542" s="12" t="s">
-        <v>1691</v>
-      </c>
-      <c r="F542" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="G542" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="H542" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="I542" s="18" t="s">
-        <v>1456</v>
-      </c>
-      <c r="J542" s="18"/>
-    </row>
-    <row r="543" s="12" customFormat="1" customHeight="1" spans="1:10">
+        <v>1715</v>
+      </c>
+      <c r="D542" s="15"/>
+      <c r="E542" s="12"/>
+      <c r="F542" s="15"/>
+      <c r="G542" s="16"/>
+    </row>
+    <row r="543" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A543" s="13">
-        <v>21058</v>
+        <v>21158</v>
       </c>
       <c r="B543" s="14" t="s">
-        <v>1692</v>
+        <v>1716</v>
       </c>
       <c r="C543" s="15" t="s">
-        <v>1693</v>
-      </c>
-      <c r="D543" s="15"/>
+        <v>1717</v>
+      </c>
+      <c r="D543" s="15">
+        <v>1841</v>
+      </c>
       <c r="E543" s="12" t="s">
-        <v>1694</v>
+        <v>1718</v>
       </c>
       <c r="F543" s="15"/>
       <c r="G543" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="H543" s="17" t="s">
-        <v>1680</v>
+        <v>249</v>
+      </c>
+      <c r="H543" s="23" t="s">
+        <v>1719</v>
       </c>
       <c r="I543" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J543" s="18"/>
     </row>
-    <row r="544" s="12" customFormat="1" customHeight="1" spans="1:10">
+    <row r="544" s="12" customFormat="1" customHeight="1" spans="1:11">
       <c r="A544" s="13">
-        <v>21059</v>
+        <v>21159</v>
       </c>
       <c r="B544" s="14" t="s">
-        <v>1695</v>
+        <v>1720</v>
       </c>
       <c r="C544" s="15" t="s">
-        <v>1696</v>
+        <v>1721</v>
       </c>
       <c r="D544" s="15">
-        <v>1827</v>
+        <v>1841</v>
       </c>
       <c r="E544" s="12" t="s">
-        <v>1697</v>
-      </c>
-      <c r="F544" s="15" t="s">
-        <v>143</v>
-      </c>
+        <v>1718</v>
+      </c>
+      <c r="F544" s="15"/>
       <c r="G544" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="H544" s="17" t="s">
-        <v>192</v>
+        <v>70</v>
+      </c>
+      <c r="H544" s="23" t="s">
+        <v>1722</v>
       </c>
       <c r="I544" s="18" t="s">
         <v>1456</v>
       </c>
       <c r="J544" s="18"/>
+      <c r="K544" s="17" t="s">
+        <v>1723</v>
+      </c>
     </row>
     <row r="545" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A545" s="13">
-        <v>21060</v>
+        <v>21161</v>
       </c>
       <c r="B545" s="14" t="s">
-        <v>1698</v>
+        <v>1724</v>
       </c>
       <c r="C545" s="15" t="s">
-        <v>1699</v>
+        <v>1725</v>
       </c>
       <c r="D545" s="15">
-        <v>1827</v>
+        <v>1842</v>
       </c>
       <c r="E545" s="12" t="s">
-        <v>1700</v>
+        <v>1726</v>
       </c>
       <c r="F545" s="15" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="G545" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H545" s="17" t="s">
-        <v>1701</v>
-      </c>
+      <c r="H545" s="17"/>
       <c r="I545" s="18" t="s">
         <v>1456</v>
       </c>
@@ -23971,29 +24011,27 @@
     </row>
     <row r="546" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A546" s="13">
-        <v>21061</v>
+        <v>21162</v>
       </c>
       <c r="B546" s="14" t="s">
-        <v>1702</v>
+        <v>1727</v>
       </c>
       <c r="C546" s="15" t="s">
-        <v>1703</v>
+        <v>1728</v>
       </c>
       <c r="D546" s="15">
-        <v>1827</v>
+        <v>1842</v>
       </c>
       <c r="E546" s="12" t="s">
-        <v>1704</v>
+        <v>1729</v>
       </c>
       <c r="F546" s="15" t="s">
-        <v>143</v>
+        <v>204</v>
       </c>
       <c r="G546" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="H546" s="17" t="s">
-        <v>144</v>
-      </c>
+      <c r="H546" s="17"/>
       <c r="I546" s="18" t="s">
         <v>1456</v>
       </c>
@@ -24001,29 +24039,27 @@
     </row>
     <row r="547" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A547" s="13">
-        <v>21062</v>
+        <v>21164</v>
       </c>
       <c r="B547" s="14" t="s">
-        <v>1705</v>
+        <v>1730</v>
       </c>
       <c r="C547" s="15" t="s">
-        <v>1706</v>
+        <v>1731</v>
       </c>
       <c r="D547" s="15">
-        <v>1827</v>
+        <v>1842</v>
       </c>
       <c r="E547" s="12" t="s">
-        <v>1707</v>
+        <v>400</v>
       </c>
       <c r="F547" s="15" t="s">
         <v>143</v>
       </c>
       <c r="G547" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H547" s="17" t="s">
-        <v>522</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="H547" s="17"/>
       <c r="I547" s="18" t="s">
         <v>1456</v>
       </c>
@@ -24031,100 +24067,111 @@
     </row>
     <row r="548" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A548" s="13">
-        <v>21064</v>
+        <v>21166</v>
       </c>
       <c r="B548" s="14" t="s">
-        <v>1708</v>
+        <v>1732</v>
       </c>
       <c r="C548" s="15" t="s">
-        <v>1709</v>
+        <v>1733</v>
       </c>
       <c r="D548" s="15">
-        <v>1827</v>
+        <v>1842</v>
       </c>
       <c r="E548" s="12" t="s">
-        <v>1710</v>
+        <v>434</v>
       </c>
       <c r="F548" s="15" t="s">
-        <v>1253</v>
+        <v>143</v>
       </c>
       <c r="G548" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="H548" s="23" t="s">
-        <v>1711</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="H548" s="17"/>
       <c r="I548" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J548" s="18" t="s">
-        <v>1712</v>
-      </c>
+      <c r="J548" s="18"/>
     </row>
     <row r="549" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A549" s="13">
-        <v>21065</v>
+        <v>21168</v>
       </c>
       <c r="B549" s="14" t="s">
-        <v>1713</v>
-      </c>
-      <c r="C549" s="15"/>
-      <c r="D549" s="15"/>
-      <c r="E549" s="12"/>
-      <c r="F549" s="15"/>
-      <c r="G549" s="16"/>
+        <v>1734</v>
+      </c>
+      <c r="C549" s="15" t="s">
+        <v>1735</v>
+      </c>
+      <c r="D549" s="15">
+        <v>1842</v>
+      </c>
+      <c r="E549" s="12" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F549" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G549" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="H549" s="17"/>
+      <c r="I549" s="18" t="s">
+        <v>1456</v>
+      </c>
+      <c r="J549" s="18"/>
     </row>
     <row r="550" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A550" s="13">
-        <v>21066</v>
+        <v>21169</v>
       </c>
       <c r="B550" s="14" t="s">
-        <v>1714</v>
+        <v>1736</v>
       </c>
       <c r="C550" s="15" t="s">
-        <v>1715</v>
-      </c>
-      <c r="D550" s="15"/>
+        <v>1737</v>
+      </c>
+      <c r="D550" s="15">
+        <v>1842</v>
+      </c>
       <c r="E550" s="12" t="s">
-        <v>1716</v>
+        <v>365</v>
       </c>
       <c r="F550" s="15" t="s">
-        <v>1377</v>
+        <v>143</v>
       </c>
       <c r="G550" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="H550" s="17" t="s">
-        <v>1463</v>
-      </c>
-      <c r="I550" s="18"/>
+        <v>191</v>
+      </c>
+      <c r="H550" s="17"/>
+      <c r="I550" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J550" s="18"/>
     </row>
     <row r="551" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A551" s="13">
-        <v>21067</v>
+        <v>21170</v>
       </c>
       <c r="B551" s="14" t="s">
-        <v>1717</v>
+        <v>1738</v>
       </c>
       <c r="C551" s="15" t="s">
-        <v>1718</v>
+        <v>1739</v>
       </c>
       <c r="D551" s="15">
-        <v>1824</v>
+        <v>1842</v>
       </c>
       <c r="E551" s="12" t="s">
-        <v>1719</v>
+        <v>186</v>
       </c>
       <c r="F551" s="15" t="s">
-        <v>1150</v>
+        <v>143</v>
       </c>
       <c r="G551" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H551" s="23" t="s">
-        <v>1720</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="H551" s="17"/>
       <c r="I551" s="18" t="s">
         <v>1456</v>
       </c>
@@ -24132,59 +24179,55 @@
     </row>
     <row r="552" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A552" s="13">
-        <v>21069</v>
+        <v>21171</v>
       </c>
       <c r="B552" s="14" t="s">
-        <v>1721</v>
+        <v>1740</v>
       </c>
       <c r="C552" s="15" t="s">
-        <v>1722</v>
+        <v>1741</v>
       </c>
       <c r="D552" s="15">
-        <v>1829</v>
+        <v>1842</v>
       </c>
       <c r="E552" s="12" t="s">
-        <v>1723</v>
-      </c>
-      <c r="F552" s="15"/>
+        <v>571</v>
+      </c>
+      <c r="F552" s="15" t="s">
+        <v>143</v>
+      </c>
       <c r="G552" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="H552" s="17" t="s">
-        <v>1680</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="H552" s="17"/>
       <c r="I552" s="18" t="s">
         <v>1456</v>
       </c>
-      <c r="J552" s="18" t="s">
-        <v>1724</v>
-      </c>
+      <c r="J552" s="18"/>
     </row>
     <row r="553" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A553" s="13">
-        <v>21070</v>
+        <v>21172</v>
       </c>
       <c r="B553" s="14" t="s">
-        <v>1725</v>
+        <v>1742</v>
       </c>
       <c r="C553" s="15" t="s">
-        <v>1726</v>
+        <v>1743</v>
       </c>
       <c r="D553" s="15">
-        <v>1829</v>
+        <v>1845</v>
       </c>
       <c r="E553" s="12" t="s">
-        <v>1727</v>
+        <v>1744</v>
       </c>
       <c r="F553" s="15" t="s">
-        <v>1728</v>
+        <v>204</v>
       </c>
       <c r="G553" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="H553" s="23" t="s">
-        <v>1729</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H553" s="17"/>
       <c r="I553" s="18" t="s">
         <v>1456</v>
       </c>
@@ -24192,29 +24235,27 @@
     </row>
     <row r="554" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A554" s="13">
-        <v>21071</v>
+        <v>21175</v>
       </c>
       <c r="B554" s="14" t="s">
-        <v>1730</v>
+        <v>1745</v>
       </c>
       <c r="C554" s="15" t="s">
-        <v>1731</v>
+        <v>1746</v>
       </c>
       <c r="D554" s="15">
-        <v>1829</v>
+        <v>1842</v>
       </c>
       <c r="E554" s="12" t="s">
-        <v>1732</v>
+        <v>1747</v>
       </c>
       <c r="F554" s="15" t="s">
-        <v>1150</v>
+        <v>204</v>
       </c>
       <c r="G554" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="H554" s="17" t="s">
-        <v>1733</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="H554" s="17"/>
       <c r="I554" s="18" t="s">
         <v>1456</v>
       </c>
@@ -24222,29 +24263,27 @@
     </row>
     <row r="555" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A555" s="13">
-        <v>21072</v>
+        <v>21177</v>
       </c>
       <c r="B555" s="14" t="s">
-        <v>1734</v>
+        <v>1748</v>
       </c>
       <c r="C555" s="15" t="s">
-        <v>1735</v>
+        <v>1749</v>
       </c>
       <c r="D555" s="15">
-        <v>1829</v>
+        <v>1843</v>
       </c>
       <c r="E555" s="12" t="s">
-        <v>1736</v>
+        <v>1750</v>
       </c>
       <c r="F555" s="15" t="s">
-        <v>1728</v>
+        <v>204</v>
       </c>
       <c r="G555" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H555" s="23" t="s">
-        <v>144</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="H555" s="17"/>
       <c r="I555" s="18" t="s">
         <v>1456</v>
       </c>
@@ -24252,25 +24291,25 @@
     </row>
     <row r="556" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A556" s="13">
-        <v>21073</v>
+        <v>21180</v>
       </c>
       <c r="B556" s="14" t="s">
-        <v>1737</v>
+        <v>1751</v>
       </c>
       <c r="C556" s="15" t="s">
-        <v>1738</v>
+        <v>1752</v>
       </c>
       <c r="D556" s="15">
-        <v>1829</v>
+        <v>1843</v>
       </c>
       <c r="E556" s="12" t="s">
-        <v>1644</v>
+        <v>144</v>
       </c>
       <c r="F556" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G556" s="16" t="s">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="H556" s="17"/>
       <c r="I556" s="18" t="s">
@@ -24280,29 +24319,27 @@
     </row>
     <row r="557" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A557" s="13">
-        <v>21074</v>
+        <v>21181</v>
       </c>
       <c r="B557" s="14" t="s">
-        <v>1739</v>
+        <v>1753</v>
       </c>
       <c r="C557" s="15" t="s">
-        <v>1740</v>
+        <v>1754</v>
       </c>
       <c r="D557" s="15">
-        <v>1827</v>
+        <v>1843</v>
       </c>
       <c r="E557" s="12" t="s">
-        <v>1741</v>
+        <v>1592</v>
       </c>
       <c r="F557" s="15" t="s">
-        <v>1728</v>
+        <v>204</v>
       </c>
       <c r="G557" s="16" t="s">
-        <v>343</v>
-      </c>
-      <c r="H557" s="23" t="s">
-        <v>1742</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="H557" s="17"/>
       <c r="I557" s="18" t="s">
         <v>1456</v>
       </c>
@@ -24310,25 +24347,25 @@
     </row>
     <row r="558" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A558" s="13">
-        <v>21077</v>
+        <v>21182</v>
       </c>
       <c r="B558" s="14" t="s">
-        <v>1743</v>
+        <v>1755</v>
       </c>
       <c r="C558" s="15" t="s">
-        <v>1744</v>
+        <v>1756</v>
       </c>
       <c r="D558" s="15">
-        <v>1834</v>
+        <v>1845</v>
       </c>
       <c r="E558" s="12" t="s">
-        <v>1219</v>
+        <v>1757</v>
       </c>
       <c r="F558" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G558" s="16" t="s">
-        <v>1511</v>
+        <v>185</v>
       </c>
       <c r="H558" s="17"/>
       <c r="I558" s="18" t="s">
@@ -24338,25 +24375,25 @@
     </row>
     <row r="559" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A559" s="13">
-        <v>21078</v>
+        <v>21184</v>
       </c>
       <c r="B559" s="14" t="s">
-        <v>1745</v>
+        <v>1758</v>
       </c>
       <c r="C559" s="15" t="s">
-        <v>1746</v>
+        <v>1759</v>
       </c>
       <c r="D559" s="15">
-        <v>1830</v>
+        <v>1844</v>
       </c>
       <c r="E559" s="12" t="s">
-        <v>1747</v>
+        <v>1524</v>
       </c>
       <c r="F559" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G559" s="16" t="s">
-        <v>167</v>
+        <v>508</v>
       </c>
       <c r="H559" s="17"/>
       <c r="I559" s="18" t="s">
@@ -24366,25 +24403,25 @@
     </row>
     <row r="560" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A560" s="13">
-        <v>21080</v>
+        <v>21185</v>
       </c>
       <c r="B560" s="14" t="s">
-        <v>1748</v>
+        <v>1760</v>
       </c>
       <c r="C560" s="15" t="s">
-        <v>1749</v>
+        <v>1761</v>
       </c>
       <c r="D560" s="15">
-        <v>1829</v>
+        <v>1844</v>
       </c>
       <c r="E560" s="12" t="s">
-        <v>1463</v>
+        <v>1501</v>
       </c>
       <c r="F560" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G560" s="16" t="s">
-        <v>349</v>
+        <v>63</v>
       </c>
       <c r="H560" s="17"/>
       <c r="I560" s="18" t="s">
@@ -24394,19 +24431,19 @@
     </row>
     <row r="561" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A561" s="13">
-        <v>21086</v>
+        <v>21188</v>
       </c>
       <c r="B561" s="14" t="s">
-        <v>1750</v>
+        <v>1762</v>
       </c>
       <c r="C561" s="15" t="s">
-        <v>1751</v>
+        <v>1763</v>
       </c>
       <c r="D561" s="15">
-        <v>1829</v>
+        <v>1844</v>
       </c>
       <c r="E561" s="12" t="s">
-        <v>365</v>
+        <v>571</v>
       </c>
       <c r="F561" s="15" t="s">
         <v>204</v>
@@ -24422,25 +24459,25 @@
     </row>
     <row r="562" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A562" s="13">
-        <v>21089</v>
+        <v>21190</v>
       </c>
       <c r="B562" s="14" t="s">
-        <v>1752</v>
+        <v>1764</v>
       </c>
       <c r="C562" s="15" t="s">
-        <v>1753</v>
+        <v>1765</v>
       </c>
       <c r="D562" s="15">
-        <v>1829</v>
+        <v>1835</v>
       </c>
       <c r="E562" s="12" t="s">
-        <v>1754</v>
+        <v>186</v>
       </c>
       <c r="F562" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G562" s="16" t="s">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="H562" s="17"/>
       <c r="I562" s="18" t="s">
@@ -24450,25 +24487,25 @@
     </row>
     <row r="563" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A563" s="13">
-        <v>21090</v>
+        <v>21191</v>
       </c>
       <c r="B563" s="14" t="s">
-        <v>1755</v>
+        <v>1766</v>
       </c>
       <c r="C563" s="15" t="s">
-        <v>1756</v>
+        <v>1767</v>
       </c>
       <c r="D563" s="15">
-        <v>1830</v>
+        <v>1835</v>
       </c>
       <c r="E563" s="12" t="s">
-        <v>1757</v>
+        <v>400</v>
       </c>
       <c r="F563" s="15" t="s">
         <v>204</v>
       </c>
       <c r="G563" s="16" t="s">
-        <v>635</v>
+        <v>21</v>
       </c>
       <c r="H563" s="17"/>
       <c r="I563" s="18" t="s">
@@ -24478,213 +24515,176 @@
     </row>
     <row r="564" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A564" s="13">
-        <v>21091</v>
+        <v>21192</v>
       </c>
       <c r="B564" s="14" t="s">
-        <v>1758</v>
+        <v>1768</v>
       </c>
       <c r="C564" s="15" t="s">
-        <v>1759</v>
-      </c>
-      <c r="D564" s="15"/>
+        <v>1769</v>
+      </c>
+      <c r="D564" s="15">
+        <v>1845</v>
+      </c>
       <c r="E564" s="12" t="s">
-        <v>1760</v>
+        <v>395</v>
       </c>
       <c r="F564" s="15" t="s">
-        <v>1377</v>
+        <v>204</v>
       </c>
       <c r="G564" s="16" t="s">
-        <v>508</v>
-      </c>
-      <c r="H564" s="17" t="s">
-        <v>1542</v>
-      </c>
-      <c r="I564" s="18"/>
+        <v>191</v>
+      </c>
+      <c r="H564" s="17"/>
+      <c r="I564" s="18" t="s">
+        <v>1456</v>
+      </c>
       <c r="J564" s="18"/>
     </row>
     <row r="565" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A565" s="13">
-        <v>21092</v>
+        <v>21193</v>
       </c>
       <c r="B565" s="14" t="s">
-        <v>1761</v>
-      </c>
-      <c r="C565" s="15" t="s">
-        <v>1762</v>
-      </c>
-      <c r="D565" s="15">
-        <v>1833</v>
-      </c>
-      <c r="E565" s="12" t="s">
-        <v>1763</v>
-      </c>
-      <c r="F565" s="15" t="s">
-        <v>1728</v>
-      </c>
-      <c r="G565" s="16" t="s">
-        <v>635</v>
-      </c>
-      <c r="H565" s="23" t="s">
-        <v>1764</v>
-      </c>
-      <c r="I565" s="18" t="s">
-        <v>1456</v>
-      </c>
+        <v>1770</v>
+      </c>
+      <c r="C565" s="15"/>
+      <c r="D565" s="15"/>
+      <c r="E565" s="24" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F565" s="15"/>
+      <c r="G565" s="16"/>
+      <c r="H565" s="17"/>
+      <c r="I565" s="18"/>
       <c r="J565" s="18"/>
     </row>
     <row r="566" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A566" s="13">
-        <v>21093</v>
+        <v>21194</v>
       </c>
       <c r="B566" s="14" t="s">
-        <v>1765</v>
+        <v>1772</v>
       </c>
       <c r="C566" s="15" t="s">
-        <v>1766</v>
-      </c>
-      <c r="D566" s="15"/>
+        <v>1773</v>
+      </c>
+      <c r="D566" s="15">
+        <v>1845</v>
+      </c>
       <c r="E566" s="12" t="s">
-        <v>1767</v>
-      </c>
-      <c r="F566" s="15"/>
+        <v>1744</v>
+      </c>
+      <c r="F566" s="15" t="s">
+        <v>204</v>
+      </c>
       <c r="G566" s="16" t="s">
-        <v>70</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="H566" s="17"/>
+      <c r="I566" s="18" t="s">
+        <v>1456</v>
+      </c>
+      <c r="J566" s="18"/>
     </row>
     <row r="567" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A567" s="13">
-        <v>21094</v>
+        <v>21195</v>
       </c>
       <c r="B567" s="14" t="s">
-        <v>1768</v>
+        <v>1774</v>
       </c>
       <c r="C567" s="15" t="s">
-        <v>1769</v>
-      </c>
-      <c r="D567" s="15"/>
-      <c r="E567" s="12"/>
-      <c r="F567" s="15"/>
+        <v>1775</v>
+      </c>
+      <c r="D567" s="15">
+        <v>1845</v>
+      </c>
+      <c r="E567" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="F567" s="15" t="s">
+        <v>204</v>
+      </c>
       <c r="G567" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="H567" s="12" t="s">
-        <v>815</v>
-      </c>
+        <v>185</v>
+      </c>
+      <c r="H567" s="17"/>
+      <c r="I567" s="18" t="s">
+        <v>1456</v>
+      </c>
+      <c r="J567" s="18"/>
     </row>
     <row r="568" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A568" s="13">
-        <v>21095</v>
+        <v>21196</v>
       </c>
       <c r="B568" s="14" t="s">
-        <v>1770</v>
-      </c>
-      <c r="C568" s="15" t="s">
-        <v>1771</v>
-      </c>
-      <c r="D568" s="15">
-        <v>1833</v>
-      </c>
-      <c r="E568" s="12" t="s">
-        <v>1772</v>
-      </c>
-      <c r="F568" s="15" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G568" s="16" t="s">
-        <v>1511</v>
-      </c>
-      <c r="H568" s="17" t="s">
-        <v>1773</v>
-      </c>
-      <c r="I568" s="18" t="s">
-        <v>1456</v>
-      </c>
+        <v>1776</v>
+      </c>
+      <c r="C568" s="15"/>
+      <c r="D568" s="15"/>
+      <c r="E568" s="22" t="s">
+        <v>1777</v>
+      </c>
+      <c r="F568" s="15"/>
+      <c r="G568" s="16"/>
+      <c r="H568" s="17"/>
+      <c r="I568" s="18"/>
       <c r="J568" s="18"/>
     </row>
     <row r="569" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A569" s="13">
-        <v>21096</v>
+        <v>21197</v>
       </c>
       <c r="B569" s="14" t="s">
-        <v>1774</v>
-      </c>
-      <c r="C569" s="15" t="s">
-        <v>1775</v>
-      </c>
-      <c r="D569" s="15">
-        <v>1833</v>
-      </c>
-      <c r="E569" s="12" t="s">
-        <v>1776</v>
-      </c>
-      <c r="F569" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="G569" s="16" t="s">
-        <v>191</v>
-      </c>
+        <v>1778</v>
+      </c>
+      <c r="C569" s="15"/>
+      <c r="D569" s="15"/>
+      <c r="E569" s="25" t="s">
+        <v>1779</v>
+      </c>
+      <c r="F569" s="15"/>
+      <c r="G569" s="16"/>
       <c r="H569" s="17"/>
-      <c r="I569" s="18" t="s">
-        <v>1456</v>
-      </c>
+      <c r="I569" s="18"/>
       <c r="J569" s="18"/>
     </row>
     <row r="570" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A570" s="13">
-        <v>21097</v>
+        <v>21198</v>
       </c>
       <c r="B570" s="14" t="s">
-        <v>1777</v>
-      </c>
-      <c r="C570" s="15" t="s">
-        <v>1778</v>
-      </c>
-      <c r="D570" s="15">
-        <v>1834</v>
-      </c>
-      <c r="E570" s="12" t="s">
-        <v>1779</v>
-      </c>
-      <c r="F570" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="G570" s="16" t="s">
-        <v>508</v>
-      </c>
+        <v>1780</v>
+      </c>
+      <c r="C570" s="15"/>
+      <c r="D570" s="15"/>
+      <c r="E570" s="24" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F570" s="15"/>
+      <c r="G570" s="16"/>
       <c r="H570" s="17"/>
-      <c r="I570" s="18" t="s">
-        <v>1456</v>
-      </c>
+      <c r="I570" s="18"/>
       <c r="J570" s="18"/>
     </row>
     <row r="571" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A571" s="13">
-        <v>21098</v>
+        <v>21199</v>
       </c>
       <c r="B571" s="14" t="s">
-        <v>1780</v>
-      </c>
-      <c r="C571" s="15" t="s">
-        <v>1781</v>
-      </c>
-      <c r="D571" s="15">
-        <v>1834</v>
-      </c>
-      <c r="E571" s="12" t="s">
         <v>1782</v>
       </c>
-      <c r="F571" s="15" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G571" s="16" t="s">
-        <v>349</v>
-      </c>
-      <c r="H571" s="17" t="s">
+      <c r="C571" s="15"/>
+      <c r="D571" s="15"/>
+      <c r="E571" s="25" t="s">
         <v>1783</v>
       </c>
-      <c r="I571" s="18" t="s">
-        <v>1456</v>
-      </c>
+      <c r="F571" s="15"/>
+      <c r="G571" s="16"/>
+      <c r="H571" s="17"/>
+      <c r="I571" s="18"/>
       <c r="J571" s="18"/>
     </row>
     <row r="572" s="12" customFormat="1" customHeight="1" spans="1:10">
@@ -24717,10 +24717,10 @@
       </c>
       <c r="D573" s="15"/>
       <c r="E573" s="12" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="F573" s="15" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="G573" s="16"/>
       <c r="H573" s="17"/>
@@ -24739,10 +24739,10 @@
       </c>
       <c r="D574" s="15"/>
       <c r="E574" s="12" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="F574" s="15" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="G574" s="16"/>
       <c r="H574" s="17"/>
@@ -24761,10 +24761,10 @@
       </c>
       <c r="D575" s="15"/>
       <c r="E575" s="12" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="F575" s="15" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="G575" s="16"/>
       <c r="H575" s="17"/>
@@ -24788,7 +24788,7 @@
         <v>1794</v>
       </c>
       <c r="F576" s="15" t="s">
-        <v>1506</v>
+        <v>1624</v>
       </c>
       <c r="G576" s="16" t="s">
         <v>154</v>
@@ -24818,7 +24818,7 @@
         <v>1799</v>
       </c>
       <c r="F577" s="15" t="s">
-        <v>1506</v>
+        <v>1624</v>
       </c>
       <c r="G577" s="16" t="s">
         <v>63</v>
@@ -24848,7 +24848,7 @@
         <v>1803</v>
       </c>
       <c r="F578" s="15" t="s">
-        <v>1506</v>
+        <v>1624</v>
       </c>
       <c r="G578" s="16" t="s">
         <v>237</v>
@@ -24878,7 +24878,7 @@
         <v>1807</v>
       </c>
       <c r="F579" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G579" s="16" t="s">
         <v>1808</v>
@@ -24908,7 +24908,7 @@
         <v>1812</v>
       </c>
       <c r="F580" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G580" s="16" t="s">
         <v>1813</v>
@@ -24938,7 +24938,7 @@
         <v>1817</v>
       </c>
       <c r="F581" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G581" s="16" t="s">
         <v>21</v>
@@ -24968,7 +24968,7 @@
         <v>1821</v>
       </c>
       <c r="F582" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G582" s="16" t="s">
         <v>70</v>
@@ -24998,7 +24998,7 @@
         <v>1825</v>
       </c>
       <c r="F583" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G583" s="16" t="s">
         <v>191</v>
@@ -25028,7 +25028,7 @@
         <v>1829</v>
       </c>
       <c r="F584" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G584" s="16" t="s">
         <v>1830</v>
@@ -25061,7 +25061,7 @@
     </row>
     <row r="586" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A586" s="13">
-        <v>24010</v>
+        <v>24002</v>
       </c>
       <c r="B586" s="14" t="s">
         <v>1834</v>
@@ -25079,14 +25079,14 @@
     </row>
     <row r="587" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A587" s="13">
-        <v>24011</v>
+        <v>24003</v>
       </c>
       <c r="B587" s="14" t="s">
         <v>1836</v>
       </c>
       <c r="C587" s="15"/>
       <c r="D587" s="15"/>
-      <c r="E587" s="25" t="s">
+      <c r="E587" s="24" t="s">
         <v>1837</v>
       </c>
       <c r="F587" s="15"/>
@@ -25097,7 +25097,7 @@
     </row>
     <row r="588" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A588" s="13">
-        <v>24012</v>
+        <v>24004</v>
       </c>
       <c r="B588" s="14" t="s">
         <v>1838</v>
@@ -25115,7 +25115,7 @@
     </row>
     <row r="589" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A589" s="13">
-        <v>24013</v>
+        <v>24005</v>
       </c>
       <c r="B589" s="14" t="s">
         <v>1840</v>
@@ -25133,7 +25133,7 @@
     </row>
     <row r="590" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A590" s="13">
-        <v>24014</v>
+        <v>24006</v>
       </c>
       <c r="B590" s="14" t="s">
         <v>1842</v>
@@ -25151,14 +25151,14 @@
     </row>
     <row r="591" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A591" s="13">
-        <v>24015</v>
+        <v>24007</v>
       </c>
       <c r="B591" s="14" t="s">
         <v>1844</v>
       </c>
       <c r="C591" s="15"/>
       <c r="D591" s="15"/>
-      <c r="E591" s="25" t="s">
+      <c r="E591" s="24" t="s">
         <v>1845</v>
       </c>
       <c r="F591" s="15"/>
@@ -25169,7 +25169,7 @@
     </row>
     <row r="592" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A592" s="13">
-        <v>24016</v>
+        <v>24008</v>
       </c>
       <c r="B592" s="14" t="s">
         <v>1846</v>
@@ -25187,14 +25187,14 @@
     </row>
     <row r="593" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A593" s="13">
-        <v>24017</v>
+        <v>24009</v>
       </c>
       <c r="B593" s="14" t="s">
         <v>1848</v>
       </c>
       <c r="C593" s="15"/>
       <c r="D593" s="15"/>
-      <c r="E593" s="24" t="s">
+      <c r="E593" s="25" t="s">
         <v>1849</v>
       </c>
       <c r="F593" s="15"/>
@@ -25205,7 +25205,7 @@
     </row>
     <row r="594" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A594" s="13">
-        <v>24002</v>
+        <v>24010</v>
       </c>
       <c r="B594" s="14" t="s">
         <v>1850</v>
@@ -25223,14 +25223,14 @@
     </row>
     <row r="595" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A595" s="13">
-        <v>24003</v>
+        <v>24011</v>
       </c>
       <c r="B595" s="14" t="s">
         <v>1852</v>
       </c>
       <c r="C595" s="15"/>
       <c r="D595" s="15"/>
-      <c r="E595" s="24" t="s">
+      <c r="E595" s="25" t="s">
         <v>1853</v>
       </c>
       <c r="F595" s="15"/>
@@ -25241,7 +25241,7 @@
     </row>
     <row r="596" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A596" s="13">
-        <v>24004</v>
+        <v>24012</v>
       </c>
       <c r="B596" s="14" t="s">
         <v>1854</v>
@@ -25259,7 +25259,7 @@
     </row>
     <row r="597" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A597" s="13">
-        <v>24005</v>
+        <v>24013</v>
       </c>
       <c r="B597" s="14" t="s">
         <v>1856</v>
@@ -25277,7 +25277,7 @@
     </row>
     <row r="598" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A598" s="13">
-        <v>24006</v>
+        <v>24014</v>
       </c>
       <c r="B598" s="14" t="s">
         <v>1858</v>
@@ -25295,14 +25295,14 @@
     </row>
     <row r="599" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A599" s="13">
-        <v>24007</v>
+        <v>24015</v>
       </c>
       <c r="B599" s="14" t="s">
         <v>1860</v>
       </c>
       <c r="C599" s="15"/>
       <c r="D599" s="15"/>
-      <c r="E599" s="24" t="s">
+      <c r="E599" s="25" t="s">
         <v>1861</v>
       </c>
       <c r="F599" s="15"/>
@@ -25313,7 +25313,7 @@
     </row>
     <row r="600" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A600" s="13">
-        <v>24008</v>
+        <v>24016</v>
       </c>
       <c r="B600" s="14" t="s">
         <v>1862</v>
@@ -25331,14 +25331,14 @@
     </row>
     <row r="601" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A601" s="13">
-        <v>24009</v>
+        <v>24017</v>
       </c>
       <c r="B601" s="14" t="s">
         <v>1864</v>
       </c>
       <c r="C601" s="15"/>
       <c r="D601" s="15"/>
-      <c r="E601" s="25" t="s">
+      <c r="E601" s="24" t="s">
         <v>1865</v>
       </c>
       <c r="F601" s="15"/>
@@ -25367,7 +25367,7 @@
     </row>
     <row r="603" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A603" s="13">
-        <v>25010</v>
+        <v>25002</v>
       </c>
       <c r="B603" s="14" t="s">
         <v>1868</v>
@@ -25385,7 +25385,7 @@
     </row>
     <row r="604" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A604" s="13">
-        <v>25011</v>
+        <v>25003</v>
       </c>
       <c r="B604" s="14" t="s">
         <v>1870</v>
@@ -25403,14 +25403,14 @@
     </row>
     <row r="605" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A605" s="13">
-        <v>25012</v>
+        <v>25004</v>
       </c>
       <c r="B605" s="14" t="s">
         <v>1872</v>
       </c>
       <c r="C605" s="15"/>
       <c r="D605" s="15"/>
-      <c r="E605" s="24" t="s">
+      <c r="E605" s="22" t="s">
         <v>1873</v>
       </c>
       <c r="F605" s="15"/>
@@ -25421,7 +25421,7 @@
     </row>
     <row r="606" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A606" s="13">
-        <v>25013</v>
+        <v>25005</v>
       </c>
       <c r="B606" s="14" t="s">
         <v>1874</v>
@@ -25439,7 +25439,7 @@
     </row>
     <row r="607" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A607" s="13">
-        <v>25014</v>
+        <v>25006</v>
       </c>
       <c r="B607" s="14" t="s">
         <v>1876</v>
@@ -25457,14 +25457,14 @@
     </row>
     <row r="608" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A608" s="13">
-        <v>25015</v>
+        <v>25007</v>
       </c>
       <c r="B608" s="14" t="s">
         <v>1878</v>
       </c>
       <c r="C608" s="15"/>
       <c r="D608" s="15"/>
-      <c r="E608" s="25" t="s">
+      <c r="E608" s="24" t="s">
         <v>1879</v>
       </c>
       <c r="F608" s="15"/>
@@ -25475,14 +25475,14 @@
     </row>
     <row r="609" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A609" s="13">
-        <v>25016</v>
+        <v>25008</v>
       </c>
       <c r="B609" s="14" t="s">
         <v>1880</v>
       </c>
       <c r="C609" s="15"/>
       <c r="D609" s="15"/>
-      <c r="E609" s="24" t="s">
+      <c r="E609" s="25" t="s">
         <v>1881</v>
       </c>
       <c r="F609" s="15"/>
@@ -25493,7 +25493,7 @@
     </row>
     <row r="610" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A610" s="13">
-        <v>25017</v>
+        <v>25009</v>
       </c>
       <c r="B610" s="14" t="s">
         <v>1882</v>
@@ -25501,7 +25501,7 @@
       <c r="C610" s="15"/>
       <c r="D610" s="15"/>
       <c r="E610" s="24" t="s">
-        <v>1883</v>
+        <v>1881</v>
       </c>
       <c r="F610" s="15"/>
       <c r="G610" s="16"/>
@@ -25511,15 +25511,15 @@
     </row>
     <row r="611" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A611" s="13">
-        <v>25018</v>
+        <v>25010</v>
       </c>
       <c r="B611" s="14" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="C611" s="15"/>
       <c r="D611" s="15"/>
       <c r="E611" s="24" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="F611" s="15"/>
       <c r="G611" s="16"/>
@@ -25529,15 +25529,15 @@
     </row>
     <row r="612" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A612" s="13">
-        <v>25019</v>
+        <v>25011</v>
       </c>
       <c r="B612" s="14" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="C612" s="15"/>
       <c r="D612" s="15"/>
       <c r="E612" s="24" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="F612" s="15"/>
       <c r="G612" s="16"/>
@@ -25547,15 +25547,15 @@
     </row>
     <row r="613" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A613" s="13">
-        <v>25002</v>
+        <v>25012</v>
       </c>
       <c r="B613" s="14" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="C613" s="15"/>
       <c r="D613" s="15"/>
       <c r="E613" s="24" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="F613" s="15"/>
       <c r="G613" s="16"/>
@@ -25565,15 +25565,15 @@
     </row>
     <row r="614" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A614" s="13">
-        <v>25020</v>
+        <v>25013</v>
       </c>
       <c r="B614" s="14" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="C614" s="15"/>
       <c r="D614" s="15"/>
       <c r="E614" s="24" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="F614" s="15"/>
       <c r="G614" s="16"/>
@@ -25583,15 +25583,15 @@
     </row>
     <row r="615" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A615" s="13">
-        <v>25021</v>
+        <v>25014</v>
       </c>
       <c r="B615" s="14" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="C615" s="15"/>
       <c r="D615" s="15"/>
       <c r="E615" s="24" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="F615" s="15"/>
       <c r="G615" s="16"/>
@@ -25601,15 +25601,15 @@
     </row>
     <row r="616" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A616" s="13">
-        <v>25003</v>
+        <v>25015</v>
       </c>
       <c r="B616" s="14" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C616" s="15"/>
       <c r="D616" s="15"/>
-      <c r="E616" s="24" t="s">
-        <v>1895</v>
+      <c r="E616" s="25" t="s">
+        <v>1894</v>
       </c>
       <c r="F616" s="15"/>
       <c r="G616" s="16"/>
@@ -25619,15 +25619,15 @@
     </row>
     <row r="617" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A617" s="13">
-        <v>25004</v>
+        <v>25016</v>
       </c>
       <c r="B617" s="14" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="C617" s="15"/>
       <c r="D617" s="15"/>
-      <c r="E617" s="22" t="s">
-        <v>1897</v>
+      <c r="E617" s="24" t="s">
+        <v>1896</v>
       </c>
       <c r="F617" s="15"/>
       <c r="G617" s="16"/>
@@ -25637,15 +25637,15 @@
     </row>
     <row r="618" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A618" s="13">
-        <v>25005</v>
+        <v>25017</v>
       </c>
       <c r="B618" s="14" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="C618" s="15"/>
       <c r="D618" s="15"/>
       <c r="E618" s="24" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="F618" s="15"/>
       <c r="G618" s="16"/>
@@ -25655,15 +25655,15 @@
     </row>
     <row r="619" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A619" s="13">
-        <v>25006</v>
+        <v>25018</v>
       </c>
       <c r="B619" s="14" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="C619" s="15"/>
       <c r="D619" s="15"/>
       <c r="E619" s="24" t="s">
-        <v>1901</v>
+        <v>1881</v>
       </c>
       <c r="F619" s="15"/>
       <c r="G619" s="16"/>
@@ -25673,15 +25673,15 @@
     </row>
     <row r="620" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A620" s="13">
-        <v>25007</v>
+        <v>25019</v>
       </c>
       <c r="B620" s="14" t="s">
-        <v>1902</v>
+        <v>1900</v>
       </c>
       <c r="C620" s="15"/>
       <c r="D620" s="15"/>
       <c r="E620" s="24" t="s">
-        <v>1903</v>
+        <v>1901</v>
       </c>
       <c r="F620" s="15"/>
       <c r="G620" s="16"/>
@@ -25691,15 +25691,15 @@
     </row>
     <row r="621" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A621" s="13">
-        <v>25008</v>
+        <v>25020</v>
       </c>
       <c r="B621" s="14" t="s">
-        <v>1904</v>
+        <v>1902</v>
       </c>
       <c r="C621" s="15"/>
       <c r="D621" s="15"/>
-      <c r="E621" s="25" t="s">
-        <v>1885</v>
+      <c r="E621" s="24" t="s">
+        <v>1903</v>
       </c>
       <c r="F621" s="15"/>
       <c r="G621" s="16"/>
@@ -25709,15 +25709,15 @@
     </row>
     <row r="622" s="12" customFormat="1" customHeight="1" spans="1:10">
       <c r="A622" s="13">
-        <v>25009</v>
+        <v>25021</v>
       </c>
       <c r="B622" s="14" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="C622" s="15"/>
       <c r="D622" s="15"/>
       <c r="E622" s="24" t="s">
-        <v>1885</v>
+        <v>1905</v>
       </c>
       <c r="F622" s="15"/>
       <c r="G622" s="16"/>
@@ -26066,7 +26066,7 @@
         <v>237</v>
       </c>
       <c r="H638" s="17" t="s">
-        <v>1474</v>
+        <v>1592</v>
       </c>
       <c r="I638" s="18" t="s">
         <v>677</v>
@@ -26155,7 +26155,7 @@
         <v>1938</v>
       </c>
       <c r="E642" s="12" t="s">
-        <v>1320</v>
+        <v>1332</v>
       </c>
       <c r="F642" s="15" t="s">
         <v>204</v>
@@ -26201,7 +26201,7 @@
         <v>1959</v>
       </c>
       <c r="E644" s="12" t="s">
-        <v>1320</v>
+        <v>1332</v>
       </c>
       <c r="F644" s="15" t="s">
         <v>204</v>
@@ -26244,7 +26244,7 @@
         <v>1964</v>
       </c>
       <c r="D646" s="15" t="s">
-        <v>1533</v>
+        <v>1650</v>
       </c>
       <c r="E646" s="12" t="s">
         <v>1952</v>
@@ -26272,7 +26272,7 @@
         <v>1967</v>
       </c>
       <c r="F647" s="15" t="s">
-        <v>1506</v>
+        <v>1624</v>
       </c>
       <c r="G647" s="16"/>
       <c r="H647" s="17"/>
@@ -26308,7 +26308,7 @@
         <v>1970</v>
       </c>
       <c r="D649" s="15" t="s">
-        <v>1521</v>
+        <v>1638</v>
       </c>
       <c r="E649" s="12" t="s">
         <v>1971</v>
@@ -26382,12 +26382,12 @@
         <v>1980</v>
       </c>
       <c r="F652" s="15" t="s">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="G652" s="16"/>
       <c r="H652" s="17"/>
       <c r="I652" s="18" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
       <c r="J652" s="18"/>
     </row>
@@ -26584,7 +26584,7 @@
         <v>2000</v>
       </c>
       <c r="F661" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G661" s="16"/>
       <c r="H661" s="17"/>
@@ -26811,7 +26811,7 @@
       <c r="G671" s="16"/>
       <c r="H671" s="17"/>
       <c r="I671" s="23" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
       <c r="J671" s="18"/>
     </row>
@@ -27030,7 +27030,7 @@
         <v>2048</v>
       </c>
       <c r="F681" s="15" t="s">
-        <v>1506</v>
+        <v>1624</v>
       </c>
       <c r="G681" s="16"/>
       <c r="H681" s="17"/>
@@ -27052,7 +27052,7 @@
         <v>2050</v>
       </c>
       <c r="F682" s="15" t="s">
-        <v>1455</v>
+        <v>1575</v>
       </c>
       <c r="G682" s="16"/>
       <c r="H682" s="17"/>
@@ -27404,7 +27404,7 @@
         <v>2093</v>
       </c>
       <c r="F704" s="15" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="G704" s="16"/>
       <c r="H704" s="17"/>
@@ -27422,7 +27422,7 @@
         <v>2095</v>
       </c>
       <c r="F705" s="15" t="s">
-        <v>1455</v>
+        <v>1575</v>
       </c>
       <c r="G705" s="16"/>
       <c r="H705" s="17"/>
@@ -27530,7 +27530,7 @@
         <v>2098</v>
       </c>
       <c r="F711" s="15" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="G711" s="16"/>
       <c r="H711" s="17"/>
@@ -27689,7 +27689,7 @@
       <c r="C720" s="15"/>
       <c r="D720" s="15"/>
       <c r="E720" s="12" t="s">
-        <v>1320</v>
+        <v>1332</v>
       </c>
       <c r="F720" s="15" t="s">
         <v>204</v>
@@ -27709,7 +27709,7 @@
       <c r="C721" s="15"/>
       <c r="D721" s="15"/>
       <c r="E721" s="12" t="s">
-        <v>1320</v>
+        <v>1332</v>
       </c>
       <c r="F721" s="15" t="s">
         <v>204</v>
@@ -27729,7 +27729,7 @@
       <c r="C722" s="15"/>
       <c r="D722" s="15"/>
       <c r="E722" s="12" t="s">
-        <v>1320</v>
+        <v>1332</v>
       </c>
       <c r="F722" s="15" t="s">
         <v>204</v>
@@ -27788,7 +27788,7 @@
         <v>2105</v>
       </c>
       <c r="F725" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G725" s="16" t="s">
         <v>249</v>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="F726" s="15"/>
       <c r="G726" s="16" t="s">
-        <v>1511</v>
+        <v>1531</v>
       </c>
       <c r="H726" s="17"/>
       <c r="I726" s="18" t="s">
@@ -27826,7 +27826,7 @@
         <v>2107</v>
       </c>
       <c r="F727" s="15" t="s">
-        <v>1455</v>
+        <v>1575</v>
       </c>
       <c r="G727" s="16" t="s">
         <v>185</v>
@@ -27846,7 +27846,7 @@
         <v>2108</v>
       </c>
       <c r="F728" s="15" t="s">
-        <v>1728</v>
+        <v>1513</v>
       </c>
       <c r="G728" s="16" t="s">
         <v>154</v>
@@ -27866,7 +27866,7 @@
         <v>2109</v>
       </c>
       <c r="F729" s="15" t="s">
-        <v>1728</v>
+        <v>1513</v>
       </c>
       <c r="G729" s="16" t="s">
         <v>237</v>
@@ -27886,7 +27886,7 @@
         <v>2110</v>
       </c>
       <c r="F730" s="15" t="s">
-        <v>1728</v>
+        <v>1513</v>
       </c>
       <c r="G730" s="16" t="s">
         <v>167</v>
@@ -27906,7 +27906,7 @@
         <v>2111</v>
       </c>
       <c r="F731" s="15" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="G731" s="16" t="s">
         <v>2103</v>
@@ -27926,7 +27926,7 @@
         <v>2112</v>
       </c>
       <c r="F732" s="15" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="G732" s="16" t="s">
         <v>2113</v>
@@ -27943,10 +27943,10 @@
       <c r="C733" s="15"/>
       <c r="D733" s="15"/>
       <c r="E733" s="12" t="s">
-        <v>1376</v>
+        <v>1386</v>
       </c>
       <c r="F733" s="15" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="G733" s="16" t="s">
         <v>249</v>
@@ -27963,13 +27963,13 @@
       <c r="C734" s="15"/>
       <c r="D734" s="15"/>
       <c r="E734" s="12" t="s">
-        <v>1473</v>
+        <v>1591</v>
       </c>
       <c r="F734" s="15" t="s">
-        <v>1377</v>
+        <v>1387</v>
       </c>
       <c r="G734" s="16" t="s">
-        <v>1254</v>
+        <v>1270</v>
       </c>
       <c r="H734" s="17"/>
       <c r="I734" s="18" t="s">
@@ -28058,7 +28058,7 @@
         <v>2117</v>
       </c>
       <c r="F739" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G739" s="16" t="s">
         <v>349</v>
@@ -28078,7 +28078,7 @@
         <v>2118</v>
       </c>
       <c r="F740" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G740" s="16" t="s">
         <v>262</v>
@@ -28095,10 +28095,10 @@
       <c r="C741" s="15"/>
       <c r="D741" s="15"/>
       <c r="E741" s="12" t="s">
-        <v>1315</v>
+        <v>1327</v>
       </c>
       <c r="F741" s="15" t="s">
-        <v>1302</v>
+        <v>1316</v>
       </c>
       <c r="G741" s="16" t="s">
         <v>154</v>
@@ -28161,7 +28161,7 @@
       </c>
       <c r="H744" s="17"/>
       <c r="I744" s="18" t="s">
-        <v>1256</v>
+        <v>1272</v>
       </c>
       <c r="J744" s="18"/>
     </row>
@@ -28174,7 +28174,7 @@
         <v>2121</v>
       </c>
       <c r="F745" s="15" t="s">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="G745" s="16" t="s">
         <v>237</v>
@@ -28212,7 +28212,7 @@
         <v>2123</v>
       </c>
       <c r="F747" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G747" s="16" t="s">
         <v>154</v>
@@ -28232,14 +28232,14 @@
         <v>2125</v>
       </c>
       <c r="F748" s="15" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="G748" s="16" t="s">
         <v>433</v>
       </c>
       <c r="H748" s="17"/>
       <c r="I748" s="18" t="s">
-        <v>1256</v>
+        <v>1272</v>
       </c>
       <c r="J748" s="18"/>
     </row>
@@ -29916,7 +29916,7 @@
     <cfRule type="duplicateValues" dxfId="0" priority="178"/>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="K387" r:id="rId1" display="https://open.spotify.com/track/44rDdbTIyoXJyWxAnUv5ys?si=e1c832cba0ca418b"/>
+    <hyperlink ref="K377" r:id="rId1" display="https://open.spotify.com/track/44rDdbTIyoXJyWxAnUv5ys?si=e1c832cba0ca418b"/>
     <hyperlink ref="K338" r:id="rId2" display="https://open.spotify.com/album/4ueh2RoK2gEjQa8ukgha77"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29955,7 +29955,7 @@
       <c r="D1" s="7" t="s">
         <v>2222</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>2223</v>
       </c>
       <c r="G1" s="5" t="s">
